--- a/Versão5/PRO/Ontologia_Documentos.xlsx
+++ b/Versão5/PRO/Ontologia_Documentos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\PRO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28BDDA26-0C86-401E-8062-49E673A0B5FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E0526A9-F4AD-4F3A-A469-AB8707D6EF4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="527" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
@@ -39,30 +39,8 @@
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
-  <metadataTypes count="1">
-    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <valueMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </valueMetadata>
-</metadata>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3469" uniqueCount="769">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3604" uniqueCount="900">
   <si>
     <t>Edição</t>
   </si>
@@ -2401,6 +2379,399 @@
   </si>
   <si>
     <t>Categoria Rvt</t>
+  </si>
+  <si>
+    <t>Define un archivo de proyecto o archivo por defecto de una aplicación, puede ser RVT, DWG, DGN, IFC, etc.</t>
+  </si>
+  <si>
+    <t>Define un archivo usado como plantilla, prototipo, plantilla, puede ser rte, dwt, etc.</t>
+  </si>
+  <si>
+    <t>Define un archivo de una aplicación. Puede ser Autolisp, Python, C#, etc.</t>
+  </si>
+  <si>
+    <t>Define un archivo usado como receptor de datos estructurados, puede ser txt, xml, etc...</t>
+  </si>
+  <si>
+    <t>Define un archivo utilizado como receptor de datos no estructurados, puede ser pdf, documento, vídeos, etc...</t>
+  </si>
+  <si>
+    <t>Símbolo de Llamada</t>
+  </si>
+  <si>
+    <t>Delimitación de Detalles de Llamada</t>
+  </si>
+  <si>
+    <t>Símbolo de Llamada - Cabeza</t>
+  </si>
+  <si>
+    <t>Símbolo de líder - Línea de guía</t>
+  </si>
+  <si>
+    <t>Reseña de Nube Simbólica de Detalle - Etiqueta o Etiqueta Textual</t>
+  </si>
+  <si>
+    <t>Vista de sección</t>
+  </si>
+  <si>
+    <t>Símbolo de corte - Cabeza</t>
+  </si>
+  <si>
+    <t>Símbolo de corte - líneas finas de la cabeza</t>
+  </si>
+  <si>
+    <t>Símbolo de corte - Líneas medias de la cabeza</t>
+  </si>
+  <si>
+    <t>Símbolo de corte - Líneas de encabezado gruesas</t>
+  </si>
+  <si>
+    <t>Símbolo de corte - Línea de corte</t>
+  </si>
+  <si>
+    <t>Línea de corte interrumpida</t>
+  </si>
+  <si>
+    <t>Calcomanía de imagen insertada</t>
+  </si>
+  <si>
+    <t>Componente de detallado 2D - Líneas ocultas</t>
+  </si>
+  <si>
+    <t>Línea de detalle repetida</t>
+  </si>
+  <si>
+    <t>Ver símbolos</t>
+  </si>
+  <si>
+    <t>Ver símbolos - Marcas</t>
+  </si>
+  <si>
+    <t>Símbolo de punto de coordenadas</t>
+  </si>
+  <si>
+    <t>Símbolos de puntos de coordenadas</t>
+  </si>
+  <si>
+    <t>Comillas</t>
+  </si>
+  <si>
+    <t>Símbolos de marca de verificación</t>
+  </si>
+  <si>
+    <t>Pendiente</t>
+  </si>
+  <si>
+    <t>Símbolos de pendiente</t>
+  </si>
+  <si>
+    <t>Dimensión citada</t>
+  </si>
+  <si>
+    <t>Estilo de elemento final de dimensión - ID de estilo de identificador único</t>
+  </si>
+  <si>
+    <t>Patrón de líneas centrales</t>
+  </si>
+  <si>
+    <t>Líneas invisibles</t>
+  </si>
+  <si>
+    <t>Líneas de aristas proyectadas</t>
+  </si>
+  <si>
+    <t>Líneas de aislamiento</t>
+  </si>
+  <si>
+    <t>Líneas centrales</t>
+  </si>
+  <si>
+    <t>Líneas centrales CL</t>
+  </si>
+  <si>
+    <t>Líneas de demolición</t>
+  </si>
+  <si>
+    <t>Líneas de proyección de bordes superiores</t>
+  </si>
+  <si>
+    <t>Líneas ocultas</t>
+  </si>
+  <si>
+    <t>Líneas ocultas del suelo</t>
+  </si>
+  <si>
+    <t>Filas ocultas de columnas estructurales</t>
+  </si>
+  <si>
+    <t>Líneas ocultas de cimientos estructurales</t>
+  </si>
+  <si>
+    <t>Líneas ocultas de vigas estructurales</t>
+  </si>
+  <si>
+    <t>Líneas ocultas de muros</t>
+  </si>
+  <si>
+    <t>Estilo de Instancia Row</t>
+  </si>
+  <si>
+    <t>Ticks tipo ticks en la línea central</t>
+  </si>
+  <si>
+    <t>Tick Mark de Cuota - Identificador único de ID de estilo</t>
+  </si>
+  <si>
+    <t>Interior de la marca Tick - Identificador único de estilo</t>
+  </si>
+  <si>
+    <t>Marca de verificación de línea de llamada - Identificador único de ID de estilo</t>
+  </si>
+  <si>
+    <t>Punta simbólica de flecha</t>
+  </si>
+  <si>
+    <t>Texto y Líder - Fuente del Texto</t>
+  </si>
+  <si>
+    <t>Texto y línea de guía - Identificador de ID único</t>
+  </si>
+  <si>
+    <t>Estilizado de objetos importados</t>
+  </si>
+  <si>
+    <t>Leyenda del Conducto</t>
+  </si>
+  <si>
+    <t>Relleno de Color de Conductos</t>
+  </si>
+  <si>
+    <t>Pipas - Leyendas de colores</t>
+  </si>
+  <si>
+    <t>Pipes - Colores</t>
+  </si>
+  <si>
+    <t>Entorno - relleno de color</t>
+  </si>
+  <si>
+    <t>Áreas de ocupación de edificios - relleno de color</t>
+  </si>
+  <si>
+    <t>MEP - Espacios HVAC - Relleno de color</t>
+  </si>
+  <si>
+    <t>Subtítulos - Esquema de colores</t>
+  </si>
+  <si>
+    <t>Legend de componentes</t>
+  </si>
+  <si>
+    <t>Líneas</t>
+  </si>
+  <si>
+    <t>Líneas - Líneas de Llamada a las Líneas de Nube</t>
+  </si>
+  <si>
+    <t>Línea direccional de los bordes</t>
+  </si>
+  <si>
+    <t>Líneas genéricas</t>
+  </si>
+  <si>
+    <t>Valor de desplazamiento</t>
+  </si>
+  <si>
+    <t>Trayectoria de desplazamiento</t>
+  </si>
+  <si>
+    <t>Advertencia gráfica - Abierto</t>
+  </si>
+  <si>
+    <t>Imagen raster o bitmap insertada en el modelo</t>
+  </si>
+  <si>
+    <t>Símbolo de ascenso o descenso en tubos - Yin y Yang</t>
+  </si>
+  <si>
+    <t>Guías de ejes estructurales</t>
+  </si>
+  <si>
+    <t>Sábanas o tablas</t>
+  </si>
+  <si>
+    <t>Sellos y tablas</t>
+  </si>
+  <si>
+    <t>Finas líneas de sellos y tablas</t>
+  </si>
+  <si>
+    <t>Líneas medias de sellos y cartones</t>
+  </si>
+  <si>
+    <t>Líneas gruesas de sellos y tablas</t>
+  </si>
+  <si>
+    <t>Revisiones de diseño</t>
+  </si>
+  <si>
+    <t>Revisiones de diseño - Numeración</t>
+  </si>
+  <si>
+    <t>Patrones de trampilla</t>
+  </si>
+  <si>
+    <t>Región con relleno de color</t>
+  </si>
+  <si>
+    <t>Región de enmascaramiento gráfico</t>
+  </si>
+  <si>
+    <t>Coincidencias</t>
+  </si>
+  <si>
+    <t>Coincidencias textuales</t>
+  </si>
+  <si>
+    <t>Coincidencias de detalles</t>
+  </si>
+  <si>
+    <t>Coincidencias - Líneas de coincidencia</t>
+  </si>
+  <si>
+    <t>Coincidencias de modelos</t>
+  </si>
+  <si>
+    <t>Coincidencias de perfil</t>
+  </si>
+  <si>
+    <t>Coincidencias de componentes de la situación</t>
+  </si>
+  <si>
+    <t>Tabla textual</t>
+  </si>
+  <si>
+    <t>Disposiciones gráficas de tablas</t>
+  </si>
+  <si>
+    <t>Conjunto de parámetros de una tabla</t>
+  </si>
+  <si>
+    <t>Plantilla de tablas de circuitos</t>
+  </si>
+  <si>
+    <t>Anotación - espacio de corte textual</t>
+  </si>
+  <si>
+    <t>Anotación - espacio especial de recortes textuales</t>
+  </si>
+  <si>
+    <t>Textos de modelos 3D</t>
+  </si>
+  <si>
+    <t>Notas textuales</t>
+  </si>
+  <si>
+    <t>Anotaciones genéricas</t>
+  </si>
+  <si>
+    <t>Múltiples referencias textuales</t>
+  </si>
+  <si>
+    <t>Anotaciones estructurales</t>
+  </si>
+  <si>
+    <t>Componente de detallado 2D - Etiqueta o etiqueta textual</t>
+  </si>
+  <si>
+    <t>Notas clave - Etiqueta o etiqueta textual</t>
+  </si>
+  <si>
+    <t>Grupos de plantillas - Etiqueta o etiqueta textual</t>
+  </si>
+  <si>
+    <t>Etiqueta textual o etiqueta Milticategoria</t>
+  </si>
+  <si>
+    <t>Etiqueta textual o etiqueta de pared</t>
+  </si>
+  <si>
+    <t>Etiqueta textual o etiqueta de puerta</t>
+  </si>
+  <si>
+    <t>Etiqueta textual o etiqueta de Windows</t>
+  </si>
+  <si>
+    <t>No se requiere licencia. El documento es de dominio público</t>
+  </si>
+  <si>
+    <t>Licencia Creative Commons</t>
+  </si>
+  <si>
+    <t>Licencia de derechos de autor</t>
+  </si>
+  <si>
+    <t>Licencia de Derecho Industrial</t>
+  </si>
+  <si>
+    <t>Derecho publicado en Brasil</t>
+  </si>
+  <si>
+    <t>Decreto publicado en Brasil</t>
+  </si>
+  <si>
+    <t>Proyecto de ley en Brasil</t>
+  </si>
+  <si>
+    <t>Guía interna de procedimientos técnicos</t>
+  </si>
+  <si>
+    <t>Manual Interno de Procedimientos Técnicos</t>
+  </si>
+  <si>
+    <t>Libro técnico</t>
+  </si>
+  <si>
+    <t>Formación</t>
+  </si>
+  <si>
+    <t>Normativo</t>
+  </si>
+  <si>
+    <t>Presentaciones de PowerPoint o similares</t>
+  </si>
+  <si>
+    <t>Carpetas internas</t>
+  </si>
+  <si>
+    <t>Formas internas</t>
+  </si>
+  <si>
+    <t>Zonas de AVAC - Relleno de color</t>
+  </si>
+  <si>
+    <t>Región com relleno de patrón lineal</t>
+  </si>
+  <si>
+    <t>Tabla gráfica</t>
+  </si>
+  <si>
+    <t>Etiqueta textual o tag</t>
+  </si>
+  <si>
+    <t>Lineas de llamada múltiple - Etiqueta textual o Tag</t>
+  </si>
+  <si>
+    <t>Nube simbólica de revisión de detalles</t>
+  </si>
+  <si>
+    <t>Componente de detallado en 2D</t>
+  </si>
+  <si>
+    <t>Líneas de control de dimensión</t>
+  </si>
+  <si>
+    <t>Dimensión de referencia débil</t>
   </si>
 </sst>
 </file>
@@ -2916,14 +3287,6 @@
         <b val="0"/>
         <i/>
         <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
         <color rgb="FFFFFFFF"/>
       </font>
     </dxf>
@@ -2987,6 +3350,14 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -3004,64 +3375,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
-<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
-  <global>
-    <keyFlags>
-      <key name="_Self">
-        <flag name="ExcludeFromFile" value="1"/>
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_DisplayString">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Flags">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Format">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_SubLabel">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Attribution">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Icon">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Display">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_CanonicalPropertyNames">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_ClassificationId">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-    </keyFlags>
-  </global>
-</rvTypesInfo>
-</file>
-
-<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
-  <rv s="0">
-    <v>9</v>
-    <v>1</v>
-  </rv>
-</rvData>
-</file>
-
-<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
-  <s t="_error">
-    <k n="errorType" t="i"/>
-    <k n="subType" t="i"/>
-  </s>
-</rvStructures>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3565,7 +3878,7 @@
       </c>
       <c r="B18" s="5">
         <f ca="1">NOW()</f>
-        <v>46253.794196990741</v>
+        <v>46253.802874305555</v>
       </c>
       <c r="C18" s="41" t="s">
         <v>304</v>
@@ -3817,9 +4130,8 @@
       <c r="P2" s="43" t="s">
         <v>591</v>
       </c>
-      <c r="Q2" s="43" t="str">
-        <f>_xlfn.TRANSLATE(P2,"pt","es")</f>
-        <v>Define un archivo de proyecto o archivo por defecto de una aplicación, puede ser RVT, DWG, DGN, IFC, etc.</v>
+      <c r="Q2" s="43" t="s">
+        <v>769</v>
       </c>
       <c r="R2" s="43" t="s">
         <v>632</v>
@@ -3915,9 +4227,8 @@
       <c r="P3" s="43" t="s">
         <v>592</v>
       </c>
-      <c r="Q3" s="43" t="str">
-        <f t="shared" ref="Q3:Q5" si="6">_xlfn.TRANSLATE(P3,"pt","es")</f>
-        <v>Define un archivo usado como plantilla, prototipo, plantilla, puede ser rte, dwt, etc.</v>
+      <c r="Q3" s="43" t="s">
+        <v>770</v>
       </c>
       <c r="R3" s="43" t="s">
         <v>633</v>
@@ -3926,15 +4237,15 @@
         <v>9</v>
       </c>
       <c r="T3" s="43" t="str">
-        <f t="shared" ref="T3:T6" si="7">SUBSTITUTE(C3, "_", " ")</f>
+        <f t="shared" ref="T3:T6" si="6">SUBSTITUTE(C3, "_", " ")</f>
         <v>Documentais</v>
       </c>
       <c r="U3" s="43" t="str">
-        <f t="shared" ref="U3:U6" si="8">SUBSTITUTE(D3, "_", " ")</f>
+        <f t="shared" ref="U3:U6" si="7">SUBSTITUTE(D3, "_", " ")</f>
         <v>Digitalizados</v>
       </c>
       <c r="V3" s="53" t="str">
-        <f t="shared" ref="V3:V6" si="9">SUBSTITUTE(E3, "_", " ")</f>
+        <f t="shared" ref="V3:V6" si="8">SUBSTITUTE(E3, "_", " ")</f>
         <v>Elemento.Digital</v>
       </c>
       <c r="W3" s="43" t="s">
@@ -4013,9 +4324,8 @@
       <c r="P4" s="43" t="s">
         <v>593</v>
       </c>
-      <c r="Q4" s="43" t="str">
-        <f t="shared" si="6"/>
-        <v>Define un archivo de una aplicación. Puede ser Autolisp, Python, C#, etc.</v>
+      <c r="Q4" s="43" t="s">
+        <v>771</v>
       </c>
       <c r="R4" s="43" t="s">
         <v>634</v>
@@ -4024,15 +4334,15 @@
         <v>9</v>
       </c>
       <c r="T4" s="43" t="str">
+        <f t="shared" si="6"/>
+        <v>Documentais</v>
+      </c>
+      <c r="U4" s="43" t="str">
         <f t="shared" si="7"/>
-        <v>Documentais</v>
-      </c>
-      <c r="U4" s="43" t="str">
+        <v>Digitalizados</v>
+      </c>
+      <c r="V4" s="53" t="str">
         <f t="shared" si="8"/>
-        <v>Digitalizados</v>
-      </c>
-      <c r="V4" s="53" t="str">
-        <f t="shared" si="9"/>
         <v>Elemento.Digital</v>
       </c>
       <c r="W4" s="43" t="s">
@@ -4111,9 +4421,8 @@
       <c r="P5" s="43" t="s">
         <v>587</v>
       </c>
-      <c r="Q5" s="43" t="str">
-        <f t="shared" si="6"/>
-        <v>Define un archivo usado como receptor de datos estructurados, puede ser txt, xml, etc...</v>
+      <c r="Q5" s="43" t="s">
+        <v>772</v>
       </c>
       <c r="R5" s="43" t="s">
         <v>635</v>
@@ -4122,15 +4431,15 @@
         <v>9</v>
       </c>
       <c r="T5" s="43" t="str">
+        <f t="shared" si="6"/>
+        <v>Documentais</v>
+      </c>
+      <c r="U5" s="43" t="str">
         <f t="shared" si="7"/>
-        <v>Documentais</v>
-      </c>
-      <c r="U5" s="43" t="str">
+        <v>Digitalizados</v>
+      </c>
+      <c r="V5" s="53" t="str">
         <f t="shared" si="8"/>
-        <v>Digitalizados</v>
-      </c>
-      <c r="V5" s="53" t="str">
-        <f t="shared" si="9"/>
         <v>Elemento.Digital</v>
       </c>
       <c r="W5" s="43" t="s">
@@ -4209,9 +4518,8 @@
       <c r="P6" s="43" t="s">
         <v>590</v>
       </c>
-      <c r="Q6" s="43" t="str">
-        <f t="shared" ref="Q6" si="10">_xlfn.TRANSLATE(P6,"pt","es")</f>
-        <v>Define un archivo utilizado como receptor de datos no estructurados, puede ser pdf, documento, vídeos, etc...</v>
+      <c r="Q6" s="43" t="s">
+        <v>773</v>
       </c>
       <c r="R6" s="43" t="s">
         <v>636</v>
@@ -4220,15 +4528,15 @@
         <v>9</v>
       </c>
       <c r="T6" s="43" t="str">
+        <f t="shared" si="6"/>
+        <v>Documentais</v>
+      </c>
+      <c r="U6" s="43" t="str">
         <f t="shared" si="7"/>
-        <v>Documentais</v>
-      </c>
-      <c r="U6" s="43" t="str">
+        <v>Digitalizados</v>
+      </c>
+      <c r="V6" s="53" t="str">
         <f t="shared" si="8"/>
-        <v>Digitalizados</v>
-      </c>
-      <c r="V6" s="53" t="str">
-        <f t="shared" si="9"/>
         <v>Elemento.Digital</v>
       </c>
       <c r="W6" s="43" t="s">
@@ -4289,19 +4597,19 @@
         <v>9</v>
       </c>
       <c r="L7" s="53" t="str">
-        <f t="shared" ref="L7" si="11">CONCATENATE("", C7)</f>
+        <f t="shared" ref="L7" si="9">CONCATENATE("", C7)</f>
         <v>Documentais</v>
       </c>
       <c r="M7" s="53" t="str">
-        <f t="shared" ref="M7" si="12">CONCATENATE("", D7)</f>
+        <f t="shared" ref="M7" si="10">CONCATENATE("", D7)</f>
         <v>Digitalizados</v>
       </c>
       <c r="N7" s="53" t="str">
-        <f t="shared" ref="N7" si="13">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E7),"."," ")," De "," de "))</f>
+        <f t="shared" ref="N7" si="11">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E7),"."," ")," De "," de "))</f>
         <v>Elemento Digital</v>
       </c>
       <c r="O7" s="53" t="str">
-        <f t="shared" ref="O7" si="14">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",F7),"."," ")," De "," de "))</f>
+        <f t="shared" ref="O7" si="12">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",F7),"."," ")," De "," de "))</f>
         <v>Biblioteca</v>
       </c>
       <c r="P7" s="43" t="s">
@@ -4404,9 +4712,8 @@
       <c r="P8" s="53" t="s">
         <v>83</v>
       </c>
-      <c r="Q8" s="43" t="str">
-        <f t="shared" ref="Q8:Q69" si="15">_xlfn.TRANSLATE(P8,"pt","es")</f>
-        <v>Símbolo de Llamada</v>
+      <c r="Q8" s="43" t="s">
+        <v>774</v>
       </c>
       <c r="R8" s="43" t="s">
         <v>638</v>
@@ -4415,15 +4722,15 @@
         <v>9</v>
       </c>
       <c r="T8" s="43" t="str">
-        <f t="shared" ref="T8:T37" si="16">SUBSTITUTE(C8, "_", " ")</f>
+        <f t="shared" ref="T8:T37" si="13">SUBSTITUTE(C8, "_", " ")</f>
         <v>Documentais</v>
       </c>
       <c r="U8" s="43" t="str">
-        <f t="shared" ref="U8:U69" si="17">SUBSTITUTE(D8, "_", " ")</f>
+        <f t="shared" ref="U8:U69" si="14">SUBSTITUTE(D8, "_", " ")</f>
         <v>Elemento.de.Detalhamento</v>
       </c>
       <c r="V8" s="53" t="str">
-        <f t="shared" ref="V8:V37" si="18">SUBSTITUTE(E8, "_", " ")</f>
+        <f t="shared" ref="V8:V37" si="15">SUBSTITUTE(E8, "_", " ")</f>
         <v>Símbolo.Chamada</v>
       </c>
       <c r="W8" s="43" t="s">
@@ -4502,9 +4809,8 @@
       <c r="P9" s="53" t="s">
         <v>84</v>
       </c>
-      <c r="Q9" s="43" t="str">
-        <f t="shared" si="15"/>
-        <v>Delimitación de Detalles de Llamada</v>
+      <c r="Q9" s="43" t="s">
+        <v>775</v>
       </c>
       <c r="R9" s="43" t="s">
         <v>639</v>
@@ -4513,15 +4819,15 @@
         <v>9</v>
       </c>
       <c r="T9" s="43" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="13"/>
         <v>Documentais</v>
       </c>
       <c r="U9" s="43" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="14"/>
         <v>Elemento.de.Detalhamento</v>
       </c>
       <c r="V9" s="53" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="15"/>
         <v>Símbolo.Chamada</v>
       </c>
       <c r="W9" s="43" t="s">
@@ -4600,9 +4906,8 @@
       <c r="P10" s="53" t="s">
         <v>85</v>
       </c>
-      <c r="Q10" s="43" t="str">
-        <f t="shared" si="15"/>
-        <v>Símbolo de Llamada - Cabeza</v>
+      <c r="Q10" s="43" t="s">
+        <v>776</v>
       </c>
       <c r="R10" s="43" t="s">
         <v>640</v>
@@ -4611,15 +4916,15 @@
         <v>9</v>
       </c>
       <c r="T10" s="43" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="13"/>
         <v>Documentais</v>
       </c>
       <c r="U10" s="43" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="14"/>
         <v>Elemento.de.Detalhamento</v>
       </c>
       <c r="V10" s="53" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="15"/>
         <v>Símbolo.Chamada</v>
       </c>
       <c r="W10" s="43" t="s">
@@ -4698,9 +5003,8 @@
       <c r="P11" s="53" t="s">
         <v>86</v>
       </c>
-      <c r="Q11" s="43" t="str">
-        <f t="shared" si="15"/>
-        <v>Símbolo de líder - Línea de guía</v>
+      <c r="Q11" s="43" t="s">
+        <v>777</v>
       </c>
       <c r="R11" s="43" t="s">
         <v>641</v>
@@ -4709,15 +5013,15 @@
         <v>9</v>
       </c>
       <c r="T11" s="43" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="13"/>
         <v>Documentais</v>
       </c>
       <c r="U11" s="43" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="14"/>
         <v>Elemento.de.Detalhamento</v>
       </c>
       <c r="V11" s="53" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="15"/>
         <v>Símbolo.Chamada</v>
       </c>
       <c r="W11" s="43" t="s">
@@ -4796,9 +5100,8 @@
       <c r="P12" s="53" t="s">
         <v>87</v>
       </c>
-      <c r="Q12" s="43" t="e" vm="1">
-        <f>_xlfn.TRANSLATE(P12,"pt","es")</f>
-        <v>#VALUE!</v>
+      <c r="Q12" s="53" t="s">
+        <v>896</v>
       </c>
       <c r="R12" s="43" t="s">
         <v>642</v>
@@ -4807,15 +5110,15 @@
         <v>9</v>
       </c>
       <c r="T12" s="43" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="13"/>
         <v>Documentais</v>
       </c>
       <c r="U12" s="43" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="14"/>
         <v>Elemento.de.Detalhamento</v>
       </c>
       <c r="V12" s="53" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="15"/>
         <v>Símbolo.Chamada</v>
       </c>
       <c r="W12" s="43" t="s">
@@ -4894,9 +5197,8 @@
       <c r="P13" s="53" t="s">
         <v>88</v>
       </c>
-      <c r="Q13" s="43" t="str">
-        <f t="shared" si="15"/>
-        <v>Reseña de Nube Simbólica de Detalle - Etiqueta o Etiqueta Textual</v>
+      <c r="Q13" s="43" t="s">
+        <v>778</v>
       </c>
       <c r="R13" s="43" t="s">
         <v>643</v>
@@ -4905,15 +5207,15 @@
         <v>9</v>
       </c>
       <c r="T13" s="43" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="13"/>
         <v>Documentais</v>
       </c>
       <c r="U13" s="43" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="14"/>
         <v>Elemento.de.Detalhamento</v>
       </c>
       <c r="V13" s="53" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="15"/>
         <v>Símbolo.Chamada</v>
       </c>
       <c r="W13" s="43" t="s">
@@ -4992,9 +5294,8 @@
       <c r="P14" s="53" t="s">
         <v>94</v>
       </c>
-      <c r="Q14" s="43" t="str">
-        <f t="shared" si="15"/>
-        <v>Vista de sección</v>
+      <c r="Q14" s="43" t="s">
+        <v>779</v>
       </c>
       <c r="R14" s="43" t="s">
         <v>644</v>
@@ -5003,15 +5304,15 @@
         <v>9</v>
       </c>
       <c r="T14" s="43" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="13"/>
         <v>Documentais</v>
       </c>
       <c r="U14" s="43" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="14"/>
         <v>Elemento.de.Detalhamento</v>
       </c>
       <c r="V14" s="53" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="15"/>
         <v>Símbolo.Corte</v>
       </c>
       <c r="W14" s="43" t="s">
@@ -5090,9 +5391,8 @@
       <c r="P15" s="53" t="s">
         <v>90</v>
       </c>
-      <c r="Q15" s="43" t="str">
-        <f t="shared" si="15"/>
-        <v>Símbolo de corte - Cabeza</v>
+      <c r="Q15" s="43" t="s">
+        <v>780</v>
       </c>
       <c r="R15" s="43" t="s">
         <v>645</v>
@@ -5101,15 +5401,15 @@
         <v>9</v>
       </c>
       <c r="T15" s="43" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="13"/>
         <v>Documentais</v>
       </c>
       <c r="U15" s="43" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="14"/>
         <v>Elemento.de.Detalhamento</v>
       </c>
       <c r="V15" s="53" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="15"/>
         <v>Símbolo.Corte</v>
       </c>
       <c r="W15" s="43" t="s">
@@ -5188,9 +5488,8 @@
       <c r="P16" s="53" t="s">
         <v>91</v>
       </c>
-      <c r="Q16" s="43" t="str">
-        <f t="shared" si="15"/>
-        <v>Símbolo de corte - líneas finas de la cabeza</v>
+      <c r="Q16" s="43" t="s">
+        <v>781</v>
       </c>
       <c r="R16" s="43" t="s">
         <v>646</v>
@@ -5199,15 +5498,15 @@
         <v>9</v>
       </c>
       <c r="T16" s="43" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="13"/>
         <v>Documentais</v>
       </c>
       <c r="U16" s="43" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="14"/>
         <v>Elemento.de.Detalhamento</v>
       </c>
       <c r="V16" s="53" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="15"/>
         <v>Símbolo.Corte</v>
       </c>
       <c r="W16" s="43" t="s">
@@ -5286,9 +5585,8 @@
       <c r="P17" s="53" t="s">
         <v>89</v>
       </c>
-      <c r="Q17" s="43" t="str">
-        <f t="shared" si="15"/>
-        <v>Símbolo de corte - Líneas medias de la cabeza</v>
+      <c r="Q17" s="43" t="s">
+        <v>782</v>
       </c>
       <c r="R17" s="43" t="s">
         <v>647</v>
@@ -5297,15 +5595,15 @@
         <v>9</v>
       </c>
       <c r="T17" s="43" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="13"/>
         <v>Documentais</v>
       </c>
       <c r="U17" s="43" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="14"/>
         <v>Elemento.de.Detalhamento</v>
       </c>
       <c r="V17" s="53" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="15"/>
         <v>Símbolo.Corte</v>
       </c>
       <c r="W17" s="43" t="s">
@@ -5384,9 +5682,8 @@
       <c r="P18" s="53" t="s">
         <v>92</v>
       </c>
-      <c r="Q18" s="43" t="str">
-        <f t="shared" si="15"/>
-        <v>Símbolo de corte - Líneas de encabezado gruesas</v>
+      <c r="Q18" s="43" t="s">
+        <v>783</v>
       </c>
       <c r="R18" s="43" t="s">
         <v>648</v>
@@ -5395,15 +5692,15 @@
         <v>9</v>
       </c>
       <c r="T18" s="43" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="13"/>
         <v>Documentais</v>
       </c>
       <c r="U18" s="43" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="14"/>
         <v>Elemento.de.Detalhamento</v>
       </c>
       <c r="V18" s="53" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="15"/>
         <v>Símbolo.Corte</v>
       </c>
       <c r="W18" s="43" t="s">
@@ -5482,9 +5779,8 @@
       <c r="P19" s="53" t="s">
         <v>93</v>
       </c>
-      <c r="Q19" s="43" t="str">
-        <f t="shared" si="15"/>
-        <v>Símbolo de corte - Línea de corte</v>
+      <c r="Q19" s="43" t="s">
+        <v>784</v>
       </c>
       <c r="R19" s="43" t="s">
         <v>649</v>
@@ -5493,15 +5789,15 @@
         <v>9</v>
       </c>
       <c r="T19" s="43" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="13"/>
         <v>Documentais</v>
       </c>
       <c r="U19" s="43" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="14"/>
         <v>Elemento.de.Detalhamento</v>
       </c>
       <c r="V19" s="53" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="15"/>
         <v>Símbolo.Corte</v>
       </c>
       <c r="W19" s="43" t="s">
@@ -5580,9 +5876,8 @@
       <c r="P20" s="53" t="s">
         <v>558</v>
       </c>
-      <c r="Q20" s="43" t="str">
-        <f t="shared" si="15"/>
-        <v>Línea de corte interrumpida</v>
+      <c r="Q20" s="43" t="s">
+        <v>785</v>
       </c>
       <c r="R20" s="43" t="s">
         <v>650</v>
@@ -5591,15 +5886,15 @@
         <v>9</v>
       </c>
       <c r="T20" s="43" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="13"/>
         <v>Documentais</v>
       </c>
       <c r="U20" s="43" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="14"/>
         <v>Elemento.de.Detalhamento</v>
       </c>
       <c r="V20" s="53" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="15"/>
         <v>Símbolo.Corte</v>
       </c>
       <c r="W20" s="43" t="s">
@@ -5678,9 +5973,8 @@
       <c r="P21" s="53" t="s">
         <v>559</v>
       </c>
-      <c r="Q21" s="43" t="str">
-        <f t="shared" si="15"/>
-        <v>Calcomanía de imagen insertada</v>
+      <c r="Q21" s="43" t="s">
+        <v>786</v>
       </c>
       <c r="R21" s="43" t="s">
         <v>651</v>
@@ -5689,15 +5983,15 @@
         <v>9</v>
       </c>
       <c r="T21" s="43" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="13"/>
         <v>Documentais</v>
       </c>
       <c r="U21" s="43" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="14"/>
         <v>Elemento.de.Detalhamento</v>
       </c>
       <c r="V21" s="53" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="15"/>
         <v>Símbolo.Detalhe</v>
       </c>
       <c r="W21" s="43" t="s">
@@ -5776,9 +6070,8 @@
       <c r="P22" s="53" t="s">
         <v>95</v>
       </c>
-      <c r="Q22" s="43" t="e" vm="1">
-        <f>_xlfn.TRANSLATE(P22,"pt","es")</f>
-        <v>#VALUE!</v>
+      <c r="Q22" s="53" t="s">
+        <v>897</v>
       </c>
       <c r="R22" s="43" t="s">
         <v>652</v>
@@ -5787,15 +6080,15 @@
         <v>9</v>
       </c>
       <c r="T22" s="43" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="13"/>
         <v>Documentais</v>
       </c>
       <c r="U22" s="43" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="14"/>
         <v>Elemento.de.Detalhamento</v>
       </c>
       <c r="V22" s="53" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="15"/>
         <v>Símbolo.Detalhe</v>
       </c>
       <c r="W22" s="43" t="s">
@@ -5874,9 +6167,8 @@
       <c r="P23" s="53" t="s">
         <v>96</v>
       </c>
-      <c r="Q23" s="43" t="str">
-        <f t="shared" si="15"/>
-        <v>Componente de detallado 2D - Líneas ocultas</v>
+      <c r="Q23" s="43" t="s">
+        <v>787</v>
       </c>
       <c r="R23" s="43" t="s">
         <v>653</v>
@@ -5885,15 +6177,15 @@
         <v>9</v>
       </c>
       <c r="T23" s="43" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="13"/>
         <v>Documentais</v>
       </c>
       <c r="U23" s="43" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="14"/>
         <v>Elemento.de.Detalhamento</v>
       </c>
       <c r="V23" s="53" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="15"/>
         <v>Símbolo.Detalhe</v>
       </c>
       <c r="W23" s="43" t="s">
@@ -5972,9 +6264,8 @@
       <c r="P24" s="53" t="s">
         <v>560</v>
       </c>
-      <c r="Q24" s="43" t="str">
-        <f t="shared" si="15"/>
-        <v>Línea de detalle repetida</v>
+      <c r="Q24" s="43" t="s">
+        <v>788</v>
       </c>
       <c r="R24" s="43" t="s">
         <v>654</v>
@@ -5983,15 +6274,15 @@
         <v>9</v>
       </c>
       <c r="T24" s="43" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="13"/>
         <v>Documentais</v>
       </c>
       <c r="U24" s="43" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="14"/>
         <v>Elemento.de.Detalhamento</v>
       </c>
       <c r="V24" s="53" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="15"/>
         <v>Símbolo.Detalhe</v>
       </c>
       <c r="W24" s="43" t="s">
@@ -6070,9 +6361,8 @@
       <c r="P25" s="53" t="s">
         <v>97</v>
       </c>
-      <c r="Q25" s="43" t="str">
-        <f t="shared" si="15"/>
-        <v>Ver símbolos</v>
+      <c r="Q25" s="43" t="s">
+        <v>789</v>
       </c>
       <c r="R25" s="43" t="s">
         <v>655</v>
@@ -6081,15 +6371,15 @@
         <v>9</v>
       </c>
       <c r="T25" s="43" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="13"/>
         <v>Documentais</v>
       </c>
       <c r="U25" s="43" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="14"/>
         <v>Elemento.de.Detalhamento</v>
       </c>
       <c r="V25" s="53" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="15"/>
         <v>Símbolo.Elevação</v>
       </c>
       <c r="W25" s="43" t="s">
@@ -6168,9 +6458,8 @@
       <c r="P26" s="53" t="s">
         <v>98</v>
       </c>
-      <c r="Q26" s="43" t="str">
-        <f t="shared" si="15"/>
-        <v>Ver símbolos - Marcas</v>
+      <c r="Q26" s="43" t="s">
+        <v>790</v>
       </c>
       <c r="R26" s="43" t="s">
         <v>656</v>
@@ -6179,15 +6468,15 @@
         <v>9</v>
       </c>
       <c r="T26" s="43" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="13"/>
         <v>Documentais</v>
       </c>
       <c r="U26" s="43" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="14"/>
         <v>Elemento.de.Detalhamento</v>
       </c>
       <c r="V26" s="53" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="15"/>
         <v>Símbolo.Elevação</v>
       </c>
       <c r="W26" s="43" t="s">
@@ -6266,9 +6555,8 @@
       <c r="P27" s="53" t="s">
         <v>99</v>
       </c>
-      <c r="Q27" s="43" t="str">
-        <f t="shared" si="15"/>
-        <v>Símbolo de punto de coordenadas</v>
+      <c r="Q27" s="43" t="s">
+        <v>791</v>
       </c>
       <c r="R27" s="43" t="s">
         <v>657</v>
@@ -6277,15 +6565,15 @@
         <v>9</v>
       </c>
       <c r="T27" s="43" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="13"/>
         <v>Documentais</v>
       </c>
       <c r="U27" s="43" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="14"/>
         <v>Elemento.de.Detalhamento</v>
       </c>
       <c r="V27" s="53" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="15"/>
         <v>Símbolo.Nível</v>
       </c>
       <c r="W27" s="43" t="s">
@@ -6364,9 +6652,8 @@
       <c r="P28" s="53" t="s">
         <v>100</v>
       </c>
-      <c r="Q28" s="43" t="str">
-        <f t="shared" si="15"/>
-        <v>Símbolos de puntos de coordenadas</v>
+      <c r="Q28" s="43" t="s">
+        <v>792</v>
       </c>
       <c r="R28" s="43" t="s">
         <v>658</v>
@@ -6375,15 +6662,15 @@
         <v>9</v>
       </c>
       <c r="T28" s="43" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="13"/>
         <v>Documentais</v>
       </c>
       <c r="U28" s="43" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="14"/>
         <v>Elemento.de.Detalhamento</v>
       </c>
       <c r="V28" s="53" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="15"/>
         <v>Símbolo.Nível</v>
       </c>
       <c r="W28" s="43" t="s">
@@ -6462,9 +6749,8 @@
       <c r="P29" s="53" t="s">
         <v>561</v>
       </c>
-      <c r="Q29" s="43" t="str">
-        <f t="shared" si="15"/>
-        <v>Comillas</v>
+      <c r="Q29" s="43" t="s">
+        <v>793</v>
       </c>
       <c r="R29" s="43" t="s">
         <v>659</v>
@@ -6473,15 +6759,15 @@
         <v>9</v>
       </c>
       <c r="T29" s="43" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="13"/>
         <v>Documentais</v>
       </c>
       <c r="U29" s="43" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="14"/>
         <v>Elemento.de.Detalhamento</v>
       </c>
       <c r="V29" s="53" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="15"/>
         <v>Símbolo.Nível</v>
       </c>
       <c r="W29" s="43" t="s">
@@ -6560,9 +6846,8 @@
       <c r="P30" s="53" t="s">
         <v>562</v>
       </c>
-      <c r="Q30" s="43" t="str">
-        <f t="shared" si="15"/>
-        <v>Símbolos de marca de verificación</v>
+      <c r="Q30" s="43" t="s">
+        <v>794</v>
       </c>
       <c r="R30" s="43" t="s">
         <v>660</v>
@@ -6571,15 +6856,15 @@
         <v>9</v>
       </c>
       <c r="T30" s="43" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="13"/>
         <v>Documentais</v>
       </c>
       <c r="U30" s="43" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="14"/>
         <v>Elemento.de.Detalhamento</v>
       </c>
       <c r="V30" s="53" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="15"/>
         <v>Símbolo.Nível</v>
       </c>
       <c r="W30" s="43" t="s">
@@ -6658,9 +6943,8 @@
       <c r="P31" s="53" t="s">
         <v>563</v>
       </c>
-      <c r="Q31" s="43" t="str">
-        <f t="shared" si="15"/>
-        <v>Pendiente</v>
+      <c r="Q31" s="43" t="s">
+        <v>795</v>
       </c>
       <c r="R31" s="43" t="s">
         <v>661</v>
@@ -6669,15 +6953,15 @@
         <v>9</v>
       </c>
       <c r="T31" s="43" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="13"/>
         <v>Documentais</v>
       </c>
       <c r="U31" s="43" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="14"/>
         <v>Elemento.de.Detalhamento</v>
       </c>
       <c r="V31" s="53" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="15"/>
         <v>Símbolo.Nível</v>
       </c>
       <c r="W31" s="43" t="s">
@@ -6756,9 +7040,8 @@
       <c r="P32" s="53" t="s">
         <v>101</v>
       </c>
-      <c r="Q32" s="43" t="str">
-        <f t="shared" si="15"/>
-        <v>Símbolos de pendiente</v>
+      <c r="Q32" s="43" t="s">
+        <v>796</v>
       </c>
       <c r="R32" s="43" t="s">
         <v>662</v>
@@ -6767,15 +7050,15 @@
         <v>9</v>
       </c>
       <c r="T32" s="43" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="13"/>
         <v>Documentais</v>
       </c>
       <c r="U32" s="43" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="14"/>
         <v>Elemento.de.Detalhamento</v>
       </c>
       <c r="V32" s="53" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="15"/>
         <v>Símbolo.Nível</v>
       </c>
       <c r="W32" s="43" t="s">
@@ -6854,9 +7137,8 @@
       <c r="P33" s="53" t="s">
         <v>564</v>
       </c>
-      <c r="Q33" s="43" t="str">
-        <f t="shared" si="15"/>
-        <v>Dimensión citada</v>
+      <c r="Q33" s="43" t="s">
+        <v>797</v>
       </c>
       <c r="R33" s="43" t="s">
         <v>663</v>
@@ -6865,15 +7147,15 @@
         <v>9</v>
       </c>
       <c r="T33" s="43" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="13"/>
         <v>Documentais</v>
       </c>
       <c r="U33" s="43" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="14"/>
         <v>Elemento.de.Dimensionamento</v>
       </c>
       <c r="V33" s="53" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="15"/>
         <v>Símbolo.Cota</v>
       </c>
       <c r="W33" s="43" t="s">
@@ -6952,9 +7234,8 @@
       <c r="P34" s="53" t="s">
         <v>102</v>
       </c>
-      <c r="Q34" s="43" t="e" vm="1">
-        <f t="shared" si="15"/>
-        <v>#VALUE!</v>
+      <c r="Q34" s="53" t="s">
+        <v>898</v>
       </c>
       <c r="R34" s="43" t="s">
         <v>664</v>
@@ -6963,15 +7244,15 @@
         <v>9</v>
       </c>
       <c r="T34" s="43" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="13"/>
         <v>Documentais</v>
       </c>
       <c r="U34" s="43" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="14"/>
         <v>Elemento.de.Dimensionamento</v>
       </c>
       <c r="V34" s="53" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="15"/>
         <v>Símbolo.Cota</v>
       </c>
       <c r="W34" s="43" t="s">
@@ -7050,9 +7331,8 @@
       <c r="P35" s="53" t="s">
         <v>103</v>
       </c>
-      <c r="Q35" s="43" t="e" vm="1">
-        <f t="shared" si="15"/>
-        <v>#VALUE!</v>
+      <c r="Q35" s="53" t="s">
+        <v>899</v>
       </c>
       <c r="R35" s="43" t="s">
         <v>665</v>
@@ -7061,15 +7341,15 @@
         <v>9</v>
       </c>
       <c r="T35" s="43" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="13"/>
         <v>Documentais</v>
       </c>
       <c r="U35" s="43" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="14"/>
         <v>Elemento.de.Dimensionamento</v>
       </c>
       <c r="V35" s="53" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="15"/>
         <v>Símbolo.Cota</v>
       </c>
       <c r="W35" s="43" t="s">
@@ -7148,9 +7428,8 @@
       <c r="P36" s="53" t="s">
         <v>104</v>
       </c>
-      <c r="Q36" s="43" t="str">
-        <f t="shared" si="15"/>
-        <v>Estilo de elemento final de dimensión - ID de estilo de identificador único</v>
+      <c r="Q36" s="43" t="s">
+        <v>798</v>
       </c>
       <c r="R36" s="43" t="s">
         <v>666</v>
@@ -7159,15 +7438,15 @@
         <v>9</v>
       </c>
       <c r="T36" s="43" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="13"/>
         <v>Documentais</v>
       </c>
       <c r="U36" s="43" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="14"/>
         <v>Elemento.de.Estilização</v>
       </c>
       <c r="V36" s="53" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="15"/>
         <v>De.Cotas</v>
       </c>
       <c r="W36" s="43" t="s">
@@ -7246,9 +7525,8 @@
       <c r="P37" s="53" t="s">
         <v>104</v>
       </c>
-      <c r="Q37" s="43" t="str">
-        <f t="shared" si="15"/>
-        <v>Estilo de elemento final de dimensión - ID de estilo de identificador único</v>
+      <c r="Q37" s="43" t="s">
+        <v>798</v>
       </c>
       <c r="R37" s="43" t="s">
         <v>666</v>
@@ -7257,15 +7535,15 @@
         <v>9</v>
       </c>
       <c r="T37" s="43" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="13"/>
         <v>Documentais</v>
       </c>
       <c r="U37" s="43" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="14"/>
         <v>Elemento.de.Estilização</v>
       </c>
       <c r="V37" s="53" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="15"/>
         <v>De.Cotas</v>
       </c>
       <c r="W37" s="43" t="s">
@@ -7344,9 +7622,8 @@
       <c r="P38" s="53" t="s">
         <v>105</v>
       </c>
-      <c r="Q38" s="43" t="str">
-        <f t="shared" si="15"/>
-        <v>Patrón de líneas centrales</v>
+      <c r="Q38" s="43" t="s">
+        <v>799</v>
       </c>
       <c r="R38" s="43" t="s">
         <v>667</v>
@@ -7355,15 +7632,15 @@
         <v>9</v>
       </c>
       <c r="T38" s="43" t="str">
-        <f t="shared" ref="T38:T69" si="19">SUBSTITUTE(C38, "_", " ")</f>
+        <f t="shared" ref="T38:T69" si="16">SUBSTITUTE(C38, "_", " ")</f>
         <v>Documentais</v>
       </c>
       <c r="U38" s="43" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="14"/>
         <v>Elemento.de.Estilização</v>
       </c>
       <c r="V38" s="53" t="str">
-        <f t="shared" ref="V38:V69" si="20">SUBSTITUTE(E38, "_", " ")</f>
+        <f t="shared" ref="V38:V69" si="17">SUBSTITUTE(E38, "_", " ")</f>
         <v>De.Linhas</v>
       </c>
       <c r="W38" s="43" t="s">
@@ -7442,9 +7719,8 @@
       <c r="P39" s="53" t="s">
         <v>556</v>
       </c>
-      <c r="Q39" s="43" t="str">
-        <f t="shared" si="15"/>
-        <v>Líneas invisibles</v>
+      <c r="Q39" s="43" t="s">
+        <v>800</v>
       </c>
       <c r="R39" s="43" t="s">
         <v>668</v>
@@ -7453,15 +7729,15 @@
         <v>9</v>
       </c>
       <c r="T39" s="43" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v>Documentais</v>
       </c>
       <c r="U39" s="43" t="str">
+        <f t="shared" si="14"/>
+        <v>Elemento.de.Estilização</v>
+      </c>
+      <c r="V39" s="53" t="str">
         <f t="shared" si="17"/>
-        <v>Elemento.de.Estilização</v>
-      </c>
-      <c r="V39" s="53" t="str">
-        <f t="shared" si="20"/>
         <v>De.Linhas</v>
       </c>
       <c r="W39" s="43" t="s">
@@ -7540,9 +7816,8 @@
       <c r="P40" s="53" t="s">
         <v>565</v>
       </c>
-      <c r="Q40" s="43" t="str">
-        <f t="shared" si="15"/>
-        <v>Líneas de aristas proyectadas</v>
+      <c r="Q40" s="43" t="s">
+        <v>801</v>
       </c>
       <c r="R40" s="43" t="s">
         <v>669</v>
@@ -7551,15 +7826,15 @@
         <v>9</v>
       </c>
       <c r="T40" s="43" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v>Documentais</v>
       </c>
       <c r="U40" s="43" t="str">
+        <f t="shared" si="14"/>
+        <v>Elemento.de.Estilização</v>
+      </c>
+      <c r="V40" s="53" t="str">
         <f t="shared" si="17"/>
-        <v>Elemento.de.Estilização</v>
-      </c>
-      <c r="V40" s="53" t="str">
-        <f t="shared" si="20"/>
         <v>De.Linhas</v>
       </c>
       <c r="W40" s="43" t="s">
@@ -7638,9 +7913,8 @@
       <c r="P41" s="53" t="s">
         <v>106</v>
       </c>
-      <c r="Q41" s="43" t="str">
-        <f t="shared" si="15"/>
-        <v>Líneas de aislamiento</v>
+      <c r="Q41" s="43" t="s">
+        <v>802</v>
       </c>
       <c r="R41" s="43" t="s">
         <v>670</v>
@@ -7649,15 +7923,15 @@
         <v>9</v>
       </c>
       <c r="T41" s="43" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v>Documentais</v>
       </c>
       <c r="U41" s="43" t="str">
+        <f t="shared" si="14"/>
+        <v>Elemento.de.Estilização</v>
+      </c>
+      <c r="V41" s="53" t="str">
         <f t="shared" si="17"/>
-        <v>Elemento.de.Estilização</v>
-      </c>
-      <c r="V41" s="53" t="str">
-        <f t="shared" si="20"/>
         <v>De.Linhas</v>
       </c>
       <c r="W41" s="43" t="s">
@@ -7736,9 +8010,8 @@
       <c r="P42" s="53" t="s">
         <v>557</v>
       </c>
-      <c r="Q42" s="43" t="str">
-        <f t="shared" si="15"/>
-        <v>Líneas centrales</v>
+      <c r="Q42" s="43" t="s">
+        <v>803</v>
       </c>
       <c r="R42" s="43" t="s">
         <v>671</v>
@@ -7747,15 +8020,15 @@
         <v>9</v>
       </c>
       <c r="T42" s="43" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v>Documentais</v>
       </c>
       <c r="U42" s="43" t="str">
+        <f t="shared" si="14"/>
+        <v>Elemento.de.Estilização</v>
+      </c>
+      <c r="V42" s="53" t="str">
         <f t="shared" si="17"/>
-        <v>Elemento.de.Estilização</v>
-      </c>
-      <c r="V42" s="53" t="str">
-        <f t="shared" si="20"/>
         <v>De.Linhas</v>
       </c>
       <c r="W42" s="43" t="s">
@@ -7834,9 +8107,8 @@
       <c r="P43" s="53" t="s">
         <v>107</v>
       </c>
-      <c r="Q43" s="43" t="str">
-        <f t="shared" si="15"/>
-        <v>Líneas centrales CL</v>
+      <c r="Q43" s="43" t="s">
+        <v>804</v>
       </c>
       <c r="R43" s="43" t="s">
         <v>672</v>
@@ -7845,15 +8117,15 @@
         <v>9</v>
       </c>
       <c r="T43" s="43" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v>Documentais</v>
       </c>
       <c r="U43" s="43" t="str">
+        <f t="shared" si="14"/>
+        <v>Elemento.de.Estilização</v>
+      </c>
+      <c r="V43" s="53" t="str">
         <f t="shared" si="17"/>
-        <v>Elemento.de.Estilização</v>
-      </c>
-      <c r="V43" s="53" t="str">
-        <f t="shared" si="20"/>
         <v>De.Linhas</v>
       </c>
       <c r="W43" s="43" t="s">
@@ -7932,9 +8204,8 @@
       <c r="P44" s="53" t="s">
         <v>108</v>
       </c>
-      <c r="Q44" s="43" t="str">
-        <f t="shared" si="15"/>
-        <v>Líneas de demolición</v>
+      <c r="Q44" s="43" t="s">
+        <v>805</v>
       </c>
       <c r="R44" s="43" t="s">
         <v>673</v>
@@ -7943,15 +8214,15 @@
         <v>9</v>
       </c>
       <c r="T44" s="43" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v>Documentais</v>
       </c>
       <c r="U44" s="43" t="str">
+        <f t="shared" si="14"/>
+        <v>Elemento.de.Estilização</v>
+      </c>
+      <c r="V44" s="53" t="str">
         <f t="shared" si="17"/>
-        <v>Elemento.de.Estilização</v>
-      </c>
-      <c r="V44" s="53" t="str">
-        <f t="shared" si="20"/>
         <v>De.Linhas</v>
       </c>
       <c r="W44" s="43" t="s">
@@ -8030,9 +8301,8 @@
       <c r="P45" s="53" t="s">
         <v>566</v>
       </c>
-      <c r="Q45" s="43" t="str">
-        <f t="shared" si="15"/>
-        <v>Líneas de proyección de bordes superiores</v>
+      <c r="Q45" s="43" t="s">
+        <v>806</v>
       </c>
       <c r="R45" s="43" t="s">
         <v>674</v>
@@ -8041,15 +8311,15 @@
         <v>9</v>
       </c>
       <c r="T45" s="43" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v>Documentais</v>
       </c>
       <c r="U45" s="43" t="str">
+        <f t="shared" si="14"/>
+        <v>Elemento.de.Estilização</v>
+      </c>
+      <c r="V45" s="53" t="str">
         <f t="shared" si="17"/>
-        <v>Elemento.de.Estilização</v>
-      </c>
-      <c r="V45" s="53" t="str">
-        <f t="shared" si="20"/>
         <v>De.Linhas</v>
       </c>
       <c r="W45" s="43" t="s">
@@ -8128,9 +8398,8 @@
       <c r="P46" s="53" t="s">
         <v>109</v>
       </c>
-      <c r="Q46" s="43" t="str">
-        <f t="shared" si="15"/>
-        <v>Líneas ocultas</v>
+      <c r="Q46" s="43" t="s">
+        <v>807</v>
       </c>
       <c r="R46" s="43" t="s">
         <v>675</v>
@@ -8139,15 +8408,15 @@
         <v>9</v>
       </c>
       <c r="T46" s="43" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v>Documentais</v>
       </c>
       <c r="U46" s="43" t="str">
+        <f t="shared" si="14"/>
+        <v>Elemento.de.Estilização</v>
+      </c>
+      <c r="V46" s="53" t="str">
         <f t="shared" si="17"/>
-        <v>Elemento.de.Estilização</v>
-      </c>
-      <c r="V46" s="53" t="str">
-        <f t="shared" si="20"/>
         <v>De.Linhas</v>
       </c>
       <c r="W46" s="43" t="s">
@@ -8226,9 +8495,8 @@
       <c r="P47" s="53" t="s">
         <v>567</v>
       </c>
-      <c r="Q47" s="43" t="str">
-        <f t="shared" si="15"/>
-        <v>Líneas ocultas del suelo</v>
+      <c r="Q47" s="43" t="s">
+        <v>808</v>
       </c>
       <c r="R47" s="43" t="s">
         <v>676</v>
@@ -8237,15 +8505,15 @@
         <v>9</v>
       </c>
       <c r="T47" s="43" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v>Documentais</v>
       </c>
       <c r="U47" s="43" t="str">
+        <f t="shared" si="14"/>
+        <v>Elemento.de.Estilização</v>
+      </c>
+      <c r="V47" s="53" t="str">
         <f t="shared" si="17"/>
-        <v>Elemento.de.Estilização</v>
-      </c>
-      <c r="V47" s="53" t="str">
-        <f t="shared" si="20"/>
         <v>De.Linhas</v>
       </c>
       <c r="W47" s="43" t="s">
@@ -8324,9 +8592,8 @@
       <c r="P48" s="53" t="s">
         <v>109</v>
       </c>
-      <c r="Q48" s="43" t="str">
-        <f t="shared" si="15"/>
-        <v>Líneas ocultas</v>
+      <c r="Q48" s="43" t="s">
+        <v>807</v>
       </c>
       <c r="R48" s="43" t="s">
         <v>675</v>
@@ -8335,15 +8602,15 @@
         <v>9</v>
       </c>
       <c r="T48" s="43" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v>Documentais</v>
       </c>
       <c r="U48" s="43" t="str">
+        <f t="shared" si="14"/>
+        <v>Elemento.de.Estilização</v>
+      </c>
+      <c r="V48" s="53" t="str">
         <f t="shared" si="17"/>
-        <v>Elemento.de.Estilização</v>
-      </c>
-      <c r="V48" s="53" t="str">
-        <f t="shared" si="20"/>
         <v>De.Linhas</v>
       </c>
       <c r="W48" s="43" t="s">
@@ -8422,9 +8689,8 @@
       <c r="P49" s="53" t="s">
         <v>568</v>
       </c>
-      <c r="Q49" s="43" t="str">
-        <f t="shared" si="15"/>
-        <v>Filas ocultas de columnas estructurales</v>
+      <c r="Q49" s="43" t="s">
+        <v>809</v>
       </c>
       <c r="R49" s="43" t="s">
         <v>677</v>
@@ -8433,15 +8699,15 @@
         <v>9</v>
       </c>
       <c r="T49" s="43" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v>Documentais</v>
       </c>
       <c r="U49" s="43" t="str">
+        <f t="shared" si="14"/>
+        <v>Elemento.de.Estilização</v>
+      </c>
+      <c r="V49" s="53" t="str">
         <f t="shared" si="17"/>
-        <v>Elemento.de.Estilização</v>
-      </c>
-      <c r="V49" s="53" t="str">
-        <f t="shared" si="20"/>
         <v>De.Linhas</v>
       </c>
       <c r="W49" s="43" t="s">
@@ -8520,9 +8786,8 @@
       <c r="P50" s="53" t="s">
         <v>569</v>
       </c>
-      <c r="Q50" s="43" t="str">
-        <f t="shared" si="15"/>
-        <v>Líneas ocultas de cimientos estructurales</v>
+      <c r="Q50" s="43" t="s">
+        <v>810</v>
       </c>
       <c r="R50" s="43" t="s">
         <v>678</v>
@@ -8531,15 +8796,15 @@
         <v>9</v>
       </c>
       <c r="T50" s="43" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v>Documentais</v>
       </c>
       <c r="U50" s="43" t="str">
+        <f t="shared" si="14"/>
+        <v>Elemento.de.Estilização</v>
+      </c>
+      <c r="V50" s="53" t="str">
         <f t="shared" si="17"/>
-        <v>Elemento.de.Estilização</v>
-      </c>
-      <c r="V50" s="53" t="str">
-        <f t="shared" si="20"/>
         <v>De.Linhas</v>
       </c>
       <c r="W50" s="43" t="s">
@@ -8618,9 +8883,8 @@
       <c r="P51" s="53" t="s">
         <v>570</v>
       </c>
-      <c r="Q51" s="43" t="str">
-        <f t="shared" si="15"/>
-        <v>Líneas ocultas de vigas estructurales</v>
+      <c r="Q51" s="43" t="s">
+        <v>811</v>
       </c>
       <c r="R51" s="43" t="s">
         <v>679</v>
@@ -8629,15 +8893,15 @@
         <v>9</v>
       </c>
       <c r="T51" s="43" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v>Documentais</v>
       </c>
       <c r="U51" s="43" t="str">
+        <f t="shared" si="14"/>
+        <v>Elemento.de.Estilização</v>
+      </c>
+      <c r="V51" s="53" t="str">
         <f t="shared" si="17"/>
-        <v>Elemento.de.Estilização</v>
-      </c>
-      <c r="V51" s="53" t="str">
-        <f t="shared" si="20"/>
         <v>De.Linhas</v>
       </c>
       <c r="W51" s="43" t="s">
@@ -8716,9 +8980,8 @@
       <c r="P52" s="53" t="s">
         <v>571</v>
       </c>
-      <c r="Q52" s="43" t="str">
-        <f t="shared" si="15"/>
-        <v>Líneas ocultas de muros</v>
+      <c r="Q52" s="43" t="s">
+        <v>812</v>
       </c>
       <c r="R52" s="43" t="s">
         <v>680</v>
@@ -8727,15 +8990,15 @@
         <v>9</v>
       </c>
       <c r="T52" s="43" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v>Documentais</v>
       </c>
       <c r="U52" s="43" t="str">
+        <f t="shared" si="14"/>
+        <v>Elemento.de.Estilização</v>
+      </c>
+      <c r="V52" s="53" t="str">
         <f t="shared" si="17"/>
-        <v>Elemento.de.Estilização</v>
-      </c>
-      <c r="V52" s="53" t="str">
-        <f t="shared" si="20"/>
         <v>De.Linhas</v>
       </c>
       <c r="W52" s="43" t="s">
@@ -8814,9 +9077,8 @@
       <c r="P53" s="53" t="s">
         <v>110</v>
       </c>
-      <c r="Q53" s="43" t="str">
-        <f t="shared" si="15"/>
-        <v>Estilo de Instancia Row</v>
+      <c r="Q53" s="43" t="s">
+        <v>813</v>
       </c>
       <c r="R53" s="43" t="s">
         <v>681</v>
@@ -8825,15 +9087,15 @@
         <v>9</v>
       </c>
       <c r="T53" s="43" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v>Documentais</v>
       </c>
       <c r="U53" s="43" t="str">
+        <f t="shared" si="14"/>
+        <v>Elemento.de.Estilização</v>
+      </c>
+      <c r="V53" s="53" t="str">
         <f t="shared" si="17"/>
-        <v>Elemento.de.Estilização</v>
-      </c>
-      <c r="V53" s="53" t="str">
-        <f t="shared" si="20"/>
         <v>De.Linhas</v>
       </c>
       <c r="W53" s="43" t="s">
@@ -8912,9 +9174,8 @@
       <c r="P54" s="53" t="s">
         <v>111</v>
       </c>
-      <c r="Q54" s="43" t="str">
-        <f t="shared" si="15"/>
-        <v>Ticks tipo ticks en la línea central</v>
+      <c r="Q54" s="43" t="s">
+        <v>814</v>
       </c>
       <c r="R54" s="43" t="s">
         <v>682</v>
@@ -8923,15 +9184,15 @@
         <v>9</v>
       </c>
       <c r="T54" s="43" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v>Documentais</v>
       </c>
       <c r="U54" s="43" t="str">
+        <f t="shared" si="14"/>
+        <v>Elemento.de.Estilização</v>
+      </c>
+      <c r="V54" s="53" t="str">
         <f t="shared" si="17"/>
-        <v>Elemento.de.Estilização</v>
-      </c>
-      <c r="V54" s="53" t="str">
-        <f t="shared" si="20"/>
         <v>De.Marcas</v>
       </c>
       <c r="W54" s="43" t="s">
@@ -9010,9 +9271,8 @@
       <c r="P55" s="53" t="s">
         <v>112</v>
       </c>
-      <c r="Q55" s="43" t="str">
-        <f t="shared" si="15"/>
-        <v>Tick Mark de Cuota - Identificador único de ID de estilo</v>
+      <c r="Q55" s="43" t="s">
+        <v>815</v>
       </c>
       <c r="R55" s="43" t="s">
         <v>683</v>
@@ -9021,15 +9281,15 @@
         <v>9</v>
       </c>
       <c r="T55" s="43" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v>Documentais</v>
       </c>
       <c r="U55" s="43" t="str">
+        <f t="shared" si="14"/>
+        <v>Elemento.de.Estilização</v>
+      </c>
+      <c r="V55" s="53" t="str">
         <f t="shared" si="17"/>
-        <v>Elemento.de.Estilização</v>
-      </c>
-      <c r="V55" s="53" t="str">
-        <f t="shared" si="20"/>
         <v>De.Marcas</v>
       </c>
       <c r="W55" s="43" t="s">
@@ -9108,9 +9368,8 @@
       <c r="P56" s="53" t="s">
         <v>113</v>
       </c>
-      <c r="Q56" s="43" t="str">
-        <f t="shared" si="15"/>
-        <v>Interior de la marca Tick - Identificador único de estilo</v>
+      <c r="Q56" s="43" t="s">
+        <v>816</v>
       </c>
       <c r="R56" s="43" t="s">
         <v>684</v>
@@ -9119,15 +9378,15 @@
         <v>9</v>
       </c>
       <c r="T56" s="43" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v>Documentais</v>
       </c>
       <c r="U56" s="43" t="str">
+        <f t="shared" si="14"/>
+        <v>Elemento.de.Estilização</v>
+      </c>
+      <c r="V56" s="53" t="str">
         <f t="shared" si="17"/>
-        <v>Elemento.de.Estilização</v>
-      </c>
-      <c r="V56" s="53" t="str">
-        <f t="shared" si="20"/>
         <v>De.Marcas</v>
       </c>
       <c r="W56" s="43" t="s">
@@ -9206,9 +9465,8 @@
       <c r="P57" s="53" t="s">
         <v>114</v>
       </c>
-      <c r="Q57" s="43" t="str">
-        <f t="shared" si="15"/>
-        <v>Marca de verificación de línea de llamada - Identificador único de ID de estilo</v>
+      <c r="Q57" s="43" t="s">
+        <v>817</v>
       </c>
       <c r="R57" s="43" t="s">
         <v>685</v>
@@ -9217,15 +9475,15 @@
         <v>9</v>
       </c>
       <c r="T57" s="43" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v>Documentais</v>
       </c>
       <c r="U57" s="43" t="str">
+        <f t="shared" si="14"/>
+        <v>Elemento.de.Estilização</v>
+      </c>
+      <c r="V57" s="53" t="str">
         <f t="shared" si="17"/>
-        <v>Elemento.de.Estilização</v>
-      </c>
-      <c r="V57" s="53" t="str">
-        <f t="shared" si="20"/>
         <v>De.Marcas</v>
       </c>
       <c r="W57" s="43" t="s">
@@ -9304,9 +9562,8 @@
       <c r="P58" s="53" t="s">
         <v>115</v>
       </c>
-      <c r="Q58" s="43" t="str">
-        <f t="shared" si="15"/>
-        <v>Punta simbólica de flecha</v>
+      <c r="Q58" s="43" t="s">
+        <v>818</v>
       </c>
       <c r="R58" s="43" t="s">
         <v>686</v>
@@ -9315,22 +9572,22 @@
         <v>9</v>
       </c>
       <c r="T58" s="43" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v>Documentais</v>
       </c>
       <c r="U58" s="43" t="str">
+        <f t="shared" si="14"/>
+        <v>Elemento.de.Estilização</v>
+      </c>
+      <c r="V58" s="53" t="str">
         <f t="shared" si="17"/>
-        <v>Elemento.de.Estilização</v>
-      </c>
-      <c r="V58" s="53" t="str">
-        <f t="shared" si="20"/>
         <v>De.Setas</v>
       </c>
       <c r="W58" s="43" t="s">
         <v>80</v>
       </c>
       <c r="X58" s="54" t="str">
-        <f t="shared" ref="X58:X121" si="21">CONCATENATE("Key-DOCU-",A58)</f>
+        <f t="shared" ref="X58:X121" si="18">CONCATENATE("Key-DOCU-",A58)</f>
         <v>Key-DOCU-58</v>
       </c>
       <c r="Y58" s="58" t="s">
@@ -9402,9 +9659,8 @@
       <c r="P59" s="53" t="s">
         <v>116</v>
       </c>
-      <c r="Q59" s="43" t="str">
-        <f t="shared" si="15"/>
-        <v>Texto y Líder - Fuente del Texto</v>
+      <c r="Q59" s="43" t="s">
+        <v>819</v>
       </c>
       <c r="R59" s="43" t="s">
         <v>687</v>
@@ -9413,22 +9669,22 @@
         <v>9</v>
       </c>
       <c r="T59" s="43" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v>Documentais</v>
       </c>
       <c r="U59" s="43" t="str">
+        <f t="shared" si="14"/>
+        <v>Elemento.de.Estilização</v>
+      </c>
+      <c r="V59" s="53" t="str">
         <f t="shared" si="17"/>
-        <v>Elemento.de.Estilização</v>
-      </c>
-      <c r="V59" s="53" t="str">
-        <f t="shared" si="20"/>
         <v>De.Textos</v>
       </c>
       <c r="W59" s="43" t="s">
         <v>80</v>
       </c>
       <c r="X59" s="54" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>Key-DOCU-59</v>
       </c>
       <c r="Y59" s="58" t="s">
@@ -9500,9 +9756,8 @@
       <c r="P60" s="53" t="s">
         <v>117</v>
       </c>
-      <c r="Q60" s="43" t="str">
-        <f t="shared" si="15"/>
-        <v>Texto y línea de guía - Identificador de ID único</v>
+      <c r="Q60" s="43" t="s">
+        <v>820</v>
       </c>
       <c r="R60" s="43" t="s">
         <v>688</v>
@@ -9511,22 +9766,22 @@
         <v>9</v>
       </c>
       <c r="T60" s="43" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v>Documentais</v>
       </c>
       <c r="U60" s="43" t="str">
+        <f t="shared" si="14"/>
+        <v>Elemento.de.Estilização</v>
+      </c>
+      <c r="V60" s="53" t="str">
         <f t="shared" si="17"/>
-        <v>Elemento.de.Estilização</v>
-      </c>
-      <c r="V60" s="53" t="str">
-        <f t="shared" si="20"/>
         <v>De.Textos</v>
       </c>
       <c r="W60" s="43" t="s">
         <v>80</v>
       </c>
       <c r="X60" s="54" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>Key-DOCU-60</v>
       </c>
       <c r="Y60" s="58" t="s">
@@ -9598,9 +9853,8 @@
       <c r="P61" s="53" t="s">
         <v>118</v>
       </c>
-      <c r="Q61" s="43" t="str">
-        <f t="shared" si="15"/>
-        <v>Estilizado de objetos importados</v>
+      <c r="Q61" s="43" t="s">
+        <v>821</v>
       </c>
       <c r="R61" s="43" t="s">
         <v>689</v>
@@ -9609,22 +9863,22 @@
         <v>9</v>
       </c>
       <c r="T61" s="43" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v>Documentais</v>
       </c>
       <c r="U61" s="43" t="str">
+        <f t="shared" si="14"/>
+        <v>Elemento.de.Estilização</v>
+      </c>
+      <c r="V61" s="53" t="str">
         <f t="shared" si="17"/>
-        <v>Elemento.de.Estilização</v>
-      </c>
-      <c r="V61" s="53" t="str">
-        <f t="shared" si="20"/>
         <v>De.Importação</v>
       </c>
       <c r="W61" s="43" t="s">
         <v>80</v>
       </c>
       <c r="X61" s="54" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>Key-DOCU-61</v>
       </c>
       <c r="Y61" s="58" t="s">
@@ -9696,9 +9950,8 @@
       <c r="P62" s="53" t="s">
         <v>119</v>
       </c>
-      <c r="Q62" s="43" t="str">
-        <f t="shared" si="15"/>
-        <v>Leyenda del Conducto</v>
+      <c r="Q62" s="43" t="s">
+        <v>822</v>
       </c>
       <c r="R62" s="43" t="s">
         <v>690</v>
@@ -9707,22 +9960,22 @@
         <v>9</v>
       </c>
       <c r="T62" s="43" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v>Documentais</v>
       </c>
       <c r="U62" s="43" t="str">
+        <f t="shared" si="14"/>
+        <v>Elemento.de.Legenda</v>
+      </c>
+      <c r="V62" s="53" t="str">
         <f t="shared" si="17"/>
-        <v>Elemento.de.Legenda</v>
-      </c>
-      <c r="V62" s="53" t="str">
-        <f t="shared" si="20"/>
         <v>Legenda.Cromática.Duto</v>
       </c>
       <c r="W62" s="43" t="s">
         <v>80</v>
       </c>
       <c r="X62" s="54" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>Key-DOCU-62</v>
       </c>
       <c r="Y62" s="58" t="s">
@@ -9794,9 +10047,8 @@
       <c r="P63" s="53" t="s">
         <v>120</v>
       </c>
-      <c r="Q63" s="43" t="str">
-        <f t="shared" si="15"/>
-        <v>Relleno de Color de Conductos</v>
+      <c r="Q63" s="43" t="s">
+        <v>823</v>
       </c>
       <c r="R63" s="43" t="s">
         <v>691</v>
@@ -9805,22 +10057,22 @@
         <v>9</v>
       </c>
       <c r="T63" s="43" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v>Documentais</v>
       </c>
       <c r="U63" s="43" t="str">
+        <f t="shared" si="14"/>
+        <v>Elemento.de.Legenda</v>
+      </c>
+      <c r="V63" s="53" t="str">
         <f t="shared" si="17"/>
-        <v>Elemento.de.Legenda</v>
-      </c>
-      <c r="V63" s="53" t="str">
-        <f t="shared" si="20"/>
         <v>Legenda.Cromática.Duto</v>
       </c>
       <c r="W63" s="43" t="s">
         <v>80</v>
       </c>
       <c r="X63" s="54" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>Key-DOCU-63</v>
       </c>
       <c r="Y63" s="58" t="s">
@@ -9892,9 +10144,8 @@
       <c r="P64" s="53" t="s">
         <v>121</v>
       </c>
-      <c r="Q64" s="43" t="str">
-        <f t="shared" si="15"/>
-        <v>Pipas - Leyendas de colores</v>
+      <c r="Q64" s="43" t="s">
+        <v>824</v>
       </c>
       <c r="R64" s="43" t="s">
         <v>692</v>
@@ -9903,22 +10154,22 @@
         <v>9</v>
       </c>
       <c r="T64" s="43" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v>Documentais</v>
       </c>
       <c r="U64" s="43" t="str">
+        <f t="shared" si="14"/>
+        <v>Elemento.de.Legenda</v>
+      </c>
+      <c r="V64" s="53" t="str">
         <f t="shared" si="17"/>
-        <v>Elemento.de.Legenda</v>
-      </c>
-      <c r="V64" s="53" t="str">
-        <f t="shared" si="20"/>
         <v>Legenda.Cromática.Tubulação</v>
       </c>
       <c r="W64" s="43" t="s">
         <v>80</v>
       </c>
       <c r="X64" s="54" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>Key-DOCU-64</v>
       </c>
       <c r="Y64" s="58" t="s">
@@ -9972,27 +10223,26 @@
         <v>9</v>
       </c>
       <c r="L65" s="53" t="str">
-        <f t="shared" ref="L65:L134" si="22">CONCATENATE("", C65)</f>
+        <f t="shared" ref="L65:L134" si="19">CONCATENATE("", C65)</f>
         <v>Documentais</v>
       </c>
       <c r="M65" s="53" t="str">
-        <f t="shared" ref="M65:M134" si="23">CONCATENATE("", D65)</f>
+        <f t="shared" ref="M65:M134" si="20">CONCATENATE("", D65)</f>
         <v>Elemento.de.Legenda</v>
       </c>
       <c r="N65" s="53" t="str">
-        <f t="shared" ref="N65:N134" si="24">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E65),"."," ")," De "," de "))</f>
+        <f t="shared" ref="N65:N134" si="21">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E65),"."," ")," De "," de "))</f>
         <v>Legenda Cromática Tubulação</v>
       </c>
       <c r="O65" s="53" t="str">
-        <f t="shared" ref="O65:O134" si="25">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",F65),"."," ")," De "," de "))</f>
+        <f t="shared" ref="O65:O134" si="22">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",F65),"."," ")," De "," de "))</f>
         <v>Tubos Cores Preenchidas</v>
       </c>
       <c r="P65" s="53" t="s">
         <v>122</v>
       </c>
-      <c r="Q65" s="43" t="str">
-        <f t="shared" si="15"/>
-        <v>Pipes - Colores</v>
+      <c r="Q65" s="43" t="s">
+        <v>825</v>
       </c>
       <c r="R65" s="43" t="s">
         <v>693</v>
@@ -10001,22 +10251,22 @@
         <v>9</v>
       </c>
       <c r="T65" s="43" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v>Documentais</v>
       </c>
       <c r="U65" s="43" t="str">
+        <f t="shared" si="14"/>
+        <v>Elemento.de.Legenda</v>
+      </c>
+      <c r="V65" s="53" t="str">
         <f t="shared" si="17"/>
-        <v>Elemento.de.Legenda</v>
-      </c>
-      <c r="V65" s="53" t="str">
-        <f t="shared" si="20"/>
         <v>Legenda.Cromática.Tubulação</v>
       </c>
       <c r="W65" s="43" t="s">
         <v>80</v>
       </c>
       <c r="X65" s="54" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>Key-DOCU-65</v>
       </c>
       <c r="Y65" s="58" t="s">
@@ -10070,27 +10320,26 @@
         <v>9</v>
       </c>
       <c r="L66" s="53" t="str">
+        <f t="shared" si="19"/>
+        <v>Documentais</v>
+      </c>
+      <c r="M66" s="53" t="str">
+        <f t="shared" si="20"/>
+        <v>Elemento.de.Legenda</v>
+      </c>
+      <c r="N66" s="53" t="str">
+        <f t="shared" si="21"/>
+        <v>Legenda Cromática Ocupação</v>
+      </c>
+      <c r="O66" s="53" t="str">
         <f t="shared" si="22"/>
-        <v>Documentais</v>
-      </c>
-      <c r="M66" s="53" t="str">
-        <f t="shared" si="23"/>
-        <v>Elemento.de.Legenda</v>
-      </c>
-      <c r="N66" s="53" t="str">
-        <f t="shared" si="24"/>
-        <v>Legenda Cromática Ocupação</v>
-      </c>
-      <c r="O66" s="53" t="str">
-        <f t="shared" si="25"/>
         <v>Ambiente Cores Preenchidas</v>
       </c>
       <c r="P66" s="53" t="s">
         <v>123</v>
       </c>
-      <c r="Q66" s="43" t="str">
-        <f t="shared" si="15"/>
-        <v>Entorno - relleno de color</v>
+      <c r="Q66" s="43" t="s">
+        <v>826</v>
       </c>
       <c r="R66" s="43" t="s">
         <v>694</v>
@@ -10099,22 +10348,22 @@
         <v>9</v>
       </c>
       <c r="T66" s="43" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v>Documentais</v>
       </c>
       <c r="U66" s="43" t="str">
+        <f t="shared" si="14"/>
+        <v>Elemento.de.Legenda</v>
+      </c>
+      <c r="V66" s="53" t="str">
         <f t="shared" si="17"/>
-        <v>Elemento.de.Legenda</v>
-      </c>
-      <c r="V66" s="53" t="str">
-        <f t="shared" si="20"/>
         <v>Legenda.Cromática.Ocupação</v>
       </c>
       <c r="W66" s="43" t="s">
         <v>80</v>
       </c>
       <c r="X66" s="54" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>Key-DOCU-66</v>
       </c>
       <c r="Y66" s="58" t="s">
@@ -10168,27 +10417,26 @@
         <v>9</v>
       </c>
       <c r="L67" s="53" t="str">
+        <f t="shared" si="19"/>
+        <v>Documentais</v>
+      </c>
+      <c r="M67" s="53" t="str">
+        <f t="shared" si="20"/>
+        <v>Elemento.de.Legenda</v>
+      </c>
+      <c r="N67" s="53" t="str">
+        <f t="shared" si="21"/>
+        <v>Legenda Cromática Ocupação</v>
+      </c>
+      <c r="O67" s="53" t="str">
         <f t="shared" si="22"/>
-        <v>Documentais</v>
-      </c>
-      <c r="M67" s="53" t="str">
-        <f t="shared" si="23"/>
-        <v>Elemento.de.Legenda</v>
-      </c>
-      <c r="N67" s="53" t="str">
-        <f t="shared" si="24"/>
-        <v>Legenda Cromática Ocupação</v>
-      </c>
-      <c r="O67" s="53" t="str">
-        <f t="shared" si="25"/>
         <v>Áreas Cores Preenchidas</v>
       </c>
       <c r="P67" s="53" t="s">
         <v>124</v>
       </c>
-      <c r="Q67" s="43" t="str">
-        <f t="shared" si="15"/>
-        <v>Áreas de ocupación de edificios - relleno de color</v>
+      <c r="Q67" s="43" t="s">
+        <v>827</v>
       </c>
       <c r="R67" s="43" t="s">
         <v>695</v>
@@ -10197,22 +10445,22 @@
         <v>9</v>
       </c>
       <c r="T67" s="43" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v>Documentais</v>
       </c>
       <c r="U67" s="43" t="str">
+        <f t="shared" si="14"/>
+        <v>Elemento.de.Legenda</v>
+      </c>
+      <c r="V67" s="53" t="str">
         <f t="shared" si="17"/>
-        <v>Elemento.de.Legenda</v>
-      </c>
-      <c r="V67" s="53" t="str">
-        <f t="shared" si="20"/>
         <v>Legenda.Cromática.Ocupação</v>
       </c>
       <c r="W67" s="43" t="s">
         <v>80</v>
       </c>
       <c r="X67" s="54" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>Key-DOCU-67</v>
       </c>
       <c r="Y67" s="58" t="s">
@@ -10266,27 +10514,26 @@
         <v>9</v>
       </c>
       <c r="L68" s="53" t="str">
+        <f t="shared" si="19"/>
+        <v>Documentais</v>
+      </c>
+      <c r="M68" s="53" t="str">
+        <f t="shared" si="20"/>
+        <v>Elemento.de.Legenda</v>
+      </c>
+      <c r="N68" s="53" t="str">
+        <f t="shared" si="21"/>
+        <v>Legenda Cromática Térmica</v>
+      </c>
+      <c r="O68" s="53" t="str">
         <f t="shared" si="22"/>
-        <v>Documentais</v>
-      </c>
-      <c r="M68" s="53" t="str">
-        <f t="shared" si="23"/>
-        <v>Elemento.de.Legenda</v>
-      </c>
-      <c r="N68" s="53" t="str">
-        <f t="shared" si="24"/>
-        <v>Legenda Cromática Térmica</v>
-      </c>
-      <c r="O68" s="53" t="str">
-        <f t="shared" si="25"/>
         <v>MEP Ambiente Cores Preenchidas</v>
       </c>
       <c r="P68" s="53" t="s">
         <v>125</v>
       </c>
-      <c r="Q68" s="43" t="str">
-        <f t="shared" si="15"/>
-        <v>MEP - Espacios HVAC - Relleno de color</v>
+      <c r="Q68" s="43" t="s">
+        <v>828</v>
       </c>
       <c r="R68" s="43" t="s">
         <v>696</v>
@@ -10295,22 +10542,22 @@
         <v>9</v>
       </c>
       <c r="T68" s="43" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v>Documentais</v>
       </c>
       <c r="U68" s="43" t="str">
+        <f t="shared" si="14"/>
+        <v>Elemento.de.Legenda</v>
+      </c>
+      <c r="V68" s="53" t="str">
         <f t="shared" si="17"/>
-        <v>Elemento.de.Legenda</v>
-      </c>
-      <c r="V68" s="53" t="str">
-        <f t="shared" si="20"/>
         <v>Legenda.Cromática.Térmica</v>
       </c>
       <c r="W68" s="43" t="s">
         <v>80</v>
       </c>
       <c r="X68" s="54" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>Key-DOCU-68</v>
       </c>
       <c r="Y68" s="58" t="s">
@@ -10364,27 +10611,26 @@
         <v>9</v>
       </c>
       <c r="L69" s="53" t="str">
+        <f t="shared" si="19"/>
+        <v>Documentais</v>
+      </c>
+      <c r="M69" s="53" t="str">
+        <f t="shared" si="20"/>
+        <v>Elemento.de.Legenda</v>
+      </c>
+      <c r="N69" s="53" t="str">
+        <f t="shared" si="21"/>
+        <v>Legenda Cromática Térmica</v>
+      </c>
+      <c r="O69" s="53" t="str">
         <f t="shared" si="22"/>
-        <v>Documentais</v>
-      </c>
-      <c r="M69" s="53" t="str">
-        <f t="shared" si="23"/>
-        <v>Elemento.de.Legenda</v>
-      </c>
-      <c r="N69" s="53" t="str">
-        <f t="shared" si="24"/>
-        <v>Legenda Cromática Térmica</v>
-      </c>
-      <c r="O69" s="53" t="str">
-        <f t="shared" si="25"/>
         <v>AVAC Zonas Cores Preenchidas</v>
       </c>
       <c r="P69" s="53" t="s">
         <v>126</v>
       </c>
-      <c r="Q69" s="43" t="e" vm="1">
-        <f t="shared" si="15"/>
-        <v>#VALUE!</v>
+      <c r="Q69" s="53" t="s">
+        <v>891</v>
       </c>
       <c r="R69" s="43" t="s">
         <v>697</v>
@@ -10393,22 +10639,22 @@
         <v>9</v>
       </c>
       <c r="T69" s="43" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v>Documentais</v>
       </c>
       <c r="U69" s="43" t="str">
+        <f t="shared" si="14"/>
+        <v>Elemento.de.Legenda</v>
+      </c>
+      <c r="V69" s="53" t="str">
         <f t="shared" si="17"/>
-        <v>Elemento.de.Legenda</v>
-      </c>
-      <c r="V69" s="53" t="str">
-        <f t="shared" si="20"/>
         <v>Legenda.Cromática.Térmica</v>
       </c>
       <c r="W69" s="43" t="s">
         <v>80</v>
       </c>
       <c r="X69" s="54" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>Key-DOCU-69</v>
       </c>
       <c r="Y69" s="58" t="s">
@@ -10462,27 +10708,26 @@
         <v>9</v>
       </c>
       <c r="L70" s="53" t="str">
+        <f t="shared" si="19"/>
+        <v>Documentais</v>
+      </c>
+      <c r="M70" s="53" t="str">
+        <f t="shared" si="20"/>
+        <v>Elemento.de.Legenda</v>
+      </c>
+      <c r="N70" s="53" t="str">
+        <f t="shared" si="21"/>
+        <v>Legenda Cromática</v>
+      </c>
+      <c r="O70" s="53" t="str">
         <f t="shared" si="22"/>
-        <v>Documentais</v>
-      </c>
-      <c r="M70" s="53" t="str">
-        <f t="shared" si="23"/>
-        <v>Elemento.de.Legenda</v>
-      </c>
-      <c r="N70" s="53" t="str">
-        <f t="shared" si="24"/>
-        <v>Legenda Cromática</v>
-      </c>
-      <c r="O70" s="53" t="str">
-        <f t="shared" si="25"/>
         <v>Esquema de Cores</v>
       </c>
       <c r="P70" s="53" t="s">
         <v>127</v>
       </c>
-      <c r="Q70" s="43" t="str">
-        <f t="shared" ref="Q70:Q136" si="26">_xlfn.TRANSLATE(P70,"pt","es")</f>
-        <v>Subtítulos - Esquema de colores</v>
+      <c r="Q70" s="43" t="s">
+        <v>829</v>
       </c>
       <c r="R70" s="43" t="s">
         <v>698</v>
@@ -10491,22 +10736,22 @@
         <v>9</v>
       </c>
       <c r="T70" s="43" t="str">
-        <f t="shared" ref="T70:T101" si="27">SUBSTITUTE(C70, "_", " ")</f>
+        <f t="shared" ref="T70:T101" si="23">SUBSTITUTE(C70, "_", " ")</f>
         <v>Documentais</v>
       </c>
       <c r="U70" s="43" t="str">
-        <f t="shared" ref="U70:U137" si="28">SUBSTITUTE(D70, "_", " ")</f>
+        <f t="shared" ref="U70:U137" si="24">SUBSTITUTE(D70, "_", " ")</f>
         <v>Elemento.de.Legenda</v>
       </c>
       <c r="V70" s="53" t="str">
-        <f t="shared" ref="V70:V101" si="29">SUBSTITUTE(E70, "_", " ")</f>
+        <f t="shared" ref="V70:V101" si="25">SUBSTITUTE(E70, "_", " ")</f>
         <v>Legenda.Cromática</v>
       </c>
       <c r="W70" s="43" t="s">
         <v>80</v>
       </c>
       <c r="X70" s="54" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>Key-DOCU-70</v>
       </c>
       <c r="Y70" s="58" t="s">
@@ -10560,27 +10805,26 @@
         <v>9</v>
       </c>
       <c r="L71" s="53" t="str">
+        <f t="shared" si="19"/>
+        <v>Documentais</v>
+      </c>
+      <c r="M71" s="53" t="str">
+        <f t="shared" si="20"/>
+        <v>Elemento.de.Legenda</v>
+      </c>
+      <c r="N71" s="53" t="str">
+        <f t="shared" si="21"/>
+        <v>Legenda Cromática</v>
+      </c>
+      <c r="O71" s="53" t="str">
         <f t="shared" si="22"/>
-        <v>Documentais</v>
-      </c>
-      <c r="M71" s="53" t="str">
-        <f t="shared" si="23"/>
-        <v>Elemento.de.Legenda</v>
-      </c>
-      <c r="N71" s="53" t="str">
-        <f t="shared" si="24"/>
-        <v>Legenda Cromática</v>
-      </c>
-      <c r="O71" s="53" t="str">
-        <f t="shared" si="25"/>
         <v>Componente Legenda</v>
       </c>
       <c r="P71" s="53" t="s">
         <v>128</v>
       </c>
-      <c r="Q71" s="43" t="str">
-        <f t="shared" si="26"/>
-        <v>Legend de componentes</v>
+      <c r="Q71" s="43" t="s">
+        <v>830</v>
       </c>
       <c r="R71" s="43" t="s">
         <v>699</v>
@@ -10589,22 +10833,22 @@
         <v>9</v>
       </c>
       <c r="T71" s="43" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v>Documentais</v>
       </c>
       <c r="U71" s="43" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="24"/>
         <v>Elemento.de.Legenda</v>
       </c>
       <c r="V71" s="53" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="25"/>
         <v>Legenda.Cromática</v>
       </c>
       <c r="W71" s="43" t="s">
         <v>80</v>
       </c>
       <c r="X71" s="54" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>Key-DOCU-71</v>
       </c>
       <c r="Y71" s="58" t="s">
@@ -10658,27 +10902,26 @@
         <v>9</v>
       </c>
       <c r="L72" s="53" t="str">
+        <f t="shared" si="19"/>
+        <v>Documentais</v>
+      </c>
+      <c r="M72" s="53" t="str">
+        <f t="shared" si="20"/>
+        <v>Elemento.de.Modelado</v>
+      </c>
+      <c r="N72" s="53" t="str">
+        <f t="shared" si="21"/>
+        <v>Contornos</v>
+      </c>
+      <c r="O72" s="53" t="str">
         <f t="shared" si="22"/>
-        <v>Documentais</v>
-      </c>
-      <c r="M72" s="53" t="str">
-        <f t="shared" si="23"/>
-        <v>Elemento.de.Modelado</v>
-      </c>
-      <c r="N72" s="53" t="str">
-        <f t="shared" si="24"/>
-        <v>Contornos</v>
-      </c>
-      <c r="O72" s="53" t="str">
-        <f t="shared" si="25"/>
         <v>Linhas</v>
       </c>
       <c r="P72" s="53" t="s">
         <v>132</v>
       </c>
-      <c r="Q72" s="43" t="str">
-        <f t="shared" si="26"/>
-        <v>Líneas</v>
+      <c r="Q72" s="43" t="s">
+        <v>831</v>
       </c>
       <c r="R72" s="43" t="s">
         <v>700</v>
@@ -10687,22 +10930,22 @@
         <v>9</v>
       </c>
       <c r="T72" s="43" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v>Documentais</v>
       </c>
       <c r="U72" s="43" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="24"/>
         <v>Elemento.de.Modelado</v>
       </c>
       <c r="V72" s="53" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="25"/>
         <v>Contornos</v>
       </c>
       <c r="W72" s="43" t="s">
         <v>80</v>
       </c>
       <c r="X72" s="54" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>Key-DOCU-72</v>
       </c>
       <c r="Y72" s="58" t="s">
@@ -10756,27 +10999,26 @@
         <v>9</v>
       </c>
       <c r="L73" s="53" t="str">
+        <f t="shared" si="19"/>
+        <v>Documentais</v>
+      </c>
+      <c r="M73" s="53" t="str">
+        <f t="shared" si="20"/>
+        <v>Elemento.de.Modelado</v>
+      </c>
+      <c r="N73" s="53" t="str">
+        <f t="shared" si="21"/>
+        <v>Contornos</v>
+      </c>
+      <c r="O73" s="53" t="str">
         <f t="shared" si="22"/>
-        <v>Documentais</v>
-      </c>
-      <c r="M73" s="53" t="str">
-        <f t="shared" si="23"/>
-        <v>Elemento.de.Modelado</v>
-      </c>
-      <c r="N73" s="53" t="str">
-        <f t="shared" si="24"/>
-        <v>Contornos</v>
-      </c>
-      <c r="O73" s="53" t="str">
-        <f t="shared" si="25"/>
         <v>Linhas Nuvem</v>
       </c>
       <c r="P73" s="53" t="s">
         <v>129</v>
       </c>
-      <c r="Q73" s="43" t="str">
-        <f t="shared" si="26"/>
-        <v>Líneas - Líneas de Llamada a las Líneas de Nube</v>
+      <c r="Q73" s="43" t="s">
+        <v>832</v>
       </c>
       <c r="R73" s="43" t="s">
         <v>701</v>
@@ -10785,22 +11027,22 @@
         <v>9</v>
       </c>
       <c r="T73" s="43" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v>Documentais</v>
       </c>
       <c r="U73" s="43" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="24"/>
         <v>Elemento.de.Modelado</v>
       </c>
       <c r="V73" s="53" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="25"/>
         <v>Contornos</v>
       </c>
       <c r="W73" s="43" t="s">
         <v>80</v>
       </c>
       <c r="X73" s="54" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>Key-DOCU-73</v>
       </c>
       <c r="Y73" s="58" t="s">
@@ -10854,27 +11096,26 @@
         <v>9</v>
       </c>
       <c r="L74" s="53" t="str">
+        <f t="shared" si="19"/>
+        <v>Documentais</v>
+      </c>
+      <c r="M74" s="53" t="str">
+        <f t="shared" si="20"/>
+        <v>Elemento.de.Modelado</v>
+      </c>
+      <c r="N74" s="53" t="str">
+        <f t="shared" si="21"/>
+        <v>Contornos</v>
+      </c>
+      <c r="O74" s="53" t="str">
         <f t="shared" si="22"/>
-        <v>Documentais</v>
-      </c>
-      <c r="M74" s="53" t="str">
-        <f t="shared" si="23"/>
-        <v>Elemento.de.Modelado</v>
-      </c>
-      <c r="N74" s="53" t="str">
-        <f t="shared" si="24"/>
-        <v>Contornos</v>
-      </c>
-      <c r="O74" s="53" t="str">
-        <f t="shared" si="25"/>
         <v>Linhas Direção</v>
       </c>
       <c r="P74" s="53" t="s">
         <v>130</v>
       </c>
-      <c r="Q74" s="43" t="str">
-        <f t="shared" si="26"/>
-        <v>Línea direccional de los bordes</v>
+      <c r="Q74" s="43" t="s">
+        <v>833</v>
       </c>
       <c r="R74" s="43" t="s">
         <v>702</v>
@@ -10883,22 +11124,22 @@
         <v>9</v>
       </c>
       <c r="T74" s="43" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v>Documentais</v>
       </c>
       <c r="U74" s="43" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="24"/>
         <v>Elemento.de.Modelado</v>
       </c>
       <c r="V74" s="53" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="25"/>
         <v>Contornos</v>
       </c>
       <c r="W74" s="43" t="s">
         <v>80</v>
       </c>
       <c r="X74" s="54" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>Key-DOCU-74</v>
       </c>
       <c r="Y74" s="58" t="s">
@@ -10952,27 +11193,26 @@
         <v>9</v>
       </c>
       <c r="L75" s="53" t="str">
+        <f t="shared" si="19"/>
+        <v>Documentais</v>
+      </c>
+      <c r="M75" s="53" t="str">
+        <f t="shared" si="20"/>
+        <v>Elemento.de.Modelado</v>
+      </c>
+      <c r="N75" s="53" t="str">
+        <f t="shared" si="21"/>
+        <v>Contornos</v>
+      </c>
+      <c r="O75" s="53" t="str">
         <f t="shared" si="22"/>
-        <v>Documentais</v>
-      </c>
-      <c r="M75" s="53" t="str">
-        <f t="shared" si="23"/>
-        <v>Elemento.de.Modelado</v>
-      </c>
-      <c r="N75" s="53" t="str">
-        <f t="shared" si="24"/>
-        <v>Contornos</v>
-      </c>
-      <c r="O75" s="53" t="str">
-        <f t="shared" si="25"/>
         <v>Linhas Genéricas</v>
       </c>
       <c r="P75" s="53" t="s">
         <v>131</v>
       </c>
-      <c r="Q75" s="43" t="str">
-        <f t="shared" si="26"/>
-        <v>Líneas genéricas</v>
+      <c r="Q75" s="43" t="s">
+        <v>834</v>
       </c>
       <c r="R75" s="43" t="s">
         <v>703</v>
@@ -10981,22 +11221,22 @@
         <v>9</v>
       </c>
       <c r="T75" s="43" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v>Documentais</v>
       </c>
       <c r="U75" s="43" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="24"/>
         <v>Elemento.de.Modelado</v>
       </c>
       <c r="V75" s="53" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="25"/>
         <v>Contornos</v>
       </c>
       <c r="W75" s="43" t="s">
         <v>80</v>
       </c>
       <c r="X75" s="54" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>Key-DOCU-75</v>
       </c>
       <c r="Y75" s="58" t="s">
@@ -11050,27 +11290,26 @@
         <v>9</v>
       </c>
       <c r="L76" s="53" t="str">
+        <f t="shared" si="19"/>
+        <v>Documentais</v>
+      </c>
+      <c r="M76" s="53" t="str">
+        <f t="shared" si="20"/>
+        <v>Elemento.de.Modelado</v>
+      </c>
+      <c r="N76" s="53" t="str">
+        <f t="shared" si="21"/>
+        <v>Indefinidos</v>
+      </c>
+      <c r="O76" s="53" t="str">
         <f t="shared" si="22"/>
-        <v>Documentais</v>
-      </c>
-      <c r="M76" s="53" t="str">
-        <f t="shared" si="23"/>
-        <v>Elemento.de.Modelado</v>
-      </c>
-      <c r="N76" s="53" t="str">
-        <f t="shared" si="24"/>
-        <v>Indefinidos</v>
-      </c>
-      <c r="O76" s="53" t="str">
-        <f t="shared" si="25"/>
         <v>Deslocamentos Elementos</v>
       </c>
       <c r="P76" s="53" t="s">
         <v>134</v>
       </c>
-      <c r="Q76" s="43" t="str">
-        <f t="shared" si="26"/>
-        <v>Valor de desplazamiento</v>
+      <c r="Q76" s="43" t="s">
+        <v>835</v>
       </c>
       <c r="R76" s="43" t="s">
         <v>704</v>
@@ -11079,22 +11318,22 @@
         <v>9</v>
       </c>
       <c r="T76" s="43" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v>Documentais</v>
       </c>
       <c r="U76" s="43" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="24"/>
         <v>Elemento.de.Modelado</v>
       </c>
       <c r="V76" s="53" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="25"/>
         <v>Indefinidos</v>
       </c>
       <c r="W76" s="43" t="s">
         <v>80</v>
       </c>
       <c r="X76" s="54" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>Key-DOCU-76</v>
       </c>
       <c r="Y76" s="58" t="s">
@@ -11148,27 +11387,26 @@
         <v>9</v>
       </c>
       <c r="L77" s="53" t="str">
+        <f t="shared" si="19"/>
+        <v>Documentais</v>
+      </c>
+      <c r="M77" s="53" t="str">
+        <f t="shared" si="20"/>
+        <v>Elemento.de.Modelado</v>
+      </c>
+      <c r="N77" s="53" t="str">
+        <f t="shared" si="21"/>
+        <v>Indefinidos</v>
+      </c>
+      <c r="O77" s="53" t="str">
         <f t="shared" si="22"/>
-        <v>Documentais</v>
-      </c>
-      <c r="M77" s="53" t="str">
-        <f t="shared" si="23"/>
-        <v>Elemento.de.Modelado</v>
-      </c>
-      <c r="N77" s="53" t="str">
-        <f t="shared" si="24"/>
-        <v>Indefinidos</v>
-      </c>
-      <c r="O77" s="53" t="str">
-        <f t="shared" si="25"/>
         <v>Deslocamentos Caminho</v>
       </c>
       <c r="P77" s="53" t="s">
         <v>135</v>
       </c>
-      <c r="Q77" s="43" t="str">
-        <f t="shared" si="26"/>
-        <v>Trayectoria de desplazamiento</v>
+      <c r="Q77" s="43" t="s">
+        <v>836</v>
       </c>
       <c r="R77" s="43" t="s">
         <v>705</v>
@@ -11177,22 +11415,22 @@
         <v>9</v>
       </c>
       <c r="T77" s="43" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v>Documentais</v>
       </c>
       <c r="U77" s="43" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="24"/>
         <v>Elemento.de.Modelado</v>
       </c>
       <c r="V77" s="53" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="25"/>
         <v>Indefinidos</v>
       </c>
       <c r="W77" s="43" t="s">
         <v>80</v>
       </c>
       <c r="X77" s="54" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>Key-DOCU-77</v>
       </c>
       <c r="Y77" s="58" t="s">
@@ -11246,27 +11484,26 @@
         <v>9</v>
       </c>
       <c r="L78" s="53" t="str">
+        <f t="shared" si="19"/>
+        <v>Documentais</v>
+      </c>
+      <c r="M78" s="53" t="str">
+        <f t="shared" si="20"/>
+        <v>Elemento.de.Modelado</v>
+      </c>
+      <c r="N78" s="53" t="str">
+        <f t="shared" si="21"/>
+        <v>Indefinidos</v>
+      </c>
+      <c r="O78" s="53" t="str">
         <f t="shared" si="22"/>
-        <v>Documentais</v>
-      </c>
-      <c r="M78" s="53" t="str">
-        <f t="shared" si="23"/>
-        <v>Elemento.de.Modelado</v>
-      </c>
-      <c r="N78" s="53" t="str">
-        <f t="shared" si="24"/>
-        <v>Indefinidos</v>
-      </c>
-      <c r="O78" s="53" t="str">
-        <f t="shared" si="25"/>
         <v>Conector Aberto Warning</v>
       </c>
       <c r="P78" s="53" t="s">
         <v>136</v>
       </c>
-      <c r="Q78" s="43" t="str">
-        <f t="shared" si="26"/>
-        <v>Advertencia gráfica - Abierto</v>
+      <c r="Q78" s="43" t="s">
+        <v>837</v>
       </c>
       <c r="R78" s="43" t="s">
         <v>706</v>
@@ -11275,22 +11512,22 @@
         <v>9</v>
       </c>
       <c r="T78" s="43" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v>Documentais</v>
       </c>
       <c r="U78" s="43" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="24"/>
         <v>Elemento.de.Modelado</v>
       </c>
       <c r="V78" s="53" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="25"/>
         <v>Indefinidos</v>
       </c>
       <c r="W78" s="43" t="s">
         <v>80</v>
       </c>
       <c r="X78" s="54" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>Key-DOCU-78</v>
       </c>
       <c r="Y78" s="58" t="s">
@@ -11344,27 +11581,26 @@
         <v>9</v>
       </c>
       <c r="L79" s="53" t="str">
+        <f t="shared" si="19"/>
+        <v>Documentais</v>
+      </c>
+      <c r="M79" s="53" t="str">
+        <f t="shared" si="20"/>
+        <v>Elemento.de.Modelado</v>
+      </c>
+      <c r="N79" s="53" t="str">
+        <f t="shared" si="21"/>
+        <v>Indefinidos</v>
+      </c>
+      <c r="O79" s="53" t="str">
         <f t="shared" si="22"/>
-        <v>Documentais</v>
-      </c>
-      <c r="M79" s="53" t="str">
-        <f t="shared" si="23"/>
-        <v>Elemento.de.Modelado</v>
-      </c>
-      <c r="N79" s="53" t="str">
-        <f t="shared" si="24"/>
-        <v>Indefinidos</v>
-      </c>
-      <c r="O79" s="53" t="str">
-        <f t="shared" si="25"/>
         <v>Imagem Raster</v>
       </c>
       <c r="P79" s="53" t="s">
         <v>137</v>
       </c>
-      <c r="Q79" s="43" t="str">
-        <f t="shared" si="26"/>
-        <v>Imagen raster o bitmap insertada en el modelo</v>
+      <c r="Q79" s="43" t="s">
+        <v>838</v>
       </c>
       <c r="R79" s="43" t="s">
         <v>707</v>
@@ -11373,22 +11609,22 @@
         <v>9</v>
       </c>
       <c r="T79" s="43" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v>Documentais</v>
       </c>
       <c r="U79" s="43" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="24"/>
         <v>Elemento.de.Modelado</v>
       </c>
       <c r="V79" s="53" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="25"/>
         <v>Indefinidos</v>
       </c>
       <c r="W79" s="43" t="s">
         <v>80</v>
       </c>
       <c r="X79" s="54" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>Key-DOCU-79</v>
       </c>
       <c r="Y79" s="58" t="s">
@@ -11442,27 +11678,26 @@
         <v>9</v>
       </c>
       <c r="L80" s="53" t="str">
+        <f t="shared" si="19"/>
+        <v>Documentais</v>
+      </c>
+      <c r="M80" s="53" t="str">
+        <f t="shared" si="20"/>
+        <v>Elemento.de.Modelado</v>
+      </c>
+      <c r="N80" s="53" t="str">
+        <f t="shared" si="21"/>
+        <v>Indefinidos</v>
+      </c>
+      <c r="O80" s="53" t="str">
         <f t="shared" si="22"/>
-        <v>Documentais</v>
-      </c>
-      <c r="M80" s="53" t="str">
-        <f t="shared" si="23"/>
-        <v>Elemento.de.Modelado</v>
-      </c>
-      <c r="N80" s="53" t="str">
-        <f t="shared" si="24"/>
-        <v>Indefinidos</v>
-      </c>
-      <c r="O80" s="53" t="str">
-        <f t="shared" si="25"/>
         <v>Símbolo Drop Rise</v>
       </c>
       <c r="P80" s="53" t="s">
         <v>138</v>
       </c>
-      <c r="Q80" s="43" t="str">
-        <f t="shared" si="26"/>
-        <v>Símbolo de ascenso o descenso en tubos - Yin y Yang</v>
+      <c r="Q80" s="43" t="s">
+        <v>839</v>
       </c>
       <c r="R80" s="43" t="s">
         <v>708</v>
@@ -11471,22 +11706,22 @@
         <v>9</v>
       </c>
       <c r="T80" s="43" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v>Documentais</v>
       </c>
       <c r="U80" s="43" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="24"/>
         <v>Elemento.de.Modelado</v>
       </c>
       <c r="V80" s="53" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="25"/>
         <v>Indefinidos</v>
       </c>
       <c r="W80" s="43" t="s">
         <v>80</v>
       </c>
       <c r="X80" s="54" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>Key-DOCU-80</v>
       </c>
       <c r="Y80" s="58" t="s">
@@ -11540,27 +11775,26 @@
         <v>9</v>
       </c>
       <c r="L81" s="53" t="str">
+        <f t="shared" si="19"/>
+        <v>Documentais</v>
+      </c>
+      <c r="M81" s="53" t="str">
+        <f t="shared" si="20"/>
+        <v>Elemento.de.Modelado</v>
+      </c>
+      <c r="N81" s="53" t="str">
+        <f t="shared" si="21"/>
+        <v>Indefinidos</v>
+      </c>
+      <c r="O81" s="53" t="str">
         <f t="shared" si="22"/>
-        <v>Documentais</v>
-      </c>
-      <c r="M81" s="53" t="str">
-        <f t="shared" si="23"/>
-        <v>Elemento.de.Modelado</v>
-      </c>
-      <c r="N81" s="53" t="str">
-        <f t="shared" si="24"/>
-        <v>Indefinidos</v>
-      </c>
-      <c r="O81" s="53" t="str">
-        <f t="shared" si="25"/>
         <v>Guia de Paginação</v>
       </c>
       <c r="P81" s="53" t="s">
         <v>139</v>
       </c>
-      <c r="Q81" s="43" t="str">
-        <f t="shared" si="26"/>
-        <v>Guías de ejes estructurales</v>
+      <c r="Q81" s="43" t="s">
+        <v>840</v>
       </c>
       <c r="R81" s="43" t="s">
         <v>709</v>
@@ -11569,22 +11803,22 @@
         <v>9</v>
       </c>
       <c r="T81" s="43" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v>Documentais</v>
       </c>
       <c r="U81" s="43" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="24"/>
         <v>Elemento.de.Modelado</v>
       </c>
       <c r="V81" s="53" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="25"/>
         <v>Indefinidos</v>
       </c>
       <c r="W81" s="43" t="s">
         <v>80</v>
       </c>
       <c r="X81" s="54" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>Key-DOCU-81</v>
       </c>
       <c r="Y81" s="58" t="s">
@@ -11638,27 +11872,26 @@
         <v>9</v>
       </c>
       <c r="L82" s="53" t="str">
-        <f t="shared" ref="L82:L83" si="30">CONCATENATE("", C82)</f>
+        <f t="shared" ref="L82:L83" si="26">CONCATENATE("", C82)</f>
         <v>Documentais</v>
       </c>
       <c r="M82" s="53" t="str">
-        <f t="shared" ref="M82:M83" si="31">CONCATENATE("", D82)</f>
+        <f t="shared" ref="M82:M83" si="27">CONCATENATE("", D82)</f>
         <v>Elemento.de.Pranchas</v>
       </c>
       <c r="N82" s="53" t="str">
-        <f t="shared" ref="N82:N83" si="32">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E82),"."," ")," De "," de "))</f>
+        <f t="shared" ref="N82:N83" si="28">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E82),"."," ")," De "," de "))</f>
         <v>Margens</v>
       </c>
       <c r="O82" s="53" t="str">
-        <f t="shared" ref="O82:O83" si="33">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",F82),"."," ")," De "," de "))</f>
+        <f t="shared" ref="O82:O83" si="29">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",F82),"."," ")," De "," de "))</f>
         <v>Margem</v>
       </c>
       <c r="P82" s="53" t="s">
         <v>149</v>
       </c>
-      <c r="Q82" s="43" t="str">
-        <f t="shared" si="26"/>
-        <v>Sábanas o tablas</v>
+      <c r="Q82" s="43" t="s">
+        <v>841</v>
       </c>
       <c r="R82" s="43" t="s">
         <v>710</v>
@@ -11667,22 +11900,22 @@
         <v>9</v>
       </c>
       <c r="T82" s="43" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v>Documentais</v>
       </c>
       <c r="U82" s="43" t="str">
-        <f t="shared" ref="U82:U83" si="34">SUBSTITUTE(D82, "_", " ")</f>
+        <f t="shared" ref="U82:U83" si="30">SUBSTITUTE(D82, "_", " ")</f>
         <v>Elemento.de.Pranchas</v>
       </c>
       <c r="V82" s="53" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="25"/>
         <v>Margens</v>
       </c>
       <c r="W82" s="43" t="s">
         <v>80</v>
       </c>
       <c r="X82" s="54" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>Key-DOCU-82</v>
       </c>
       <c r="Y82" s="58" t="s">
@@ -11736,27 +11969,26 @@
         <v>9</v>
       </c>
       <c r="L83" s="53" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="26"/>
         <v>Documentais</v>
       </c>
       <c r="M83" s="53" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="27"/>
         <v>Elemento.de.Pranchas</v>
       </c>
       <c r="N83" s="53" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="28"/>
         <v>Margens</v>
       </c>
       <c r="O83" s="53" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="29"/>
         <v>Prancha</v>
       </c>
       <c r="P83" s="53" t="s">
         <v>149</v>
       </c>
-      <c r="Q83" s="43" t="str">
-        <f t="shared" si="26"/>
-        <v>Sábanas o tablas</v>
+      <c r="Q83" s="43" t="s">
+        <v>841</v>
       </c>
       <c r="R83" s="43" t="s">
         <v>710</v>
@@ -11765,22 +11997,22 @@
         <v>9</v>
       </c>
       <c r="T83" s="43" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v>Documentais</v>
       </c>
       <c r="U83" s="43" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="30"/>
         <v>Elemento.de.Pranchas</v>
       </c>
       <c r="V83" s="53" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="25"/>
         <v>Margens</v>
       </c>
       <c r="W83" s="43" t="s">
         <v>80</v>
       </c>
       <c r="X83" s="54" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>Key-DOCU-83</v>
       </c>
       <c r="Y83" s="58" t="s">
@@ -11834,27 +12066,26 @@
         <v>9</v>
       </c>
       <c r="L84" s="53" t="str">
+        <f t="shared" si="19"/>
+        <v>Documentais</v>
+      </c>
+      <c r="M84" s="53" t="str">
+        <f t="shared" si="20"/>
+        <v>Elemento.de.Pranchas</v>
+      </c>
+      <c r="N84" s="53" t="str">
+        <f t="shared" si="21"/>
+        <v>Margens</v>
+      </c>
+      <c r="O84" s="53" t="str">
         <f t="shared" si="22"/>
-        <v>Documentais</v>
-      </c>
-      <c r="M84" s="53" t="str">
-        <f t="shared" si="23"/>
-        <v>Elemento.de.Pranchas</v>
-      </c>
-      <c r="N84" s="53" t="str">
-        <f t="shared" si="24"/>
-        <v>Margens</v>
-      </c>
-      <c r="O84" s="53" t="str">
-        <f t="shared" si="25"/>
         <v>Folha</v>
       </c>
       <c r="P84" s="53" t="s">
         <v>149</v>
       </c>
-      <c r="Q84" s="43" t="str">
-        <f t="shared" si="26"/>
-        <v>Sábanas o tablas</v>
+      <c r="Q84" s="43" t="s">
+        <v>841</v>
       </c>
       <c r="R84" s="43" t="s">
         <v>710</v>
@@ -11863,22 +12094,22 @@
         <v>9</v>
       </c>
       <c r="T84" s="43" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v>Documentais</v>
       </c>
       <c r="U84" s="43" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="24"/>
         <v>Elemento.de.Pranchas</v>
       </c>
       <c r="V84" s="53" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="25"/>
         <v>Margens</v>
       </c>
       <c r="W84" s="43" t="s">
         <v>80</v>
       </c>
       <c r="X84" s="54" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>Key-DOCU-84</v>
       </c>
       <c r="Y84" s="58" t="s">
@@ -11932,27 +12163,26 @@
         <v>9</v>
       </c>
       <c r="L85" s="53" t="str">
+        <f t="shared" si="19"/>
+        <v>Documentais</v>
+      </c>
+      <c r="M85" s="53" t="str">
+        <f t="shared" si="20"/>
+        <v>Elemento.de.Pranchas</v>
+      </c>
+      <c r="N85" s="53" t="str">
+        <f t="shared" si="21"/>
+        <v>Carimbos</v>
+      </c>
+      <c r="O85" s="53" t="str">
         <f t="shared" si="22"/>
-        <v>Documentais</v>
-      </c>
-      <c r="M85" s="53" t="str">
-        <f t="shared" si="23"/>
-        <v>Elemento.de.Pranchas</v>
-      </c>
-      <c r="N85" s="53" t="str">
-        <f t="shared" si="24"/>
-        <v>Carimbos</v>
-      </c>
-      <c r="O85" s="53" t="str">
-        <f t="shared" si="25"/>
         <v>Carimbo</v>
       </c>
       <c r="P85" s="53" t="s">
         <v>145</v>
       </c>
-      <c r="Q85" s="43" t="str">
-        <f t="shared" si="26"/>
-        <v>Sellos y tablas</v>
+      <c r="Q85" s="43" t="s">
+        <v>842</v>
       </c>
       <c r="R85" s="43" t="s">
         <v>711</v>
@@ -11961,22 +12191,22 @@
         <v>9</v>
       </c>
       <c r="T85" s="43" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v>Documentais</v>
       </c>
       <c r="U85" s="43" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="24"/>
         <v>Elemento.de.Pranchas</v>
       </c>
       <c r="V85" s="53" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="25"/>
         <v>Carimbos</v>
       </c>
       <c r="W85" s="43" t="s">
         <v>80</v>
       </c>
       <c r="X85" s="54" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>Key-DOCU-85</v>
       </c>
       <c r="Y85" s="58" t="s">
@@ -12030,27 +12260,26 @@
         <v>9</v>
       </c>
       <c r="L86" s="53" t="str">
+        <f t="shared" si="19"/>
+        <v>Documentais</v>
+      </c>
+      <c r="M86" s="53" t="str">
+        <f t="shared" si="20"/>
+        <v>Elemento.de.Pranchas</v>
+      </c>
+      <c r="N86" s="53" t="str">
+        <f t="shared" si="21"/>
+        <v>Carimbos</v>
+      </c>
+      <c r="O86" s="53" t="str">
         <f t="shared" si="22"/>
-        <v>Documentais</v>
-      </c>
-      <c r="M86" s="53" t="str">
-        <f t="shared" si="23"/>
-        <v>Elemento.de.Pranchas</v>
-      </c>
-      <c r="N86" s="53" t="str">
-        <f t="shared" si="24"/>
-        <v>Carimbos</v>
-      </c>
-      <c r="O86" s="53" t="str">
-        <f t="shared" si="25"/>
         <v>Carimbo Corte Linha Fina</v>
       </c>
       <c r="P86" s="53" t="s">
         <v>146</v>
       </c>
-      <c r="Q86" s="43" t="str">
-        <f t="shared" si="26"/>
-        <v>Finas líneas de sellos y tablas</v>
+      <c r="Q86" s="43" t="s">
+        <v>843</v>
       </c>
       <c r="R86" s="43" t="s">
         <v>712</v>
@@ -12059,22 +12288,22 @@
         <v>9</v>
       </c>
       <c r="T86" s="43" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v>Documentais</v>
       </c>
       <c r="U86" s="43" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="24"/>
         <v>Elemento.de.Pranchas</v>
       </c>
       <c r="V86" s="53" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="25"/>
         <v>Carimbos</v>
       </c>
       <c r="W86" s="43" t="s">
         <v>80</v>
       </c>
       <c r="X86" s="54" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>Key-DOCU-86</v>
       </c>
       <c r="Y86" s="58" t="s">
@@ -12128,27 +12357,26 @@
         <v>9</v>
       </c>
       <c r="L87" s="53" t="str">
+        <f t="shared" si="19"/>
+        <v>Documentais</v>
+      </c>
+      <c r="M87" s="53" t="str">
+        <f t="shared" si="20"/>
+        <v>Elemento.de.Pranchas</v>
+      </c>
+      <c r="N87" s="53" t="str">
+        <f t="shared" si="21"/>
+        <v>Carimbos</v>
+      </c>
+      <c r="O87" s="53" t="str">
         <f t="shared" si="22"/>
-        <v>Documentais</v>
-      </c>
-      <c r="M87" s="53" t="str">
-        <f t="shared" si="23"/>
-        <v>Elemento.de.Pranchas</v>
-      </c>
-      <c r="N87" s="53" t="str">
-        <f t="shared" si="24"/>
-        <v>Carimbos</v>
-      </c>
-      <c r="O87" s="53" t="str">
-        <f t="shared" si="25"/>
         <v>Carimbo Corte Linha Média</v>
       </c>
       <c r="P87" s="53" t="s">
         <v>144</v>
       </c>
-      <c r="Q87" s="43" t="str">
-        <f t="shared" si="26"/>
-        <v>Líneas medias de sellos y cartones</v>
+      <c r="Q87" s="43" t="s">
+        <v>844</v>
       </c>
       <c r="R87" s="43" t="s">
         <v>713</v>
@@ -12157,22 +12385,22 @@
         <v>9</v>
       </c>
       <c r="T87" s="43" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v>Documentais</v>
       </c>
       <c r="U87" s="43" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="24"/>
         <v>Elemento.de.Pranchas</v>
       </c>
       <c r="V87" s="53" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="25"/>
         <v>Carimbos</v>
       </c>
       <c r="W87" s="43" t="s">
         <v>80</v>
       </c>
       <c r="X87" s="54" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>Key-DOCU-87</v>
       </c>
       <c r="Y87" s="58" t="s">
@@ -12226,27 +12454,26 @@
         <v>9</v>
       </c>
       <c r="L88" s="53" t="str">
+        <f t="shared" si="19"/>
+        <v>Documentais</v>
+      </c>
+      <c r="M88" s="53" t="str">
+        <f t="shared" si="20"/>
+        <v>Elemento.de.Pranchas</v>
+      </c>
+      <c r="N88" s="53" t="str">
+        <f t="shared" si="21"/>
+        <v>Carimbos</v>
+      </c>
+      <c r="O88" s="53" t="str">
         <f t="shared" si="22"/>
-        <v>Documentais</v>
-      </c>
-      <c r="M88" s="53" t="str">
-        <f t="shared" si="23"/>
-        <v>Elemento.de.Pranchas</v>
-      </c>
-      <c r="N88" s="53" t="str">
-        <f t="shared" si="24"/>
-        <v>Carimbos</v>
-      </c>
-      <c r="O88" s="53" t="str">
-        <f t="shared" si="25"/>
         <v>Carimbo Corte Linha Grossa</v>
       </c>
       <c r="P88" s="53" t="s">
         <v>147</v>
       </c>
-      <c r="Q88" s="43" t="str">
-        <f t="shared" si="26"/>
-        <v>Líneas gruesas de sellos y tablas</v>
+      <c r="Q88" s="43" t="s">
+        <v>845</v>
       </c>
       <c r="R88" s="43" t="s">
         <v>714</v>
@@ -12255,22 +12482,22 @@
         <v>9</v>
       </c>
       <c r="T88" s="43" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v>Documentais</v>
       </c>
       <c r="U88" s="43" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="24"/>
         <v>Elemento.de.Pranchas</v>
       </c>
       <c r="V88" s="53" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="25"/>
         <v>Carimbos</v>
       </c>
       <c r="W88" s="43" t="s">
         <v>80</v>
       </c>
       <c r="X88" s="54" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>Key-DOCU-88</v>
       </c>
       <c r="Y88" s="58" t="s">
@@ -12324,27 +12551,26 @@
         <v>9</v>
       </c>
       <c r="L89" s="53" t="str">
+        <f t="shared" si="19"/>
+        <v>Documentais</v>
+      </c>
+      <c r="M89" s="53" t="str">
+        <f t="shared" si="20"/>
+        <v>Elemento.de.Pranchas</v>
+      </c>
+      <c r="N89" s="53" t="str">
+        <f t="shared" si="21"/>
+        <v>Carimbos</v>
+      </c>
+      <c r="O89" s="53" t="str">
         <f t="shared" si="22"/>
-        <v>Documentais</v>
-      </c>
-      <c r="M89" s="53" t="str">
-        <f t="shared" si="23"/>
-        <v>Elemento.de.Pranchas</v>
-      </c>
-      <c r="N89" s="53" t="str">
-        <f t="shared" si="24"/>
-        <v>Carimbos</v>
-      </c>
-      <c r="O89" s="53" t="str">
-        <f t="shared" si="25"/>
         <v>Revisões</v>
       </c>
       <c r="P89" s="53" t="s">
         <v>142</v>
       </c>
-      <c r="Q89" s="43" t="str">
-        <f t="shared" si="26"/>
-        <v>Revisiones de diseño</v>
+      <c r="Q89" s="43" t="s">
+        <v>846</v>
       </c>
       <c r="R89" s="43" t="s">
         <v>715</v>
@@ -12353,22 +12579,22 @@
         <v>9</v>
       </c>
       <c r="T89" s="43" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v>Documentais</v>
       </c>
       <c r="U89" s="43" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="24"/>
         <v>Elemento.de.Pranchas</v>
       </c>
       <c r="V89" s="53" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="25"/>
         <v>Carimbos</v>
       </c>
       <c r="W89" s="43" t="s">
         <v>80</v>
       </c>
       <c r="X89" s="54" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>Key-DOCU-89</v>
       </c>
       <c r="Y89" s="58" t="s">
@@ -12422,27 +12648,26 @@
         <v>9</v>
       </c>
       <c r="L90" s="53" t="str">
+        <f t="shared" si="19"/>
+        <v>Documentais</v>
+      </c>
+      <c r="M90" s="53" t="str">
+        <f t="shared" si="20"/>
+        <v>Elemento.de.Pranchas</v>
+      </c>
+      <c r="N90" s="53" t="str">
+        <f t="shared" si="21"/>
+        <v>Carimbos</v>
+      </c>
+      <c r="O90" s="53" t="str">
         <f t="shared" si="22"/>
-        <v>Documentais</v>
-      </c>
-      <c r="M90" s="53" t="str">
-        <f t="shared" si="23"/>
-        <v>Elemento.de.Pranchas</v>
-      </c>
-      <c r="N90" s="53" t="str">
-        <f t="shared" si="24"/>
-        <v>Carimbos</v>
-      </c>
-      <c r="O90" s="53" t="str">
-        <f t="shared" si="25"/>
         <v>Revisões Revisão</v>
       </c>
       <c r="P90" s="53" t="s">
         <v>143</v>
       </c>
-      <c r="Q90" s="43" t="str">
-        <f t="shared" si="26"/>
-        <v>Revisiones de diseño - Numeración</v>
+      <c r="Q90" s="43" t="s">
+        <v>847</v>
       </c>
       <c r="R90" s="43" t="s">
         <v>716</v>
@@ -12451,22 +12676,22 @@
         <v>9</v>
       </c>
       <c r="T90" s="43" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v>Documentais</v>
       </c>
       <c r="U90" s="43" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="24"/>
         <v>Elemento.de.Pranchas</v>
       </c>
       <c r="V90" s="53" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="25"/>
         <v>Carimbos</v>
       </c>
       <c r="W90" s="43" t="s">
         <v>80</v>
       </c>
       <c r="X90" s="54" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>Key-DOCU-90</v>
       </c>
       <c r="Y90" s="58" t="s">
@@ -12520,27 +12745,26 @@
         <v>9</v>
       </c>
       <c r="L91" s="53" t="str">
+        <f t="shared" si="19"/>
+        <v>Documentais</v>
+      </c>
+      <c r="M91" s="53" t="str">
+        <f t="shared" si="20"/>
+        <v>Elemento.de.Preenchimentos</v>
+      </c>
+      <c r="N91" s="53" t="str">
+        <f t="shared" si="21"/>
+        <v>Hachuras</v>
+      </c>
+      <c r="O91" s="53" t="str">
         <f t="shared" si="22"/>
-        <v>Documentais</v>
-      </c>
-      <c r="M91" s="53" t="str">
-        <f t="shared" si="23"/>
-        <v>Elemento.de.Preenchimentos</v>
-      </c>
-      <c r="N91" s="53" t="str">
-        <f t="shared" si="24"/>
-        <v>Hachuras</v>
-      </c>
-      <c r="O91" s="53" t="str">
-        <f t="shared" si="25"/>
         <v>Padrão Preenchimento</v>
       </c>
       <c r="P91" s="53" t="s">
         <v>150</v>
       </c>
-      <c r="Q91" s="43" t="e" vm="1">
-        <f t="shared" si="26"/>
-        <v>#VALUE!</v>
+      <c r="Q91" s="53" t="s">
+        <v>892</v>
       </c>
       <c r="R91" s="43" t="s">
         <v>717</v>
@@ -12549,22 +12773,22 @@
         <v>9</v>
       </c>
       <c r="T91" s="43" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v>Documentais</v>
       </c>
       <c r="U91" s="43" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="24"/>
         <v>Elemento.de.Preenchimentos</v>
       </c>
       <c r="V91" s="53" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="25"/>
         <v>Hachuras</v>
       </c>
       <c r="W91" s="43" t="s">
         <v>80</v>
       </c>
       <c r="X91" s="54" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>Key-DOCU-91</v>
       </c>
       <c r="Y91" s="58" t="s">
@@ -12618,27 +12842,26 @@
         <v>9</v>
       </c>
       <c r="L92" s="53" t="str">
+        <f t="shared" si="19"/>
+        <v>Documentais</v>
+      </c>
+      <c r="M92" s="53" t="str">
+        <f t="shared" si="20"/>
+        <v>Elemento.de.Preenchimentos</v>
+      </c>
+      <c r="N92" s="53" t="str">
+        <f t="shared" si="21"/>
+        <v>Hachuras</v>
+      </c>
+      <c r="O92" s="53" t="str">
         <f t="shared" si="22"/>
-        <v>Documentais</v>
-      </c>
-      <c r="M92" s="53" t="str">
-        <f t="shared" si="23"/>
-        <v>Elemento.de.Preenchimentos</v>
-      </c>
-      <c r="N92" s="53" t="str">
-        <f t="shared" si="24"/>
-        <v>Hachuras</v>
-      </c>
-      <c r="O92" s="53" t="str">
-        <f t="shared" si="25"/>
         <v>Padrão Hachura</v>
       </c>
       <c r="P92" s="53" t="s">
         <v>151</v>
       </c>
-      <c r="Q92" s="43" t="str">
-        <f t="shared" si="26"/>
-        <v>Patrones de trampilla</v>
+      <c r="Q92" s="43" t="s">
+        <v>848</v>
       </c>
       <c r="R92" s="43" t="s">
         <v>718</v>
@@ -12647,22 +12870,22 @@
         <v>9</v>
       </c>
       <c r="T92" s="43" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v>Documentais</v>
       </c>
       <c r="U92" s="43" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="24"/>
         <v>Elemento.de.Preenchimentos</v>
       </c>
       <c r="V92" s="53" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="25"/>
         <v>Hachuras</v>
       </c>
       <c r="W92" s="43" t="s">
         <v>80</v>
       </c>
       <c r="X92" s="54" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>Key-DOCU-92</v>
       </c>
       <c r="Y92" s="58" t="s">
@@ -12716,27 +12939,26 @@
         <v>9</v>
       </c>
       <c r="L93" s="53" t="str">
+        <f t="shared" si="19"/>
+        <v>Documentais</v>
+      </c>
+      <c r="M93" s="53" t="str">
+        <f t="shared" si="20"/>
+        <v>Elemento.de.Preenchimentos</v>
+      </c>
+      <c r="N93" s="53" t="str">
+        <f t="shared" si="21"/>
+        <v>Máscaras</v>
+      </c>
+      <c r="O93" s="53" t="str">
         <f t="shared" si="22"/>
-        <v>Documentais</v>
-      </c>
-      <c r="M93" s="53" t="str">
-        <f t="shared" si="23"/>
-        <v>Elemento.de.Preenchimentos</v>
-      </c>
-      <c r="N93" s="53" t="str">
-        <f t="shared" si="24"/>
-        <v>Máscaras</v>
-      </c>
-      <c r="O93" s="53" t="str">
-        <f t="shared" si="25"/>
         <v>Região Preenchida</v>
       </c>
       <c r="P93" s="53" t="s">
         <v>152</v>
       </c>
-      <c r="Q93" s="43" t="str">
-        <f t="shared" si="26"/>
-        <v>Región con relleno de color</v>
+      <c r="Q93" s="43" t="s">
+        <v>849</v>
       </c>
       <c r="R93" s="43" t="s">
         <v>719</v>
@@ -12745,22 +12967,22 @@
         <v>9</v>
       </c>
       <c r="T93" s="43" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v>Documentais</v>
       </c>
       <c r="U93" s="43" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="24"/>
         <v>Elemento.de.Preenchimentos</v>
       </c>
       <c r="V93" s="53" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="25"/>
         <v>Máscaras</v>
       </c>
       <c r="W93" s="43" t="s">
         <v>80</v>
       </c>
       <c r="X93" s="54" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>Key-DOCU-93</v>
       </c>
       <c r="Y93" s="58" t="s">
@@ -12814,27 +13036,26 @@
         <v>9</v>
       </c>
       <c r="L94" s="53" t="str">
+        <f t="shared" si="19"/>
+        <v>Documentais</v>
+      </c>
+      <c r="M94" s="53" t="str">
+        <f t="shared" si="20"/>
+        <v>Elemento.de.Preenchimentos</v>
+      </c>
+      <c r="N94" s="53" t="str">
+        <f t="shared" si="21"/>
+        <v>Máscaras</v>
+      </c>
+      <c r="O94" s="53" t="str">
         <f t="shared" si="22"/>
-        <v>Documentais</v>
-      </c>
-      <c r="M94" s="53" t="str">
-        <f t="shared" si="23"/>
-        <v>Elemento.de.Preenchimentos</v>
-      </c>
-      <c r="N94" s="53" t="str">
-        <f t="shared" si="24"/>
-        <v>Máscaras</v>
-      </c>
-      <c r="O94" s="53" t="str">
-        <f t="shared" si="25"/>
         <v>Região Máscara</v>
       </c>
       <c r="P94" s="53" t="s">
         <v>153</v>
       </c>
-      <c r="Q94" s="43" t="str">
-        <f t="shared" si="26"/>
-        <v>Región de enmascaramiento gráfico</v>
+      <c r="Q94" s="43" t="s">
+        <v>850</v>
       </c>
       <c r="R94" s="43" t="s">
         <v>720</v>
@@ -12843,22 +13064,22 @@
         <v>9</v>
       </c>
       <c r="T94" s="43" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v>Documentais</v>
       </c>
       <c r="U94" s="43" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="24"/>
         <v>Elemento.de.Preenchimentos</v>
       </c>
       <c r="V94" s="53" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="25"/>
         <v>Máscaras</v>
       </c>
       <c r="W94" s="43" t="s">
         <v>80</v>
       </c>
       <c r="X94" s="54" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>Key-DOCU-94</v>
       </c>
       <c r="Y94" s="58" t="s">
@@ -12912,27 +13133,26 @@
         <v>9</v>
       </c>
       <c r="L95" s="53" t="str">
+        <f t="shared" si="19"/>
+        <v>Documentais</v>
+      </c>
+      <c r="M95" s="53" t="str">
+        <f t="shared" si="20"/>
+        <v>Elemento.de.Relacionamento</v>
+      </c>
+      <c r="N95" s="53" t="str">
+        <f t="shared" si="21"/>
+        <v>Matches</v>
+      </c>
+      <c r="O95" s="53" t="str">
         <f t="shared" si="22"/>
-        <v>Documentais</v>
-      </c>
-      <c r="M95" s="53" t="str">
-        <f t="shared" si="23"/>
-        <v>Elemento.de.Relacionamento</v>
-      </c>
-      <c r="N95" s="53" t="str">
-        <f t="shared" si="24"/>
-        <v>Matches</v>
-      </c>
-      <c r="O95" s="53" t="str">
-        <f t="shared" si="25"/>
         <v>Combina Todo</v>
       </c>
       <c r="P95" s="53" t="s">
         <v>154</v>
       </c>
-      <c r="Q95" s="43" t="str">
-        <f t="shared" si="26"/>
-        <v>Coincidencias</v>
+      <c r="Q95" s="43" t="s">
+        <v>851</v>
       </c>
       <c r="R95" s="43" t="s">
         <v>721</v>
@@ -12941,22 +13161,22 @@
         <v>9</v>
       </c>
       <c r="T95" s="43" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v>Documentais</v>
       </c>
       <c r="U95" s="43" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="24"/>
         <v>Elemento.de.Relacionamento</v>
       </c>
       <c r="V95" s="53" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="25"/>
         <v>Matches</v>
       </c>
       <c r="W95" s="43" t="s">
         <v>80</v>
       </c>
       <c r="X95" s="54" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>Key-DOCU-95</v>
       </c>
       <c r="Y95" s="58" t="s">
@@ -13010,27 +13230,26 @@
         <v>9</v>
       </c>
       <c r="L96" s="53" t="str">
+        <f t="shared" si="19"/>
+        <v>Documentais</v>
+      </c>
+      <c r="M96" s="53" t="str">
+        <f t="shared" si="20"/>
+        <v>Elemento.de.Relacionamento</v>
+      </c>
+      <c r="N96" s="53" t="str">
+        <f t="shared" si="21"/>
+        <v>Matches</v>
+      </c>
+      <c r="O96" s="53" t="str">
         <f t="shared" si="22"/>
-        <v>Documentais</v>
-      </c>
-      <c r="M96" s="53" t="str">
-        <f t="shared" si="23"/>
-        <v>Elemento.de.Relacionamento</v>
-      </c>
-      <c r="N96" s="53" t="str">
-        <f t="shared" si="24"/>
-        <v>Matches</v>
-      </c>
-      <c r="O96" s="53" t="str">
-        <f t="shared" si="25"/>
         <v>Combina Anotação</v>
       </c>
       <c r="P96" s="53" t="s">
         <v>155</v>
       </c>
-      <c r="Q96" s="43" t="str">
-        <f t="shared" si="26"/>
-        <v>Coincidencias textuales</v>
+      <c r="Q96" s="43" t="s">
+        <v>852</v>
       </c>
       <c r="R96" s="43" t="s">
         <v>722</v>
@@ -13039,22 +13258,22 @@
         <v>9</v>
       </c>
       <c r="T96" s="43" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v>Documentais</v>
       </c>
       <c r="U96" s="43" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="24"/>
         <v>Elemento.de.Relacionamento</v>
       </c>
       <c r="V96" s="53" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="25"/>
         <v>Matches</v>
       </c>
       <c r="W96" s="43" t="s">
         <v>80</v>
       </c>
       <c r="X96" s="54" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>Key-DOCU-96</v>
       </c>
       <c r="Y96" s="58" t="s">
@@ -13108,27 +13327,26 @@
         <v>9</v>
       </c>
       <c r="L97" s="53" t="str">
+        <f t="shared" si="19"/>
+        <v>Documentais</v>
+      </c>
+      <c r="M97" s="53" t="str">
+        <f t="shared" si="20"/>
+        <v>Elemento.de.Relacionamento</v>
+      </c>
+      <c r="N97" s="53" t="str">
+        <f t="shared" si="21"/>
+        <v>Matches</v>
+      </c>
+      <c r="O97" s="53" t="str">
         <f t="shared" si="22"/>
-        <v>Documentais</v>
-      </c>
-      <c r="M97" s="53" t="str">
-        <f t="shared" si="23"/>
-        <v>Elemento.de.Relacionamento</v>
-      </c>
-      <c r="N97" s="53" t="str">
-        <f t="shared" si="24"/>
-        <v>Matches</v>
-      </c>
-      <c r="O97" s="53" t="str">
-        <f t="shared" si="25"/>
         <v>Combina Detalhe</v>
       </c>
       <c r="P97" s="53" t="s">
         <v>156</v>
       </c>
-      <c r="Q97" s="43" t="str">
-        <f t="shared" si="26"/>
-        <v>Coincidencias de detalles</v>
+      <c r="Q97" s="43" t="s">
+        <v>853</v>
       </c>
       <c r="R97" s="43" t="s">
         <v>723</v>
@@ -13137,22 +13355,22 @@
         <v>9</v>
       </c>
       <c r="T97" s="43" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v>Documentais</v>
       </c>
       <c r="U97" s="43" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="24"/>
         <v>Elemento.de.Relacionamento</v>
       </c>
       <c r="V97" s="53" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="25"/>
         <v>Matches</v>
       </c>
       <c r="W97" s="43" t="s">
         <v>80</v>
       </c>
       <c r="X97" s="54" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>Key-DOCU-97</v>
       </c>
       <c r="Y97" s="58" t="s">
@@ -13206,27 +13424,26 @@
         <v>9</v>
       </c>
       <c r="L98" s="53" t="str">
+        <f t="shared" si="19"/>
+        <v>Documentais</v>
+      </c>
+      <c r="M98" s="53" t="str">
+        <f t="shared" si="20"/>
+        <v>Elemento.de.Relacionamento</v>
+      </c>
+      <c r="N98" s="53" t="str">
+        <f t="shared" si="21"/>
+        <v>Matches</v>
+      </c>
+      <c r="O98" s="53" t="str">
         <f t="shared" si="22"/>
-        <v>Documentais</v>
-      </c>
-      <c r="M98" s="53" t="str">
-        <f t="shared" si="23"/>
-        <v>Elemento.de.Relacionamento</v>
-      </c>
-      <c r="N98" s="53" t="str">
-        <f t="shared" si="24"/>
-        <v>Matches</v>
-      </c>
-      <c r="O98" s="53" t="str">
-        <f t="shared" si="25"/>
         <v>Combina Linha</v>
       </c>
       <c r="P98" s="53" t="s">
         <v>157</v>
       </c>
-      <c r="Q98" s="43" t="str">
-        <f t="shared" si="26"/>
-        <v>Coincidencias - Líneas de coincidencia</v>
+      <c r="Q98" s="43" t="s">
+        <v>854</v>
       </c>
       <c r="R98" s="43" t="s">
         <v>724</v>
@@ -13235,22 +13452,22 @@
         <v>9</v>
       </c>
       <c r="T98" s="43" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v>Documentais</v>
       </c>
       <c r="U98" s="43" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="24"/>
         <v>Elemento.de.Relacionamento</v>
       </c>
       <c r="V98" s="53" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="25"/>
         <v>Matches</v>
       </c>
       <c r="W98" s="43" t="s">
         <v>80</v>
       </c>
       <c r="X98" s="54" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>Key-DOCU-98</v>
       </c>
       <c r="Y98" s="58" t="s">
@@ -13304,27 +13521,26 @@
         <v>9</v>
       </c>
       <c r="L99" s="53" t="str">
+        <f t="shared" si="19"/>
+        <v>Documentais</v>
+      </c>
+      <c r="M99" s="53" t="str">
+        <f t="shared" si="20"/>
+        <v>Elemento.de.Relacionamento</v>
+      </c>
+      <c r="N99" s="53" t="str">
+        <f t="shared" si="21"/>
+        <v>Matches</v>
+      </c>
+      <c r="O99" s="53" t="str">
         <f t="shared" si="22"/>
-        <v>Documentais</v>
-      </c>
-      <c r="M99" s="53" t="str">
-        <f t="shared" si="23"/>
-        <v>Elemento.de.Relacionamento</v>
-      </c>
-      <c r="N99" s="53" t="str">
-        <f t="shared" si="24"/>
-        <v>Matches</v>
-      </c>
-      <c r="O99" s="53" t="str">
-        <f t="shared" si="25"/>
         <v>Combina Modelo</v>
       </c>
       <c r="P99" s="53" t="s">
         <v>158</v>
       </c>
-      <c r="Q99" s="43" t="str">
-        <f t="shared" si="26"/>
-        <v>Coincidencias de modelos</v>
+      <c r="Q99" s="43" t="s">
+        <v>855</v>
       </c>
       <c r="R99" s="43" t="s">
         <v>725</v>
@@ -13333,22 +13549,22 @@
         <v>9</v>
       </c>
       <c r="T99" s="43" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v>Documentais</v>
       </c>
       <c r="U99" s="43" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="24"/>
         <v>Elemento.de.Relacionamento</v>
       </c>
       <c r="V99" s="53" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="25"/>
         <v>Matches</v>
       </c>
       <c r="W99" s="43" t="s">
         <v>80</v>
       </c>
       <c r="X99" s="54" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>Key-DOCU-99</v>
       </c>
       <c r="Y99" s="58" t="s">
@@ -13402,27 +13618,26 @@
         <v>9</v>
       </c>
       <c r="L100" s="53" t="str">
+        <f t="shared" si="19"/>
+        <v>Documentais</v>
+      </c>
+      <c r="M100" s="53" t="str">
+        <f t="shared" si="20"/>
+        <v>Elemento.de.Relacionamento</v>
+      </c>
+      <c r="N100" s="53" t="str">
+        <f t="shared" si="21"/>
+        <v>Matches</v>
+      </c>
+      <c r="O100" s="53" t="str">
         <f t="shared" si="22"/>
-        <v>Documentais</v>
-      </c>
-      <c r="M100" s="53" t="str">
-        <f t="shared" si="23"/>
-        <v>Elemento.de.Relacionamento</v>
-      </c>
-      <c r="N100" s="53" t="str">
-        <f t="shared" si="24"/>
-        <v>Matches</v>
-      </c>
-      <c r="O100" s="53" t="str">
-        <f t="shared" si="25"/>
         <v>Combina Perfil</v>
       </c>
       <c r="P100" s="53" t="s">
         <v>159</v>
       </c>
-      <c r="Q100" s="43" t="str">
-        <f t="shared" si="26"/>
-        <v>Coincidencias de perfil</v>
+      <c r="Q100" s="43" t="s">
+        <v>856</v>
       </c>
       <c r="R100" s="43" t="s">
         <v>726</v>
@@ -13431,22 +13646,22 @@
         <v>9</v>
       </c>
       <c r="T100" s="43" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v>Documentais</v>
       </c>
       <c r="U100" s="43" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="24"/>
         <v>Elemento.de.Relacionamento</v>
       </c>
       <c r="V100" s="53" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="25"/>
         <v>Matches</v>
       </c>
       <c r="W100" s="43" t="s">
         <v>80</v>
       </c>
       <c r="X100" s="54" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>Key-DOCU-100</v>
       </c>
       <c r="Y100" s="58" t="s">
@@ -13500,27 +13715,26 @@
         <v>9</v>
       </c>
       <c r="L101" s="53" t="str">
+        <f t="shared" si="19"/>
+        <v>Documentais</v>
+      </c>
+      <c r="M101" s="53" t="str">
+        <f t="shared" si="20"/>
+        <v>Elemento.de.Relacionamento</v>
+      </c>
+      <c r="N101" s="53" t="str">
+        <f t="shared" si="21"/>
+        <v>Matches</v>
+      </c>
+      <c r="O101" s="53" t="str">
         <f t="shared" si="22"/>
-        <v>Documentais</v>
-      </c>
-      <c r="M101" s="53" t="str">
-        <f t="shared" si="23"/>
-        <v>Elemento.de.Relacionamento</v>
-      </c>
-      <c r="N101" s="53" t="str">
-        <f t="shared" si="24"/>
-        <v>Matches</v>
-      </c>
-      <c r="O101" s="53" t="str">
-        <f t="shared" si="25"/>
         <v>Combina Sítio</v>
       </c>
       <c r="P101" s="53" t="s">
         <v>160</v>
       </c>
-      <c r="Q101" s="43" t="str">
-        <f t="shared" si="26"/>
-        <v>Coincidencias de componentes de la situación</v>
+      <c r="Q101" s="43" t="s">
+        <v>857</v>
       </c>
       <c r="R101" s="43" t="s">
         <v>727</v>
@@ -13529,22 +13743,22 @@
         <v>9</v>
       </c>
       <c r="T101" s="43" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v>Documentais</v>
       </c>
       <c r="U101" s="43" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="24"/>
         <v>Elemento.de.Relacionamento</v>
       </c>
       <c r="V101" s="53" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="25"/>
         <v>Matches</v>
       </c>
       <c r="W101" s="43" t="s">
         <v>80</v>
       </c>
       <c r="X101" s="54" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>Key-DOCU-101</v>
       </c>
       <c r="Y101" s="58" t="s">
@@ -13598,27 +13812,26 @@
         <v>9</v>
       </c>
       <c r="L102" s="53" t="str">
-        <f t="shared" ref="L102" si="35">CONCATENATE("", C102)</f>
+        <f t="shared" ref="L102" si="31">CONCATENATE("", C102)</f>
         <v>Documentais</v>
       </c>
       <c r="M102" s="53" t="str">
-        <f t="shared" ref="M102" si="36">CONCATENATE("", D102)</f>
+        <f t="shared" ref="M102" si="32">CONCATENATE("", D102)</f>
         <v>Elemento.de.Planilhamento</v>
       </c>
       <c r="N102" s="53" t="str">
-        <f t="shared" ref="N102" si="37">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E102),"."," ")," De "," de "))</f>
+        <f t="shared" ref="N102" si="33">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E102),"."," ")," De "," de "))</f>
         <v>Tabelas</v>
       </c>
       <c r="O102" s="53" t="str">
-        <f t="shared" ref="O102" si="38">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",F102),"."," ")," De "," de "))</f>
+        <f t="shared" ref="O102" si="34">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",F102),"."," ")," De "," de "))</f>
         <v>Tabela</v>
       </c>
       <c r="P102" s="53" t="s">
         <v>164</v>
       </c>
-      <c r="Q102" s="43" t="str">
-        <f t="shared" si="26"/>
-        <v>Tabla textual</v>
+      <c r="Q102" s="43" t="s">
+        <v>858</v>
       </c>
       <c r="R102" s="43" t="s">
         <v>728</v>
@@ -13627,22 +13840,22 @@
         <v>9</v>
       </c>
       <c r="T102" s="43" t="str">
-        <f t="shared" ref="T102:T137" si="39">SUBSTITUTE(C102, "_", " ")</f>
+        <f t="shared" ref="T102:T137" si="35">SUBSTITUTE(C102, "_", " ")</f>
         <v>Documentais</v>
       </c>
       <c r="U102" s="43" t="str">
-        <f t="shared" ref="U102" si="40">SUBSTITUTE(D102, "_", " ")</f>
+        <f t="shared" ref="U102" si="36">SUBSTITUTE(D102, "_", " ")</f>
         <v>Elemento.de.Planilhamento</v>
       </c>
       <c r="V102" s="53" t="str">
-        <f t="shared" ref="V102:V137" si="41">SUBSTITUTE(E102, "_", " ")</f>
+        <f t="shared" ref="V102:V137" si="37">SUBSTITUTE(E102, "_", " ")</f>
         <v>Tabelas</v>
       </c>
       <c r="W102" s="43" t="s">
         <v>80</v>
       </c>
       <c r="X102" s="54" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>Key-DOCU-102</v>
       </c>
       <c r="Y102" s="58" t="s">
@@ -13696,27 +13909,26 @@
         <v>9</v>
       </c>
       <c r="L103" s="53" t="str">
+        <f t="shared" si="19"/>
+        <v>Documentais</v>
+      </c>
+      <c r="M103" s="53" t="str">
+        <f t="shared" si="20"/>
+        <v>Elemento.de.Planilhamento</v>
+      </c>
+      <c r="N103" s="53" t="str">
+        <f t="shared" si="21"/>
+        <v>Tabelas</v>
+      </c>
+      <c r="O103" s="53" t="str">
         <f t="shared" si="22"/>
-        <v>Documentais</v>
-      </c>
-      <c r="M103" s="53" t="str">
-        <f t="shared" si="23"/>
-        <v>Elemento.de.Planilhamento</v>
-      </c>
-      <c r="N103" s="53" t="str">
-        <f t="shared" si="24"/>
-        <v>Tabelas</v>
-      </c>
-      <c r="O103" s="53" t="str">
-        <f t="shared" si="25"/>
         <v>Tabela Painéis</v>
       </c>
       <c r="P103" s="53" t="s">
         <v>162</v>
       </c>
-      <c r="Q103" s="43" t="str">
-        <f t="shared" si="26"/>
-        <v>Disposiciones gráficas de tablas</v>
+      <c r="Q103" s="43" t="s">
+        <v>859</v>
       </c>
       <c r="R103" s="43" t="s">
         <v>729</v>
@@ -13725,22 +13937,22 @@
         <v>9</v>
       </c>
       <c r="T103" s="43" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="35"/>
         <v>Documentais</v>
       </c>
       <c r="U103" s="43" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="24"/>
         <v>Elemento.de.Planilhamento</v>
       </c>
       <c r="V103" s="53" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="37"/>
         <v>Tabelas</v>
       </c>
       <c r="W103" s="43" t="s">
         <v>80</v>
       </c>
       <c r="X103" s="54" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>Key-DOCU-103</v>
       </c>
       <c r="Y103" s="58" t="s">
@@ -13794,27 +14006,26 @@
         <v>9</v>
       </c>
       <c r="L104" s="53" t="str">
+        <f t="shared" si="19"/>
+        <v>Documentais</v>
+      </c>
+      <c r="M104" s="53" t="str">
+        <f t="shared" si="20"/>
+        <v>Elemento.de.Planilhamento</v>
+      </c>
+      <c r="N104" s="53" t="str">
+        <f t="shared" si="21"/>
+        <v>Tabelas</v>
+      </c>
+      <c r="O104" s="53" t="str">
         <f t="shared" si="22"/>
-        <v>Documentais</v>
-      </c>
-      <c r="M104" s="53" t="str">
-        <f t="shared" si="23"/>
-        <v>Elemento.de.Planilhamento</v>
-      </c>
-      <c r="N104" s="53" t="str">
-        <f t="shared" si="24"/>
-        <v>Tabelas</v>
-      </c>
-      <c r="O104" s="53" t="str">
-        <f t="shared" si="25"/>
         <v>Tabela Gráfica</v>
       </c>
       <c r="P104" s="53" t="s">
         <v>163</v>
       </c>
-      <c r="Q104" s="43" t="e" vm="1">
-        <f t="shared" si="26"/>
-        <v>#VALUE!</v>
+      <c r="Q104" s="43" t="s">
+        <v>893</v>
       </c>
       <c r="R104" s="43" t="s">
         <v>730</v>
@@ -13823,22 +14034,22 @@
         <v>9</v>
       </c>
       <c r="T104" s="43" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="35"/>
         <v>Documentais</v>
       </c>
       <c r="U104" s="43" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="24"/>
         <v>Elemento.de.Planilhamento</v>
       </c>
       <c r="V104" s="53" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="37"/>
         <v>Tabelas</v>
       </c>
       <c r="W104" s="43" t="s">
         <v>80</v>
       </c>
       <c r="X104" s="54" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>Key-DOCU-104</v>
       </c>
       <c r="Y104" s="58" t="s">
@@ -13892,27 +14103,26 @@
         <v>9</v>
       </c>
       <c r="L105" s="53" t="str">
+        <f t="shared" si="19"/>
+        <v>Documentais</v>
+      </c>
+      <c r="M105" s="53" t="str">
+        <f t="shared" si="20"/>
+        <v>Elemento.de.Planilhamento</v>
+      </c>
+      <c r="N105" s="53" t="str">
+        <f t="shared" si="21"/>
+        <v>Tabelas</v>
+      </c>
+      <c r="O105" s="53" t="str">
         <f t="shared" si="22"/>
-        <v>Documentais</v>
-      </c>
-      <c r="M105" s="53" t="str">
-        <f t="shared" si="23"/>
-        <v>Elemento.de.Planilhamento</v>
-      </c>
-      <c r="N105" s="53" t="str">
-        <f t="shared" si="24"/>
-        <v>Tabelas</v>
-      </c>
-      <c r="O105" s="53" t="str">
-        <f t="shared" si="25"/>
         <v>Tabela Vistas</v>
       </c>
       <c r="P105" s="53" t="s">
         <v>165</v>
       </c>
-      <c r="Q105" s="43" t="str">
-        <f t="shared" si="26"/>
-        <v>Conjunto de parámetros de una tabla</v>
+      <c r="Q105" s="43" t="s">
+        <v>860</v>
       </c>
       <c r="R105" s="43" t="s">
         <v>731</v>
@@ -13921,22 +14131,22 @@
         <v>9</v>
       </c>
       <c r="T105" s="43" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="35"/>
         <v>Documentais</v>
       </c>
       <c r="U105" s="43" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="24"/>
         <v>Elemento.de.Planilhamento</v>
       </c>
       <c r="V105" s="53" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="37"/>
         <v>Tabelas</v>
       </c>
       <c r="W105" s="43" t="s">
         <v>80</v>
       </c>
       <c r="X105" s="54" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>Key-DOCU-105</v>
       </c>
       <c r="Y105" s="58" t="s">
@@ -13990,27 +14200,26 @@
         <v>9</v>
       </c>
       <c r="L106" s="53" t="str">
+        <f t="shared" si="19"/>
+        <v>Documentais</v>
+      </c>
+      <c r="M106" s="53" t="str">
+        <f t="shared" si="20"/>
+        <v>Elemento.de.Planilhamento</v>
+      </c>
+      <c r="N106" s="53" t="str">
+        <f t="shared" si="21"/>
+        <v>Tabelas</v>
+      </c>
+      <c r="O106" s="53" t="str">
         <f t="shared" si="22"/>
-        <v>Documentais</v>
-      </c>
-      <c r="M106" s="53" t="str">
-        <f t="shared" si="23"/>
-        <v>Elemento.de.Planilhamento</v>
-      </c>
-      <c r="N106" s="53" t="str">
-        <f t="shared" si="24"/>
-        <v>Tabelas</v>
-      </c>
-      <c r="O106" s="53" t="str">
-        <f t="shared" si="25"/>
         <v>Tabela Ramais</v>
       </c>
       <c r="P106" s="53" t="s">
         <v>166</v>
       </c>
-      <c r="Q106" s="43" t="str">
-        <f t="shared" si="26"/>
-        <v>Plantilla de tablas de circuitos</v>
+      <c r="Q106" s="43" t="s">
+        <v>861</v>
       </c>
       <c r="R106" s="43" t="s">
         <v>732</v>
@@ -14019,22 +14228,22 @@
         <v>9</v>
       </c>
       <c r="T106" s="43" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="35"/>
         <v>Documentais</v>
       </c>
       <c r="U106" s="43" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="24"/>
         <v>Elemento.de.Planilhamento</v>
       </c>
       <c r="V106" s="53" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="37"/>
         <v>Tabelas</v>
       </c>
       <c r="W106" s="43" t="s">
         <v>80</v>
       </c>
       <c r="X106" s="54" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>Key-DOCU-106</v>
       </c>
       <c r="Y106" s="58" t="s">
@@ -14088,27 +14297,26 @@
         <v>9</v>
       </c>
       <c r="L107" s="53" t="str">
+        <f t="shared" si="19"/>
+        <v>Documentais</v>
+      </c>
+      <c r="M107" s="53" t="str">
+        <f t="shared" si="20"/>
+        <v>Elemento.de.Anotação</v>
+      </c>
+      <c r="N107" s="53" t="str">
+        <f t="shared" si="21"/>
+        <v>Area Textual</v>
+      </c>
+      <c r="O107" s="53" t="str">
         <f t="shared" si="22"/>
-        <v>Documentais</v>
-      </c>
-      <c r="M107" s="53" t="str">
-        <f t="shared" si="23"/>
-        <v>Elemento.de.Anotação</v>
-      </c>
-      <c r="N107" s="53" t="str">
-        <f t="shared" si="24"/>
-        <v>Area Textual</v>
-      </c>
-      <c r="O107" s="53" t="str">
-        <f t="shared" si="25"/>
         <v>RecortedeAnotação</v>
       </c>
       <c r="P107" s="53" t="s">
         <v>81</v>
       </c>
-      <c r="Q107" s="43" t="str">
-        <f t="shared" si="26"/>
-        <v>Anotación - espacio de corte textual</v>
+      <c r="Q107" s="43" t="s">
+        <v>862</v>
       </c>
       <c r="R107" s="43" t="s">
         <v>733</v>
@@ -14117,22 +14325,22 @@
         <v>9</v>
       </c>
       <c r="T107" s="43" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="35"/>
         <v>Documentais</v>
       </c>
       <c r="U107" s="43" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="24"/>
         <v>Elemento.de.Anotação</v>
       </c>
       <c r="V107" s="53" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="37"/>
         <v>Area.Textual</v>
       </c>
       <c r="W107" s="43" t="s">
         <v>80</v>
       </c>
       <c r="X107" s="54" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>Key-DOCU-107</v>
       </c>
       <c r="Y107" s="58" t="s">
@@ -14186,27 +14394,26 @@
         <v>9</v>
       </c>
       <c r="L108" s="53" t="str">
+        <f t="shared" si="19"/>
+        <v>Documentais</v>
+      </c>
+      <c r="M108" s="53" t="str">
+        <f t="shared" si="20"/>
+        <v>Elemento.de.Anotação</v>
+      </c>
+      <c r="N108" s="53" t="str">
+        <f t="shared" si="21"/>
+        <v>Area Textual</v>
+      </c>
+      <c r="O108" s="53" t="str">
         <f t="shared" si="22"/>
-        <v>Documentais</v>
-      </c>
-      <c r="M108" s="53" t="str">
-        <f t="shared" si="23"/>
-        <v>Elemento.de.Anotação</v>
-      </c>
-      <c r="N108" s="53" t="str">
-        <f t="shared" si="24"/>
-        <v>Area Textual</v>
-      </c>
-      <c r="O108" s="53" t="str">
-        <f t="shared" si="25"/>
         <v>EspecialdeRecortedeAnotação</v>
       </c>
       <c r="P108" s="53" t="s">
         <v>82</v>
       </c>
-      <c r="Q108" s="43" t="str">
-        <f t="shared" si="26"/>
-        <v>Anotación - espacio especial de recortes textuales</v>
+      <c r="Q108" s="43" t="s">
+        <v>863</v>
       </c>
       <c r="R108" s="43" t="s">
         <v>734</v>
@@ -14215,22 +14422,22 @@
         <v>9</v>
       </c>
       <c r="T108" s="43" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="35"/>
         <v>Documentais</v>
       </c>
       <c r="U108" s="43" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="24"/>
         <v>Elemento.de.Anotação</v>
       </c>
       <c r="V108" s="53" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="37"/>
         <v>Area.Textual</v>
       </c>
       <c r="W108" s="43" t="s">
         <v>80</v>
       </c>
       <c r="X108" s="54" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>Key-DOCU-108</v>
       </c>
       <c r="Y108" s="58" t="s">
@@ -14284,27 +14491,26 @@
         <v>9</v>
       </c>
       <c r="L109" s="53" t="str">
+        <f t="shared" si="19"/>
+        <v>Documentais</v>
+      </c>
+      <c r="M109" s="53" t="str">
+        <f t="shared" si="20"/>
+        <v>Elemento.de.Anotação</v>
+      </c>
+      <c r="N109" s="53" t="str">
+        <f t="shared" si="21"/>
+        <v>Anotações</v>
+      </c>
+      <c r="O109" s="53" t="str">
         <f t="shared" si="22"/>
-        <v>Documentais</v>
-      </c>
-      <c r="M109" s="53" t="str">
-        <f t="shared" si="23"/>
-        <v>Elemento.de.Anotação</v>
-      </c>
-      <c r="N109" s="53" t="str">
-        <f t="shared" si="24"/>
-        <v>Anotações</v>
-      </c>
-      <c r="O109" s="53" t="str">
-        <f t="shared" si="25"/>
         <v>Texto Modelado</v>
       </c>
       <c r="P109" s="53" t="s">
         <v>133</v>
       </c>
-      <c r="Q109" s="43" t="str">
-        <f t="shared" si="26"/>
-        <v>Textos de modelos 3D</v>
+      <c r="Q109" s="43" t="s">
+        <v>864</v>
       </c>
       <c r="R109" s="43" t="s">
         <v>735</v>
@@ -14313,22 +14519,22 @@
         <v>9</v>
       </c>
       <c r="T109" s="43" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="35"/>
         <v>Documentais</v>
       </c>
       <c r="U109" s="43" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="24"/>
         <v>Elemento.de.Anotação</v>
       </c>
       <c r="V109" s="53" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="37"/>
         <v>Anotações</v>
       </c>
       <c r="W109" s="43" t="s">
         <v>80</v>
       </c>
       <c r="X109" s="54" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>Key-DOCU-109</v>
       </c>
       <c r="Y109" s="58" t="s">
@@ -14382,27 +14588,26 @@
         <v>9</v>
       </c>
       <c r="L110" s="53" t="str">
-        <f t="shared" ref="L110" si="42">CONCATENATE("", C110)</f>
+        <f t="shared" ref="L110" si="38">CONCATENATE("", C110)</f>
         <v>Documentais</v>
       </c>
       <c r="M110" s="53" t="str">
-        <f t="shared" ref="M110" si="43">CONCATENATE("", D110)</f>
+        <f t="shared" ref="M110" si="39">CONCATENATE("", D110)</f>
         <v>Elemento.de.Anotação</v>
       </c>
       <c r="N110" s="53" t="str">
-        <f t="shared" ref="N110" si="44">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E110),"."," ")," De "," de "))</f>
+        <f t="shared" ref="N110" si="40">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E110),"."," ")," De "," de "))</f>
         <v>Anotações</v>
       </c>
       <c r="O110" s="53" t="str">
-        <f t="shared" ref="O110" si="45">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",F110),"."," ")," De "," de "))</f>
+        <f t="shared" ref="O110" si="41">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",F110),"."," ")," De "," de "))</f>
         <v>Anotação Textual</v>
       </c>
       <c r="P110" s="53" t="s">
         <v>170</v>
       </c>
-      <c r="Q110" s="43" t="str">
-        <f t="shared" si="26"/>
-        <v>Notas textuales</v>
+      <c r="Q110" s="43" t="s">
+        <v>865</v>
       </c>
       <c r="R110" s="43" t="s">
         <v>736</v>
@@ -14411,22 +14616,22 @@
         <v>9</v>
       </c>
       <c r="T110" s="43" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="35"/>
         <v>Documentais</v>
       </c>
       <c r="U110" s="43" t="str">
-        <f t="shared" ref="U110" si="46">SUBSTITUTE(D110, "_", " ")</f>
+        <f t="shared" ref="U110" si="42">SUBSTITUTE(D110, "_", " ")</f>
         <v>Elemento.de.Anotação</v>
       </c>
       <c r="V110" s="53" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="37"/>
         <v>Anotações</v>
       </c>
       <c r="W110" s="43" t="s">
         <v>80</v>
       </c>
       <c r="X110" s="54" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>Key-DOCU-110</v>
       </c>
       <c r="Y110" s="58" t="s">
@@ -14480,27 +14685,26 @@
         <v>9</v>
       </c>
       <c r="L111" s="53" t="str">
+        <f t="shared" si="19"/>
+        <v>Documentais</v>
+      </c>
+      <c r="M111" s="53" t="str">
+        <f t="shared" si="20"/>
+        <v>Elemento.de.Anotação</v>
+      </c>
+      <c r="N111" s="53" t="str">
+        <f t="shared" si="21"/>
+        <v>Anotações</v>
+      </c>
+      <c r="O111" s="53" t="str">
         <f t="shared" si="22"/>
-        <v>Documentais</v>
-      </c>
-      <c r="M111" s="53" t="str">
-        <f t="shared" si="23"/>
-        <v>Elemento.de.Anotação</v>
-      </c>
-      <c r="N111" s="53" t="str">
-        <f t="shared" si="24"/>
-        <v>Anotações</v>
-      </c>
-      <c r="O111" s="53" t="str">
-        <f t="shared" si="25"/>
         <v>Anotação Genérica</v>
       </c>
       <c r="P111" s="53" t="s">
         <v>167</v>
       </c>
-      <c r="Q111" s="43" t="str">
-        <f t="shared" si="26"/>
-        <v>Anotaciones genéricas</v>
+      <c r="Q111" s="43" t="s">
+        <v>866</v>
       </c>
       <c r="R111" s="43" t="s">
         <v>737</v>
@@ -14509,22 +14713,22 @@
         <v>9</v>
       </c>
       <c r="T111" s="43" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="35"/>
         <v>Documentais</v>
       </c>
       <c r="U111" s="43" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="24"/>
         <v>Elemento.de.Anotação</v>
       </c>
       <c r="V111" s="53" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="37"/>
         <v>Anotações</v>
       </c>
       <c r="W111" s="43" t="s">
         <v>80</v>
       </c>
       <c r="X111" s="54" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>Key-DOCU-111</v>
       </c>
       <c r="Y111" s="58" t="s">
@@ -14578,27 +14782,26 @@
         <v>9</v>
       </c>
       <c r="L112" s="53" t="str">
+        <f t="shared" si="19"/>
+        <v>Documentais</v>
+      </c>
+      <c r="M112" s="53" t="str">
+        <f t="shared" si="20"/>
+        <v>Elemento.de.Anotação</v>
+      </c>
+      <c r="N112" s="53" t="str">
+        <f t="shared" si="21"/>
+        <v>Anotações</v>
+      </c>
+      <c r="O112" s="53" t="str">
         <f t="shared" si="22"/>
-        <v>Documentais</v>
-      </c>
-      <c r="M112" s="53" t="str">
-        <f t="shared" si="23"/>
-        <v>Elemento.de.Anotação</v>
-      </c>
-      <c r="N112" s="53" t="str">
-        <f t="shared" si="24"/>
-        <v>Anotações</v>
-      </c>
-      <c r="O112" s="53" t="str">
-        <f t="shared" si="25"/>
         <v>Anotação Múltiple</v>
       </c>
       <c r="P112" s="53" t="s">
         <v>168</v>
       </c>
-      <c r="Q112" s="43" t="str">
-        <f t="shared" si="26"/>
-        <v>Múltiples referencias textuales</v>
+      <c r="Q112" s="43" t="s">
+        <v>867</v>
       </c>
       <c r="R112" s="43" t="s">
         <v>738</v>
@@ -14607,22 +14810,22 @@
         <v>9</v>
       </c>
       <c r="T112" s="43" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="35"/>
         <v>Documentais</v>
       </c>
       <c r="U112" s="43" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="24"/>
         <v>Elemento.de.Anotação</v>
       </c>
       <c r="V112" s="53" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="37"/>
         <v>Anotações</v>
       </c>
       <c r="W112" s="43" t="s">
         <v>80</v>
       </c>
       <c r="X112" s="54" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>Key-DOCU-112</v>
       </c>
       <c r="Y112" s="58" t="s">
@@ -14676,27 +14879,26 @@
         <v>9</v>
       </c>
       <c r="L113" s="53" t="str">
+        <f t="shared" si="19"/>
+        <v>Documentais</v>
+      </c>
+      <c r="M113" s="53" t="str">
+        <f t="shared" si="20"/>
+        <v>Elemento.de.Anotação</v>
+      </c>
+      <c r="N113" s="53" t="str">
+        <f t="shared" si="21"/>
+        <v>Anotações</v>
+      </c>
+      <c r="O113" s="53" t="str">
         <f t="shared" si="22"/>
-        <v>Documentais</v>
-      </c>
-      <c r="M113" s="53" t="str">
-        <f t="shared" si="23"/>
-        <v>Elemento.de.Anotação</v>
-      </c>
-      <c r="N113" s="53" t="str">
-        <f t="shared" si="24"/>
-        <v>Anotações</v>
-      </c>
-      <c r="O113" s="53" t="str">
-        <f t="shared" si="25"/>
         <v>Anotação Estrutural</v>
       </c>
       <c r="P113" s="53" t="s">
         <v>169</v>
       </c>
-      <c r="Q113" s="43" t="str">
-        <f t="shared" si="26"/>
-        <v>Anotaciones estructurales</v>
+      <c r="Q113" s="43" t="s">
+        <v>868</v>
       </c>
       <c r="R113" s="43" t="s">
         <v>739</v>
@@ -14705,22 +14907,22 @@
         <v>9</v>
       </c>
       <c r="T113" s="43" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="35"/>
         <v>Documentais</v>
       </c>
       <c r="U113" s="43" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="24"/>
         <v>Elemento.de.Anotação</v>
       </c>
       <c r="V113" s="53" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="37"/>
         <v>Anotações</v>
       </c>
       <c r="W113" s="43" t="s">
         <v>80</v>
       </c>
       <c r="X113" s="54" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>Key-DOCU-113</v>
       </c>
       <c r="Y113" s="58" t="s">
@@ -14774,27 +14976,26 @@
         <v>9</v>
       </c>
       <c r="L114" s="53" t="str">
+        <f t="shared" si="19"/>
+        <v>Documentais</v>
+      </c>
+      <c r="M114" s="53" t="str">
+        <f t="shared" si="20"/>
+        <v>Elemento.de.Anotação</v>
+      </c>
+      <c r="N114" s="53" t="str">
+        <f t="shared" si="21"/>
+        <v>Etiquetas</v>
+      </c>
+      <c r="O114" s="53" t="str">
         <f t="shared" si="22"/>
-        <v>Documentais</v>
-      </c>
-      <c r="M114" s="53" t="str">
-        <f t="shared" si="23"/>
-        <v>Elemento.de.Anotação</v>
-      </c>
-      <c r="N114" s="53" t="str">
-        <f t="shared" si="24"/>
-        <v>Etiquetas</v>
-      </c>
-      <c r="O114" s="53" t="str">
-        <f t="shared" si="25"/>
         <v>Etiqueta Detalhe</v>
       </c>
       <c r="P114" s="53" t="s">
         <v>172</v>
       </c>
-      <c r="Q114" s="43" t="str">
-        <f t="shared" si="26"/>
-        <v>Componente de detallado 2D - Etiqueta o etiqueta textual</v>
+      <c r="Q114" s="43" t="s">
+        <v>869</v>
       </c>
       <c r="R114" s="43" t="s">
         <v>740</v>
@@ -14803,22 +15004,22 @@
         <v>9</v>
       </c>
       <c r="T114" s="43" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="35"/>
         <v>Documentais</v>
       </c>
       <c r="U114" s="43" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="24"/>
         <v>Elemento.de.Anotação</v>
       </c>
       <c r="V114" s="53" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="37"/>
         <v>Etiquetas</v>
       </c>
       <c r="W114" s="43" t="s">
         <v>80</v>
       </c>
       <c r="X114" s="54" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>Key-DOCU-114</v>
       </c>
       <c r="Y114" s="58" t="s">
@@ -14872,27 +15073,26 @@
         <v>9</v>
       </c>
       <c r="L115" s="53" t="str">
+        <f t="shared" si="19"/>
+        <v>Documentais</v>
+      </c>
+      <c r="M115" s="53" t="str">
+        <f t="shared" si="20"/>
+        <v>Elemento.de.Anotação</v>
+      </c>
+      <c r="N115" s="53" t="str">
+        <f t="shared" si="21"/>
+        <v>Etiquetas</v>
+      </c>
+      <c r="O115" s="53" t="str">
         <f t="shared" si="22"/>
-        <v>Documentais</v>
-      </c>
-      <c r="M115" s="53" t="str">
-        <f t="shared" si="23"/>
-        <v>Elemento.de.Anotação</v>
-      </c>
-      <c r="N115" s="53" t="str">
-        <f t="shared" si="24"/>
-        <v>Etiquetas</v>
-      </c>
-      <c r="O115" s="53" t="str">
-        <f t="shared" si="25"/>
         <v>Etiqueta KeyNote</v>
       </c>
       <c r="P115" s="53" t="s">
         <v>173</v>
       </c>
-      <c r="Q115" s="43" t="str">
-        <f t="shared" si="26"/>
-        <v>Notas clave - Etiqueta o etiqueta textual</v>
+      <c r="Q115" s="43" t="s">
+        <v>870</v>
       </c>
       <c r="R115" s="43" t="s">
         <v>741</v>
@@ -14901,22 +15101,22 @@
         <v>9</v>
       </c>
       <c r="T115" s="43" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="35"/>
         <v>Documentais</v>
       </c>
       <c r="U115" s="43" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="24"/>
         <v>Elemento.de.Anotação</v>
       </c>
       <c r="V115" s="53" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="37"/>
         <v>Etiquetas</v>
       </c>
       <c r="W115" s="43" t="s">
         <v>80</v>
       </c>
       <c r="X115" s="54" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>Key-DOCU-115</v>
       </c>
       <c r="Y115" s="58" t="s">
@@ -14970,27 +15170,26 @@
         <v>9</v>
       </c>
       <c r="L116" s="53" t="str">
+        <f t="shared" si="19"/>
+        <v>Documentais</v>
+      </c>
+      <c r="M116" s="53" t="str">
+        <f t="shared" si="20"/>
+        <v>Elemento.de.Anotação</v>
+      </c>
+      <c r="N116" s="53" t="str">
+        <f t="shared" si="21"/>
+        <v>Etiquetas</v>
+      </c>
+      <c r="O116" s="53" t="str">
         <f t="shared" si="22"/>
-        <v>Documentais</v>
-      </c>
-      <c r="M116" s="53" t="str">
-        <f t="shared" si="23"/>
-        <v>Elemento.de.Anotação</v>
-      </c>
-      <c r="N116" s="53" t="str">
-        <f t="shared" si="24"/>
-        <v>Etiquetas</v>
-      </c>
-      <c r="O116" s="53" t="str">
-        <f t="shared" si="25"/>
         <v>Etiqueta Grupos</v>
       </c>
       <c r="P116" s="53" t="s">
         <v>174</v>
       </c>
-      <c r="Q116" s="43" t="str">
-        <f t="shared" si="26"/>
-        <v>Grupos de plantillas - Etiqueta o etiqueta textual</v>
+      <c r="Q116" s="43" t="s">
+        <v>871</v>
       </c>
       <c r="R116" s="43" t="s">
         <v>742</v>
@@ -14999,22 +15198,22 @@
         <v>9</v>
       </c>
       <c r="T116" s="43" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="35"/>
         <v>Documentais</v>
       </c>
       <c r="U116" s="43" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="24"/>
         <v>Elemento.de.Anotação</v>
       </c>
       <c r="V116" s="53" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="37"/>
         <v>Etiquetas</v>
       </c>
       <c r="W116" s="43" t="s">
         <v>80</v>
       </c>
       <c r="X116" s="54" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>Key-DOCU-116</v>
       </c>
       <c r="Y116" s="58" t="s">
@@ -15068,27 +15267,26 @@
         <v>9</v>
       </c>
       <c r="L117" s="53" t="str">
+        <f t="shared" si="19"/>
+        <v>Documentais</v>
+      </c>
+      <c r="M117" s="53" t="str">
+        <f t="shared" si="20"/>
+        <v>Elemento.de.Anotação</v>
+      </c>
+      <c r="N117" s="53" t="str">
+        <f t="shared" si="21"/>
+        <v>Etiquetas</v>
+      </c>
+      <c r="O117" s="53" t="str">
         <f t="shared" si="22"/>
-        <v>Documentais</v>
-      </c>
-      <c r="M117" s="53" t="str">
-        <f t="shared" si="23"/>
-        <v>Elemento.de.Anotação</v>
-      </c>
-      <c r="N117" s="53" t="str">
-        <f t="shared" si="24"/>
-        <v>Etiquetas</v>
-      </c>
-      <c r="O117" s="53" t="str">
-        <f t="shared" si="25"/>
         <v>Etiqueta Categoria</v>
       </c>
       <c r="P117" s="53" t="s">
         <v>175</v>
       </c>
-      <c r="Q117" s="43" t="str">
-        <f t="shared" si="26"/>
-        <v>Etiqueta textual o etiqueta Milticategoria</v>
+      <c r="Q117" s="43" t="s">
+        <v>872</v>
       </c>
       <c r="R117" s="43" t="s">
         <v>743</v>
@@ -15097,22 +15295,22 @@
         <v>9</v>
       </c>
       <c r="T117" s="43" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="35"/>
         <v>Documentais</v>
       </c>
       <c r="U117" s="43" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="24"/>
         <v>Elemento.de.Anotação</v>
       </c>
       <c r="V117" s="53" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="37"/>
         <v>Etiquetas</v>
       </c>
       <c r="W117" s="43" t="s">
         <v>80</v>
       </c>
       <c r="X117" s="54" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>Key-DOCU-117</v>
       </c>
       <c r="Y117" s="58" t="s">
@@ -15166,27 +15364,26 @@
         <v>9</v>
       </c>
       <c r="L118" s="53" t="str">
+        <f t="shared" si="19"/>
+        <v>Documentais</v>
+      </c>
+      <c r="M118" s="53" t="str">
+        <f t="shared" si="20"/>
+        <v>Elemento.de.Anotação</v>
+      </c>
+      <c r="N118" s="53" t="str">
+        <f t="shared" si="21"/>
+        <v>Etiquetas</v>
+      </c>
+      <c r="O118" s="53" t="str">
         <f t="shared" si="22"/>
-        <v>Documentais</v>
-      </c>
-      <c r="M118" s="53" t="str">
-        <f t="shared" si="23"/>
-        <v>Elemento.de.Anotação</v>
-      </c>
-      <c r="N118" s="53" t="str">
-        <f t="shared" si="24"/>
-        <v>Etiquetas</v>
-      </c>
-      <c r="O118" s="53" t="str">
-        <f t="shared" si="25"/>
         <v>Etiqueta Múltiple</v>
       </c>
       <c r="P118" s="53" t="s">
         <v>176</v>
       </c>
-      <c r="Q118" s="43" t="e" vm="1">
-        <f t="shared" si="26"/>
-        <v>#VALUE!</v>
+      <c r="Q118" s="53" t="s">
+        <v>895</v>
       </c>
       <c r="R118" s="43" t="s">
         <v>744</v>
@@ -15195,22 +15392,22 @@
         <v>9</v>
       </c>
       <c r="T118" s="43" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="35"/>
         <v>Documentais</v>
       </c>
       <c r="U118" s="43" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="24"/>
         <v>Elemento.de.Anotação</v>
       </c>
       <c r="V118" s="53" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="37"/>
         <v>Etiquetas</v>
       </c>
       <c r="W118" s="43" t="s">
         <v>80</v>
       </c>
       <c r="X118" s="54" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>Key-DOCU-118</v>
       </c>
       <c r="Y118" s="58" t="s">
@@ -15264,27 +15461,26 @@
         <v>9</v>
       </c>
       <c r="L119" s="53" t="str">
-        <f t="shared" ref="L119:L121" si="47">CONCATENATE("", C119)</f>
+        <f t="shared" ref="L119:L121" si="43">CONCATENATE("", C119)</f>
         <v>Documentais</v>
       </c>
       <c r="M119" s="53" t="str">
-        <f t="shared" ref="M119:M121" si="48">CONCATENATE("", D119)</f>
+        <f t="shared" ref="M119:M121" si="44">CONCATENATE("", D119)</f>
         <v>Elemento.de.Anotação</v>
       </c>
       <c r="N119" s="53" t="str">
-        <f t="shared" ref="N119:N121" si="49">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E119),"."," ")," De "," de "))</f>
+        <f t="shared" ref="N119:N121" si="45">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E119),"."," ")," De "," de "))</f>
         <v>Etiquetas</v>
       </c>
       <c r="O119" s="53" t="str">
-        <f t="shared" ref="O119:O121" si="50">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",F119),"."," ")," De "," de "))</f>
+        <f t="shared" ref="O119:O121" si="46">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",F119),"."," ")," De "," de "))</f>
         <v>Etiqueta</v>
       </c>
       <c r="P119" s="53" t="s">
         <v>177</v>
       </c>
-      <c r="Q119" s="43" t="e" vm="1">
-        <f t="shared" si="26"/>
-        <v>#VALUE!</v>
+      <c r="Q119" s="43" t="s">
+        <v>894</v>
       </c>
       <c r="R119" s="43" t="s">
         <v>745</v>
@@ -15293,22 +15489,22 @@
         <v>9</v>
       </c>
       <c r="T119" s="43" t="str">
-        <f t="shared" ref="T119:T121" si="51">SUBSTITUTE(C119, "_", " ")</f>
+        <f t="shared" ref="T119:T121" si="47">SUBSTITUTE(C119, "_", " ")</f>
         <v>Documentais</v>
       </c>
       <c r="U119" s="43" t="str">
-        <f t="shared" ref="U119:U121" si="52">SUBSTITUTE(D119, "_", " ")</f>
+        <f t="shared" ref="U119:U121" si="48">SUBSTITUTE(D119, "_", " ")</f>
         <v>Elemento.de.Anotação</v>
       </c>
       <c r="V119" s="53" t="str">
-        <f t="shared" ref="V119:V121" si="53">SUBSTITUTE(E119, "_", " ")</f>
+        <f t="shared" ref="V119:V121" si="49">SUBSTITUTE(E119, "_", " ")</f>
         <v>Etiquetas</v>
       </c>
       <c r="W119" s="43" t="s">
         <v>80</v>
       </c>
       <c r="X119" s="54" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>Key-DOCU-119</v>
       </c>
       <c r="Y119" s="58" t="s">
@@ -15362,51 +15558,50 @@
         <v>9</v>
       </c>
       <c r="L120" s="53" t="str">
+        <f t="shared" si="43"/>
+        <v>Documentais</v>
+      </c>
+      <c r="M120" s="53" t="str">
+        <f t="shared" si="44"/>
+        <v>Elemento.de.Anotação</v>
+      </c>
+      <c r="N120" s="53" t="str">
+        <f t="shared" si="45"/>
+        <v>Etiquetas</v>
+      </c>
+      <c r="O120" s="53" t="str">
+        <f t="shared" si="46"/>
+        <v>Etiqueta Parede</v>
+      </c>
+      <c r="P120" s="53" t="s">
+        <v>578</v>
+      </c>
+      <c r="Q120" s="43" t="s">
+        <v>873</v>
+      </c>
+      <c r="R120" s="43" t="s">
+        <v>746</v>
+      </c>
+      <c r="S120" s="43" t="s">
+        <v>9</v>
+      </c>
+      <c r="T120" s="43" t="str">
         <f t="shared" si="47"/>
         <v>Documentais</v>
       </c>
-      <c r="M120" s="53" t="str">
+      <c r="U120" s="43" t="str">
         <f t="shared" si="48"/>
         <v>Elemento.de.Anotação</v>
       </c>
-      <c r="N120" s="53" t="str">
+      <c r="V120" s="53" t="str">
         <f t="shared" si="49"/>
         <v>Etiquetas</v>
       </c>
-      <c r="O120" s="53" t="str">
-        <f t="shared" si="50"/>
-        <v>Etiqueta Parede</v>
-      </c>
-      <c r="P120" s="53" t="s">
-        <v>578</v>
-      </c>
-      <c r="Q120" s="43" t="str">
-        <f t="shared" si="26"/>
-        <v>Etiqueta textual o etiqueta de pared</v>
-      </c>
-      <c r="R120" s="43" t="s">
-        <v>746</v>
-      </c>
-      <c r="S120" s="43" t="s">
-        <v>9</v>
-      </c>
-      <c r="T120" s="43" t="str">
-        <f t="shared" si="51"/>
-        <v>Documentais</v>
-      </c>
-      <c r="U120" s="43" t="str">
-        <f t="shared" si="52"/>
-        <v>Elemento.de.Anotação</v>
-      </c>
-      <c r="V120" s="53" t="str">
-        <f t="shared" si="53"/>
-        <v>Etiquetas</v>
-      </c>
       <c r="W120" s="43" t="s">
         <v>80</v>
       </c>
       <c r="X120" s="54" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>Key-DOCU-120</v>
       </c>
       <c r="Y120" s="58" t="s">
@@ -15460,51 +15655,50 @@
         <v>9</v>
       </c>
       <c r="L121" s="53" t="str">
+        <f t="shared" si="43"/>
+        <v>Documentais</v>
+      </c>
+      <c r="M121" s="53" t="str">
+        <f t="shared" si="44"/>
+        <v>Elemento.de.Anotação</v>
+      </c>
+      <c r="N121" s="53" t="str">
+        <f t="shared" si="45"/>
+        <v>Etiquetas</v>
+      </c>
+      <c r="O121" s="53" t="str">
+        <f t="shared" si="46"/>
+        <v>Etiqueta Porta</v>
+      </c>
+      <c r="P121" s="53" t="s">
+        <v>579</v>
+      </c>
+      <c r="Q121" s="43" t="s">
+        <v>874</v>
+      </c>
+      <c r="R121" s="43" t="s">
+        <v>747</v>
+      </c>
+      <c r="S121" s="43" t="s">
+        <v>9</v>
+      </c>
+      <c r="T121" s="43" t="str">
         <f t="shared" si="47"/>
         <v>Documentais</v>
       </c>
-      <c r="M121" s="53" t="str">
+      <c r="U121" s="43" t="str">
         <f t="shared" si="48"/>
         <v>Elemento.de.Anotação</v>
       </c>
-      <c r="N121" s="53" t="str">
+      <c r="V121" s="53" t="str">
         <f t="shared" si="49"/>
         <v>Etiquetas</v>
       </c>
-      <c r="O121" s="53" t="str">
-        <f t="shared" si="50"/>
-        <v>Etiqueta Porta</v>
-      </c>
-      <c r="P121" s="53" t="s">
-        <v>579</v>
-      </c>
-      <c r="Q121" s="43" t="str">
-        <f t="shared" si="26"/>
-        <v>Etiqueta textual o etiqueta de puerta</v>
-      </c>
-      <c r="R121" s="43" t="s">
-        <v>747</v>
-      </c>
-      <c r="S121" s="43" t="s">
-        <v>9</v>
-      </c>
-      <c r="T121" s="43" t="str">
-        <f t="shared" si="51"/>
-        <v>Documentais</v>
-      </c>
-      <c r="U121" s="43" t="str">
-        <f t="shared" si="52"/>
-        <v>Elemento.de.Anotação</v>
-      </c>
-      <c r="V121" s="53" t="str">
-        <f t="shared" si="53"/>
-        <v>Etiquetas</v>
-      </c>
       <c r="W121" s="43" t="s">
         <v>80</v>
       </c>
       <c r="X121" s="54" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>Key-DOCU-121</v>
       </c>
       <c r="Y121" s="58" t="s">
@@ -15558,27 +15752,26 @@
         <v>9</v>
       </c>
       <c r="L122" s="53" t="str">
+        <f t="shared" si="19"/>
+        <v>Documentais</v>
+      </c>
+      <c r="M122" s="53" t="str">
+        <f t="shared" si="20"/>
+        <v>Elemento.de.Anotação</v>
+      </c>
+      <c r="N122" s="53" t="str">
+        <f t="shared" si="21"/>
+        <v>Etiquetas</v>
+      </c>
+      <c r="O122" s="53" t="str">
         <f t="shared" si="22"/>
-        <v>Documentais</v>
-      </c>
-      <c r="M122" s="53" t="str">
-        <f t="shared" si="23"/>
-        <v>Elemento.de.Anotação</v>
-      </c>
-      <c r="N122" s="53" t="str">
-        <f t="shared" si="24"/>
-        <v>Etiquetas</v>
-      </c>
-      <c r="O122" s="53" t="str">
-        <f t="shared" si="25"/>
         <v>Etiqueta Janela</v>
       </c>
       <c r="P122" s="53" t="s">
         <v>580</v>
       </c>
-      <c r="Q122" s="43" t="str">
-        <f t="shared" si="26"/>
-        <v>Etiqueta textual o etiqueta de Windows</v>
+      <c r="Q122" s="43" t="s">
+        <v>875</v>
       </c>
       <c r="R122" s="43" t="s">
         <v>748</v>
@@ -15587,22 +15780,22 @@
         <v>9</v>
       </c>
       <c r="T122" s="43" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="35"/>
         <v>Documentais</v>
       </c>
       <c r="U122" s="43" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="24"/>
         <v>Elemento.de.Anotação</v>
       </c>
       <c r="V122" s="53" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="37"/>
         <v>Etiquetas</v>
       </c>
       <c r="W122" s="43" t="s">
         <v>80</v>
       </c>
       <c r="X122" s="54" t="str">
-        <f t="shared" ref="X122:X137" si="54">CONCATENATE("Key-DOCU-",A122)</f>
+        <f t="shared" ref="X122:X137" si="50">CONCATENATE("Key-DOCU-",A122)</f>
         <v>Key-DOCU-122</v>
       </c>
       <c r="Y122" s="58" t="s">
@@ -15656,27 +15849,26 @@
         <v>9</v>
       </c>
       <c r="L123" s="53" t="str">
-        <f t="shared" ref="L123" si="55">CONCATENATE("", C123)</f>
+        <f t="shared" ref="L123" si="51">CONCATENATE("", C123)</f>
         <v>Documentais</v>
       </c>
       <c r="M123" s="53" t="str">
-        <f t="shared" ref="M123" si="56">CONCATENATE("", D123)</f>
+        <f t="shared" ref="M123" si="52">CONCATENATE("", D123)</f>
         <v>Elemento.de.Legallização</v>
       </c>
       <c r="N123" s="53" t="str">
-        <f t="shared" ref="N123" si="57">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E123),"."," ")," De "," de "))</f>
+        <f t="shared" ref="N123" si="53">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E123),"."," ")," De "," de "))</f>
         <v>Licenças</v>
       </c>
       <c r="O123" s="53" t="str">
-        <f t="shared" ref="O123" si="58">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",F123),"."," ")," De "," de "))</f>
+        <f t="shared" ref="O123" si="54">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",F123),"."," ")," De "," de "))</f>
         <v>Domínio Público</v>
       </c>
       <c r="P123" s="53" t="s">
         <v>555</v>
       </c>
-      <c r="Q123" s="43" t="str">
-        <f t="shared" si="26"/>
-        <v>No se requiere licencia. El documento es de dominio público</v>
+      <c r="Q123" s="43" t="s">
+        <v>876</v>
       </c>
       <c r="R123" s="43" t="s">
         <v>749</v>
@@ -15685,22 +15877,22 @@
         <v>9</v>
       </c>
       <c r="T123" s="43" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="35"/>
         <v>Documentais</v>
       </c>
       <c r="U123" s="43" t="str">
-        <f t="shared" ref="U123" si="59">SUBSTITUTE(D123, "_", " ")</f>
+        <f t="shared" ref="U123" si="55">SUBSTITUTE(D123, "_", " ")</f>
         <v>Elemento.de.Legallização</v>
       </c>
       <c r="V123" s="53" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="37"/>
         <v>Licenças</v>
       </c>
       <c r="W123" s="43" t="s">
         <v>80</v>
       </c>
       <c r="X123" s="54" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="50"/>
         <v>Key-DOCU-123</v>
       </c>
       <c r="Y123" s="43" t="s">
@@ -15754,27 +15946,26 @@
         <v>9</v>
       </c>
       <c r="L124" s="53" t="str">
+        <f t="shared" si="19"/>
+        <v>Documentais</v>
+      </c>
+      <c r="M124" s="53" t="str">
+        <f t="shared" si="20"/>
+        <v>Elemento.de.Legallização</v>
+      </c>
+      <c r="N124" s="53" t="str">
+        <f t="shared" si="21"/>
+        <v>Licenças</v>
+      </c>
+      <c r="O124" s="53" t="str">
         <f t="shared" si="22"/>
-        <v>Documentais</v>
-      </c>
-      <c r="M124" s="53" t="str">
-        <f t="shared" si="23"/>
-        <v>Elemento.de.Legallização</v>
-      </c>
-      <c r="N124" s="53" t="str">
-        <f t="shared" si="24"/>
-        <v>Licenças</v>
-      </c>
-      <c r="O124" s="53" t="str">
-        <f t="shared" si="25"/>
         <v>CCommons</v>
       </c>
       <c r="P124" s="53" t="s">
         <v>247</v>
       </c>
-      <c r="Q124" s="43" t="str">
-        <f t="shared" si="26"/>
-        <v>Licencia Creative Commons</v>
+      <c r="Q124" s="43" t="s">
+        <v>877</v>
       </c>
       <c r="R124" s="43" t="s">
         <v>750</v>
@@ -15783,22 +15974,22 @@
         <v>9</v>
       </c>
       <c r="T124" s="43" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="35"/>
         <v>Documentais</v>
       </c>
       <c r="U124" s="43" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="24"/>
         <v>Elemento.de.Legallização</v>
       </c>
       <c r="V124" s="53" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="37"/>
         <v>Licenças</v>
       </c>
       <c r="W124" s="43" t="s">
         <v>80</v>
       </c>
       <c r="X124" s="54" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="50"/>
         <v>Key-DOCU-124</v>
       </c>
       <c r="Y124" s="43" t="s">
@@ -15852,27 +16043,26 @@
         <v>9</v>
       </c>
       <c r="L125" s="53" t="str">
+        <f t="shared" si="19"/>
+        <v>Documentais</v>
+      </c>
+      <c r="M125" s="53" t="str">
+        <f t="shared" si="20"/>
+        <v>Elemento.de.Legallização</v>
+      </c>
+      <c r="N125" s="53" t="str">
+        <f t="shared" si="21"/>
+        <v>Licenças</v>
+      </c>
+      <c r="O125" s="53" t="str">
         <f t="shared" si="22"/>
-        <v>Documentais</v>
-      </c>
-      <c r="M125" s="53" t="str">
-        <f t="shared" si="23"/>
-        <v>Elemento.de.Legallização</v>
-      </c>
-      <c r="N125" s="53" t="str">
-        <f t="shared" si="24"/>
-        <v>Licenças</v>
-      </c>
-      <c r="O125" s="53" t="str">
-        <f t="shared" si="25"/>
         <v>Direito Autoral</v>
       </c>
       <c r="P125" s="53" t="s">
         <v>245</v>
       </c>
-      <c r="Q125" s="43" t="str">
-        <f t="shared" si="26"/>
-        <v>Licencia de derechos de autor</v>
+      <c r="Q125" s="43" t="s">
+        <v>878</v>
       </c>
       <c r="R125" s="43" t="s">
         <v>751</v>
@@ -15881,22 +16071,22 @@
         <v>9</v>
       </c>
       <c r="T125" s="43" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="35"/>
         <v>Documentais</v>
       </c>
       <c r="U125" s="43" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="24"/>
         <v>Elemento.de.Legallização</v>
       </c>
       <c r="V125" s="53" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="37"/>
         <v>Licenças</v>
       </c>
       <c r="W125" s="43" t="s">
         <v>80</v>
       </c>
       <c r="X125" s="54" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="50"/>
         <v>Key-DOCU-125</v>
       </c>
       <c r="Y125" s="43" t="s">
@@ -15950,27 +16140,26 @@
         <v>9</v>
       </c>
       <c r="L126" s="53" t="str">
+        <f t="shared" si="19"/>
+        <v>Documentais</v>
+      </c>
+      <c r="M126" s="53" t="str">
+        <f t="shared" si="20"/>
+        <v>Elemento.de.Legallização</v>
+      </c>
+      <c r="N126" s="53" t="str">
+        <f t="shared" si="21"/>
+        <v>Licenças</v>
+      </c>
+      <c r="O126" s="53" t="str">
         <f t="shared" si="22"/>
-        <v>Documentais</v>
-      </c>
-      <c r="M126" s="53" t="str">
-        <f t="shared" si="23"/>
-        <v>Elemento.de.Legallização</v>
-      </c>
-      <c r="N126" s="53" t="str">
-        <f t="shared" si="24"/>
-        <v>Licenças</v>
-      </c>
-      <c r="O126" s="53" t="str">
-        <f t="shared" si="25"/>
         <v>Direito Industrial</v>
       </c>
       <c r="P126" s="53" t="s">
         <v>246</v>
       </c>
-      <c r="Q126" s="43" t="str">
-        <f t="shared" si="26"/>
-        <v>Licencia de Derecho Industrial</v>
+      <c r="Q126" s="43" t="s">
+        <v>879</v>
       </c>
       <c r="R126" s="43" t="s">
         <v>752</v>
@@ -15979,22 +16168,22 @@
         <v>9</v>
       </c>
       <c r="T126" s="43" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="35"/>
         <v>Documentais</v>
       </c>
       <c r="U126" s="43" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="24"/>
         <v>Elemento.de.Legallização</v>
       </c>
       <c r="V126" s="53" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="37"/>
         <v>Licenças</v>
       </c>
       <c r="W126" s="43" t="s">
         <v>80</v>
       </c>
       <c r="X126" s="54" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="50"/>
         <v>Key-DOCU-126</v>
       </c>
       <c r="Y126" s="43" t="s">
@@ -16048,27 +16237,26 @@
         <v>9</v>
       </c>
       <c r="L127" s="53" t="str">
+        <f t="shared" si="19"/>
+        <v>Documentais</v>
+      </c>
+      <c r="M127" s="53" t="str">
+        <f t="shared" si="20"/>
+        <v>Elemento.de.Legallização</v>
+      </c>
+      <c r="N127" s="53" t="str">
+        <f t="shared" si="21"/>
+        <v>Governança</v>
+      </c>
+      <c r="O127" s="53" t="str">
         <f t="shared" si="22"/>
-        <v>Documentais</v>
-      </c>
-      <c r="M127" s="53" t="str">
-        <f t="shared" si="23"/>
-        <v>Elemento.de.Legallização</v>
-      </c>
-      <c r="N127" s="53" t="str">
-        <f t="shared" si="24"/>
-        <v>Governança</v>
-      </c>
-      <c r="O127" s="53" t="str">
-        <f t="shared" si="25"/>
         <v>Lei</v>
       </c>
       <c r="P127" s="53" t="s">
         <v>268</v>
       </c>
-      <c r="Q127" s="43" t="str">
-        <f t="shared" si="26"/>
-        <v>Derecho publicado en Brasil</v>
+      <c r="Q127" s="43" t="s">
+        <v>880</v>
       </c>
       <c r="R127" s="43" t="s">
         <v>753</v>
@@ -16077,22 +16265,22 @@
         <v>9</v>
       </c>
       <c r="T127" s="43" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="35"/>
         <v>Documentais</v>
       </c>
       <c r="U127" s="43" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="24"/>
         <v>Elemento.de.Legallização</v>
       </c>
       <c r="V127" s="53" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="37"/>
         <v>Governança</v>
       </c>
       <c r="W127" s="43" t="s">
         <v>80</v>
       </c>
       <c r="X127" s="54" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="50"/>
         <v>Key-DOCU-127</v>
       </c>
       <c r="Y127" s="43" t="s">
@@ -16146,27 +16334,26 @@
         <v>9</v>
       </c>
       <c r="L128" s="53" t="str">
+        <f t="shared" si="19"/>
+        <v>Documentais</v>
+      </c>
+      <c r="M128" s="53" t="str">
+        <f t="shared" si="20"/>
+        <v>Elemento.de.Legallização</v>
+      </c>
+      <c r="N128" s="53" t="str">
+        <f t="shared" si="21"/>
+        <v>Governança</v>
+      </c>
+      <c r="O128" s="53" t="str">
         <f t="shared" si="22"/>
-        <v>Documentais</v>
-      </c>
-      <c r="M128" s="53" t="str">
-        <f t="shared" si="23"/>
-        <v>Elemento.de.Legallização</v>
-      </c>
-      <c r="N128" s="53" t="str">
-        <f t="shared" si="24"/>
-        <v>Governança</v>
-      </c>
-      <c r="O128" s="53" t="str">
-        <f t="shared" si="25"/>
         <v>Decreto</v>
       </c>
       <c r="P128" s="53" t="s">
         <v>269</v>
       </c>
-      <c r="Q128" s="43" t="str">
-        <f t="shared" si="26"/>
-        <v>Decreto publicado en Brasil</v>
+      <c r="Q128" s="43" t="s">
+        <v>881</v>
       </c>
       <c r="R128" s="43" t="s">
         <v>754</v>
@@ -16175,22 +16362,22 @@
         <v>9</v>
       </c>
       <c r="T128" s="43" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="35"/>
         <v>Documentais</v>
       </c>
       <c r="U128" s="43" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="24"/>
         <v>Elemento.de.Legallização</v>
       </c>
       <c r="V128" s="53" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="37"/>
         <v>Governança</v>
       </c>
       <c r="W128" s="43" t="s">
         <v>80</v>
       </c>
       <c r="X128" s="54" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="50"/>
         <v>Key-DOCU-128</v>
       </c>
       <c r="Y128" s="43" t="s">
@@ -16244,27 +16431,26 @@
         <v>9</v>
       </c>
       <c r="L129" s="53" t="str">
+        <f t="shared" si="19"/>
+        <v>Documentais</v>
+      </c>
+      <c r="M129" s="53" t="str">
+        <f t="shared" si="20"/>
+        <v>Elemento.de.Legallização</v>
+      </c>
+      <c r="N129" s="53" t="str">
+        <f t="shared" si="21"/>
+        <v>Governança</v>
+      </c>
+      <c r="O129" s="53" t="str">
         <f t="shared" si="22"/>
-        <v>Documentais</v>
-      </c>
-      <c r="M129" s="53" t="str">
-        <f t="shared" si="23"/>
-        <v>Elemento.de.Legallização</v>
-      </c>
-      <c r="N129" s="53" t="str">
-        <f t="shared" si="24"/>
-        <v>Governança</v>
-      </c>
-      <c r="O129" s="53" t="str">
-        <f t="shared" si="25"/>
         <v>Projeto de Lei</v>
       </c>
       <c r="P129" s="53" t="s">
         <v>271</v>
       </c>
-      <c r="Q129" s="43" t="str">
-        <f t="shared" si="26"/>
-        <v>Proyecto de ley en Brasil</v>
+      <c r="Q129" s="43" t="s">
+        <v>882</v>
       </c>
       <c r="R129" s="43" t="s">
         <v>755</v>
@@ -16273,22 +16459,22 @@
         <v>9</v>
       </c>
       <c r="T129" s="43" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="35"/>
         <v>Documentais</v>
       </c>
       <c r="U129" s="43" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="24"/>
         <v>Elemento.de.Legallização</v>
       </c>
       <c r="V129" s="53" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="37"/>
         <v>Governança</v>
       </c>
       <c r="W129" s="43" t="s">
         <v>80</v>
       </c>
       <c r="X129" s="54" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="50"/>
         <v>Key-DOCU-129</v>
       </c>
       <c r="Y129" s="43" t="s">
@@ -16342,27 +16528,26 @@
         <v>9</v>
       </c>
       <c r="L130" s="53" t="str">
+        <f t="shared" si="19"/>
+        <v>Documentais</v>
+      </c>
+      <c r="M130" s="53" t="str">
+        <f t="shared" si="20"/>
+        <v>Elemento.de.Publicação</v>
+      </c>
+      <c r="N130" s="53" t="str">
+        <f t="shared" si="21"/>
+        <v>Empresarial</v>
+      </c>
+      <c r="O130" s="53" t="str">
         <f t="shared" si="22"/>
-        <v>Documentais</v>
-      </c>
-      <c r="M130" s="53" t="str">
-        <f t="shared" si="23"/>
-        <v>Elemento.de.Publicação</v>
-      </c>
-      <c r="N130" s="53" t="str">
-        <f t="shared" si="24"/>
-        <v>Empresarial</v>
-      </c>
-      <c r="O130" s="53" t="str">
-        <f t="shared" si="25"/>
         <v>Guia</v>
       </c>
       <c r="P130" s="53" t="s">
         <v>280</v>
       </c>
-      <c r="Q130" s="43" t="str">
-        <f t="shared" si="26"/>
-        <v>Guía interna de procedimientos técnicos</v>
+      <c r="Q130" s="43" t="s">
+        <v>883</v>
       </c>
       <c r="R130" s="43" t="s">
         <v>756</v>
@@ -16371,22 +16556,22 @@
         <v>9</v>
       </c>
       <c r="T130" s="43" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="35"/>
         <v>Documentais</v>
       </c>
       <c r="U130" s="43" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="24"/>
         <v>Elemento.de.Publicação</v>
       </c>
       <c r="V130" s="53" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="37"/>
         <v>Empresarial</v>
       </c>
       <c r="W130" s="43" t="s">
         <v>80</v>
       </c>
       <c r="X130" s="54" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="50"/>
         <v>Key-DOCU-130</v>
       </c>
       <c r="Y130" s="43" t="s">
@@ -16440,27 +16625,26 @@
         <v>9</v>
       </c>
       <c r="L131" s="53" t="str">
+        <f t="shared" si="19"/>
+        <v>Documentais</v>
+      </c>
+      <c r="M131" s="53" t="str">
+        <f t="shared" si="20"/>
+        <v>Elemento.de.Publicação</v>
+      </c>
+      <c r="N131" s="53" t="str">
+        <f t="shared" si="21"/>
+        <v>Empresarial</v>
+      </c>
+      <c r="O131" s="53" t="str">
         <f t="shared" si="22"/>
-        <v>Documentais</v>
-      </c>
-      <c r="M131" s="53" t="str">
-        <f t="shared" si="23"/>
-        <v>Elemento.de.Publicação</v>
-      </c>
-      <c r="N131" s="53" t="str">
-        <f t="shared" si="24"/>
-        <v>Empresarial</v>
-      </c>
-      <c r="O131" s="53" t="str">
-        <f t="shared" si="25"/>
         <v>Manual</v>
       </c>
       <c r="P131" s="53" t="s">
         <v>281</v>
       </c>
-      <c r="Q131" s="43" t="str">
-        <f t="shared" si="26"/>
-        <v>Manual Interno de Procedimientos Técnicos</v>
+      <c r="Q131" s="43" t="s">
+        <v>884</v>
       </c>
       <c r="R131" s="43" t="s">
         <v>757</v>
@@ -16469,22 +16653,22 @@
         <v>9</v>
       </c>
       <c r="T131" s="43" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="35"/>
         <v>Documentais</v>
       </c>
       <c r="U131" s="43" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="24"/>
         <v>Elemento.de.Publicação</v>
       </c>
       <c r="V131" s="53" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="37"/>
         <v>Empresarial</v>
       </c>
       <c r="W131" s="43" t="s">
         <v>80</v>
       </c>
       <c r="X131" s="54" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="50"/>
         <v>Key-DOCU-131</v>
       </c>
       <c r="Y131" s="43" t="s">
@@ -16538,27 +16722,26 @@
         <v>9</v>
       </c>
       <c r="L132" s="53" t="str">
+        <f t="shared" si="19"/>
+        <v>Documentais</v>
+      </c>
+      <c r="M132" s="53" t="str">
+        <f t="shared" si="20"/>
+        <v>Elemento.de.Publicação</v>
+      </c>
+      <c r="N132" s="53" t="str">
+        <f t="shared" si="21"/>
+        <v>Empresarial</v>
+      </c>
+      <c r="O132" s="53" t="str">
         <f t="shared" si="22"/>
-        <v>Documentais</v>
-      </c>
-      <c r="M132" s="53" t="str">
-        <f t="shared" si="23"/>
-        <v>Elemento.de.Publicação</v>
-      </c>
-      <c r="N132" s="53" t="str">
-        <f t="shared" si="24"/>
-        <v>Empresarial</v>
-      </c>
-      <c r="O132" s="53" t="str">
-        <f t="shared" si="25"/>
         <v>Livro</v>
       </c>
       <c r="P132" s="53" t="s">
         <v>282</v>
       </c>
-      <c r="Q132" s="43" t="str">
-        <f t="shared" si="26"/>
-        <v>Libro técnico</v>
+      <c r="Q132" s="43" t="s">
+        <v>885</v>
       </c>
       <c r="R132" s="43" t="s">
         <v>758</v>
@@ -16567,22 +16750,22 @@
         <v>9</v>
       </c>
       <c r="T132" s="43" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="35"/>
         <v>Documentais</v>
       </c>
       <c r="U132" s="43" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="24"/>
         <v>Elemento.de.Publicação</v>
       </c>
       <c r="V132" s="53" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="37"/>
         <v>Empresarial</v>
       </c>
       <c r="W132" s="43" t="s">
         <v>80</v>
       </c>
       <c r="X132" s="54" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="50"/>
         <v>Key-DOCU-132</v>
       </c>
       <c r="Y132" s="43" t="s">
@@ -16636,27 +16819,26 @@
         <v>9</v>
       </c>
       <c r="L133" s="53" t="str">
+        <f t="shared" si="19"/>
+        <v>Documentais</v>
+      </c>
+      <c r="M133" s="53" t="str">
+        <f t="shared" si="20"/>
+        <v>Elemento.de.Publicação</v>
+      </c>
+      <c r="N133" s="53" t="str">
+        <f t="shared" si="21"/>
+        <v>Empresarial</v>
+      </c>
+      <c r="O133" s="53" t="str">
         <f t="shared" si="22"/>
-        <v>Documentais</v>
-      </c>
-      <c r="M133" s="53" t="str">
-        <f t="shared" si="23"/>
-        <v>Elemento.de.Publicação</v>
-      </c>
-      <c r="N133" s="53" t="str">
-        <f t="shared" si="24"/>
-        <v>Empresarial</v>
-      </c>
-      <c r="O133" s="53" t="str">
-        <f t="shared" si="25"/>
         <v>Treinamento</v>
       </c>
       <c r="P133" s="53" t="s">
         <v>283</v>
       </c>
-      <c r="Q133" s="43" t="str">
-        <f t="shared" si="26"/>
-        <v>Formación</v>
+      <c r="Q133" s="43" t="s">
+        <v>886</v>
       </c>
       <c r="R133" s="43" t="s">
         <v>759</v>
@@ -16665,22 +16847,22 @@
         <v>9</v>
       </c>
       <c r="T133" s="43" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="35"/>
         <v>Documentais</v>
       </c>
       <c r="U133" s="43" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="24"/>
         <v>Elemento.de.Publicação</v>
       </c>
       <c r="V133" s="53" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="37"/>
         <v>Empresarial</v>
       </c>
       <c r="W133" s="43" t="s">
         <v>80</v>
       </c>
       <c r="X133" s="54" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="50"/>
         <v>Key-DOCU-133</v>
       </c>
       <c r="Y133" s="43" t="s">
@@ -16734,27 +16916,26 @@
         <v>9</v>
       </c>
       <c r="L134" s="53" t="str">
+        <f t="shared" si="19"/>
+        <v>Documentais</v>
+      </c>
+      <c r="M134" s="53" t="str">
+        <f t="shared" si="20"/>
+        <v>Elemento.de.Publicação</v>
+      </c>
+      <c r="N134" s="53" t="str">
+        <f t="shared" si="21"/>
+        <v>Empresarial</v>
+      </c>
+      <c r="O134" s="53" t="str">
         <f t="shared" si="22"/>
-        <v>Documentais</v>
-      </c>
-      <c r="M134" s="53" t="str">
-        <f t="shared" si="23"/>
-        <v>Elemento.de.Publicação</v>
-      </c>
-      <c r="N134" s="53" t="str">
-        <f t="shared" si="24"/>
-        <v>Empresarial</v>
-      </c>
-      <c r="O134" s="53" t="str">
-        <f t="shared" si="25"/>
         <v>Normativa</v>
       </c>
       <c r="P134" s="53" t="s">
         <v>278</v>
       </c>
-      <c r="Q134" s="43" t="str">
-        <f t="shared" si="26"/>
-        <v>Normativo</v>
+      <c r="Q134" s="43" t="s">
+        <v>887</v>
       </c>
       <c r="R134" s="43" t="s">
         <v>760</v>
@@ -16763,22 +16944,22 @@
         <v>9</v>
       </c>
       <c r="T134" s="43" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="35"/>
         <v>Documentais</v>
       </c>
       <c r="U134" s="43" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="24"/>
         <v>Elemento.de.Publicação</v>
       </c>
       <c r="V134" s="53" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="37"/>
         <v>Empresarial</v>
       </c>
       <c r="W134" s="43" t="s">
         <v>80</v>
       </c>
       <c r="X134" s="54" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="50"/>
         <v>Key-DOCU-134</v>
       </c>
       <c r="Y134" s="43" t="s">
@@ -16832,27 +17013,26 @@
         <v>9</v>
       </c>
       <c r="L135" s="53" t="str">
-        <f t="shared" ref="L135:L137" si="60">CONCATENATE("", C135)</f>
+        <f t="shared" ref="L135:L137" si="56">CONCATENATE("", C135)</f>
         <v>Documentais</v>
       </c>
       <c r="M135" s="53" t="str">
-        <f t="shared" ref="M135:M137" si="61">CONCATENATE("", D135)</f>
+        <f t="shared" ref="M135:M137" si="57">CONCATENATE("", D135)</f>
         <v>Elemento.de.Publicação</v>
       </c>
       <c r="N135" s="53" t="str">
-        <f t="shared" ref="N135:N137" si="62">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E135),"."," ")," De "," de "))</f>
+        <f t="shared" ref="N135:N137" si="58">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E135),"."," ")," De "," de "))</f>
         <v>Empresarial</v>
       </c>
       <c r="O135" s="53" t="str">
-        <f t="shared" ref="O135:O137" si="63">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",F135),"."," ")," De "," de "))</f>
+        <f t="shared" ref="O135:O137" si="59">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",F135),"."," ")," De "," de "))</f>
         <v>Apresentação</v>
       </c>
       <c r="P135" s="53" t="s">
         <v>285</v>
       </c>
-      <c r="Q135" s="43" t="str">
-        <f t="shared" si="26"/>
-        <v>Presentaciones de PowerPoint o similares</v>
+      <c r="Q135" s="43" t="s">
+        <v>888</v>
       </c>
       <c r="R135" s="43" t="s">
         <v>761</v>
@@ -16861,22 +17041,22 @@
         <v>9</v>
       </c>
       <c r="T135" s="43" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="35"/>
         <v>Documentais</v>
       </c>
       <c r="U135" s="43" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="24"/>
         <v>Elemento.de.Publicação</v>
       </c>
       <c r="V135" s="53" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="37"/>
         <v>Empresarial</v>
       </c>
       <c r="W135" s="43" t="s">
         <v>80</v>
       </c>
       <c r="X135" s="54" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="50"/>
         <v>Key-DOCU-135</v>
       </c>
       <c r="Y135" s="43" t="s">
@@ -16930,27 +17110,26 @@
         <v>9</v>
       </c>
       <c r="L136" s="53" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="56"/>
         <v>Documentais</v>
       </c>
       <c r="M136" s="53" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="57"/>
         <v>Elemento.de.Publicação</v>
       </c>
       <c r="N136" s="53" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="58"/>
         <v>Empresarial</v>
       </c>
       <c r="O136" s="53" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="59"/>
         <v>Fichário</v>
       </c>
       <c r="P136" s="53" t="s">
         <v>289</v>
       </c>
-      <c r="Q136" s="43" t="str">
-        <f t="shared" si="26"/>
-        <v>Carpetas internas</v>
+      <c r="Q136" s="43" t="s">
+        <v>889</v>
       </c>
       <c r="R136" s="43" t="s">
         <v>762</v>
@@ -16959,22 +17138,22 @@
         <v>9</v>
       </c>
       <c r="T136" s="43" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="35"/>
         <v>Documentais</v>
       </c>
       <c r="U136" s="43" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="24"/>
         <v>Elemento.de.Publicação</v>
       </c>
       <c r="V136" s="53" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="37"/>
         <v>Empresarial</v>
       </c>
       <c r="W136" s="43" t="s">
         <v>80</v>
       </c>
       <c r="X136" s="54" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="50"/>
         <v>Key-DOCU-136</v>
       </c>
       <c r="Y136" s="43" t="s">
@@ -17028,27 +17207,26 @@
         <v>9</v>
       </c>
       <c r="L137" s="53" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="56"/>
         <v>Documentais</v>
       </c>
       <c r="M137" s="53" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="57"/>
         <v>Elemento.de.Publicação</v>
       </c>
       <c r="N137" s="53" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="58"/>
         <v>Empresarial</v>
       </c>
       <c r="O137" s="53" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="59"/>
         <v>Formulário</v>
       </c>
       <c r="P137" s="53" t="s">
         <v>290</v>
       </c>
-      <c r="Q137" s="43" t="str">
-        <f t="shared" ref="Q137" si="64">_xlfn.TRANSLATE(P137,"pt","es")</f>
-        <v>Formas internas</v>
+      <c r="Q137" s="43" t="s">
+        <v>890</v>
       </c>
       <c r="R137" s="43" t="s">
         <v>763</v>
@@ -17057,22 +17235,22 @@
         <v>9</v>
       </c>
       <c r="T137" s="43" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="35"/>
         <v>Documentais</v>
       </c>
       <c r="U137" s="43" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="24"/>
         <v>Elemento.de.Publicação</v>
       </c>
       <c r="V137" s="53" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="37"/>
         <v>Empresarial</v>
       </c>
       <c r="W137" s="43" t="s">
         <v>80</v>
       </c>
       <c r="X137" s="54" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="50"/>
         <v>Key-DOCU-137</v>
       </c>
       <c r="Y137" s="43" t="s">
@@ -17095,23 +17273,23 @@
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A8:AC138">
     <sortCondition ref="A1:A138"/>
   </sortState>
-  <conditionalFormatting sqref="F1">
-    <cfRule type="duplicateValues" dxfId="9" priority="33"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="34"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="35"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="36"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="37"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F1:F1048576">
-    <cfRule type="duplicateValues" dxfId="4" priority="9"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G1:O1">
-    <cfRule type="cellIs" dxfId="3" priority="27" operator="equal">
+  <conditionalFormatting sqref="A2:B137">
+    <cfRule type="cellIs" dxfId="9" priority="7" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:B137">
-    <cfRule type="cellIs" dxfId="2" priority="7" operator="equal">
+  <conditionalFormatting sqref="F1">
+    <cfRule type="duplicateValues" dxfId="8" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="37"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F1:F1048576">
+    <cfRule type="duplicateValues" dxfId="3" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G1:O1">
+    <cfRule type="cellIs" dxfId="2" priority="27" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17122,7 +17300,7 @@
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <ignoredErrors>
-    <ignoredError sqref="AC1 AC138:AC1048576 B36:D61 B95:D95 AD1:XFD1048576 F95:Q95 B96:Q117 F36:Q61 B62:Q94 B3:Q11 A138:Q1048576 A1:Q2 AA8:AA122 S1:X1 S8:Y122 S2:X2 S3:X7 AA138:AA1048576 S138:Y1048576 S123:X123 S124:X137 B120:Q137 B119:P119 B118:P118 B13:Q21 B12:P12 B23:Q35 B22:P22" numberStoredAsText="1"/>
+    <ignoredError sqref="AC1 AC138:AC1048576 B36:D61 B95:D95 AD1:XFD1048576 F95:P95 B96:P117 F36:P61 B62:P94 B3:P11 A138:P1048576 A1:P2 AA8:AA122 S1:X1 S8:Y122 S2:X2 S3:X7 AA138:AA1048576 S138:Y1048576 S123:X123 S124:X137 B120:P137 B119:P119 B118:P118 B13:P21 B12:P12 B23:P35 B22:P22" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Versão5/PRO/Ontologia_Documentos.xlsx
+++ b/Versão5/PRO/Ontologia_Documentos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\PRO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E0526A9-F4AD-4F3A-A469-AB8707D6EF4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86524CD3-531E-48FE-A04E-B45EAB2B1CB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="527" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="527" activeTab="4" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="31" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3604" uniqueCount="900">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4391" uniqueCount="930">
   <si>
     <t>Edição</t>
   </si>
@@ -2375,9 +2375,6 @@
     <t>Classe IFC</t>
   </si>
   <si>
-    <t>[ - ]</t>
-  </si>
-  <si>
     <t>Categoria Rvt</t>
   </si>
   <si>
@@ -2772,6 +2769,99 @@
   </si>
   <si>
     <t>Dimensión de referencia débil</t>
+  </si>
+  <si>
+    <t>Projeto</t>
+  </si>
+  <si>
+    <t>De.API</t>
+  </si>
+  <si>
+    <t>Métodos</t>
+  </si>
+  <si>
+    <t>Macros</t>
+  </si>
+  <si>
+    <t>API.Revit</t>
+  </si>
+  <si>
+    <t>Aplicação Revit</t>
+  </si>
+  <si>
+    <t>Aplicativo Revit</t>
+  </si>
+  <si>
+    <t>Revit Aplication</t>
+  </si>
+  <si>
+    <t>API_Ambiente</t>
+  </si>
+  <si>
+    <t>tema</t>
+  </si>
+  <si>
+    <t>"API"</t>
+  </si>
+  <si>
+    <t>subtema</t>
+  </si>
+  <si>
+    <t>"Elementos Ambientes"</t>
+  </si>
+  <si>
+    <t>"Individuo indicador de método API para selecionar ambientes do projeto"</t>
+  </si>
+  <si>
+    <t>"[ Ambientes ]"</t>
+  </si>
+  <si>
+    <t>API_Andar</t>
+  </si>
+  <si>
+    <t>"Elementos Andares"</t>
+  </si>
+  <si>
+    <t>"Individuo indicador de método API para selecionar andares do projeto"</t>
+  </si>
+  <si>
+    <t>"[ Pavimentos ]"</t>
+  </si>
+  <si>
+    <t>API_Instância</t>
+  </si>
+  <si>
+    <t>"Elementos Instanciados"</t>
+  </si>
+  <si>
+    <t>"Individuo indicador de método API para selecionar instâncias do projeto"</t>
+  </si>
+  <si>
+    <t>"[ Elementos ]"</t>
+  </si>
+  <si>
+    <t>API_Simbolo</t>
+  </si>
+  <si>
+    <t>"Elementos Tipificados"</t>
+  </si>
+  <si>
+    <t>"Individuo indicador de método API para selecionar elementos tipificados do projeto"</t>
+  </si>
+  <si>
+    <t>"[ Tipos ]"</t>
+  </si>
+  <si>
+    <t>API_Material</t>
+  </si>
+  <si>
+    <t>"Elementos Materiais"</t>
+  </si>
+  <si>
+    <t>"Individuo indicador de método API para selecionar materiais do projeto"</t>
+  </si>
+  <si>
+    <t>"[ Materiais ]"</t>
   </si>
 </sst>
 </file>
@@ -2862,7 +2952,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="26">
+  <fills count="31">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3013,6 +3103,36 @@
         <bgColor rgb="FFD9F2D0"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor rgb="FFFEF2CB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF99FF"/>
+        <bgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor rgb="FFFEF2CB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="5">
     <border>
@@ -3078,7 +3198,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -3259,11 +3379,246 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="34">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3289,6 +3644,16 @@
         <strike val="0"/>
         <color rgb="FFFFFFFF"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -3675,15 +4040,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1124724F-B8C4-4B86-9028-743FC73CDDB0}">
   <dimension ref="A1:C24"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="10.5" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="10.3828125" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="53.69140625" style="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="3.3828125" style="42" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.15234375" style="13"/>
+    <col min="1" max="1" width="10.42578125" style="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="53.7109375" style="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3.42578125" style="42" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.140625" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="10" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" s="10" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -3694,7 +4059,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="2" t="s">
         <v>17</v>
       </c>
@@ -3705,7 +4070,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="2" t="s">
         <v>18</v>
       </c>
@@ -3716,7 +4081,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
@@ -3727,7 +4092,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
@@ -3739,7 +4104,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="2" t="s">
         <v>8</v>
       </c>
@@ -3751,7 +4116,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="2" t="s">
         <v>4</v>
       </c>
@@ -3762,7 +4127,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="8" spans="1:3" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>5</v>
       </c>
@@ -3773,7 +4138,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="2" t="s">
         <v>20</v>
       </c>
@@ -3784,7 +4149,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="2" t="s">
         <v>22</v>
       </c>
@@ -3795,7 +4160,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="2" t="s">
         <v>0</v>
       </c>
@@ -3806,7 +4171,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="2" t="s">
         <v>1</v>
       </c>
@@ -3817,7 +4182,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="2" t="s">
         <v>23</v>
       </c>
@@ -3828,7 +4193,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="2" t="s">
         <v>24</v>
       </c>
@@ -3839,7 +4204,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="2" t="s">
         <v>25</v>
       </c>
@@ -3850,7 +4215,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="2" t="s">
         <v>26</v>
       </c>
@@ -3861,7 +4226,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="2" t="s">
         <v>10</v>
       </c>
@@ -3872,19 +4237,19 @@
         <v>304</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B18" s="5">
         <f ca="1">NOW()</f>
-        <v>46253.802874305555</v>
+        <v>46259.689483680559</v>
       </c>
       <c r="C18" s="41" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="2" t="s">
         <v>28</v>
       </c>
@@ -3895,7 +4260,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="2" t="s">
         <v>29</v>
       </c>
@@ -3906,7 +4271,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="2" t="s">
         <v>11</v>
       </c>
@@ -3917,7 +4282,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="4" t="s">
         <v>34</v>
       </c>
@@ -3928,7 +4293,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="4" t="s">
         <v>35</v>
       </c>
@@ -3939,7 +4304,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="24" spans="1:3" s="39" customFormat="1" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:3" s="39" customFormat="1" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>302</v>
       </c>
@@ -3958,37 +4323,38 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19BE914A-3965-4A61-9195-D2681A91581F}">
-  <dimension ref="A1:AC137"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6" customHeight="1" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:AC138"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="1.921875" style="61" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.23046875" style="44" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.3828125" style="44" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.3828125" style="44" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.921875" style="44" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.61328125" style="44" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="6.4609375" style="44" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="5.3828125" style="44" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.3828125" style="44" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.140625" style="61" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.28515625" style="44" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.42578125" style="44" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.42578125" style="44" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.85546875" style="44" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5703125" style="44" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="6.42578125" style="44" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.42578125" style="44" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.42578125" style="44" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12" style="44" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.921875" style="44" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="39.15234375" style="44" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="42.69140625" style="44" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="33.23046875" style="44" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="3.69140625" style="44" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="5.3828125" style="44" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="12.3828125" style="44" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="11.921875" style="44" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="4.921875" style="44" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="6.53515625" style="44" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="17.3828125" style="44" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="12.3828125" style="44" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="6.23046875" style="44" customWidth="1"/>
-    <col min="29" max="29" width="4.3828125" style="44" customWidth="1"/>
-    <col min="30" max="16384" width="9.15234375" style="44"/>
+    <col min="15" max="15" width="13.85546875" style="44" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="39.140625" style="44" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="42.7109375" style="44" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="33.28515625" style="44" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="3.7109375" style="44" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.42578125" style="44" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12.42578125" style="44" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.85546875" style="44" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="8.5703125" style="44" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="6.5703125" style="44" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="21.5703125" style="44" customWidth="1"/>
+    <col min="26" max="26" width="13.5703125" style="44" customWidth="1"/>
+    <col min="27" max="27" width="16.140625" style="44" customWidth="1"/>
+    <col min="28" max="28" width="6.28515625" style="44" customWidth="1"/>
+    <col min="29" max="29" width="4.28515625" style="44" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="44"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="39.549999999999997" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:29" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="60" t="s">
         <v>36</v>
       </c>
@@ -4062,7 +4428,7 @@
         <v>60</v>
       </c>
       <c r="Y1" s="49" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="Z1" s="49" t="s">
         <v>765</v>
@@ -4077,7 +4443,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="2" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="45">
         <v>2</v>
       </c>
@@ -4131,7 +4497,7 @@
         <v>591</v>
       </c>
       <c r="Q2" s="43" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="R2" s="43" t="s">
         <v>632</v>
@@ -4158,23 +4524,23 @@
         <f t="shared" ref="X2:X57" si="5">CONCATENATE("Key-DOCU-",A2)</f>
         <v>Key-DOCU-2</v>
       </c>
-      <c r="Y2" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="Z2" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AA2" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AB2" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC2" s="43" t="s">
-        <v>767</v>
+      <c r="Y2" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z2" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA2" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB2" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC2" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="45">
         <v>3</v>
       </c>
@@ -4228,7 +4594,7 @@
         <v>592</v>
       </c>
       <c r="Q3" s="43" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="R3" s="43" t="s">
         <v>633</v>
@@ -4255,23 +4621,23 @@
         <f t="shared" si="5"/>
         <v>Key-DOCU-3</v>
       </c>
-      <c r="Y3" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="Z3" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AA3" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AB3" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC3" s="43" t="s">
-        <v>767</v>
+      <c r="Y3" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z3" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA3" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB3" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC3" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="45">
         <v>4</v>
       </c>
@@ -4325,7 +4691,7 @@
         <v>593</v>
       </c>
       <c r="Q4" s="43" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="R4" s="43" t="s">
         <v>634</v>
@@ -4352,23 +4718,23 @@
         <f t="shared" si="5"/>
         <v>Key-DOCU-4</v>
       </c>
-      <c r="Y4" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="Z4" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AA4" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AB4" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC4" s="43" t="s">
-        <v>767</v>
+      <c r="Y4" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z4" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA4" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB4" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC4" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="45">
         <v>5</v>
       </c>
@@ -4422,7 +4788,7 @@
         <v>587</v>
       </c>
       <c r="Q5" s="43" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="R5" s="43" t="s">
         <v>635</v>
@@ -4449,23 +4815,23 @@
         <f t="shared" si="5"/>
         <v>Key-DOCU-5</v>
       </c>
-      <c r="Y5" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="Z5" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AA5" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AB5" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC5" s="43" t="s">
-        <v>767</v>
+      <c r="Y5" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z5" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA5" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB5" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC5" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="45">
         <v>6</v>
       </c>
@@ -4519,7 +4885,7 @@
         <v>590</v>
       </c>
       <c r="Q6" s="43" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="R6" s="43" t="s">
         <v>636</v>
@@ -4546,23 +4912,23 @@
         <f t="shared" si="5"/>
         <v>Key-DOCU-6</v>
       </c>
-      <c r="Y6" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="Z6" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AA6" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AB6" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC6" s="43" t="s">
-        <v>767</v>
+      <c r="Y6" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z6" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA6" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB6" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC6" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="45">
         <v>7</v>
       </c>
@@ -4643,23 +5009,23 @@
         <f t="shared" si="5"/>
         <v>Key-DOCU-7</v>
       </c>
-      <c r="Y7" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="Z7" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AA7" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AB7" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC7" s="43" t="s">
-        <v>767</v>
+      <c r="Y7" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z7" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA7" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB7" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC7" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="45">
         <v>8</v>
       </c>
@@ -4713,7 +5079,7 @@
         <v>83</v>
       </c>
       <c r="Q8" s="43" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="R8" s="43" t="s">
         <v>638</v>
@@ -4749,14 +5115,14 @@
       <c r="AA8" s="59" t="s">
         <v>413</v>
       </c>
-      <c r="AB8" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC8" s="43" t="s">
-        <v>767</v>
+      <c r="AB8" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC8" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="45">
         <v>9</v>
       </c>
@@ -4810,7 +5176,7 @@
         <v>84</v>
       </c>
       <c r="Q9" s="43" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="R9" s="43" t="s">
         <v>639</v>
@@ -4846,14 +5212,14 @@
       <c r="AA9" s="59" t="s">
         <v>413</v>
       </c>
-      <c r="AB9" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC9" s="43" t="s">
-        <v>767</v>
+      <c r="AB9" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC9" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="45">
         <v>10</v>
       </c>
@@ -4907,7 +5273,7 @@
         <v>85</v>
       </c>
       <c r="Q10" s="43" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="R10" s="43" t="s">
         <v>640</v>
@@ -4943,14 +5309,14 @@
       <c r="AA10" s="59" t="s">
         <v>413</v>
       </c>
-      <c r="AB10" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC10" s="43" t="s">
-        <v>767</v>
+      <c r="AB10" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC10" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="45">
         <v>11</v>
       </c>
@@ -5004,7 +5370,7 @@
         <v>86</v>
       </c>
       <c r="Q11" s="43" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="R11" s="43" t="s">
         <v>641</v>
@@ -5040,14 +5406,14 @@
       <c r="AA11" s="59" t="s">
         <v>416</v>
       </c>
-      <c r="AB11" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC11" s="43" t="s">
-        <v>767</v>
+      <c r="AB11" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC11" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="45">
         <v>12</v>
       </c>
@@ -5101,7 +5467,7 @@
         <v>87</v>
       </c>
       <c r="Q12" s="53" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="R12" s="43" t="s">
         <v>642</v>
@@ -5137,14 +5503,14 @@
       <c r="AA12" s="59" t="s">
         <v>413</v>
       </c>
-      <c r="AB12" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC12" s="43" t="s">
-        <v>767</v>
+      <c r="AB12" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC12" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="45">
         <v>13</v>
       </c>
@@ -5198,7 +5564,7 @@
         <v>88</v>
       </c>
       <c r="Q13" s="43" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="R13" s="43" t="s">
         <v>643</v>
@@ -5234,14 +5600,14 @@
       <c r="AA13" s="59" t="s">
         <v>413</v>
       </c>
-      <c r="AB13" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC13" s="43" t="s">
-        <v>767</v>
+      <c r="AB13" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC13" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="45">
         <v>14</v>
       </c>
@@ -5295,7 +5661,7 @@
         <v>94</v>
       </c>
       <c r="Q14" s="43" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="R14" s="43" t="s">
         <v>644</v>
@@ -5331,14 +5697,14 @@
       <c r="AA14" s="59" t="s">
         <v>413</v>
       </c>
-      <c r="AB14" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC14" s="43" t="s">
-        <v>767</v>
+      <c r="AB14" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC14" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="45">
         <v>15</v>
       </c>
@@ -5392,7 +5758,7 @@
         <v>90</v>
       </c>
       <c r="Q15" s="43" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="R15" s="43" t="s">
         <v>645</v>
@@ -5428,14 +5794,14 @@
       <c r="AA15" s="59" t="s">
         <v>413</v>
       </c>
-      <c r="AB15" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC15" s="43" t="s">
-        <v>767</v>
+      <c r="AB15" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC15" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="45">
         <v>16</v>
       </c>
@@ -5489,7 +5855,7 @@
         <v>91</v>
       </c>
       <c r="Q16" s="43" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="R16" s="43" t="s">
         <v>646</v>
@@ -5525,14 +5891,14 @@
       <c r="AA16" s="59" t="s">
         <v>413</v>
       </c>
-      <c r="AB16" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC16" s="43" t="s">
-        <v>767</v>
+      <c r="AB16" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC16" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="45">
         <v>17</v>
       </c>
@@ -5586,7 +5952,7 @@
         <v>89</v>
       </c>
       <c r="Q17" s="43" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="R17" s="43" t="s">
         <v>647</v>
@@ -5622,14 +5988,14 @@
       <c r="AA17" s="59" t="s">
         <v>413</v>
       </c>
-      <c r="AB17" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC17" s="43" t="s">
-        <v>767</v>
+      <c r="AB17" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC17" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="45">
         <v>18</v>
       </c>
@@ -5683,7 +6049,7 @@
         <v>92</v>
       </c>
       <c r="Q18" s="43" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="R18" s="43" t="s">
         <v>648</v>
@@ -5719,14 +6085,14 @@
       <c r="AA18" s="59" t="s">
         <v>413</v>
       </c>
-      <c r="AB18" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC18" s="43" t="s">
-        <v>767</v>
+      <c r="AB18" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC18" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="45">
         <v>19</v>
       </c>
@@ -5780,7 +6146,7 @@
         <v>93</v>
       </c>
       <c r="Q19" s="43" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="R19" s="43" t="s">
         <v>649</v>
@@ -5816,14 +6182,14 @@
       <c r="AA19" s="59" t="s">
         <v>413</v>
       </c>
-      <c r="AB19" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC19" s="43" t="s">
-        <v>767</v>
+      <c r="AB19" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC19" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="45">
         <v>20</v>
       </c>
@@ -5877,7 +6243,7 @@
         <v>558</v>
       </c>
       <c r="Q20" s="43" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="R20" s="43" t="s">
         <v>650</v>
@@ -5913,14 +6279,14 @@
       <c r="AA20" s="59" t="s">
         <v>413</v>
       </c>
-      <c r="AB20" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC20" s="43" t="s">
-        <v>767</v>
+      <c r="AB20" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC20" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="45">
         <v>21</v>
       </c>
@@ -5974,7 +6340,7 @@
         <v>559</v>
       </c>
       <c r="Q21" s="43" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="R21" s="43" t="s">
         <v>651</v>
@@ -6010,14 +6376,14 @@
       <c r="AA21" s="59" t="s">
         <v>413</v>
       </c>
-      <c r="AB21" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC21" s="43" t="s">
-        <v>767</v>
+      <c r="AB21" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC21" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="45">
         <v>22</v>
       </c>
@@ -6071,7 +6437,7 @@
         <v>95</v>
       </c>
       <c r="Q22" s="53" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="R22" s="43" t="s">
         <v>652</v>
@@ -6107,14 +6473,14 @@
       <c r="AA22" s="59" t="s">
         <v>413</v>
       </c>
-      <c r="AB22" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC22" s="43" t="s">
-        <v>767</v>
+      <c r="AB22" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC22" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="45">
         <v>23</v>
       </c>
@@ -6168,7 +6534,7 @@
         <v>96</v>
       </c>
       <c r="Q23" s="43" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="R23" s="43" t="s">
         <v>653</v>
@@ -6204,14 +6570,14 @@
       <c r="AA23" s="59" t="s">
         <v>413</v>
       </c>
-      <c r="AB23" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC23" s="43" t="s">
-        <v>767</v>
+      <c r="AB23" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC23" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="45">
         <v>24</v>
       </c>
@@ -6265,7 +6631,7 @@
         <v>560</v>
       </c>
       <c r="Q24" s="43" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="R24" s="43" t="s">
         <v>654</v>
@@ -6301,14 +6667,14 @@
       <c r="AA24" s="59" t="s">
         <v>413</v>
       </c>
-      <c r="AB24" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC24" s="43" t="s">
-        <v>767</v>
+      <c r="AB24" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC24" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="45">
         <v>25</v>
       </c>
@@ -6362,7 +6728,7 @@
         <v>97</v>
       </c>
       <c r="Q25" s="43" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="R25" s="43" t="s">
         <v>655</v>
@@ -6398,14 +6764,14 @@
       <c r="AA25" s="59" t="s">
         <v>413</v>
       </c>
-      <c r="AB25" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC25" s="43" t="s">
-        <v>767</v>
+      <c r="AB25" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC25" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="45">
         <v>26</v>
       </c>
@@ -6459,7 +6825,7 @@
         <v>98</v>
       </c>
       <c r="Q26" s="43" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="R26" s="43" t="s">
         <v>656</v>
@@ -6495,14 +6861,14 @@
       <c r="AA26" s="59" t="s">
         <v>413</v>
       </c>
-      <c r="AB26" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC26" s="43" t="s">
-        <v>767</v>
+      <c r="AB26" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC26" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="45">
         <v>27</v>
       </c>
@@ -6556,7 +6922,7 @@
         <v>99</v>
       </c>
       <c r="Q27" s="43" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="R27" s="43" t="s">
         <v>657</v>
@@ -6592,14 +6958,14 @@
       <c r="AA27" s="59" t="s">
         <v>417</v>
       </c>
-      <c r="AB27" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC27" s="43" t="s">
-        <v>767</v>
+      <c r="AB27" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC27" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="45">
         <v>28</v>
       </c>
@@ -6653,7 +7019,7 @@
         <v>100</v>
       </c>
       <c r="Q28" s="43" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="R28" s="43" t="s">
         <v>658</v>
@@ -6689,14 +7055,14 @@
       <c r="AA28" s="59" t="s">
         <v>417</v>
       </c>
-      <c r="AB28" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC28" s="43" t="s">
-        <v>767</v>
+      <c r="AB28" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC28" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="45">
         <v>29</v>
       </c>
@@ -6750,7 +7116,7 @@
         <v>561</v>
       </c>
       <c r="Q29" s="43" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="R29" s="43" t="s">
         <v>659</v>
@@ -6786,14 +7152,14 @@
       <c r="AA29" s="59" t="s">
         <v>417</v>
       </c>
-      <c r="AB29" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC29" s="43" t="s">
-        <v>767</v>
+      <c r="AB29" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC29" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="30" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="45">
         <v>30</v>
       </c>
@@ -6847,7 +7213,7 @@
         <v>562</v>
       </c>
       <c r="Q30" s="43" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="R30" s="43" t="s">
         <v>660</v>
@@ -6883,14 +7249,14 @@
       <c r="AA30" s="59" t="s">
         <v>417</v>
       </c>
-      <c r="AB30" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC30" s="43" t="s">
-        <v>767</v>
+      <c r="AB30" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC30" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="45">
         <v>31</v>
       </c>
@@ -6944,7 +7310,7 @@
         <v>563</v>
       </c>
       <c r="Q31" s="43" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="R31" s="43" t="s">
         <v>661</v>
@@ -6980,14 +7346,14 @@
       <c r="AA31" s="59" t="s">
         <v>417</v>
       </c>
-      <c r="AB31" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC31" s="43" t="s">
-        <v>767</v>
+      <c r="AB31" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC31" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="45">
         <v>32</v>
       </c>
@@ -7041,7 +7407,7 @@
         <v>101</v>
       </c>
       <c r="Q32" s="43" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="R32" s="43" t="s">
         <v>662</v>
@@ -7077,14 +7443,14 @@
       <c r="AA32" s="59" t="s">
         <v>417</v>
       </c>
-      <c r="AB32" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC32" s="43" t="s">
-        <v>767</v>
+      <c r="AB32" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC32" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="33" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="45">
         <v>33</v>
       </c>
@@ -7138,7 +7504,7 @@
         <v>564</v>
       </c>
       <c r="Q33" s="43" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="R33" s="43" t="s">
         <v>663</v>
@@ -7174,14 +7540,14 @@
       <c r="AA33" s="59" t="s">
         <v>414</v>
       </c>
-      <c r="AB33" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC33" s="43" t="s">
-        <v>767</v>
+      <c r="AB33" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC33" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="34" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="45">
         <v>34</v>
       </c>
@@ -7235,7 +7601,7 @@
         <v>102</v>
       </c>
       <c r="Q34" s="53" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="R34" s="43" t="s">
         <v>664</v>
@@ -7271,14 +7637,14 @@
       <c r="AA34" s="59" t="s">
         <v>414</v>
       </c>
-      <c r="AB34" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC34" s="43" t="s">
-        <v>767</v>
+      <c r="AB34" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC34" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="35" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="45">
         <v>35</v>
       </c>
@@ -7332,7 +7698,7 @@
         <v>103</v>
       </c>
       <c r="Q35" s="53" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="R35" s="43" t="s">
         <v>665</v>
@@ -7368,14 +7734,14 @@
       <c r="AA35" s="59" t="s">
         <v>414</v>
       </c>
-      <c r="AB35" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC35" s="43" t="s">
-        <v>767</v>
+      <c r="AB35" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC35" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="45">
         <v>36</v>
       </c>
@@ -7429,7 +7795,7 @@
         <v>104</v>
       </c>
       <c r="Q36" s="43" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="R36" s="43" t="s">
         <v>666</v>
@@ -7465,14 +7831,14 @@
       <c r="AA36" s="59" t="s">
         <v>414</v>
       </c>
-      <c r="AB36" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC36" s="43" t="s">
-        <v>767</v>
+      <c r="AB36" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC36" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="37" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="45">
         <v>37</v>
       </c>
@@ -7526,7 +7892,7 @@
         <v>104</v>
       </c>
       <c r="Q37" s="43" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="R37" s="43" t="s">
         <v>666</v>
@@ -7562,14 +7928,14 @@
       <c r="AA37" s="59" t="s">
         <v>414</v>
       </c>
-      <c r="AB37" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC37" s="43" t="s">
-        <v>767</v>
+      <c r="AB37" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC37" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="45">
         <v>38</v>
       </c>
@@ -7623,7 +7989,7 @@
         <v>105</v>
       </c>
       <c r="Q38" s="43" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="R38" s="43" t="s">
         <v>667</v>
@@ -7659,14 +8025,14 @@
       <c r="AA38" s="59" t="s">
         <v>415</v>
       </c>
-      <c r="AB38" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC38" s="43" t="s">
-        <v>767</v>
+      <c r="AB38" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC38" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="39" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="45">
         <v>39</v>
       </c>
@@ -7720,7 +8086,7 @@
         <v>556</v>
       </c>
       <c r="Q39" s="43" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="R39" s="43" t="s">
         <v>668</v>
@@ -7756,14 +8122,14 @@
       <c r="AA39" s="59" t="s">
         <v>415</v>
       </c>
-      <c r="AB39" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC39" s="43" t="s">
-        <v>767</v>
+      <c r="AB39" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC39" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="40" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="45">
         <v>40</v>
       </c>
@@ -7817,7 +8183,7 @@
         <v>565</v>
       </c>
       <c r="Q40" s="43" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="R40" s="43" t="s">
         <v>669</v>
@@ -7853,14 +8219,14 @@
       <c r="AA40" s="59" t="s">
         <v>415</v>
       </c>
-      <c r="AB40" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC40" s="43" t="s">
-        <v>767</v>
+      <c r="AB40" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC40" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="41" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="45">
         <v>41</v>
       </c>
@@ -7914,7 +8280,7 @@
         <v>106</v>
       </c>
       <c r="Q41" s="43" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="R41" s="43" t="s">
         <v>670</v>
@@ -7950,14 +8316,14 @@
       <c r="AA41" s="59" t="s">
         <v>415</v>
       </c>
-      <c r="AB41" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC41" s="43" t="s">
-        <v>767</v>
+      <c r="AB41" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC41" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="42" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="45">
         <v>42</v>
       </c>
@@ -8011,7 +8377,7 @@
         <v>557</v>
       </c>
       <c r="Q42" s="43" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="R42" s="43" t="s">
         <v>671</v>
@@ -8047,14 +8413,14 @@
       <c r="AA42" s="59" t="s">
         <v>415</v>
       </c>
-      <c r="AB42" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC42" s="43" t="s">
-        <v>767</v>
+      <c r="AB42" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC42" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="43" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="45">
         <v>43</v>
       </c>
@@ -8108,7 +8474,7 @@
         <v>107</v>
       </c>
       <c r="Q43" s="43" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="R43" s="43" t="s">
         <v>672</v>
@@ -8144,14 +8510,14 @@
       <c r="AA43" s="59" t="s">
         <v>415</v>
       </c>
-      <c r="AB43" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC43" s="43" t="s">
-        <v>767</v>
+      <c r="AB43" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC43" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="44" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="45">
         <v>44</v>
       </c>
@@ -8205,7 +8571,7 @@
         <v>108</v>
       </c>
       <c r="Q44" s="43" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="R44" s="43" t="s">
         <v>673</v>
@@ -8241,14 +8607,14 @@
       <c r="AA44" s="59" t="s">
         <v>415</v>
       </c>
-      <c r="AB44" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC44" s="43" t="s">
-        <v>767</v>
+      <c r="AB44" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC44" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="45" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="45">
         <v>45</v>
       </c>
@@ -8302,7 +8668,7 @@
         <v>566</v>
       </c>
       <c r="Q45" s="43" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="R45" s="43" t="s">
         <v>674</v>
@@ -8338,14 +8704,14 @@
       <c r="AA45" s="59" t="s">
         <v>415</v>
       </c>
-      <c r="AB45" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC45" s="43" t="s">
-        <v>767</v>
+      <c r="AB45" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC45" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="46" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="45">
         <v>46</v>
       </c>
@@ -8399,7 +8765,7 @@
         <v>109</v>
       </c>
       <c r="Q46" s="43" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="R46" s="43" t="s">
         <v>675</v>
@@ -8435,14 +8801,14 @@
       <c r="AA46" s="59" t="s">
         <v>415</v>
       </c>
-      <c r="AB46" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC46" s="43" t="s">
-        <v>767</v>
+      <c r="AB46" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC46" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="47" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="45">
         <v>47</v>
       </c>
@@ -8496,7 +8862,7 @@
         <v>567</v>
       </c>
       <c r="Q47" s="43" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="R47" s="43" t="s">
         <v>676</v>
@@ -8532,14 +8898,14 @@
       <c r="AA47" s="59" t="s">
         <v>415</v>
       </c>
-      <c r="AB47" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC47" s="43" t="s">
-        <v>767</v>
+      <c r="AB47" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC47" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="48" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="45">
         <v>48</v>
       </c>
@@ -8593,7 +8959,7 @@
         <v>109</v>
       </c>
       <c r="Q48" s="43" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="R48" s="43" t="s">
         <v>675</v>
@@ -8629,14 +8995,14 @@
       <c r="AA48" s="59" t="s">
         <v>415</v>
       </c>
-      <c r="AB48" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC48" s="43" t="s">
-        <v>767</v>
+      <c r="AB48" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC48" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="49" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="45">
         <v>49</v>
       </c>
@@ -8690,7 +9056,7 @@
         <v>568</v>
       </c>
       <c r="Q49" s="43" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="R49" s="43" t="s">
         <v>677</v>
@@ -8726,14 +9092,14 @@
       <c r="AA49" s="59" t="s">
         <v>415</v>
       </c>
-      <c r="AB49" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC49" s="43" t="s">
-        <v>767</v>
+      <c r="AB49" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC49" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="50" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="45">
         <v>50</v>
       </c>
@@ -8787,7 +9153,7 @@
         <v>569</v>
       </c>
       <c r="Q50" s="43" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="R50" s="43" t="s">
         <v>678</v>
@@ -8823,14 +9189,14 @@
       <c r="AA50" s="59" t="s">
         <v>415</v>
       </c>
-      <c r="AB50" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC50" s="43" t="s">
-        <v>767</v>
+      <c r="AB50" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC50" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="51" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="45">
         <v>51</v>
       </c>
@@ -8884,7 +9250,7 @@
         <v>570</v>
       </c>
       <c r="Q51" s="43" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="R51" s="43" t="s">
         <v>679</v>
@@ -8920,14 +9286,14 @@
       <c r="AA51" s="59" t="s">
         <v>415</v>
       </c>
-      <c r="AB51" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC51" s="43" t="s">
-        <v>767</v>
+      <c r="AB51" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC51" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="52" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="45">
         <v>52</v>
       </c>
@@ -8981,7 +9347,7 @@
         <v>571</v>
       </c>
       <c r="Q52" s="43" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="R52" s="43" t="s">
         <v>680</v>
@@ -9017,14 +9383,14 @@
       <c r="AA52" s="59" t="s">
         <v>415</v>
       </c>
-      <c r="AB52" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC52" s="43" t="s">
-        <v>767</v>
+      <c r="AB52" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC52" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="53" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="45">
         <v>53</v>
       </c>
@@ -9078,7 +9444,7 @@
         <v>110</v>
       </c>
       <c r="Q53" s="43" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="R53" s="43" t="s">
         <v>681</v>
@@ -9114,14 +9480,14 @@
       <c r="AA53" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB53" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC53" s="43" t="s">
-        <v>767</v>
+      <c r="AB53" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC53" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="54" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="45">
         <v>54</v>
       </c>
@@ -9175,7 +9541,7 @@
         <v>111</v>
       </c>
       <c r="Q54" s="43" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="R54" s="43" t="s">
         <v>682</v>
@@ -9211,14 +9577,14 @@
       <c r="AA54" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB54" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC54" s="43" t="s">
-        <v>767</v>
+      <c r="AB54" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC54" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="55" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="45">
         <v>55</v>
       </c>
@@ -9272,7 +9638,7 @@
         <v>112</v>
       </c>
       <c r="Q55" s="43" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="R55" s="43" t="s">
         <v>683</v>
@@ -9308,14 +9674,14 @@
       <c r="AA55" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB55" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC55" s="43" t="s">
-        <v>767</v>
+      <c r="AB55" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC55" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="56" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="45">
         <v>56</v>
       </c>
@@ -9369,7 +9735,7 @@
         <v>113</v>
       </c>
       <c r="Q56" s="43" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="R56" s="43" t="s">
         <v>684</v>
@@ -9405,14 +9771,14 @@
       <c r="AA56" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB56" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC56" s="43" t="s">
-        <v>767</v>
+      <c r="AB56" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC56" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="57" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="45">
         <v>57</v>
       </c>
@@ -9466,7 +9832,7 @@
         <v>114</v>
       </c>
       <c r="Q57" s="43" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="R57" s="43" t="s">
         <v>685</v>
@@ -9502,14 +9868,14 @@
       <c r="AA57" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB57" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC57" s="43" t="s">
-        <v>767</v>
+      <c r="AB57" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC57" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="58" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="45">
         <v>58</v>
       </c>
@@ -9563,7 +9929,7 @@
         <v>115</v>
       </c>
       <c r="Q58" s="43" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="R58" s="43" t="s">
         <v>686</v>
@@ -9599,14 +9965,14 @@
       <c r="AA58" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB58" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC58" s="43" t="s">
-        <v>767</v>
+      <c r="AB58" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC58" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="59" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="45">
         <v>59</v>
       </c>
@@ -9660,7 +10026,7 @@
         <v>116</v>
       </c>
       <c r="Q59" s="43" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="R59" s="43" t="s">
         <v>687</v>
@@ -9696,14 +10062,14 @@
       <c r="AA59" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB59" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC59" s="43" t="s">
-        <v>767</v>
+      <c r="AB59" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC59" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="60" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="45">
         <v>60</v>
       </c>
@@ -9757,7 +10123,7 @@
         <v>117</v>
       </c>
       <c r="Q60" s="43" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="R60" s="43" t="s">
         <v>688</v>
@@ -9793,14 +10159,14 @@
       <c r="AA60" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB60" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC60" s="43" t="s">
-        <v>767</v>
+      <c r="AB60" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC60" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="61" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="45">
         <v>61</v>
       </c>
@@ -9854,7 +10220,7 @@
         <v>118</v>
       </c>
       <c r="Q61" s="43" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="R61" s="43" t="s">
         <v>689</v>
@@ -9890,14 +10256,14 @@
       <c r="AA61" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB61" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC61" s="43" t="s">
-        <v>767</v>
+      <c r="AB61" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC61" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="62" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="45">
         <v>62</v>
       </c>
@@ -9951,7 +10317,7 @@
         <v>119</v>
       </c>
       <c r="Q62" s="43" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="R62" s="43" t="s">
         <v>690</v>
@@ -9987,14 +10353,14 @@
       <c r="AA62" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB62" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC62" s="43" t="s">
-        <v>767</v>
+      <c r="AB62" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC62" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="63" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="45">
         <v>63</v>
       </c>
@@ -10048,7 +10414,7 @@
         <v>120</v>
       </c>
       <c r="Q63" s="43" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="R63" s="43" t="s">
         <v>691</v>
@@ -10084,14 +10450,14 @@
       <c r="AA63" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB63" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC63" s="43" t="s">
-        <v>767</v>
+      <c r="AB63" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC63" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="64" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="45">
         <v>64</v>
       </c>
@@ -10145,7 +10511,7 @@
         <v>121</v>
       </c>
       <c r="Q64" s="43" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="R64" s="43" t="s">
         <v>692</v>
@@ -10181,14 +10547,14 @@
       <c r="AA64" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB64" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC64" s="43" t="s">
-        <v>767</v>
+      <c r="AB64" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC64" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="65" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="45">
         <v>65</v>
       </c>
@@ -10242,7 +10608,7 @@
         <v>122</v>
       </c>
       <c r="Q65" s="43" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="R65" s="43" t="s">
         <v>693</v>
@@ -10278,14 +10644,14 @@
       <c r="AA65" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB65" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC65" s="43" t="s">
-        <v>767</v>
+      <c r="AB65" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC65" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="66" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="45">
         <v>66</v>
       </c>
@@ -10339,7 +10705,7 @@
         <v>123</v>
       </c>
       <c r="Q66" s="43" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="R66" s="43" t="s">
         <v>694</v>
@@ -10375,14 +10741,14 @@
       <c r="AA66" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB66" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC66" s="43" t="s">
-        <v>767</v>
+      <c r="AB66" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC66" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="67" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="45">
         <v>67</v>
       </c>
@@ -10436,7 +10802,7 @@
         <v>124</v>
       </c>
       <c r="Q67" s="43" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="R67" s="43" t="s">
         <v>695</v>
@@ -10472,14 +10838,14 @@
       <c r="AA67" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB67" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC67" s="43" t="s">
-        <v>767</v>
+      <c r="AB67" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC67" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="68" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="45">
         <v>68</v>
       </c>
@@ -10533,7 +10899,7 @@
         <v>125</v>
       </c>
       <c r="Q68" s="43" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="R68" s="43" t="s">
         <v>696</v>
@@ -10569,14 +10935,14 @@
       <c r="AA68" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB68" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC68" s="43" t="s">
-        <v>767</v>
+      <c r="AB68" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC68" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="69" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="45">
         <v>69</v>
       </c>
@@ -10630,7 +10996,7 @@
         <v>126</v>
       </c>
       <c r="Q69" s="53" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="R69" s="43" t="s">
         <v>697</v>
@@ -10666,14 +11032,14 @@
       <c r="AA69" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB69" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC69" s="43" t="s">
-        <v>767</v>
+      <c r="AB69" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC69" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="70" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="45">
         <v>70</v>
       </c>
@@ -10727,7 +11093,7 @@
         <v>127</v>
       </c>
       <c r="Q70" s="43" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="R70" s="43" t="s">
         <v>698</v>
@@ -10763,14 +11129,14 @@
       <c r="AA70" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB70" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC70" s="43" t="s">
-        <v>767</v>
+      <c r="AB70" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC70" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="71" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="45">
         <v>71</v>
       </c>
@@ -10824,7 +11190,7 @@
         <v>128</v>
       </c>
       <c r="Q71" s="43" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="R71" s="43" t="s">
         <v>699</v>
@@ -10860,14 +11226,14 @@
       <c r="AA71" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB71" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC71" s="43" t="s">
-        <v>767</v>
+      <c r="AB71" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC71" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="72" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="45">
         <v>72</v>
       </c>
@@ -10921,7 +11287,7 @@
         <v>132</v>
       </c>
       <c r="Q72" s="43" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="R72" s="43" t="s">
         <v>700</v>
@@ -10957,14 +11323,14 @@
       <c r="AA72" s="59" t="s">
         <v>415</v>
       </c>
-      <c r="AB72" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC72" s="43" t="s">
-        <v>767</v>
+      <c r="AB72" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC72" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="73" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="45">
         <v>73</v>
       </c>
@@ -11018,7 +11384,7 @@
         <v>129</v>
       </c>
       <c r="Q73" s="43" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="R73" s="43" t="s">
         <v>701</v>
@@ -11054,14 +11420,14 @@
       <c r="AA73" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB73" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC73" s="43" t="s">
-        <v>767</v>
+      <c r="AB73" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC73" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="74" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="45">
         <v>74</v>
       </c>
@@ -11115,7 +11481,7 @@
         <v>130</v>
       </c>
       <c r="Q74" s="43" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="R74" s="43" t="s">
         <v>702</v>
@@ -11151,14 +11517,14 @@
       <c r="AA74" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB74" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC74" s="43" t="s">
-        <v>767</v>
+      <c r="AB74" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC74" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="75" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="45">
         <v>75</v>
       </c>
@@ -11212,7 +11578,7 @@
         <v>131</v>
       </c>
       <c r="Q75" s="43" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="R75" s="43" t="s">
         <v>703</v>
@@ -11248,14 +11614,14 @@
       <c r="AA75" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB75" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC75" s="43" t="s">
-        <v>767</v>
+      <c r="AB75" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC75" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="76" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="45">
         <v>76</v>
       </c>
@@ -11309,7 +11675,7 @@
         <v>134</v>
       </c>
       <c r="Q76" s="43" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="R76" s="43" t="s">
         <v>704</v>
@@ -11345,14 +11711,14 @@
       <c r="AA76" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB76" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC76" s="43" t="s">
-        <v>767</v>
+      <c r="AB76" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC76" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="77" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="45">
         <v>77</v>
       </c>
@@ -11406,7 +11772,7 @@
         <v>135</v>
       </c>
       <c r="Q77" s="43" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="R77" s="43" t="s">
         <v>705</v>
@@ -11442,14 +11808,14 @@
       <c r="AA77" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB77" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC77" s="43" t="s">
-        <v>767</v>
+      <c r="AB77" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC77" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="78" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="45">
         <v>78</v>
       </c>
@@ -11503,7 +11869,7 @@
         <v>136</v>
       </c>
       <c r="Q78" s="43" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="R78" s="43" t="s">
         <v>706</v>
@@ -11539,14 +11905,14 @@
       <c r="AA78" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB78" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC78" s="43" t="s">
-        <v>767</v>
+      <c r="AB78" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC78" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="79" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="45">
         <v>79</v>
       </c>
@@ -11600,7 +11966,7 @@
         <v>137</v>
       </c>
       <c r="Q79" s="43" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="R79" s="43" t="s">
         <v>707</v>
@@ -11636,14 +12002,14 @@
       <c r="AA79" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB79" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC79" s="43" t="s">
-        <v>767</v>
+      <c r="AB79" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC79" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="80" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="45">
         <v>80</v>
       </c>
@@ -11697,7 +12063,7 @@
         <v>138</v>
       </c>
       <c r="Q80" s="43" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="R80" s="43" t="s">
         <v>708</v>
@@ -11733,14 +12099,14 @@
       <c r="AA80" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB80" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC80" s="43" t="s">
-        <v>767</v>
+      <c r="AB80" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC80" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="81" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="45">
         <v>81</v>
       </c>
@@ -11794,7 +12160,7 @@
         <v>139</v>
       </c>
       <c r="Q81" s="43" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="R81" s="43" t="s">
         <v>709</v>
@@ -11830,14 +12196,14 @@
       <c r="AA81" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB81" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC81" s="43" t="s">
-        <v>767</v>
+      <c r="AB81" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC81" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="82" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="45">
         <v>82</v>
       </c>
@@ -11891,7 +12257,7 @@
         <v>149</v>
       </c>
       <c r="Q82" s="43" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="R82" s="43" t="s">
         <v>710</v>
@@ -11927,14 +12293,14 @@
       <c r="AA82" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB82" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC82" s="43" t="s">
-        <v>767</v>
+      <c r="AB82" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC82" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="83" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="45">
         <v>83</v>
       </c>
@@ -11988,7 +12354,7 @@
         <v>149</v>
       </c>
       <c r="Q83" s="43" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="R83" s="43" t="s">
         <v>710</v>
@@ -12024,14 +12390,14 @@
       <c r="AA83" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB83" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC83" s="43" t="s">
-        <v>767</v>
+      <c r="AB83" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC83" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="84" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="45">
         <v>84</v>
       </c>
@@ -12085,7 +12451,7 @@
         <v>149</v>
       </c>
       <c r="Q84" s="43" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="R84" s="43" t="s">
         <v>710</v>
@@ -12121,14 +12487,14 @@
       <c r="AA84" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB84" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC84" s="43" t="s">
-        <v>767</v>
+      <c r="AB84" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC84" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="85" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="45">
         <v>85</v>
       </c>
@@ -12182,7 +12548,7 @@
         <v>145</v>
       </c>
       <c r="Q85" s="43" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="R85" s="43" t="s">
         <v>711</v>
@@ -12218,14 +12584,14 @@
       <c r="AA85" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB85" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC85" s="43" t="s">
-        <v>767</v>
+      <c r="AB85" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC85" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="86" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="45">
         <v>86</v>
       </c>
@@ -12279,7 +12645,7 @@
         <v>146</v>
       </c>
       <c r="Q86" s="43" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="R86" s="43" t="s">
         <v>712</v>
@@ -12315,14 +12681,14 @@
       <c r="AA86" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB86" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC86" s="43" t="s">
-        <v>767</v>
+      <c r="AB86" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC86" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="87" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="45">
         <v>87</v>
       </c>
@@ -12376,7 +12742,7 @@
         <v>144</v>
       </c>
       <c r="Q87" s="43" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="R87" s="43" t="s">
         <v>713</v>
@@ -12412,14 +12778,14 @@
       <c r="AA87" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB87" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC87" s="43" t="s">
-        <v>767</v>
+      <c r="AB87" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC87" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="88" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="45">
         <v>88</v>
       </c>
@@ -12473,7 +12839,7 @@
         <v>147</v>
       </c>
       <c r="Q88" s="43" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="R88" s="43" t="s">
         <v>714</v>
@@ -12509,14 +12875,14 @@
       <c r="AA88" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB88" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC88" s="43" t="s">
-        <v>767</v>
+      <c r="AB88" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC88" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="89" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="45">
         <v>89</v>
       </c>
@@ -12570,7 +12936,7 @@
         <v>142</v>
       </c>
       <c r="Q89" s="43" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="R89" s="43" t="s">
         <v>715</v>
@@ -12606,14 +12972,14 @@
       <c r="AA89" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB89" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC89" s="43" t="s">
-        <v>767</v>
+      <c r="AB89" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC89" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="90" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="45">
         <v>90</v>
       </c>
@@ -12667,7 +13033,7 @@
         <v>143</v>
       </c>
       <c r="Q90" s="43" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="R90" s="43" t="s">
         <v>716</v>
@@ -12703,14 +13069,14 @@
       <c r="AA90" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB90" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC90" s="43" t="s">
-        <v>767</v>
+      <c r="AB90" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC90" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="91" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="45">
         <v>91</v>
       </c>
@@ -12764,7 +13130,7 @@
         <v>150</v>
       </c>
       <c r="Q91" s="53" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="R91" s="43" t="s">
         <v>717</v>
@@ -12800,14 +13166,14 @@
       <c r="AA91" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB91" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC91" s="43" t="s">
-        <v>767</v>
+      <c r="AB91" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC91" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="92" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="45">
         <v>92</v>
       </c>
@@ -12861,7 +13227,7 @@
         <v>151</v>
       </c>
       <c r="Q92" s="43" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="R92" s="43" t="s">
         <v>718</v>
@@ -12897,14 +13263,14 @@
       <c r="AA92" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB92" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC92" s="43" t="s">
-        <v>767</v>
+      <c r="AB92" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC92" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="93" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="45">
         <v>93</v>
       </c>
@@ -12958,7 +13324,7 @@
         <v>152</v>
       </c>
       <c r="Q93" s="43" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="R93" s="43" t="s">
         <v>719</v>
@@ -12994,14 +13360,14 @@
       <c r="AA93" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB93" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC93" s="43" t="s">
-        <v>767</v>
+      <c r="AB93" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC93" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="94" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="45">
         <v>94</v>
       </c>
@@ -13055,7 +13421,7 @@
         <v>153</v>
       </c>
       <c r="Q94" s="43" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="R94" s="43" t="s">
         <v>720</v>
@@ -13091,14 +13457,14 @@
       <c r="AA94" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB94" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC94" s="43" t="s">
-        <v>767</v>
+      <c r="AB94" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC94" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="95" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="45">
         <v>95</v>
       </c>
@@ -13152,7 +13518,7 @@
         <v>154</v>
       </c>
       <c r="Q95" s="43" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="R95" s="43" t="s">
         <v>721</v>
@@ -13188,14 +13554,14 @@
       <c r="AA95" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB95" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC95" s="43" t="s">
-        <v>767</v>
+      <c r="AB95" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC95" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="96" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="45">
         <v>96</v>
       </c>
@@ -13249,7 +13615,7 @@
         <v>155</v>
       </c>
       <c r="Q96" s="43" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="R96" s="43" t="s">
         <v>722</v>
@@ -13285,14 +13651,14 @@
       <c r="AA96" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB96" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC96" s="43" t="s">
-        <v>767</v>
+      <c r="AB96" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC96" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="97" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="45">
         <v>97</v>
       </c>
@@ -13346,7 +13712,7 @@
         <v>156</v>
       </c>
       <c r="Q97" s="43" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="R97" s="43" t="s">
         <v>723</v>
@@ -13382,14 +13748,14 @@
       <c r="AA97" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB97" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC97" s="43" t="s">
-        <v>767</v>
+      <c r="AB97" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC97" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="98" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="45">
         <v>98</v>
       </c>
@@ -13443,7 +13809,7 @@
         <v>157</v>
       </c>
       <c r="Q98" s="43" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="R98" s="43" t="s">
         <v>724</v>
@@ -13479,14 +13845,14 @@
       <c r="AA98" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB98" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC98" s="43" t="s">
-        <v>767</v>
+      <c r="AB98" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC98" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="99" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="45">
         <v>99</v>
       </c>
@@ -13540,7 +13906,7 @@
         <v>158</v>
       </c>
       <c r="Q99" s="43" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="R99" s="43" t="s">
         <v>725</v>
@@ -13576,14 +13942,14 @@
       <c r="AA99" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB99" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC99" s="43" t="s">
-        <v>767</v>
+      <c r="AB99" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC99" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="100" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="45">
         <v>100</v>
       </c>
@@ -13637,7 +14003,7 @@
         <v>159</v>
       </c>
       <c r="Q100" s="43" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="R100" s="43" t="s">
         <v>726</v>
@@ -13673,14 +14039,14 @@
       <c r="AA100" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB100" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC100" s="43" t="s">
-        <v>767</v>
+      <c r="AB100" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC100" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="101" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="45">
         <v>101</v>
       </c>
@@ -13734,7 +14100,7 @@
         <v>160</v>
       </c>
       <c r="Q101" s="43" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="R101" s="43" t="s">
         <v>727</v>
@@ -13770,14 +14136,14 @@
       <c r="AA101" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB101" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC101" s="43" t="s">
-        <v>767</v>
+      <c r="AB101" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC101" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="102" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="45">
         <v>102</v>
       </c>
@@ -13831,7 +14197,7 @@
         <v>164</v>
       </c>
       <c r="Q102" s="43" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="R102" s="43" t="s">
         <v>728</v>
@@ -13867,14 +14233,14 @@
       <c r="AA102" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB102" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC102" s="43" t="s">
-        <v>767</v>
+      <c r="AB102" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC102" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="103" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="45">
         <v>103</v>
       </c>
@@ -13928,7 +14294,7 @@
         <v>162</v>
       </c>
       <c r="Q103" s="43" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="R103" s="43" t="s">
         <v>729</v>
@@ -13964,14 +14330,14 @@
       <c r="AA103" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB103" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC103" s="43" t="s">
-        <v>767</v>
+      <c r="AB103" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC103" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="104" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="45">
         <v>104</v>
       </c>
@@ -14025,7 +14391,7 @@
         <v>163</v>
       </c>
       <c r="Q104" s="43" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="R104" s="43" t="s">
         <v>730</v>
@@ -14061,14 +14427,14 @@
       <c r="AA104" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB104" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC104" s="43" t="s">
-        <v>767</v>
+      <c r="AB104" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC104" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="105" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="45">
         <v>105</v>
       </c>
@@ -14122,7 +14488,7 @@
         <v>165</v>
       </c>
       <c r="Q105" s="43" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="R105" s="43" t="s">
         <v>731</v>
@@ -14158,14 +14524,14 @@
       <c r="AA105" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB105" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC105" s="43" t="s">
-        <v>767</v>
+      <c r="AB105" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC105" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="106" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="45">
         <v>106</v>
       </c>
@@ -14219,7 +14585,7 @@
         <v>166</v>
       </c>
       <c r="Q106" s="43" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="R106" s="43" t="s">
         <v>732</v>
@@ -14255,14 +14621,14 @@
       <c r="AA106" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB106" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC106" s="43" t="s">
-        <v>767</v>
+      <c r="AB106" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC106" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="107" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="45">
         <v>107</v>
       </c>
@@ -14316,7 +14682,7 @@
         <v>81</v>
       </c>
       <c r="Q107" s="43" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="R107" s="43" t="s">
         <v>733</v>
@@ -14352,14 +14718,14 @@
       <c r="AA107" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB107" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC107" s="43" t="s">
-        <v>767</v>
+      <c r="AB107" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC107" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="108" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="45">
         <v>108</v>
       </c>
@@ -14413,7 +14779,7 @@
         <v>82</v>
       </c>
       <c r="Q108" s="43" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="R108" s="43" t="s">
         <v>734</v>
@@ -14449,14 +14815,14 @@
       <c r="AA108" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB108" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC108" s="43" t="s">
-        <v>767</v>
+      <c r="AB108" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC108" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="109" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="45">
         <v>109</v>
       </c>
@@ -14510,7 +14876,7 @@
         <v>133</v>
       </c>
       <c r="Q109" s="43" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="R109" s="43" t="s">
         <v>735</v>
@@ -14546,14 +14912,14 @@
       <c r="AA109" s="59" t="s">
         <v>412</v>
       </c>
-      <c r="AB109" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC109" s="43" t="s">
-        <v>767</v>
+      <c r="AB109" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC109" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="110" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="45">
         <v>110</v>
       </c>
@@ -14607,7 +14973,7 @@
         <v>170</v>
       </c>
       <c r="Q110" s="43" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="R110" s="43" t="s">
         <v>736</v>
@@ -14643,14 +15009,14 @@
       <c r="AA110" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB110" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC110" s="43" t="s">
-        <v>767</v>
+      <c r="AB110" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC110" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="111" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="45">
         <v>111</v>
       </c>
@@ -14704,7 +15070,7 @@
         <v>167</v>
       </c>
       <c r="Q111" s="43" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="R111" s="43" t="s">
         <v>737</v>
@@ -14740,14 +15106,14 @@
       <c r="AA111" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB111" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC111" s="43" t="s">
-        <v>767</v>
+      <c r="AB111" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC111" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="112" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="45">
         <v>112</v>
       </c>
@@ -14801,7 +15167,7 @@
         <v>168</v>
       </c>
       <c r="Q112" s="43" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="R112" s="43" t="s">
         <v>738</v>
@@ -14837,14 +15203,14 @@
       <c r="AA112" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB112" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC112" s="43" t="s">
-        <v>767</v>
+      <c r="AB112" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC112" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="113" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="45">
         <v>113</v>
       </c>
@@ -14898,7 +15264,7 @@
         <v>169</v>
       </c>
       <c r="Q113" s="43" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="R113" s="43" t="s">
         <v>739</v>
@@ -14934,14 +15300,14 @@
       <c r="AA113" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB113" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC113" s="43" t="s">
-        <v>767</v>
+      <c r="AB113" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC113" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="114" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="45">
         <v>114</v>
       </c>
@@ -14995,7 +15361,7 @@
         <v>172</v>
       </c>
       <c r="Q114" s="43" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="R114" s="43" t="s">
         <v>740</v>
@@ -15031,14 +15397,14 @@
       <c r="AA114" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB114" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC114" s="43" t="s">
-        <v>767</v>
+      <c r="AB114" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC114" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="115" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="45">
         <v>115</v>
       </c>
@@ -15092,7 +15458,7 @@
         <v>173</v>
       </c>
       <c r="Q115" s="43" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="R115" s="43" t="s">
         <v>741</v>
@@ -15128,14 +15494,14 @@
       <c r="AA115" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB115" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC115" s="43" t="s">
-        <v>767</v>
+      <c r="AB115" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC115" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="116" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="45">
         <v>116</v>
       </c>
@@ -15189,7 +15555,7 @@
         <v>174</v>
       </c>
       <c r="Q116" s="43" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="R116" s="43" t="s">
         <v>742</v>
@@ -15225,14 +15591,14 @@
       <c r="AA116" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB116" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC116" s="43" t="s">
-        <v>767</v>
+      <c r="AB116" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC116" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="117" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="45">
         <v>117</v>
       </c>
@@ -15286,7 +15652,7 @@
         <v>175</v>
       </c>
       <c r="Q117" s="43" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="R117" s="43" t="s">
         <v>743</v>
@@ -15322,14 +15688,14 @@
       <c r="AA117" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB117" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC117" s="43" t="s">
-        <v>767</v>
+      <c r="AB117" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC117" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="118" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="45">
         <v>118</v>
       </c>
@@ -15383,7 +15749,7 @@
         <v>176</v>
       </c>
       <c r="Q118" s="53" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="R118" s="43" t="s">
         <v>744</v>
@@ -15419,14 +15785,14 @@
       <c r="AA118" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB118" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC118" s="43" t="s">
-        <v>767</v>
+      <c r="AB118" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC118" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="119" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="45">
         <v>119</v>
       </c>
@@ -15480,7 +15846,7 @@
         <v>177</v>
       </c>
       <c r="Q119" s="43" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="R119" s="43" t="s">
         <v>745</v>
@@ -15516,14 +15882,14 @@
       <c r="AA119" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB119" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC119" s="43" t="s">
-        <v>767</v>
+      <c r="AB119" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC119" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="120" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="45">
         <v>120</v>
       </c>
@@ -15577,7 +15943,7 @@
         <v>578</v>
       </c>
       <c r="Q120" s="43" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="R120" s="43" t="s">
         <v>746</v>
@@ -15613,14 +15979,14 @@
       <c r="AA120" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB120" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC120" s="43" t="s">
-        <v>767</v>
+      <c r="AB120" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC120" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="121" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="45">
         <v>121</v>
       </c>
@@ -15674,7 +16040,7 @@
         <v>579</v>
       </c>
       <c r="Q121" s="43" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="R121" s="43" t="s">
         <v>747</v>
@@ -15710,14 +16076,14 @@
       <c r="AA121" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB121" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC121" s="43" t="s">
-        <v>767</v>
+      <c r="AB121" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC121" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="122" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="45">
         <v>122</v>
       </c>
@@ -15771,7 +16137,7 @@
         <v>580</v>
       </c>
       <c r="Q122" s="43" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="R122" s="43" t="s">
         <v>748</v>
@@ -15795,7 +16161,7 @@
         <v>80</v>
       </c>
       <c r="X122" s="54" t="str">
-        <f t="shared" ref="X122:X137" si="50">CONCATENATE("Key-DOCU-",A122)</f>
+        <f t="shared" ref="X122:X138" si="50">CONCATENATE("Key-DOCU-",A122)</f>
         <v>Key-DOCU-122</v>
       </c>
       <c r="Y122" s="58" t="s">
@@ -15807,14 +16173,14 @@
       <c r="AA122" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB122" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC122" s="43" t="s">
-        <v>767</v>
+      <c r="AB122" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC122" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="123" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="45">
         <v>123</v>
       </c>
@@ -15868,7 +16234,7 @@
         <v>555</v>
       </c>
       <c r="Q123" s="43" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="R123" s="43" t="s">
         <v>749</v>
@@ -15895,23 +16261,23 @@
         <f t="shared" si="50"/>
         <v>Key-DOCU-123</v>
       </c>
-      <c r="Y123" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="Z123" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AA123" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AB123" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC123" s="43" t="s">
-        <v>767</v>
+      <c r="Y123" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z123" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA123" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB123" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC123" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="124" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="45">
         <v>124</v>
       </c>
@@ -15965,7 +16331,7 @@
         <v>247</v>
       </c>
       <c r="Q124" s="43" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="R124" s="43" t="s">
         <v>750</v>
@@ -15992,23 +16358,23 @@
         <f t="shared" si="50"/>
         <v>Key-DOCU-124</v>
       </c>
-      <c r="Y124" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="Z124" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AA124" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AB124" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC124" s="43" t="s">
-        <v>767</v>
+      <c r="Y124" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z124" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA124" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB124" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC124" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="125" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="45">
         <v>125</v>
       </c>
@@ -16062,7 +16428,7 @@
         <v>245</v>
       </c>
       <c r="Q125" s="43" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="R125" s="43" t="s">
         <v>751</v>
@@ -16089,23 +16455,23 @@
         <f t="shared" si="50"/>
         <v>Key-DOCU-125</v>
       </c>
-      <c r="Y125" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="Z125" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AA125" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AB125" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC125" s="43" t="s">
-        <v>767</v>
+      <c r="Y125" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z125" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA125" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB125" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC125" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="126" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="45">
         <v>126</v>
       </c>
@@ -16159,7 +16525,7 @@
         <v>246</v>
       </c>
       <c r="Q126" s="43" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="R126" s="43" t="s">
         <v>752</v>
@@ -16186,23 +16552,23 @@
         <f t="shared" si="50"/>
         <v>Key-DOCU-126</v>
       </c>
-      <c r="Y126" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="Z126" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AA126" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AB126" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC126" s="43" t="s">
-        <v>767</v>
+      <c r="Y126" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z126" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA126" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB126" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC126" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="127" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="45">
         <v>127</v>
       </c>
@@ -16256,7 +16622,7 @@
         <v>268</v>
       </c>
       <c r="Q127" s="43" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="R127" s="43" t="s">
         <v>753</v>
@@ -16283,23 +16649,23 @@
         <f t="shared" si="50"/>
         <v>Key-DOCU-127</v>
       </c>
-      <c r="Y127" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="Z127" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AA127" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AB127" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC127" s="43" t="s">
-        <v>767</v>
+      <c r="Y127" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z127" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA127" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB127" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC127" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="128" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="45">
         <v>128</v>
       </c>
@@ -16353,7 +16719,7 @@
         <v>269</v>
       </c>
       <c r="Q128" s="43" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="R128" s="43" t="s">
         <v>754</v>
@@ -16380,23 +16746,23 @@
         <f t="shared" si="50"/>
         <v>Key-DOCU-128</v>
       </c>
-      <c r="Y128" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="Z128" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AA128" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AB128" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC128" s="43" t="s">
-        <v>767</v>
+      <c r="Y128" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z128" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA128" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB128" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC128" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="129" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="45">
         <v>129</v>
       </c>
@@ -16450,7 +16816,7 @@
         <v>271</v>
       </c>
       <c r="Q129" s="43" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="R129" s="43" t="s">
         <v>755</v>
@@ -16477,23 +16843,23 @@
         <f t="shared" si="50"/>
         <v>Key-DOCU-129</v>
       </c>
-      <c r="Y129" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="Z129" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AA129" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AB129" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC129" s="43" t="s">
-        <v>767</v>
+      <c r="Y129" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z129" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA129" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB129" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC129" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="130" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="45">
         <v>130</v>
       </c>
@@ -16547,7 +16913,7 @@
         <v>280</v>
       </c>
       <c r="Q130" s="43" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="R130" s="43" t="s">
         <v>756</v>
@@ -16574,23 +16940,23 @@
         <f t="shared" si="50"/>
         <v>Key-DOCU-130</v>
       </c>
-      <c r="Y130" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="Z130" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AA130" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AB130" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC130" s="43" t="s">
-        <v>767</v>
+      <c r="Y130" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z130" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA130" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB130" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC130" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="131" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="45">
         <v>131</v>
       </c>
@@ -16644,7 +17010,7 @@
         <v>281</v>
       </c>
       <c r="Q131" s="43" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="R131" s="43" t="s">
         <v>757</v>
@@ -16671,23 +17037,23 @@
         <f t="shared" si="50"/>
         <v>Key-DOCU-131</v>
       </c>
-      <c r="Y131" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="Z131" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AA131" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AB131" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC131" s="43" t="s">
-        <v>767</v>
+      <c r="Y131" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z131" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA131" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB131" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC131" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="132" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="45">
         <v>132</v>
       </c>
@@ -16741,7 +17107,7 @@
         <v>282</v>
       </c>
       <c r="Q132" s="43" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="R132" s="43" t="s">
         <v>758</v>
@@ -16768,23 +17134,23 @@
         <f t="shared" si="50"/>
         <v>Key-DOCU-132</v>
       </c>
-      <c r="Y132" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="Z132" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AA132" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AB132" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC132" s="43" t="s">
-        <v>767</v>
+      <c r="Y132" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z132" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA132" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB132" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC132" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="133" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="45">
         <v>133</v>
       </c>
@@ -16838,7 +17204,7 @@
         <v>283</v>
       </c>
       <c r="Q133" s="43" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="R133" s="43" t="s">
         <v>759</v>
@@ -16865,23 +17231,23 @@
         <f t="shared" si="50"/>
         <v>Key-DOCU-133</v>
       </c>
-      <c r="Y133" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="Z133" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AA133" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AB133" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC133" s="43" t="s">
-        <v>767</v>
+      <c r="Y133" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z133" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA133" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB133" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC133" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="134" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="45">
         <v>134</v>
       </c>
@@ -16935,7 +17301,7 @@
         <v>278</v>
       </c>
       <c r="Q134" s="43" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="R134" s="43" t="s">
         <v>760</v>
@@ -16962,23 +17328,23 @@
         <f t="shared" si="50"/>
         <v>Key-DOCU-134</v>
       </c>
-      <c r="Y134" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="Z134" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AA134" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AB134" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC134" s="43" t="s">
-        <v>767</v>
+      <c r="Y134" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z134" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA134" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB134" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC134" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="135" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="45">
         <v>135</v>
       </c>
@@ -17032,7 +17398,7 @@
         <v>285</v>
       </c>
       <c r="Q135" s="43" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="R135" s="43" t="s">
         <v>761</v>
@@ -17059,23 +17425,23 @@
         <f t="shared" si="50"/>
         <v>Key-DOCU-135</v>
       </c>
-      <c r="Y135" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="Z135" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AA135" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AB135" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC135" s="43" t="s">
-        <v>767</v>
+      <c r="Y135" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z135" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA135" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB135" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC135" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="136" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="45">
         <v>136</v>
       </c>
@@ -17129,7 +17495,7 @@
         <v>289</v>
       </c>
       <c r="Q136" s="43" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="R136" s="43" t="s">
         <v>762</v>
@@ -17156,23 +17522,23 @@
         <f t="shared" si="50"/>
         <v>Key-DOCU-136</v>
       </c>
-      <c r="Y136" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="Z136" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AA136" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AB136" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC136" s="43" t="s">
-        <v>767</v>
+      <c r="Y136" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z136" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA136" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB136" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC136" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="137" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="45">
         <v>137</v>
       </c>
@@ -17226,7 +17592,7 @@
         <v>290</v>
       </c>
       <c r="Q137" s="43" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="R137" s="43" t="s">
         <v>763</v>
@@ -17253,54 +17619,154 @@
         <f t="shared" si="50"/>
         <v>Key-DOCU-137</v>
       </c>
-      <c r="Y137" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="Z137" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AA137" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AB137" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="AC137" s="43" t="s">
-        <v>767</v>
+      <c r="Y137" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z137" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA137" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB137" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC137" s="67" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="138" spans="1:29" s="68" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A138" s="45">
+        <v>138</v>
+      </c>
+      <c r="B138" s="62" t="s">
+        <v>899</v>
+      </c>
+      <c r="C138" s="63" t="s">
+        <v>900</v>
+      </c>
+      <c r="D138" s="63" t="s">
+        <v>901</v>
+      </c>
+      <c r="E138" s="63" t="s">
+        <v>902</v>
+      </c>
+      <c r="F138" s="63" t="s">
+        <v>903</v>
+      </c>
+      <c r="G138" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="H138" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="I138" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="J138" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="K138" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="L138" s="65" t="str">
+        <f t="shared" ref="L138:O138" si="60">SUBSTITUTE(CONCATENATE("", C138), ".", " ")</f>
+        <v>De API</v>
+      </c>
+      <c r="M138" s="65" t="str">
+        <f t="shared" si="60"/>
+        <v>Métodos</v>
+      </c>
+      <c r="N138" s="65" t="str">
+        <f t="shared" si="60"/>
+        <v>Macros</v>
+      </c>
+      <c r="O138" s="65" t="str">
+        <f t="shared" si="60"/>
+        <v>API Revit</v>
+      </c>
+      <c r="P138" s="66" t="s">
+        <v>904</v>
+      </c>
+      <c r="Q138" s="66" t="s">
+        <v>905</v>
+      </c>
+      <c r="R138" s="66" t="s">
+        <v>906</v>
+      </c>
+      <c r="S138" s="66" t="s">
+        <v>9</v>
+      </c>
+      <c r="T138" s="66" t="str">
+        <f t="shared" ref="T138:V138" si="61">SUBSTITUTE(C138, ".", " ")</f>
+        <v>De API</v>
+      </c>
+      <c r="U138" s="66" t="str">
+        <f t="shared" si="61"/>
+        <v>Métodos</v>
+      </c>
+      <c r="V138" s="43" t="str">
+        <f t="shared" si="61"/>
+        <v>Macros</v>
+      </c>
+      <c r="W138" s="43" t="s">
+        <v>80</v>
+      </c>
+      <c r="X138" s="54" t="str">
+        <f t="shared" si="50"/>
+        <v>Key-DOCU-138</v>
+      </c>
+      <c r="Y138" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z138" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA138" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB138" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC138" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A8:AC138">
     <sortCondition ref="A1:A138"/>
   </sortState>
-  <conditionalFormatting sqref="A2:B137">
-    <cfRule type="cellIs" dxfId="9" priority="7" operator="equal">
+  <conditionalFormatting sqref="A2:B138">
+    <cfRule type="cellIs" dxfId="33" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="duplicateValues" dxfId="8" priority="33"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="34"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="35"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="36"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="41"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F1:F1048576">
-    <cfRule type="duplicateValues" dxfId="3" priority="9"/>
+  <conditionalFormatting sqref="F1:F137 F139:F1048576">
+    <cfRule type="duplicateValues" dxfId="27" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F138">
+    <cfRule type="duplicateValues" dxfId="26" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G1:O1">
-    <cfRule type="cellIs" dxfId="2" priority="27" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="31" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R1:R137">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+  <conditionalFormatting sqref="R1:R138">
+    <cfRule type="cellIs" dxfId="24" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <ignoredErrors>
-    <ignoredError sqref="AC1 AC138:AC1048576 B36:D61 B95:D95 AD1:XFD1048576 F95:P95 B96:P117 F36:P61 B62:P94 B3:P11 A138:P1048576 A1:P2 AA8:AA122 S1:X1 S8:Y122 S2:X2 S3:X7 AA138:AA1048576 S138:Y1048576 S123:X123 S124:X137 B120:P137 B119:P119 B118:P118 B13:P21 B12:P12 B23:P35 B22:P22" numberStoredAsText="1"/>
+    <ignoredError sqref="AC1 AC139:AC1048576 B36:D61 B95:D95 AD1:XFD137 F95:P95 B96:P117 F36:P61 B62:P94 B3:P11 A139:P1048576 A1:P2 AA8:AA122 S1:X1 S8:Y121 S2:X2 S3:X7 AA139:AA1048576 S139:Y1048576 S123:V123 S124:V134 B120:P137 B119:P119 B118:P118 B13:P21 B12:P12 B23:P35 B22:P22 AD139:XFD1048576 S135:V137 S122:V122 X122:Y122 X123 X124:X134" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -17308,14 +17774,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{779E4F22-2568-4D5A-A538-DD63A5C43724}">
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultColWidth="5.69140625" defaultRowHeight="7.95" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="5.7109375" defaultRowHeight="7.9" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.69140625" style="11" customWidth="1"/>
-    <col min="2" max="10" width="5.69140625" style="12"/>
-    <col min="11" max="16384" width="5.69140625" style="24"/>
+    <col min="1" max="1" width="2.7109375" style="11" customWidth="1"/>
+    <col min="2" max="10" width="5.7109375" style="12"/>
+    <col min="11" max="16384" width="5.7109375" style="24"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="7.75" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" ht="16.5" x14ac:dyDescent="0.15">
       <c r="A1" s="22">
         <v>1</v>
       </c>
@@ -17380,7 +17846,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="7.75" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21" ht="8.25" x14ac:dyDescent="0.15">
       <c r="A2" s="22">
         <v>2</v>
       </c>
@@ -17453,15 +17919,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4328B84A-AA24-421E-9F4E-92D6A71CA3BE}">
   <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="3" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.15234375" style="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" style="13" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="11" style="13" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="9.15234375" style="13"/>
+    <col min="5" max="16384" width="9.140625" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="8">
         <v>1</v>
       </c>
@@ -17475,7 +17941,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" ht="6.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="7">
         <v>2</v>
       </c>
@@ -17496,33 +17962,49 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{429087C4-377B-4931-BC50-C00BD9684F83}">
-  <dimension ref="A1:U37"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:AK42"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="1.765625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.23046875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.765625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.61328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.23046875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.23046875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="3.765625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="2.3828125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="2.84375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="2.3828125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="2.84375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="2.3828125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="2.84375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="4.07421875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="58.4609375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="5.69140625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.07421875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="3.765625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="5.61328125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="2.3828125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.07421875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="6" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="81.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.85546875" customWidth="1"/>
+    <col min="18" max="18" width="6.7109375" customWidth="1"/>
+    <col min="19" max="19" width="7" customWidth="1"/>
+    <col min="20" max="20" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12.140625" customWidth="1"/>
+    <col min="22" max="22" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="4.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="24.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:37" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="14" t="s">
         <v>30</v>
       </c>
@@ -17586,8 +18068,56 @@
       <c r="U1" s="15" t="s">
         <v>2</v>
       </c>
+      <c r="V1" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="W1" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="X1" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="Y1" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z1" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="AA1" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="AB1" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="AC1" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="AD1" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="AE1" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="AF1" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="AG1" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="AH1" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="AI1" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="AJ1" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="AK1" s="15" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="2" spans="1:21" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="16">
         <v>2</v>
       </c>
@@ -17651,8 +18181,56 @@
       <c r="U2" s="21" t="s">
         <v>9</v>
       </c>
+      <c r="V2" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="W2" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="X2" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y2" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z2" s="76" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA2" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB2" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC2" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD2" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE2" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF2" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG2" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH2" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI2" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ2" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK2" s="75" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="3" spans="1:21" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="16">
         <v>3</v>
       </c>
@@ -17716,8 +18294,56 @@
       <c r="U3" s="21" t="s">
         <v>9</v>
       </c>
+      <c r="V3" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="W3" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="X3" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y3" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z3" s="76" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA3" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB3" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC3" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD3" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE3" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF3" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG3" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH3" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI3" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ3" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK3" s="75" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="4" spans="1:21" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="16">
         <v>4</v>
       </c>
@@ -17781,8 +18407,56 @@
       <c r="U4" s="21" t="s">
         <v>9</v>
       </c>
+      <c r="V4" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="W4" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="X4" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y4" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z4" s="76" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA4" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB4" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC4" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD4" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE4" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF4" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG4" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH4" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI4" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ4" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK4" s="75" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="5" spans="1:21" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="16">
         <v>5</v>
       </c>
@@ -17846,8 +18520,56 @@
       <c r="U5" s="21" t="s">
         <v>9</v>
       </c>
+      <c r="V5" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="W5" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="X5" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y5" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z5" s="76" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA5" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB5" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC5" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD5" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE5" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF5" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG5" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH5" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI5" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ5" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK5" s="75" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="6" spans="1:21" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="16">
         <v>6</v>
       </c>
@@ -17911,8 +18633,56 @@
       <c r="U6" s="21" t="s">
         <v>9</v>
       </c>
+      <c r="V6" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="W6" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="X6" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y6" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z6" s="76" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA6" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB6" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC6" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD6" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE6" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF6" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG6" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH6" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI6" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ6" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK6" s="75" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="7" spans="1:21" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="16">
         <v>7</v>
       </c>
@@ -17976,8 +18746,56 @@
       <c r="U7" s="21" t="s">
         <v>611</v>
       </c>
+      <c r="V7" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="W7" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="X7" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y7" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z7" s="76" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA7" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB7" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC7" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD7" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE7" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF7" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG7" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH7" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI7" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ7" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK7" s="75" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="8" spans="1:21" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="16">
         <v>8</v>
       </c>
@@ -18041,8 +18859,56 @@
       <c r="U8" s="21" t="s">
         <v>9</v>
       </c>
+      <c r="V8" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="W8" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="X8" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y8" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z8" s="76" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA8" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB8" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC8" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD8" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE8" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF8" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG8" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH8" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI8" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ8" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK8" s="75" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="9" spans="1:21" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="16">
         <v>9</v>
       </c>
@@ -18106,8 +18972,56 @@
       <c r="U9" s="21" t="s">
         <v>9</v>
       </c>
+      <c r="V9" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="W9" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="X9" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y9" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z9" s="76" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA9" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB9" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC9" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD9" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE9" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF9" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG9" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH9" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI9" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ9" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK9" s="75" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="10" spans="1:21" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="16">
         <v>10</v>
       </c>
@@ -18171,8 +19085,56 @@
       <c r="U10" s="21" t="s">
         <v>9</v>
       </c>
+      <c r="V10" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="W10" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="X10" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y10" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z10" s="76" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA10" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB10" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC10" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD10" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE10" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF10" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG10" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH10" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI10" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ10" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK10" s="75" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="11" spans="1:21" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="16">
         <v>11</v>
       </c>
@@ -18236,8 +19198,56 @@
       <c r="U11" s="21" t="s">
         <v>9</v>
       </c>
+      <c r="V11" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="W11" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="X11" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y11" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z11" s="76" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA11" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB11" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC11" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD11" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE11" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF11" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG11" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH11" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI11" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ11" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK11" s="75" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="12" spans="1:21" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="16">
         <v>12</v>
       </c>
@@ -18301,8 +19311,56 @@
       <c r="U12" s="21" t="s">
         <v>9</v>
       </c>
+      <c r="V12" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="W12" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="X12" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y12" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z12" s="76" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA12" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB12" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC12" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD12" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE12" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF12" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG12" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH12" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI12" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ12" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK12" s="75" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="13" spans="1:21" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="16">
         <v>13</v>
       </c>
@@ -18366,8 +19424,56 @@
       <c r="U13" s="21" t="s">
         <v>9</v>
       </c>
+      <c r="V13" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="W13" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="X13" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y13" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z13" s="76" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA13" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB13" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC13" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD13" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE13" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF13" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG13" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH13" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI13" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ13" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK13" s="75" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="14" spans="1:21" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="16">
         <v>14</v>
       </c>
@@ -18431,8 +19537,56 @@
       <c r="U14" s="21" t="s">
         <v>9</v>
       </c>
+      <c r="V14" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="W14" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="X14" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y14" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z14" s="76" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA14" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB14" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC14" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD14" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE14" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF14" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG14" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH14" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI14" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ14" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK14" s="75" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="15" spans="1:21" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="16">
         <v>15</v>
       </c>
@@ -18496,8 +19650,56 @@
       <c r="U15" s="21" t="s">
         <v>9</v>
       </c>
+      <c r="V15" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="W15" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="X15" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y15" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z15" s="76" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA15" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB15" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC15" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD15" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE15" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF15" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG15" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH15" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI15" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ15" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK15" s="75" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="16" spans="1:21" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="16">
         <v>16</v>
       </c>
@@ -18561,8 +19763,56 @@
       <c r="U16" s="21" t="s">
         <v>9</v>
       </c>
+      <c r="V16" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="W16" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="X16" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y16" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z16" s="76" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA16" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB16" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC16" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD16" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE16" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF16" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG16" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH16" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI16" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ16" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK16" s="75" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="17" spans="1:21" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="16">
         <v>17</v>
       </c>
@@ -18626,8 +19876,56 @@
       <c r="U17" s="21" t="s">
         <v>9</v>
       </c>
+      <c r="V17" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="W17" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="X17" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y17" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z17" s="76" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA17" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB17" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC17" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD17" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE17" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF17" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG17" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH17" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI17" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ17" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK17" s="75" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="18" spans="1:21" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="16">
         <v>18</v>
       </c>
@@ -18691,8 +19989,56 @@
       <c r="U18" s="21" t="s">
         <v>9</v>
       </c>
+      <c r="V18" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="W18" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="X18" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y18" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z18" s="76" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA18" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB18" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC18" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD18" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE18" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF18" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG18" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH18" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI18" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ18" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK18" s="75" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="19" spans="1:21" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="16">
         <v>19</v>
       </c>
@@ -18756,8 +20102,56 @@
       <c r="U19" s="21" t="s">
         <v>9</v>
       </c>
+      <c r="V19" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="W19" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="X19" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y19" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z19" s="76" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA19" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB19" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC19" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD19" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE19" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF19" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG19" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH19" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI19" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ19" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK19" s="75" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="20" spans="1:21" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="16">
         <v>20</v>
       </c>
@@ -18821,8 +20215,56 @@
       <c r="U20" s="21" t="s">
         <v>9</v>
       </c>
+      <c r="V20" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="W20" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="X20" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y20" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z20" s="76" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA20" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB20" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC20" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD20" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE20" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF20" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG20" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH20" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI20" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ20" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK20" s="75" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="21" spans="1:21" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="16">
         <v>21</v>
       </c>
@@ -18886,8 +20328,56 @@
       <c r="U21" s="21" t="s">
         <v>9</v>
       </c>
+      <c r="V21" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="W21" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="X21" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y21" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z21" s="76" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA21" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB21" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC21" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD21" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE21" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF21" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG21" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH21" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI21" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ21" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK21" s="75" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="22" spans="1:21" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="16">
         <v>22</v>
       </c>
@@ -18951,8 +20441,56 @@
       <c r="U22" s="21" t="s">
         <v>9</v>
       </c>
+      <c r="V22" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="W22" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="X22" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y22" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z22" s="76" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA22" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB22" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC22" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD22" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE22" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF22" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG22" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH22" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI22" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ22" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK22" s="75" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="23" spans="1:21" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="16">
         <v>23</v>
       </c>
@@ -19016,8 +20554,56 @@
       <c r="U23" s="21" t="s">
         <v>9</v>
       </c>
+      <c r="V23" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="W23" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="X23" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y23" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z23" s="76" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA23" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB23" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC23" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD23" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE23" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF23" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG23" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH23" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI23" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ23" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK23" s="75" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="24" spans="1:21" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="16">
         <v>24</v>
       </c>
@@ -19081,8 +20667,56 @@
       <c r="U24" s="21" t="s">
         <v>9</v>
       </c>
+      <c r="V24" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="W24" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="X24" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y24" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z24" s="76" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA24" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB24" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC24" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD24" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE24" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF24" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG24" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH24" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI24" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ24" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK24" s="75" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="25" spans="1:21" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="16">
         <v>25</v>
       </c>
@@ -19146,8 +20780,56 @@
       <c r="U25" s="21" t="s">
         <v>9</v>
       </c>
+      <c r="V25" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="W25" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="X25" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y25" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z25" s="76" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA25" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB25" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC25" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD25" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE25" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF25" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG25" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH25" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI25" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ25" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK25" s="75" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="26" spans="1:21" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="16">
         <v>26</v>
       </c>
@@ -19211,8 +20893,56 @@
       <c r="U26" s="21" t="s">
         <v>9</v>
       </c>
+      <c r="V26" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="W26" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="X26" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y26" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z26" s="76" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA26" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB26" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC26" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD26" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE26" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF26" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG26" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH26" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI26" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ26" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK26" s="75" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="27" spans="1:21" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="16">
         <v>27</v>
       </c>
@@ -19276,8 +21006,56 @@
       <c r="U27" s="21" t="s">
         <v>9</v>
       </c>
+      <c r="V27" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="W27" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="X27" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y27" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z27" s="76" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA27" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB27" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC27" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD27" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE27" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF27" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG27" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH27" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI27" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ27" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK27" s="75" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="28" spans="1:21" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="16">
         <v>28</v>
       </c>
@@ -19341,8 +21119,56 @@
       <c r="U28" s="21" t="s">
         <v>9</v>
       </c>
+      <c r="V28" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="W28" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="X28" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y28" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z28" s="76" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA28" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB28" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC28" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD28" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE28" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF28" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG28" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH28" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI28" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ28" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK28" s="75" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="29" spans="1:21" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="16">
         <v>29</v>
       </c>
@@ -19406,8 +21232,56 @@
       <c r="U29" s="21" t="s">
         <v>9</v>
       </c>
+      <c r="V29" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="W29" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="X29" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y29" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z29" s="76" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA29" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB29" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC29" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD29" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE29" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF29" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG29" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH29" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI29" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ29" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK29" s="75" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="30" spans="1:21" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="16">
         <v>30</v>
       </c>
@@ -19471,8 +21345,56 @@
       <c r="U30" s="21" t="s">
         <v>9</v>
       </c>
+      <c r="V30" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="W30" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="X30" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y30" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z30" s="76" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA30" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB30" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC30" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD30" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE30" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF30" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG30" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH30" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI30" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ30" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK30" s="75" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="31" spans="1:21" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="16">
         <v>31</v>
       </c>
@@ -19536,8 +21458,56 @@
       <c r="U31" s="21" t="s">
         <v>9</v>
       </c>
+      <c r="V31" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="W31" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="X31" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y31" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z31" s="76" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA31" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB31" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC31" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD31" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE31" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF31" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG31" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH31" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI31" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ31" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK31" s="75" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="32" spans="1:21" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="16">
         <v>32</v>
       </c>
@@ -19601,8 +21571,56 @@
       <c r="U32" s="21" t="s">
         <v>9</v>
       </c>
+      <c r="V32" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="W32" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="X32" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y32" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z32" s="76" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA32" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB32" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC32" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD32" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE32" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF32" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG32" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH32" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI32" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ32" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK32" s="75" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="33" spans="1:21" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="16">
         <v>33</v>
       </c>
@@ -19666,8 +21684,56 @@
       <c r="U33" s="21" t="s">
         <v>9</v>
       </c>
+      <c r="V33" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="W33" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="X33" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y33" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z33" s="76" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA33" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB33" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC33" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD33" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE33" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF33" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG33" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH33" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI33" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ33" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK33" s="75" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="34" spans="1:21" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="16">
         <v>34</v>
       </c>
@@ -19731,8 +21797,56 @@
       <c r="U34" s="21" t="s">
         <v>9</v>
       </c>
+      <c r="V34" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="W34" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="X34" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y34" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z34" s="76" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA34" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB34" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC34" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD34" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE34" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF34" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG34" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH34" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI34" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ34" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK34" s="75" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="35" spans="1:21" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="16">
         <v>35</v>
       </c>
@@ -19796,8 +21910,56 @@
       <c r="U35" s="21" t="s">
         <v>9</v>
       </c>
+      <c r="V35" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="W35" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="X35" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y35" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z35" s="76" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA35" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB35" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC35" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD35" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE35" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF35" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG35" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH35" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI35" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ35" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK35" s="75" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="36" spans="1:21" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="16">
         <v>36</v>
       </c>
@@ -19861,8 +22023,56 @@
       <c r="U36" s="21" t="s">
         <v>9</v>
       </c>
+      <c r="V36" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="W36" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="X36" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y36" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z36" s="76" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA36" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB36" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC36" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD36" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE36" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF36" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG36" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH36" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI36" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ36" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK36" s="75" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="37" spans="1:21" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="16">
         <v>37</v>
       </c>
@@ -19924,13 +22134,675 @@
         <v>9</v>
       </c>
       <c r="U37" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="V37" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="W37" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="X37" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y37" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z37" s="76" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA37" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB37" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC37" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD37" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE37" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF37" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG37" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH37" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI37" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ37" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK37" s="75" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="38" spans="1:37" s="73" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="16">
+        <v>38</v>
+      </c>
+      <c r="B38" s="69" t="s">
+        <v>907</v>
+      </c>
+      <c r="C38" s="63" t="s">
+        <v>903</v>
+      </c>
+      <c r="D38" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E38" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="F38" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="G38" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="H38" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="I38" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J38" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="K38" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="L38" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="M38" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="N38" s="70" t="s">
+        <v>16</v>
+      </c>
+      <c r="O38" s="21" t="s">
+        <v>912</v>
+      </c>
+      <c r="P38" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q38" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="R38" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S38" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="T38" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="U38" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="V38" s="30" t="s">
+        <v>908</v>
+      </c>
+      <c r="W38" s="21" t="s">
+        <v>909</v>
+      </c>
+      <c r="X38" s="30" t="s">
+        <v>910</v>
+      </c>
+      <c r="Y38" s="21" t="s">
+        <v>911</v>
+      </c>
+      <c r="Z38" s="71" t="str">
+        <f t="shared" ref="Z38:Z42" si="0">IF(AA38="null", "null", "método.revit")</f>
+        <v>método.revit</v>
+      </c>
+      <c r="AA38" s="72" t="s">
+        <v>913</v>
+      </c>
+      <c r="AB38" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC38" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD38" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE38" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF38" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG38" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH38" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI38" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ38" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK38" s="75" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="39" spans="1:37" s="73" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="16">
+        <v>39</v>
+      </c>
+      <c r="B39" s="69" t="s">
+        <v>914</v>
+      </c>
+      <c r="C39" s="63" t="s">
+        <v>903</v>
+      </c>
+      <c r="D39" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E39" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="F39" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="G39" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="H39" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="I39" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J39" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="K39" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="L39" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="M39" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="N39" s="70" t="s">
+        <v>16</v>
+      </c>
+      <c r="O39" s="21" t="s">
+        <v>916</v>
+      </c>
+      <c r="P39" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q39" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="R39" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S39" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="T39" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="U39" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="V39" s="30" t="s">
+        <v>908</v>
+      </c>
+      <c r="W39" s="21" t="s">
+        <v>909</v>
+      </c>
+      <c r="X39" s="30" t="s">
+        <v>910</v>
+      </c>
+      <c r="Y39" s="21" t="s">
+        <v>915</v>
+      </c>
+      <c r="Z39" s="71" t="str">
+        <f t="shared" si="0"/>
+        <v>método.revit</v>
+      </c>
+      <c r="AA39" s="72" t="s">
+        <v>917</v>
+      </c>
+      <c r="AB39" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC39" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD39" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE39" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF39" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG39" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH39" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI39" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ39" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK39" s="75" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="40" spans="1:37" s="73" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="16">
+        <v>40</v>
+      </c>
+      <c r="B40" s="69" t="s">
+        <v>918</v>
+      </c>
+      <c r="C40" s="63" t="s">
+        <v>903</v>
+      </c>
+      <c r="D40" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E40" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="F40" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="G40" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="H40" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="I40" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J40" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="K40" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="L40" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="M40" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="N40" s="70" t="s">
+        <v>16</v>
+      </c>
+      <c r="O40" s="21" t="s">
+        <v>920</v>
+      </c>
+      <c r="P40" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q40" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="R40" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S40" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="T40" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="U40" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="V40" s="30" t="s">
+        <v>908</v>
+      </c>
+      <c r="W40" s="21" t="s">
+        <v>909</v>
+      </c>
+      <c r="X40" s="30" t="s">
+        <v>910</v>
+      </c>
+      <c r="Y40" s="21" t="s">
+        <v>919</v>
+      </c>
+      <c r="Z40" s="71" t="str">
+        <f t="shared" si="0"/>
+        <v>método.revit</v>
+      </c>
+      <c r="AA40" s="72" t="s">
+        <v>921</v>
+      </c>
+      <c r="AB40" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC40" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD40" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE40" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF40" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG40" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH40" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI40" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ40" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK40" s="75" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="41" spans="1:37" s="73" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="16">
+        <v>41</v>
+      </c>
+      <c r="B41" s="69" t="s">
+        <v>922</v>
+      </c>
+      <c r="C41" s="63" t="s">
+        <v>903</v>
+      </c>
+      <c r="D41" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E41" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="F41" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="G41" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="H41" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="I41" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J41" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="K41" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="L41" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="M41" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="N41" s="70" t="s">
+        <v>16</v>
+      </c>
+      <c r="O41" s="21" t="s">
+        <v>924</v>
+      </c>
+      <c r="P41" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q41" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="R41" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S41" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="T41" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="U41" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="V41" s="30" t="s">
+        <v>908</v>
+      </c>
+      <c r="W41" s="21" t="s">
+        <v>909</v>
+      </c>
+      <c r="X41" s="30" t="s">
+        <v>910</v>
+      </c>
+      <c r="Y41" s="21" t="s">
+        <v>923</v>
+      </c>
+      <c r="Z41" s="71" t="str">
+        <f t="shared" si="0"/>
+        <v>método.revit</v>
+      </c>
+      <c r="AA41" s="72" t="s">
+        <v>925</v>
+      </c>
+      <c r="AB41" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC41" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD41" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE41" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF41" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG41" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH41" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI41" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ41" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK41" s="75" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="42" spans="1:37" s="73" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="16">
+        <v>42</v>
+      </c>
+      <c r="B42" s="69" t="s">
+        <v>926</v>
+      </c>
+      <c r="C42" s="63" t="s">
+        <v>903</v>
+      </c>
+      <c r="D42" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E42" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="F42" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="G42" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="H42" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="I42" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J42" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="K42" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="L42" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="M42" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="N42" s="70" t="s">
+        <v>16</v>
+      </c>
+      <c r="O42" s="21" t="s">
+        <v>928</v>
+      </c>
+      <c r="P42" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q42" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="R42" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S42" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="T42" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="U42" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="V42" s="30" t="s">
+        <v>908</v>
+      </c>
+      <c r="W42" s="21" t="s">
+        <v>909</v>
+      </c>
+      <c r="X42" s="30" t="s">
+        <v>910</v>
+      </c>
+      <c r="Y42" s="21" t="s">
+        <v>927</v>
+      </c>
+      <c r="Z42" s="71" t="str">
+        <f t="shared" si="0"/>
+        <v>método.revit</v>
+      </c>
+      <c r="AA42" s="72" t="s">
+        <v>929</v>
+      </c>
+      <c r="AB42" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC42" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD42" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE42" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF42" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG42" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH42" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI42" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ42" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK42" s="75" t="s">
         <v>9</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="9" type="noConversion"/>
   <conditionalFormatting sqref="B18:B37 B1:B13">
-    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="34"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B38:B42">
+    <cfRule type="duplicateValues" dxfId="15" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X38:AA42 Z2:AA42">
+    <cfRule type="cellIs" dxfId="13" priority="14" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD2:AE42">
+    <cfRule type="cellIs" dxfId="11" priority="12" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AF2:AG42">
+    <cfRule type="cellIs" dxfId="10" priority="11" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AH2:AI42">
+    <cfRule type="cellIs" dxfId="9" priority="10" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AJ2:AK42">
+    <cfRule type="cellIs" dxfId="8" priority="9" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AB2:AC42">
+    <cfRule type="cellIs" dxfId="6" priority="7" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X38:Y42">
+    <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V38:W42">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/Versão5/PRO/Ontologia_Documentos.xlsx
+++ b/Versão5/PRO/Ontologia_Documentos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\PRO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86524CD3-531E-48FE-A04E-B45EAB2B1CB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2B84308-F06C-4F6E-8EB9-65AEB6FA65C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="527" activeTab="4" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="527" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="31" r:id="rId1"/>
@@ -3426,163 +3426,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="34">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
+  <dxfs count="15">
     <dxf>
       <font>
         <b val="0"/>
@@ -4040,15 +3884,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1124724F-B8C4-4B86-9028-743FC73CDDB0}">
   <dimension ref="A1:C24"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="10.5" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="53.7109375" style="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="3.42578125" style="42" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.140625" style="13"/>
+    <col min="1" max="1" width="10.3828125" style="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="53.69140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3.3828125" style="42" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.15234375" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="10" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" s="10" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -4059,7 +3903,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>17</v>
       </c>
@@ -4070,7 +3914,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>18</v>
       </c>
@@ -4081,7 +3925,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
@@ -4092,7 +3936,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
@@ -4104,7 +3948,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>8</v>
       </c>
@@ -4116,7 +3960,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>4</v>
       </c>
@@ -4127,7 +3971,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="8" spans="1:3" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="2" t="s">
         <v>5</v>
       </c>
@@ -4138,7 +3982,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>20</v>
       </c>
@@ -4149,7 +3993,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>22</v>
       </c>
@@ -4160,7 +4004,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>0</v>
       </c>
@@ -4171,7 +4015,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>1</v>
       </c>
@@ -4182,7 +4026,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>23</v>
       </c>
@@ -4193,7 +4037,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>24</v>
       </c>
@@ -4204,7 +4048,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>25</v>
       </c>
@@ -4215,7 +4059,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>26</v>
       </c>
@@ -4226,7 +4070,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>10</v>
       </c>
@@ -4237,19 +4081,19 @@
         <v>304</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B18" s="5">
         <f ca="1">NOW()</f>
-        <v>46259.689483680559</v>
+        <v>46264.568395486109</v>
       </c>
       <c r="C18" s="41" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>28</v>
       </c>
@@ -4260,7 +4104,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>29</v>
       </c>
@@ -4271,7 +4115,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>11</v>
       </c>
@@ -4282,7 +4126,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:3" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
         <v>34</v>
       </c>
@@ -4293,7 +4137,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:3" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
         <v>35</v>
       </c>
@@ -4304,7 +4148,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="24" spans="1:3" s="39" customFormat="1" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" s="39" customFormat="1" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="4" t="s">
         <v>302</v>
       </c>
@@ -4324,37 +4168,37 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19BE914A-3965-4A61-9195-D2681A91581F}">
   <dimension ref="A1:AC138"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.140625" style="61" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.28515625" style="44" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.42578125" style="44" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.42578125" style="44" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.85546875" style="44" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5703125" style="44" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="6.42578125" style="44" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="5.42578125" style="44" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.42578125" style="44" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.15234375" style="61" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.3046875" style="44" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.3828125" style="44" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.3828125" style="44" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.84375" style="44" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.53515625" style="44" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="6.3828125" style="44" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.3828125" style="44" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.3828125" style="44" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12" style="44" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.85546875" style="44" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="39.140625" style="44" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="42.7109375" style="44" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="33.28515625" style="44" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="3.7109375" style="44" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="5.42578125" style="44" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="12.42578125" style="44" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="11.85546875" style="44" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="8.5703125" style="44" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="6.5703125" style="44" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="21.5703125" style="44" customWidth="1"/>
-    <col min="26" max="26" width="13.5703125" style="44" customWidth="1"/>
-    <col min="27" max="27" width="16.140625" style="44" customWidth="1"/>
-    <col min="28" max="28" width="6.28515625" style="44" customWidth="1"/>
-    <col min="29" max="29" width="4.28515625" style="44" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="44"/>
+    <col min="15" max="15" width="13.84375" style="44" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="39.15234375" style="44" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="42.69140625" style="44" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="33.3046875" style="44" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="3.69140625" style="44" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.3828125" style="44" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12.3828125" style="44" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.84375" style="44" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="8.53515625" style="44" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="6.53515625" style="44" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="21.53515625" style="44" customWidth="1"/>
+    <col min="26" max="26" width="13.53515625" style="44" customWidth="1"/>
+    <col min="27" max="27" width="16.15234375" style="44" customWidth="1"/>
+    <col min="28" max="28" width="6.3046875" style="44" customWidth="1"/>
+    <col min="29" max="29" width="4.3046875" style="44" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.15234375" style="44"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:29" ht="39.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="60" t="s">
         <v>36</v>
       </c>
@@ -4443,7 +4287,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="2" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="45">
         <v>2</v>
       </c>
@@ -4540,7 +4384,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="45">
         <v>3</v>
       </c>
@@ -4637,7 +4481,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="45">
         <v>4</v>
       </c>
@@ -4734,7 +4578,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="45">
         <v>5</v>
       </c>
@@ -4831,7 +4675,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="45">
         <v>6</v>
       </c>
@@ -4928,7 +4772,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="45">
         <v>7</v>
       </c>
@@ -5025,7 +4869,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="45">
         <v>8</v>
       </c>
@@ -5122,7 +4966,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="45">
         <v>9</v>
       </c>
@@ -5219,7 +5063,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="45">
         <v>10</v>
       </c>
@@ -5316,7 +5160,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="45">
         <v>11</v>
       </c>
@@ -5413,7 +5257,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="45">
         <v>12</v>
       </c>
@@ -5510,7 +5354,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="45">
         <v>13</v>
       </c>
@@ -5607,7 +5451,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="45">
         <v>14</v>
       </c>
@@ -5704,7 +5548,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="45">
         <v>15</v>
       </c>
@@ -5801,7 +5645,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="45">
         <v>16</v>
       </c>
@@ -5898,7 +5742,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="45">
         <v>17</v>
       </c>
@@ -5995,7 +5839,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="45">
         <v>18</v>
       </c>
@@ -6092,7 +5936,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="45">
         <v>19</v>
       </c>
@@ -6189,7 +6033,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="45">
         <v>20</v>
       </c>
@@ -6286,7 +6130,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="45">
         <v>21</v>
       </c>
@@ -6383,7 +6227,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="45">
         <v>22</v>
       </c>
@@ -6480,7 +6324,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="45">
         <v>23</v>
       </c>
@@ -6577,7 +6421,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="45">
         <v>24</v>
       </c>
@@ -6674,7 +6518,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="45">
         <v>25</v>
       </c>
@@ -6771,7 +6615,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="45">
         <v>26</v>
       </c>
@@ -6868,7 +6712,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="45">
         <v>27</v>
       </c>
@@ -6965,7 +6809,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="45">
         <v>28</v>
       </c>
@@ -7062,7 +6906,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="45">
         <v>29</v>
       </c>
@@ -7159,7 +7003,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="30" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="45">
         <v>30</v>
       </c>
@@ -7256,7 +7100,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="45">
         <v>31</v>
       </c>
@@ -7353,7 +7197,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="45">
         <v>32</v>
       </c>
@@ -7450,7 +7294,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="33" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="45">
         <v>33</v>
       </c>
@@ -7547,7 +7391,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="45">
         <v>34</v>
       </c>
@@ -7644,7 +7488,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="45">
         <v>35</v>
       </c>
@@ -7741,7 +7585,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="45">
         <v>36</v>
       </c>
@@ -7838,7 +7682,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="37" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="45">
         <v>37</v>
       </c>
@@ -7935,7 +7779,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="45">
         <v>38</v>
       </c>
@@ -8032,7 +7876,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="39" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="45">
         <v>39</v>
       </c>
@@ -8129,7 +7973,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="40" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" s="45">
         <v>40</v>
       </c>
@@ -8226,7 +8070,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="41" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="45">
         <v>41</v>
       </c>
@@ -8323,7 +8167,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" s="45">
         <v>42</v>
       </c>
@@ -8420,7 +8264,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="43" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A43" s="45">
         <v>43</v>
       </c>
@@ -8517,7 +8361,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="44" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A44" s="45">
         <v>44</v>
       </c>
@@ -8614,7 +8458,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="45" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A45" s="45">
         <v>45</v>
       </c>
@@ -8711,7 +8555,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="46" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A46" s="45">
         <v>46</v>
       </c>
@@ -8808,7 +8652,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="47" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A47" s="45">
         <v>47</v>
       </c>
@@ -8905,7 +8749,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="48" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A48" s="45">
         <v>48</v>
       </c>
@@ -9002,7 +8846,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="49" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="45">
         <v>49</v>
       </c>
@@ -9099,7 +8943,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="50" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A50" s="45">
         <v>50</v>
       </c>
@@ -9196,7 +9040,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="51" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A51" s="45">
         <v>51</v>
       </c>
@@ -9293,7 +9137,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="52" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A52" s="45">
         <v>52</v>
       </c>
@@ -9390,7 +9234,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="53" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A53" s="45">
         <v>53</v>
       </c>
@@ -9487,7 +9331,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="54" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A54" s="45">
         <v>54</v>
       </c>
@@ -9584,7 +9428,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="55" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A55" s="45">
         <v>55</v>
       </c>
@@ -9681,7 +9525,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="56" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A56" s="45">
         <v>56</v>
       </c>
@@ -9778,7 +9622,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="57" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A57" s="45">
         <v>57</v>
       </c>
@@ -9875,7 +9719,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="58" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="45">
         <v>58</v>
       </c>
@@ -9972,7 +9816,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="59" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" s="45">
         <v>59</v>
       </c>
@@ -10069,7 +9913,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="60" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" s="45">
         <v>60</v>
       </c>
@@ -10166,7 +10010,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="61" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="45">
         <v>61</v>
       </c>
@@ -10263,7 +10107,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="62" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A62" s="45">
         <v>62</v>
       </c>
@@ -10360,7 +10204,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="63" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A63" s="45">
         <v>63</v>
       </c>
@@ -10457,7 +10301,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="64" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A64" s="45">
         <v>64</v>
       </c>
@@ -10554,7 +10398,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="65" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65" s="45">
         <v>65</v>
       </c>
@@ -10651,7 +10495,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="66" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" s="45">
         <v>66</v>
       </c>
@@ -10748,7 +10592,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="67" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="45">
         <v>67</v>
       </c>
@@ -10845,7 +10689,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="68" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" s="45">
         <v>68</v>
       </c>
@@ -10942,7 +10786,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="69" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A69" s="45">
         <v>69</v>
       </c>
@@ -11039,7 +10883,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="70" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A70" s="45">
         <v>70</v>
       </c>
@@ -11136,7 +10980,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="71" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A71" s="45">
         <v>71</v>
       </c>
@@ -11233,7 +11077,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="72" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A72" s="45">
         <v>72</v>
       </c>
@@ -11330,7 +11174,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="73" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A73" s="45">
         <v>73</v>
       </c>
@@ -11427,7 +11271,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="74" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A74" s="45">
         <v>74</v>
       </c>
@@ -11524,7 +11368,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="75" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A75" s="45">
         <v>75</v>
       </c>
@@ -11621,7 +11465,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="76" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A76" s="45">
         <v>76</v>
       </c>
@@ -11718,7 +11562,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="77" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A77" s="45">
         <v>77</v>
       </c>
@@ -11815,7 +11659,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="78" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A78" s="45">
         <v>78</v>
       </c>
@@ -11912,7 +11756,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="79" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A79" s="45">
         <v>79</v>
       </c>
@@ -12009,7 +11853,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="80" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A80" s="45">
         <v>80</v>
       </c>
@@ -12106,7 +11950,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="81" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A81" s="45">
         <v>81</v>
       </c>
@@ -12203,7 +12047,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="82" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A82" s="45">
         <v>82</v>
       </c>
@@ -12300,7 +12144,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="83" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A83" s="45">
         <v>83</v>
       </c>
@@ -12397,7 +12241,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="84" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A84" s="45">
         <v>84</v>
       </c>
@@ -12494,7 +12338,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="85" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A85" s="45">
         <v>85</v>
       </c>
@@ -12591,7 +12435,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="86" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A86" s="45">
         <v>86</v>
       </c>
@@ -12688,7 +12532,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="87" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A87" s="45">
         <v>87</v>
       </c>
@@ -12785,7 +12629,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="88" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A88" s="45">
         <v>88</v>
       </c>
@@ -12882,7 +12726,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="89" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A89" s="45">
         <v>89</v>
       </c>
@@ -12979,7 +12823,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="90" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A90" s="45">
         <v>90</v>
       </c>
@@ -13076,7 +12920,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="91" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A91" s="45">
         <v>91</v>
       </c>
@@ -13173,7 +13017,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="92" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A92" s="45">
         <v>92</v>
       </c>
@@ -13270,7 +13114,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="93" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A93" s="45">
         <v>93</v>
       </c>
@@ -13367,7 +13211,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="94" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A94" s="45">
         <v>94</v>
       </c>
@@ -13464,7 +13308,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="95" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A95" s="45">
         <v>95</v>
       </c>
@@ -13561,7 +13405,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="96" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A96" s="45">
         <v>96</v>
       </c>
@@ -13658,7 +13502,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="97" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A97" s="45">
         <v>97</v>
       </c>
@@ -13755,7 +13599,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="98" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A98" s="45">
         <v>98</v>
       </c>
@@ -13852,7 +13696,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="99" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A99" s="45">
         <v>99</v>
       </c>
@@ -13949,7 +13793,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="100" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A100" s="45">
         <v>100</v>
       </c>
@@ -14046,7 +13890,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="101" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A101" s="45">
         <v>101</v>
       </c>
@@ -14143,7 +13987,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="102" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A102" s="45">
         <v>102</v>
       </c>
@@ -14240,7 +14084,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="103" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A103" s="45">
         <v>103</v>
       </c>
@@ -14337,7 +14181,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="104" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A104" s="45">
         <v>104</v>
       </c>
@@ -14434,7 +14278,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="105" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A105" s="45">
         <v>105</v>
       </c>
@@ -14531,7 +14375,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="106" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A106" s="45">
         <v>106</v>
       </c>
@@ -14628,7 +14472,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="107" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A107" s="45">
         <v>107</v>
       </c>
@@ -14725,7 +14569,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="108" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A108" s="45">
         <v>108</v>
       </c>
@@ -14822,7 +14666,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="109" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A109" s="45">
         <v>109</v>
       </c>
@@ -14919,7 +14763,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="110" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A110" s="45">
         <v>110</v>
       </c>
@@ -15016,7 +14860,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="111" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A111" s="45">
         <v>111</v>
       </c>
@@ -15113,7 +14957,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="112" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A112" s="45">
         <v>112</v>
       </c>
@@ -15210,7 +15054,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="113" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A113" s="45">
         <v>113</v>
       </c>
@@ -15307,7 +15151,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="114" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A114" s="45">
         <v>114</v>
       </c>
@@ -15404,7 +15248,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="115" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A115" s="45">
         <v>115</v>
       </c>
@@ -15501,7 +15345,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="116" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A116" s="45">
         <v>116</v>
       </c>
@@ -15598,7 +15442,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="117" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A117" s="45">
         <v>117</v>
       </c>
@@ -15695,7 +15539,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="118" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A118" s="45">
         <v>118</v>
       </c>
@@ -15792,7 +15636,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="119" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A119" s="45">
         <v>119</v>
       </c>
@@ -15889,7 +15733,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="120" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A120" s="45">
         <v>120</v>
       </c>
@@ -15986,7 +15830,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="121" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A121" s="45">
         <v>121</v>
       </c>
@@ -16083,7 +15927,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="122" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A122" s="45">
         <v>122</v>
       </c>
@@ -16180,7 +16024,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="123" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A123" s="45">
         <v>123</v>
       </c>
@@ -16277,7 +16121,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="124" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A124" s="45">
         <v>124</v>
       </c>
@@ -16374,7 +16218,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="125" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A125" s="45">
         <v>125</v>
       </c>
@@ -16471,7 +16315,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="126" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A126" s="45">
         <v>126</v>
       </c>
@@ -16568,7 +16412,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="127" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A127" s="45">
         <v>127</v>
       </c>
@@ -16665,7 +16509,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="128" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A128" s="45">
         <v>128</v>
       </c>
@@ -16762,7 +16606,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="129" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A129" s="45">
         <v>129</v>
       </c>
@@ -16859,7 +16703,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="130" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A130" s="45">
         <v>130</v>
       </c>
@@ -16956,7 +16800,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="131" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A131" s="45">
         <v>131</v>
       </c>
@@ -17053,7 +16897,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="132" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A132" s="45">
         <v>132</v>
       </c>
@@ -17150,7 +16994,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="133" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A133" s="45">
         <v>133</v>
       </c>
@@ -17247,7 +17091,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="134" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A134" s="45">
         <v>134</v>
       </c>
@@ -17344,7 +17188,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="135" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A135" s="45">
         <v>135</v>
       </c>
@@ -17441,7 +17285,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="136" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A136" s="45">
         <v>136</v>
       </c>
@@ -17538,7 +17382,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="137" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A137" s="45">
         <v>137</v>
       </c>
@@ -17635,7 +17479,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="138" spans="1:29" s="68" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:29" s="68" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="45">
         <v>138</v>
       </c>
@@ -17646,10 +17490,10 @@
         <v>900</v>
       </c>
       <c r="D138" s="63" t="s">
+        <v>902</v>
+      </c>
+      <c r="E138" s="63" t="s">
         <v>901</v>
-      </c>
-      <c r="E138" s="63" t="s">
-        <v>902</v>
       </c>
       <c r="F138" s="63" t="s">
         <v>903</v>
@@ -17675,11 +17519,11 @@
       </c>
       <c r="M138" s="65" t="str">
         <f t="shared" si="60"/>
-        <v>Métodos</v>
+        <v>Macros</v>
       </c>
       <c r="N138" s="65" t="str">
         <f t="shared" si="60"/>
-        <v>Macros</v>
+        <v>Métodos</v>
       </c>
       <c r="O138" s="65" t="str">
         <f t="shared" si="60"/>
@@ -17703,11 +17547,11 @@
       </c>
       <c r="U138" s="66" t="str">
         <f t="shared" si="61"/>
-        <v>Métodos</v>
+        <v>Macros</v>
       </c>
       <c r="V138" s="43" t="str">
         <f t="shared" si="61"/>
-        <v>Macros</v>
+        <v>Métodos</v>
       </c>
       <c r="W138" s="43" t="s">
         <v>80</v>
@@ -17737,30 +17581,30 @@
     <sortCondition ref="A1:A138"/>
   </sortState>
   <conditionalFormatting sqref="A2:B138">
-    <cfRule type="cellIs" dxfId="33" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="duplicateValues" dxfId="32" priority="37"/>
-    <cfRule type="duplicateValues" dxfId="31" priority="38"/>
-    <cfRule type="duplicateValues" dxfId="30" priority="39"/>
-    <cfRule type="duplicateValues" dxfId="29" priority="40"/>
-    <cfRule type="duplicateValues" dxfId="28" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:F137 F139:F1048576">
-    <cfRule type="duplicateValues" dxfId="27" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F138">
-    <cfRule type="duplicateValues" dxfId="26" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G1:O1">
-    <cfRule type="cellIs" dxfId="25" priority="31" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="31" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1:R138">
-    <cfRule type="cellIs" dxfId="24" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17774,14 +17618,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{779E4F22-2568-4D5A-A538-DD63A5C43724}">
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultColWidth="5.7109375" defaultRowHeight="7.9" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="5.69140625" defaultRowHeight="7.95" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.7109375" style="11" customWidth="1"/>
-    <col min="2" max="10" width="5.7109375" style="12"/>
-    <col min="11" max="16384" width="5.7109375" style="24"/>
+    <col min="1" max="1" width="2.69140625" style="11" customWidth="1"/>
+    <col min="2" max="10" width="5.69140625" style="12"/>
+    <col min="11" max="16384" width="5.69140625" style="24"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="16.5" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:21" ht="7.75" x14ac:dyDescent="0.2">
       <c r="A1" s="22">
         <v>1</v>
       </c>
@@ -17846,7 +17690,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="8.25" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:21" ht="7.75" x14ac:dyDescent="0.2">
       <c r="A2" s="22">
         <v>2</v>
       </c>
@@ -17919,15 +17763,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4328B84A-AA24-421E-9F4E-92D6A71CA3BE}">
   <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.15234375" style="13" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="11" style="13" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="9.140625" style="13"/>
+    <col min="5" max="16384" width="9.15234375" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:4" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="8">
         <v>1</v>
       </c>
@@ -17941,7 +17785,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="6.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:4" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="7">
         <v>2</v>
       </c>
@@ -17963,48 +17807,48 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{429087C4-377B-4931-BC50-C00BD9684F83}">
   <dimension ref="A1:AK42"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.53515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.84375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.53515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.15234375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.84375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.69140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.69140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="4.3046875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="4.84375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.3046875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="4.84375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.3046875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="4.84375" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="6" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="81.140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="15.85546875" customWidth="1"/>
-    <col min="18" max="18" width="6.7109375" customWidth="1"/>
+    <col min="15" max="15" width="81.15234375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8.3828125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.84375" customWidth="1"/>
+    <col min="18" max="18" width="6.69140625" customWidth="1"/>
     <col min="19" max="19" width="7" customWidth="1"/>
-    <col min="20" max="20" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="12.140625" customWidth="1"/>
-    <col min="22" max="22" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="7.53515625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12.15234375" customWidth="1"/>
+    <col min="22" max="22" width="7.53515625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.84375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="7.53515625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.84375" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="7.53515625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="9.3828125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="4.3046875" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="4.84375" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="4.3046875" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="4.84375" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="4.3046875" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="4.84375" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="4.3046875" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="4.84375" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="4.3046875" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="4.84375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:37" ht="25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="14" t="s">
         <v>30</v>
       </c>
@@ -18117,7 +17961,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="16">
         <v>2</v>
       </c>
@@ -18230,7 +18074,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="16">
         <v>3</v>
       </c>
@@ -18343,7 +18187,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="16">
         <v>4</v>
       </c>
@@ -18456,7 +18300,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="16">
         <v>5</v>
       </c>
@@ -18569,7 +18413,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="16">
         <v>6</v>
       </c>
@@ -18682,7 +18526,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="16">
         <v>7</v>
       </c>
@@ -18795,7 +18639,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="16">
         <v>8</v>
       </c>
@@ -18908,7 +18752,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="16">
         <v>9</v>
       </c>
@@ -19021,7 +18865,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="16">
         <v>10</v>
       </c>
@@ -19134,7 +18978,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="16">
         <v>11</v>
       </c>
@@ -19247,7 +19091,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="16">
         <v>12</v>
       </c>
@@ -19360,7 +19204,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="16">
         <v>13</v>
       </c>
@@ -19473,7 +19317,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="16">
         <v>14</v>
       </c>
@@ -19586,7 +19430,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="16">
         <v>15</v>
       </c>
@@ -19699,7 +19543,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="16">
         <v>16</v>
       </c>
@@ -19812,7 +19656,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="16">
         <v>17</v>
       </c>
@@ -19925,7 +19769,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="16">
         <v>18</v>
       </c>
@@ -20038,7 +19882,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="16">
         <v>19</v>
       </c>
@@ -20151,7 +19995,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="16">
         <v>20</v>
       </c>
@@ -20264,7 +20108,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="16">
         <v>21</v>
       </c>
@@ -20377,7 +20221,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="16">
         <v>22</v>
       </c>
@@ -20490,7 +20334,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="16">
         <v>23</v>
       </c>
@@ -20603,7 +20447,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="16">
         <v>24</v>
       </c>
@@ -20716,7 +20560,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="16">
         <v>25</v>
       </c>
@@ -20829,7 +20673,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="16">
         <v>26</v>
       </c>
@@ -20942,7 +20786,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="16">
         <v>27</v>
       </c>
@@ -21055,7 +20899,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="16">
         <v>28</v>
       </c>
@@ -21168,7 +21012,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="16">
         <v>29</v>
       </c>
@@ -21281,7 +21125,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="30" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="16">
         <v>30</v>
       </c>
@@ -21394,7 +21238,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="16">
         <v>31</v>
       </c>
@@ -21507,7 +21351,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="16">
         <v>32</v>
       </c>
@@ -21620,7 +21464,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="33" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="16">
         <v>33</v>
       </c>
@@ -21733,7 +21577,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="16">
         <v>34</v>
       </c>
@@ -21846,7 +21690,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="16">
         <v>35</v>
       </c>
@@ -21959,7 +21803,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="16">
         <v>36</v>
       </c>
@@ -22072,7 +21916,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="37" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="16">
         <v>37</v>
       </c>
@@ -22185,7 +22029,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:37" s="73" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:37" s="73" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="16">
         <v>38</v>
       </c>
@@ -22299,7 +22143,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="39" spans="1:37" s="73" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:37" s="73" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="16">
         <v>39</v>
       </c>
@@ -22413,7 +22257,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="40" spans="1:37" s="73" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:37" s="73" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="16">
         <v>40</v>
       </c>
@@ -22527,7 +22371,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="41" spans="1:37" s="73" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:37" s="73" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="16">
         <v>41</v>
       </c>
@@ -22641,7 +22485,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="1:37" s="73" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:37" s="73" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="16">
         <v>42</v>
       </c>
@@ -22758,49 +22602,19 @@
   </sheetData>
   <phoneticPr fontId="9" type="noConversion"/>
   <conditionalFormatting sqref="B18:B37 B1:B13">
-    <cfRule type="duplicateValues" dxfId="23" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B38:B42">
-    <cfRule type="duplicateValues" dxfId="15" priority="15"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="16"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="X38:AA42 Z2:AA42">
-    <cfRule type="cellIs" dxfId="13" priority="14" operator="equal">
+  <conditionalFormatting sqref="V38:AA42">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AD2:AE42">
-    <cfRule type="cellIs" dxfId="11" priority="12" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AF2:AG42">
-    <cfRule type="cellIs" dxfId="10" priority="11" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AH2:AI42">
-    <cfRule type="cellIs" dxfId="9" priority="10" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AJ2:AK42">
-    <cfRule type="cellIs" dxfId="8" priority="9" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AB2:AC42">
-    <cfRule type="cellIs" dxfId="6" priority="7" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="X38:Y42">
-    <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="V38:W42">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+  <conditionalFormatting sqref="Z2:AK42">
+    <cfRule type="cellIs" dxfId="0" priority="7" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/PRO/Ontologia_Documentos.xlsx
+++ b/Versão5/PRO/Ontologia_Documentos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\PRO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2B84308-F06C-4F6E-8EB9-65AEB6FA65C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A66F9C5-B6CA-4197-A17F-EA6F1CA3D202}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="527" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="527" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="31" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4391" uniqueCount="930">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4613" uniqueCount="948">
   <si>
     <t>Edição</t>
   </si>
@@ -2783,18 +2783,6 @@
     <t>Macros</t>
   </si>
   <si>
-    <t>API.Revit</t>
-  </si>
-  <si>
-    <t>Aplicação Revit</t>
-  </si>
-  <si>
-    <t>Aplicativo Revit</t>
-  </si>
-  <si>
-    <t>Revit Aplication</t>
-  </si>
-  <si>
     <t>API_Ambiente</t>
   </si>
   <si>
@@ -2862,6 +2850,72 @@
   </si>
   <si>
     <t>"[ Materiais ]"</t>
+  </si>
+  <si>
+    <t>Função.Auxiliar</t>
+  </si>
+  <si>
+    <t>Define uma Função Auxiliar (helper) numa aplicação</t>
+  </si>
+  <si>
+    <t>Defina un rol de ayudante en una aplicación</t>
+  </si>
+  <si>
+    <t>Define a Helper Role in an application</t>
+  </si>
+  <si>
+    <t>Função.Global</t>
+  </si>
+  <si>
+    <t>Define uma Função Global numa aplicação</t>
+  </si>
+  <si>
+    <t>Defina un rol global en una aplicación</t>
+  </si>
+  <si>
+    <t>Define a Global Role in an application</t>
+  </si>
+  <si>
+    <t>Função.Local</t>
+  </si>
+  <si>
+    <t>Define uma Função Local numa aplicação</t>
+  </si>
+  <si>
+    <t>Defina un rol local en una aplicación</t>
+  </si>
+  <si>
+    <t>Define a Local Role in an application</t>
+  </si>
+  <si>
+    <t>Função.Filtro</t>
+  </si>
+  <si>
+    <t>Define uma Função para filtrar objetos numa aplicação</t>
+  </si>
+  <si>
+    <t>Defina una función para filtrar objetos en una aplicación</t>
+  </si>
+  <si>
+    <t>Define a Function to filter objects in an application</t>
+  </si>
+  <si>
+    <t>Códigos.Visuais</t>
+  </si>
+  <si>
+    <t>Bloco.de.Código</t>
+  </si>
+  <si>
+    <t>Define um Código escrito em sistemas de programação visual</t>
+  </si>
+  <si>
+    <t>Define un código escrito en sistemas de programación visual</t>
+  </si>
+  <si>
+    <t>Defines a Code written in visual programming systems</t>
+  </si>
+  <si>
+    <t>KML</t>
   </si>
 </sst>
 </file>
@@ -2952,7 +3006,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="31">
+  <fills count="32">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3131,6 +3185,12 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFE89F"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -3379,12 +3439,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -3422,11 +3476,17 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="15">
+  <dxfs count="16">
     <dxf>
       <font>
         <b val="0"/>
@@ -3488,6 +3548,16 @@
         <strike val="0"/>
         <color rgb="FFFFFFFF"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -3884,15 +3954,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1124724F-B8C4-4B86-9028-743FC73CDDB0}">
   <dimension ref="A1:C24"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="10.5" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="10.3828125" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="53.69140625" style="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="3.3828125" style="42" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.15234375" style="13"/>
+    <col min="1" max="1" width="10.42578125" style="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="53.7109375" style="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3.42578125" style="42" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.140625" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="10" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" s="10" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -3903,7 +3973,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="2" t="s">
         <v>17</v>
       </c>
@@ -3914,7 +3984,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="2" t="s">
         <v>18</v>
       </c>
@@ -3925,7 +3995,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
@@ -3936,7 +4006,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
@@ -3948,7 +4018,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="2" t="s">
         <v>8</v>
       </c>
@@ -3960,7 +4030,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="2" t="s">
         <v>4</v>
       </c>
@@ -3971,7 +4041,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="8" spans="1:3" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>5</v>
       </c>
@@ -3982,7 +4052,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="2" t="s">
         <v>20</v>
       </c>
@@ -3993,7 +4063,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="2" t="s">
         <v>22</v>
       </c>
@@ -4004,7 +4074,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="2" t="s">
         <v>0</v>
       </c>
@@ -4015,7 +4085,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="2" t="s">
         <v>1</v>
       </c>
@@ -4026,7 +4096,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="2" t="s">
         <v>23</v>
       </c>
@@ -4037,7 +4107,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="2" t="s">
         <v>24</v>
       </c>
@@ -4048,7 +4118,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="2" t="s">
         <v>25</v>
       </c>
@@ -4059,7 +4129,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="2" t="s">
         <v>26</v>
       </c>
@@ -4070,7 +4140,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="2" t="s">
         <v>10</v>
       </c>
@@ -4081,19 +4151,19 @@
         <v>304</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B18" s="5">
         <f ca="1">NOW()</f>
-        <v>46264.568395486109</v>
+        <v>46268.699871874996</v>
       </c>
       <c r="C18" s="41" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="2" t="s">
         <v>28</v>
       </c>
@@ -4104,7 +4174,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="2" t="s">
         <v>29</v>
       </c>
@@ -4115,7 +4185,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="2" t="s">
         <v>11</v>
       </c>
@@ -4126,7 +4196,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="4" t="s">
         <v>34</v>
       </c>
@@ -4137,7 +4207,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="4" t="s">
         <v>35</v>
       </c>
@@ -4148,7 +4218,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="24" spans="1:3" s="39" customFormat="1" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:3" s="39" customFormat="1" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>302</v>
       </c>
@@ -4167,38 +4237,39 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19BE914A-3965-4A61-9195-D2681A91581F}">
-  <dimension ref="A1:AC138"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6" customHeight="1" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:AD142"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.15234375" style="61" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.3046875" style="44" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.3828125" style="44" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.3828125" style="44" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.84375" style="44" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.53515625" style="44" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="6.3828125" style="44" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="5.3828125" style="44" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.3828125" style="44" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12" style="44" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.84375" style="44" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="39.15234375" style="44" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="42.69140625" style="44" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="33.3046875" style="44" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="3.69140625" style="44" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="5.3828125" style="44" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="12.3828125" style="44" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="11.84375" style="44" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="8.53515625" style="44" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="6.53515625" style="44" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="21.53515625" style="44" customWidth="1"/>
-    <col min="26" max="26" width="13.53515625" style="44" customWidth="1"/>
-    <col min="27" max="27" width="16.15234375" style="44" customWidth="1"/>
-    <col min="28" max="28" width="6.3046875" style="44" customWidth="1"/>
-    <col min="29" max="29" width="4.3046875" style="44" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.15234375" style="44"/>
+    <col min="1" max="1" width="3.140625" style="61" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.28515625" style="44" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.5703125" style="44" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.7109375" style="44" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.5703125" style="44" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.7109375" style="44" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="10.140625" style="44" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.5703125" style="44" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.7109375" style="44" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.5703125" style="44" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="19.140625" style="44" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="53.5703125" style="44" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="59" style="44" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="45.5703125" style="44" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="3.7109375" style="44" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="7.5703125" style="44" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="16.7109375" style="44" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.5703125" style="44" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="7.7109375" style="44" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="9" style="44" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="21.5703125" style="44" customWidth="1"/>
+    <col min="26" max="26" width="10.42578125" style="44" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="16.140625" style="44" customWidth="1"/>
+    <col min="28" max="28" width="6.28515625" style="44" customWidth="1"/>
+    <col min="29" max="29" width="4.28515625" style="44" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="4.140625" style="44" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="44"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="39.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:30" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="60" t="s">
         <v>36</v>
       </c>
@@ -4286,8 +4357,11 @@
       <c r="AC1" s="49" t="s">
         <v>299</v>
       </c>
+      <c r="AD1" s="49" t="s">
+        <v>947</v>
+      </c>
     </row>
-    <row r="2" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="45">
         <v>2</v>
       </c>
@@ -4368,23 +4442,26 @@
         <f t="shared" ref="X2:X57" si="5">CONCATENATE("Key-DOCU-",A2)</f>
         <v>Key-DOCU-2</v>
       </c>
-      <c r="Y2" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z2" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA2" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB2" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC2" s="67" t="s">
+      <c r="Y2" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z2" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA2" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB2" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC2" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD2" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="45">
         <v>3</v>
       </c>
@@ -4465,23 +4542,26 @@
         <f t="shared" si="5"/>
         <v>Key-DOCU-3</v>
       </c>
-      <c r="Y3" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z3" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA3" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB3" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC3" s="67" t="s">
+      <c r="Y3" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z3" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA3" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB3" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC3" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD3" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="45">
         <v>4</v>
       </c>
@@ -4562,23 +4642,26 @@
         <f t="shared" si="5"/>
         <v>Key-DOCU-4</v>
       </c>
-      <c r="Y4" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z4" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA4" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB4" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC4" s="67" t="s">
+      <c r="Y4" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z4" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA4" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB4" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC4" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD4" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="45">
         <v>5</v>
       </c>
@@ -4659,23 +4742,26 @@
         <f t="shared" si="5"/>
         <v>Key-DOCU-5</v>
       </c>
-      <c r="Y5" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z5" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA5" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB5" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC5" s="67" t="s">
+      <c r="Y5" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z5" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA5" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB5" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC5" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD5" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="45">
         <v>6</v>
       </c>
@@ -4756,23 +4842,26 @@
         <f t="shared" si="5"/>
         <v>Key-DOCU-6</v>
       </c>
-      <c r="Y6" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z6" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA6" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB6" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC6" s="67" t="s">
+      <c r="Y6" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z6" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA6" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB6" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC6" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD6" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="45">
         <v>7</v>
       </c>
@@ -4853,23 +4942,26 @@
         <f t="shared" si="5"/>
         <v>Key-DOCU-7</v>
       </c>
-      <c r="Y7" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z7" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA7" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB7" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC7" s="67" t="s">
+      <c r="Y7" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z7" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA7" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB7" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC7" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD7" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="45">
         <v>8</v>
       </c>
@@ -4953,20 +5045,23 @@
       <c r="Y8" s="58" t="s">
         <v>310</v>
       </c>
-      <c r="Z8" s="59" t="s">
-        <v>413</v>
+      <c r="Z8" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA8" s="59" t="s">
         <v>413</v>
       </c>
-      <c r="AB8" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC8" s="67" t="s">
+      <c r="AB8" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC8" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD8" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="45">
         <v>9</v>
       </c>
@@ -5050,20 +5145,23 @@
       <c r="Y9" s="58" t="s">
         <v>311</v>
       </c>
-      <c r="Z9" s="59" t="s">
-        <v>413</v>
+      <c r="Z9" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA9" s="59" t="s">
         <v>413</v>
       </c>
-      <c r="AB9" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC9" s="67" t="s">
+      <c r="AB9" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC9" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD9" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="45">
         <v>10</v>
       </c>
@@ -5147,20 +5245,23 @@
       <c r="Y10" s="58" t="s">
         <v>312</v>
       </c>
-      <c r="Z10" s="59" t="s">
-        <v>413</v>
+      <c r="Z10" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA10" s="59" t="s">
         <v>413</v>
       </c>
-      <c r="AB10" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC10" s="67" t="s">
+      <c r="AB10" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC10" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD10" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="45">
         <v>11</v>
       </c>
@@ -5244,20 +5345,23 @@
       <c r="Y11" s="58" t="s">
         <v>313</v>
       </c>
-      <c r="Z11" s="59" t="s">
-        <v>416</v>
+      <c r="Z11" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA11" s="59" t="s">
         <v>416</v>
       </c>
-      <c r="AB11" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC11" s="67" t="s">
+      <c r="AB11" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC11" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD11" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="45">
         <v>12</v>
       </c>
@@ -5341,20 +5445,23 @@
       <c r="Y12" s="58" t="s">
         <v>314</v>
       </c>
-      <c r="Z12" s="59" t="s">
-        <v>413</v>
+      <c r="Z12" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA12" s="59" t="s">
         <v>413</v>
       </c>
-      <c r="AB12" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC12" s="67" t="s">
+      <c r="AB12" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC12" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD12" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="45">
         <v>13</v>
       </c>
@@ -5438,20 +5545,23 @@
       <c r="Y13" s="58" t="s">
         <v>315</v>
       </c>
-      <c r="Z13" s="59" t="s">
-        <v>413</v>
+      <c r="Z13" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA13" s="59" t="s">
         <v>413</v>
       </c>
-      <c r="AB13" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC13" s="67" t="s">
+      <c r="AB13" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC13" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD13" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="45">
         <v>14</v>
       </c>
@@ -5535,20 +5645,23 @@
       <c r="Y14" s="58" t="s">
         <v>322</v>
       </c>
-      <c r="Z14" s="59" t="s">
-        <v>413</v>
+      <c r="Z14" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA14" s="59" t="s">
         <v>413</v>
       </c>
-      <c r="AB14" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC14" s="67" t="s">
+      <c r="AB14" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC14" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD14" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="45">
         <v>15</v>
       </c>
@@ -5632,20 +5745,23 @@
       <c r="Y15" s="58" t="s">
         <v>317</v>
       </c>
-      <c r="Z15" s="59" t="s">
-        <v>413</v>
+      <c r="Z15" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA15" s="59" t="s">
         <v>413</v>
       </c>
-      <c r="AB15" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC15" s="67" t="s">
+      <c r="AB15" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC15" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD15" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="45">
         <v>16</v>
       </c>
@@ -5729,20 +5845,23 @@
       <c r="Y16" s="58" t="s">
         <v>318</v>
       </c>
-      <c r="Z16" s="59" t="s">
-        <v>413</v>
+      <c r="Z16" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA16" s="59" t="s">
         <v>413</v>
       </c>
-      <c r="AB16" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC16" s="67" t="s">
+      <c r="AB16" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC16" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD16" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="45">
         <v>17</v>
       </c>
@@ -5826,20 +5945,23 @@
       <c r="Y17" s="58" t="s">
         <v>316</v>
       </c>
-      <c r="Z17" s="59" t="s">
-        <v>413</v>
+      <c r="Z17" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA17" s="59" t="s">
         <v>413</v>
       </c>
-      <c r="AB17" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC17" s="67" t="s">
+      <c r="AB17" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC17" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD17" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="45">
         <v>18</v>
       </c>
@@ -5923,20 +6045,23 @@
       <c r="Y18" s="58" t="s">
         <v>319</v>
       </c>
-      <c r="Z18" s="59" t="s">
-        <v>413</v>
+      <c r="Z18" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA18" s="59" t="s">
         <v>413</v>
       </c>
-      <c r="AB18" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC18" s="67" t="s">
+      <c r="AB18" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC18" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD18" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="45">
         <v>19</v>
       </c>
@@ -6020,20 +6145,23 @@
       <c r="Y19" s="58" t="s">
         <v>320</v>
       </c>
-      <c r="Z19" s="59" t="s">
-        <v>413</v>
+      <c r="Z19" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA19" s="59" t="s">
         <v>413</v>
       </c>
-      <c r="AB19" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC19" s="67" t="s">
+      <c r="AB19" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC19" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD19" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="45">
         <v>20</v>
       </c>
@@ -6117,20 +6245,23 @@
       <c r="Y20" s="58" t="s">
         <v>321</v>
       </c>
-      <c r="Z20" s="59" t="s">
-        <v>413</v>
+      <c r="Z20" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA20" s="59" t="s">
         <v>413</v>
       </c>
-      <c r="AB20" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC20" s="67" t="s">
+      <c r="AB20" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC20" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD20" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="45">
         <v>21</v>
       </c>
@@ -6214,20 +6345,23 @@
       <c r="Y21" s="58" t="s">
         <v>323</v>
       </c>
-      <c r="Z21" s="59" t="s">
-        <v>413</v>
+      <c r="Z21" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA21" s="59" t="s">
         <v>413</v>
       </c>
-      <c r="AB21" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC21" s="67" t="s">
+      <c r="AB21" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC21" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD21" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="45">
         <v>22</v>
       </c>
@@ -6311,20 +6445,23 @@
       <c r="Y22" s="58" t="s">
         <v>324</v>
       </c>
-      <c r="Z22" s="59" t="s">
-        <v>413</v>
+      <c r="Z22" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA22" s="59" t="s">
         <v>413</v>
       </c>
-      <c r="AB22" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC22" s="67" t="s">
+      <c r="AB22" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC22" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD22" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="45">
         <v>23</v>
       </c>
@@ -6408,20 +6545,23 @@
       <c r="Y23" s="58" t="s">
         <v>325</v>
       </c>
-      <c r="Z23" s="59" t="s">
-        <v>413</v>
+      <c r="Z23" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA23" s="59" t="s">
         <v>413</v>
       </c>
-      <c r="AB23" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC23" s="67" t="s">
+      <c r="AB23" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC23" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD23" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="45">
         <v>24</v>
       </c>
@@ -6505,20 +6645,23 @@
       <c r="Y24" s="58" t="s">
         <v>326</v>
       </c>
-      <c r="Z24" s="59" t="s">
-        <v>413</v>
+      <c r="Z24" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA24" s="59" t="s">
         <v>413</v>
       </c>
-      <c r="AB24" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC24" s="67" t="s">
+      <c r="AB24" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC24" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD24" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="45">
         <v>25</v>
       </c>
@@ -6602,20 +6745,23 @@
       <c r="Y25" s="58" t="s">
         <v>327</v>
       </c>
-      <c r="Z25" s="59" t="s">
-        <v>413</v>
+      <c r="Z25" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA25" s="59" t="s">
         <v>413</v>
       </c>
-      <c r="AB25" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC25" s="67" t="s">
+      <c r="AB25" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC25" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD25" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="45">
         <v>26</v>
       </c>
@@ -6699,20 +6845,23 @@
       <c r="Y26" s="58" t="s">
         <v>328</v>
       </c>
-      <c r="Z26" s="59" t="s">
-        <v>413</v>
+      <c r="Z26" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA26" s="59" t="s">
         <v>413</v>
       </c>
-      <c r="AB26" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC26" s="67" t="s">
+      <c r="AB26" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC26" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD26" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="45">
         <v>27</v>
       </c>
@@ -6796,20 +6945,23 @@
       <c r="Y27" s="58" t="s">
         <v>329</v>
       </c>
-      <c r="Z27" s="59" t="s">
-        <v>417</v>
+      <c r="Z27" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA27" s="59" t="s">
         <v>417</v>
       </c>
-      <c r="AB27" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC27" s="67" t="s">
+      <c r="AB27" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC27" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD27" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="45">
         <v>28</v>
       </c>
@@ -6893,20 +7045,23 @@
       <c r="Y28" s="58" t="s">
         <v>330</v>
       </c>
-      <c r="Z28" s="59" t="s">
-        <v>417</v>
+      <c r="Z28" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA28" s="59" t="s">
         <v>417</v>
       </c>
-      <c r="AB28" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC28" s="67" t="s">
+      <c r="AB28" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC28" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD28" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="45">
         <v>29</v>
       </c>
@@ -6990,20 +7145,23 @@
       <c r="Y29" s="58" t="s">
         <v>331</v>
       </c>
-      <c r="Z29" s="59" t="s">
-        <v>417</v>
+      <c r="Z29" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA29" s="59" t="s">
         <v>417</v>
       </c>
-      <c r="AB29" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC29" s="67" t="s">
+      <c r="AB29" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC29" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD29" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="30" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="45">
         <v>30</v>
       </c>
@@ -7087,20 +7245,23 @@
       <c r="Y30" s="58" t="s">
         <v>332</v>
       </c>
-      <c r="Z30" s="59" t="s">
-        <v>417</v>
+      <c r="Z30" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA30" s="59" t="s">
         <v>417</v>
       </c>
-      <c r="AB30" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC30" s="67" t="s">
+      <c r="AB30" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC30" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD30" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="45">
         <v>31</v>
       </c>
@@ -7184,20 +7345,23 @@
       <c r="Y31" s="58" t="s">
         <v>333</v>
       </c>
-      <c r="Z31" s="59" t="s">
-        <v>417</v>
+      <c r="Z31" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA31" s="59" t="s">
         <v>417</v>
       </c>
-      <c r="AB31" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC31" s="67" t="s">
+      <c r="AB31" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC31" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD31" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="45">
         <v>32</v>
       </c>
@@ -7281,20 +7445,23 @@
       <c r="Y32" s="58" t="s">
         <v>334</v>
       </c>
-      <c r="Z32" s="59" t="s">
-        <v>417</v>
+      <c r="Z32" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA32" s="59" t="s">
         <v>417</v>
       </c>
-      <c r="AB32" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC32" s="67" t="s">
+      <c r="AB32" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC32" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD32" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="33" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="45">
         <v>33</v>
       </c>
@@ -7378,20 +7545,23 @@
       <c r="Y33" s="58" t="s">
         <v>335</v>
       </c>
-      <c r="Z33" s="59" t="s">
-        <v>414</v>
+      <c r="Z33" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA33" s="59" t="s">
         <v>414</v>
       </c>
-      <c r="AB33" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC33" s="67" t="s">
+      <c r="AB33" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC33" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD33" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="45">
         <v>34</v>
       </c>
@@ -7475,20 +7645,23 @@
       <c r="Y34" s="58" t="s">
         <v>336</v>
       </c>
-      <c r="Z34" s="59" t="s">
-        <v>414</v>
+      <c r="Z34" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA34" s="59" t="s">
         <v>414</v>
       </c>
-      <c r="AB34" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC34" s="67" t="s">
+      <c r="AB34" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC34" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD34" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="45">
         <v>35</v>
       </c>
@@ -7572,20 +7745,23 @@
       <c r="Y35" s="58" t="s">
         <v>337</v>
       </c>
-      <c r="Z35" s="59" t="s">
-        <v>414</v>
+      <c r="Z35" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA35" s="59" t="s">
         <v>414</v>
       </c>
-      <c r="AB35" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC35" s="67" t="s">
+      <c r="AB35" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC35" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD35" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="45">
         <v>36</v>
       </c>
@@ -7669,20 +7845,23 @@
       <c r="Y36" s="58" t="s">
         <v>338</v>
       </c>
-      <c r="Z36" s="59" t="s">
-        <v>414</v>
+      <c r="Z36" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA36" s="59" t="s">
         <v>414</v>
       </c>
-      <c r="AB36" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC36" s="67" t="s">
+      <c r="AB36" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC36" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD36" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="37" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="45">
         <v>37</v>
       </c>
@@ -7766,20 +7945,23 @@
       <c r="Y37" s="58" t="s">
         <v>339</v>
       </c>
-      <c r="Z37" s="59" t="s">
-        <v>414</v>
+      <c r="Z37" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA37" s="59" t="s">
         <v>414</v>
       </c>
-      <c r="AB37" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC37" s="67" t="s">
+      <c r="AB37" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC37" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD37" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="45">
         <v>38</v>
       </c>
@@ -7863,20 +8045,23 @@
       <c r="Y38" s="58" t="s">
         <v>340</v>
       </c>
-      <c r="Z38" s="59" t="s">
-        <v>415</v>
+      <c r="Z38" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA38" s="59" t="s">
         <v>415</v>
       </c>
-      <c r="AB38" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC38" s="67" t="s">
+      <c r="AB38" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC38" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD38" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="39" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="45">
         <v>39</v>
       </c>
@@ -7960,20 +8145,23 @@
       <c r="Y39" s="58" t="s">
         <v>341</v>
       </c>
-      <c r="Z39" s="59" t="s">
-        <v>415</v>
+      <c r="Z39" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA39" s="59" t="s">
         <v>415</v>
       </c>
-      <c r="AB39" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC39" s="67" t="s">
+      <c r="AB39" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC39" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD39" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="40" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="45">
         <v>40</v>
       </c>
@@ -8057,20 +8245,23 @@
       <c r="Y40" s="58" t="s">
         <v>342</v>
       </c>
-      <c r="Z40" s="59" t="s">
-        <v>415</v>
+      <c r="Z40" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA40" s="59" t="s">
         <v>415</v>
       </c>
-      <c r="AB40" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC40" s="67" t="s">
+      <c r="AB40" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC40" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD40" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="41" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="45">
         <v>41</v>
       </c>
@@ -8154,20 +8345,23 @@
       <c r="Y41" s="58" t="s">
         <v>343</v>
       </c>
-      <c r="Z41" s="59" t="s">
-        <v>415</v>
+      <c r="Z41" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA41" s="59" t="s">
         <v>415</v>
       </c>
-      <c r="AB41" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC41" s="67" t="s">
+      <c r="AB41" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC41" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD41" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="45">
         <v>42</v>
       </c>
@@ -8251,20 +8445,23 @@
       <c r="Y42" s="58" t="s">
         <v>344</v>
       </c>
-      <c r="Z42" s="59" t="s">
-        <v>415</v>
+      <c r="Z42" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA42" s="59" t="s">
         <v>415</v>
       </c>
-      <c r="AB42" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC42" s="67" t="s">
+      <c r="AB42" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC42" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD42" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="43" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="45">
         <v>43</v>
       </c>
@@ -8348,20 +8545,23 @@
       <c r="Y43" s="58" t="s">
         <v>345</v>
       </c>
-      <c r="Z43" s="59" t="s">
-        <v>415</v>
+      <c r="Z43" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA43" s="59" t="s">
         <v>415</v>
       </c>
-      <c r="AB43" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC43" s="67" t="s">
+      <c r="AB43" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC43" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD43" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="44" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="45">
         <v>44</v>
       </c>
@@ -8445,20 +8645,23 @@
       <c r="Y44" s="58" t="s">
         <v>346</v>
       </c>
-      <c r="Z44" s="59" t="s">
-        <v>415</v>
+      <c r="Z44" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA44" s="59" t="s">
         <v>415</v>
       </c>
-      <c r="AB44" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC44" s="67" t="s">
+      <c r="AB44" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC44" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD44" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="45" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="45">
         <v>45</v>
       </c>
@@ -8542,20 +8745,23 @@
       <c r="Y45" s="58" t="s">
         <v>347</v>
       </c>
-      <c r="Z45" s="59" t="s">
-        <v>415</v>
+      <c r="Z45" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA45" s="59" t="s">
         <v>415</v>
       </c>
-      <c r="AB45" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC45" s="67" t="s">
+      <c r="AB45" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC45" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD45" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="46" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="45">
         <v>46</v>
       </c>
@@ -8639,20 +8845,23 @@
       <c r="Y46" s="58" t="s">
         <v>348</v>
       </c>
-      <c r="Z46" s="59" t="s">
-        <v>415</v>
+      <c r="Z46" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA46" s="59" t="s">
         <v>415</v>
       </c>
-      <c r="AB46" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC46" s="67" t="s">
+      <c r="AB46" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC46" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD46" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="47" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="45">
         <v>47</v>
       </c>
@@ -8736,20 +8945,23 @@
       <c r="Y47" s="58" t="s">
         <v>349</v>
       </c>
-      <c r="Z47" s="59" t="s">
-        <v>415</v>
+      <c r="Z47" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA47" s="59" t="s">
         <v>415</v>
       </c>
-      <c r="AB47" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC47" s="67" t="s">
+      <c r="AB47" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC47" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD47" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="48" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="45">
         <v>48</v>
       </c>
@@ -8833,20 +9045,23 @@
       <c r="Y48" s="58" t="s">
         <v>350</v>
       </c>
-      <c r="Z48" s="59" t="s">
-        <v>415</v>
+      <c r="Z48" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA48" s="59" t="s">
         <v>415</v>
       </c>
-      <c r="AB48" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC48" s="67" t="s">
+      <c r="AB48" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC48" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD48" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="49" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="45">
         <v>49</v>
       </c>
@@ -8930,20 +9145,23 @@
       <c r="Y49" s="58" t="s">
         <v>351</v>
       </c>
-      <c r="Z49" s="59" t="s">
-        <v>415</v>
+      <c r="Z49" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA49" s="59" t="s">
         <v>415</v>
       </c>
-      <c r="AB49" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC49" s="67" t="s">
+      <c r="AB49" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC49" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD49" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="50" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="45">
         <v>50</v>
       </c>
@@ -9027,20 +9245,23 @@
       <c r="Y50" s="58" t="s">
         <v>352</v>
       </c>
-      <c r="Z50" s="59" t="s">
-        <v>415</v>
+      <c r="Z50" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA50" s="59" t="s">
         <v>415</v>
       </c>
-      <c r="AB50" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC50" s="67" t="s">
+      <c r="AB50" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC50" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD50" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="51" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="45">
         <v>51</v>
       </c>
@@ -9124,20 +9345,23 @@
       <c r="Y51" s="58" t="s">
         <v>353</v>
       </c>
-      <c r="Z51" s="59" t="s">
-        <v>415</v>
+      <c r="Z51" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA51" s="59" t="s">
         <v>415</v>
       </c>
-      <c r="AB51" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC51" s="67" t="s">
+      <c r="AB51" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC51" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD51" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="52" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="45">
         <v>52</v>
       </c>
@@ -9221,20 +9445,23 @@
       <c r="Y52" s="58" t="s">
         <v>354</v>
       </c>
-      <c r="Z52" s="59" t="s">
-        <v>415</v>
+      <c r="Z52" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA52" s="59" t="s">
         <v>415</v>
       </c>
-      <c r="AB52" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC52" s="67" t="s">
+      <c r="AB52" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC52" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD52" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="53" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="45">
         <v>53</v>
       </c>
@@ -9318,20 +9545,23 @@
       <c r="Y53" s="58" t="s">
         <v>355</v>
       </c>
-      <c r="Z53" s="59" t="s">
-        <v>307</v>
+      <c r="Z53" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA53" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB53" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC53" s="67" t="s">
+      <c r="AB53" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC53" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD53" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="54" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="45">
         <v>54</v>
       </c>
@@ -9415,20 +9645,23 @@
       <c r="Y54" s="58" t="s">
         <v>356</v>
       </c>
-      <c r="Z54" s="59" t="s">
-        <v>307</v>
+      <c r="Z54" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA54" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB54" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC54" s="67" t="s">
+      <c r="AB54" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC54" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD54" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="55" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="45">
         <v>55</v>
       </c>
@@ -9512,20 +9745,23 @@
       <c r="Y55" s="58" t="s">
         <v>357</v>
       </c>
-      <c r="Z55" s="59" t="s">
-        <v>307</v>
+      <c r="Z55" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA55" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB55" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC55" s="67" t="s">
+      <c r="AB55" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC55" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD55" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="56" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="45">
         <v>56</v>
       </c>
@@ -9609,20 +9845,23 @@
       <c r="Y56" s="58" t="s">
         <v>358</v>
       </c>
-      <c r="Z56" s="59" t="s">
-        <v>307</v>
+      <c r="Z56" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA56" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB56" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC56" s="67" t="s">
+      <c r="AB56" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC56" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD56" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="57" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="45">
         <v>57</v>
       </c>
@@ -9706,20 +9945,23 @@
       <c r="Y57" s="58" t="s">
         <v>359</v>
       </c>
-      <c r="Z57" s="59" t="s">
-        <v>307</v>
+      <c r="Z57" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA57" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB57" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC57" s="67" t="s">
+      <c r="AB57" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC57" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD57" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="58" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="45">
         <v>58</v>
       </c>
@@ -9803,20 +10045,23 @@
       <c r="Y58" s="58" t="s">
         <v>360</v>
       </c>
-      <c r="Z58" s="59" t="s">
-        <v>307</v>
+      <c r="Z58" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA58" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB58" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC58" s="67" t="s">
+      <c r="AB58" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC58" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD58" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="59" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="45">
         <v>59</v>
       </c>
@@ -9900,20 +10145,23 @@
       <c r="Y59" s="58" t="s">
         <v>361</v>
       </c>
-      <c r="Z59" s="59" t="s">
-        <v>307</v>
+      <c r="Z59" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA59" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB59" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC59" s="67" t="s">
+      <c r="AB59" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC59" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD59" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="60" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="45">
         <v>60</v>
       </c>
@@ -9997,20 +10245,23 @@
       <c r="Y60" s="58" t="s">
         <v>362</v>
       </c>
-      <c r="Z60" s="59" t="s">
-        <v>307</v>
+      <c r="Z60" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA60" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB60" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC60" s="67" t="s">
+      <c r="AB60" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC60" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD60" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="61" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="45">
         <v>61</v>
       </c>
@@ -10094,20 +10345,23 @@
       <c r="Y61" s="58" t="s">
         <v>363</v>
       </c>
-      <c r="Z61" s="59" t="s">
-        <v>307</v>
+      <c r="Z61" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA61" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB61" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC61" s="67" t="s">
+      <c r="AB61" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC61" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD61" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="62" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="45">
         <v>62</v>
       </c>
@@ -10191,20 +10445,23 @@
       <c r="Y62" s="58" t="s">
         <v>364</v>
       </c>
-      <c r="Z62" s="59" t="s">
-        <v>307</v>
+      <c r="Z62" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA62" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB62" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC62" s="67" t="s">
+      <c r="AB62" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC62" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD62" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="63" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="45">
         <v>63</v>
       </c>
@@ -10288,20 +10545,23 @@
       <c r="Y63" s="58" t="s">
         <v>365</v>
       </c>
-      <c r="Z63" s="59" t="s">
-        <v>307</v>
+      <c r="Z63" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA63" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB63" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC63" s="67" t="s">
+      <c r="AB63" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC63" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD63" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="64" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="45">
         <v>64</v>
       </c>
@@ -10385,20 +10645,23 @@
       <c r="Y64" s="58" t="s">
         <v>366</v>
       </c>
-      <c r="Z64" s="59" t="s">
-        <v>307</v>
+      <c r="Z64" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA64" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB64" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC64" s="67" t="s">
+      <c r="AB64" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC64" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD64" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="65" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="45">
         <v>65</v>
       </c>
@@ -10482,20 +10745,23 @@
       <c r="Y65" s="58" t="s">
         <v>367</v>
       </c>
-      <c r="Z65" s="59" t="s">
-        <v>307</v>
+      <c r="Z65" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA65" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB65" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC65" s="67" t="s">
+      <c r="AB65" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC65" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD65" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="66" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="45">
         <v>66</v>
       </c>
@@ -10579,20 +10845,23 @@
       <c r="Y66" s="58" t="s">
         <v>368</v>
       </c>
-      <c r="Z66" s="59" t="s">
-        <v>307</v>
+      <c r="Z66" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA66" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB66" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC66" s="67" t="s">
+      <c r="AB66" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC66" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD66" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="67" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="45">
         <v>67</v>
       </c>
@@ -10676,20 +10945,23 @@
       <c r="Y67" s="58" t="s">
         <v>369</v>
       </c>
-      <c r="Z67" s="59" t="s">
-        <v>307</v>
+      <c r="Z67" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA67" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB67" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC67" s="67" t="s">
+      <c r="AB67" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC67" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD67" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="68" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="45">
         <v>68</v>
       </c>
@@ -10773,20 +11045,23 @@
       <c r="Y68" s="58" t="s">
         <v>370</v>
       </c>
-      <c r="Z68" s="59" t="s">
-        <v>307</v>
+      <c r="Z68" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA68" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB68" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC68" s="67" t="s">
+      <c r="AB68" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC68" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD68" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="69" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="45">
         <v>69</v>
       </c>
@@ -10870,20 +11145,23 @@
       <c r="Y69" s="58" t="s">
         <v>371</v>
       </c>
-      <c r="Z69" s="59" t="s">
-        <v>307</v>
+      <c r="Z69" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA69" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB69" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC69" s="67" t="s">
+      <c r="AB69" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC69" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD69" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="70" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="45">
         <v>70</v>
       </c>
@@ -10967,20 +11245,23 @@
       <c r="Y70" s="58" t="s">
         <v>372</v>
       </c>
-      <c r="Z70" s="59" t="s">
-        <v>307</v>
+      <c r="Z70" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA70" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB70" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC70" s="67" t="s">
+      <c r="AB70" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC70" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD70" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="71" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="45">
         <v>71</v>
       </c>
@@ -11064,20 +11345,23 @@
       <c r="Y71" s="58" t="s">
         <v>373</v>
       </c>
-      <c r="Z71" s="59" t="s">
-        <v>307</v>
+      <c r="Z71" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA71" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB71" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC71" s="67" t="s">
+      <c r="AB71" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC71" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD71" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="72" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="45">
         <v>72</v>
       </c>
@@ -11161,20 +11445,23 @@
       <c r="Y72" s="58" t="s">
         <v>377</v>
       </c>
-      <c r="Z72" s="59" t="s">
-        <v>415</v>
+      <c r="Z72" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA72" s="59" t="s">
         <v>415</v>
       </c>
-      <c r="AB72" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC72" s="67" t="s">
+      <c r="AB72" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC72" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD72" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="73" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="45">
         <v>73</v>
       </c>
@@ -11258,20 +11545,23 @@
       <c r="Y73" s="58" t="s">
         <v>374</v>
       </c>
-      <c r="Z73" s="59" t="s">
-        <v>307</v>
+      <c r="Z73" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA73" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB73" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC73" s="67" t="s">
+      <c r="AB73" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC73" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD73" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="74" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="45">
         <v>74</v>
       </c>
@@ -11355,20 +11645,23 @@
       <c r="Y74" s="58" t="s">
         <v>375</v>
       </c>
-      <c r="Z74" s="59" t="s">
-        <v>307</v>
+      <c r="Z74" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA74" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB74" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC74" s="67" t="s">
+      <c r="AB74" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC74" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD74" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="75" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="45">
         <v>75</v>
       </c>
@@ -11452,20 +11745,23 @@
       <c r="Y75" s="58" t="s">
         <v>376</v>
       </c>
-      <c r="Z75" s="59" t="s">
-        <v>307</v>
+      <c r="Z75" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA75" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB75" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC75" s="67" t="s">
+      <c r="AB75" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC75" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD75" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="76" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="45">
         <v>76</v>
       </c>
@@ -11549,20 +11845,23 @@
       <c r="Y76" s="58" t="s">
         <v>422</v>
       </c>
-      <c r="Z76" s="59" t="s">
-        <v>307</v>
+      <c r="Z76" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA76" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB76" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC76" s="67" t="s">
+      <c r="AB76" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC76" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD76" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="77" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="45">
         <v>77</v>
       </c>
@@ -11646,20 +11945,23 @@
       <c r="Y77" s="58" t="s">
         <v>423</v>
       </c>
-      <c r="Z77" s="59" t="s">
-        <v>307</v>
+      <c r="Z77" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA77" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB77" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC77" s="67" t="s">
+      <c r="AB77" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC77" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD77" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="78" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="45">
         <v>78</v>
       </c>
@@ -11743,20 +12045,23 @@
       <c r="Y78" s="58" t="s">
         <v>379</v>
       </c>
-      <c r="Z78" s="59" t="s">
-        <v>307</v>
+      <c r="Z78" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA78" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB78" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC78" s="67" t="s">
+      <c r="AB78" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC78" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD78" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="79" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="45">
         <v>79</v>
       </c>
@@ -11840,20 +12145,23 @@
       <c r="Y79" s="58" t="s">
         <v>380</v>
       </c>
-      <c r="Z79" s="59" t="s">
-        <v>307</v>
+      <c r="Z79" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA79" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB79" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC79" s="67" t="s">
+      <c r="AB79" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC79" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD79" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="80" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="45">
         <v>80</v>
       </c>
@@ -11937,20 +12245,23 @@
       <c r="Y80" s="58" t="s">
         <v>381</v>
       </c>
-      <c r="Z80" s="59" t="s">
-        <v>307</v>
+      <c r="Z80" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA80" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB80" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC80" s="67" t="s">
+      <c r="AB80" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC80" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD80" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="81" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="45">
         <v>81</v>
       </c>
@@ -12034,20 +12345,23 @@
       <c r="Y81" s="58" t="s">
         <v>382</v>
       </c>
-      <c r="Z81" s="59" t="s">
-        <v>307</v>
+      <c r="Z81" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA81" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB81" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC81" s="67" t="s">
+      <c r="AB81" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC81" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD81" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="82" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="45">
         <v>82</v>
       </c>
@@ -12131,20 +12445,23 @@
       <c r="Y82" s="58" t="s">
         <v>385</v>
       </c>
-      <c r="Z82" s="59" t="s">
-        <v>307</v>
+      <c r="Z82" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA82" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB82" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC82" s="67" t="s">
+      <c r="AB82" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC82" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD82" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="83" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="45">
         <v>83</v>
       </c>
@@ -12228,20 +12545,23 @@
       <c r="Y83" s="58" t="s">
         <v>385</v>
       </c>
-      <c r="Z83" s="59" t="s">
-        <v>307</v>
+      <c r="Z83" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA83" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB83" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC83" s="67" t="s">
+      <c r="AB83" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC83" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD83" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="84" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="45">
         <v>84</v>
       </c>
@@ -12325,20 +12645,23 @@
       <c r="Y84" s="58" t="s">
         <v>385</v>
       </c>
-      <c r="Z84" s="59" t="s">
-        <v>307</v>
+      <c r="Z84" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA84" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB84" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC84" s="67" t="s">
+      <c r="AB84" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC84" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD84" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="85" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="45">
         <v>85</v>
       </c>
@@ -12422,20 +12745,23 @@
       <c r="Y85" s="58" t="s">
         <v>419</v>
       </c>
-      <c r="Z85" s="59" t="s">
-        <v>307</v>
+      <c r="Z85" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA85" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB85" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC85" s="67" t="s">
+      <c r="AB85" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC85" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD85" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="86" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="45">
         <v>86</v>
       </c>
@@ -12519,20 +12845,23 @@
       <c r="Y86" s="58" t="s">
         <v>420</v>
       </c>
-      <c r="Z86" s="59" t="s">
-        <v>307</v>
+      <c r="Z86" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA86" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB86" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC86" s="67" t="s">
+      <c r="AB86" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC86" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD86" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="87" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="45">
         <v>87</v>
       </c>
@@ -12616,20 +12945,23 @@
       <c r="Y87" s="58" t="s">
         <v>418</v>
       </c>
-      <c r="Z87" s="59" t="s">
-        <v>307</v>
+      <c r="Z87" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA87" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB87" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC87" s="67" t="s">
+      <c r="AB87" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC87" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD87" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="88" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="45">
         <v>88</v>
       </c>
@@ -12713,20 +13045,23 @@
       <c r="Y88" s="58" t="s">
         <v>421</v>
       </c>
-      <c r="Z88" s="59" t="s">
-        <v>307</v>
+      <c r="Z88" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA88" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB88" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC88" s="67" t="s">
+      <c r="AB88" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC88" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD88" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="89" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="45">
         <v>89</v>
       </c>
@@ -12810,20 +13145,23 @@
       <c r="Y89" s="58" t="s">
         <v>383</v>
       </c>
-      <c r="Z89" s="59" t="s">
-        <v>307</v>
+      <c r="Z89" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA89" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB89" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC89" s="67" t="s">
+      <c r="AB89" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC89" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD89" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="90" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="45">
         <v>90</v>
       </c>
@@ -12907,20 +13245,23 @@
       <c r="Y90" s="58" t="s">
         <v>384</v>
       </c>
-      <c r="Z90" s="59" t="s">
-        <v>307</v>
+      <c r="Z90" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA90" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB90" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC90" s="67" t="s">
+      <c r="AB90" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC90" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD90" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="91" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="45">
         <v>91</v>
       </c>
@@ -13004,20 +13345,23 @@
       <c r="Y91" s="58" t="s">
         <v>386</v>
       </c>
-      <c r="Z91" s="59" t="s">
-        <v>307</v>
+      <c r="Z91" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA91" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB91" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC91" s="67" t="s">
+      <c r="AB91" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC91" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD91" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="92" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="45">
         <v>92</v>
       </c>
@@ -13101,20 +13445,23 @@
       <c r="Y92" s="58" t="s">
         <v>387</v>
       </c>
-      <c r="Z92" s="59" t="s">
-        <v>307</v>
+      <c r="Z92" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA92" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB92" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC92" s="67" t="s">
+      <c r="AB92" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC92" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD92" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="93" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="45">
         <v>93</v>
       </c>
@@ -13198,20 +13545,23 @@
       <c r="Y93" s="58" t="s">
         <v>388</v>
       </c>
-      <c r="Z93" s="59" t="s">
-        <v>307</v>
+      <c r="Z93" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA93" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB93" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC93" s="67" t="s">
+      <c r="AB93" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC93" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD93" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="94" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="45">
         <v>94</v>
       </c>
@@ -13295,20 +13645,23 @@
       <c r="Y94" s="58" t="s">
         <v>389</v>
       </c>
-      <c r="Z94" s="59" t="s">
-        <v>307</v>
+      <c r="Z94" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA94" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB94" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC94" s="67" t="s">
+      <c r="AB94" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC94" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD94" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="95" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="45">
         <v>95</v>
       </c>
@@ -13392,20 +13745,23 @@
       <c r="Y95" s="58" t="s">
         <v>390</v>
       </c>
-      <c r="Z95" s="59" t="s">
-        <v>307</v>
+      <c r="Z95" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA95" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB95" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC95" s="67" t="s">
+      <c r="AB95" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC95" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD95" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="96" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="45">
         <v>96</v>
       </c>
@@ -13489,20 +13845,23 @@
       <c r="Y96" s="58" t="s">
         <v>391</v>
       </c>
-      <c r="Z96" s="59" t="s">
-        <v>307</v>
+      <c r="Z96" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA96" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB96" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC96" s="67" t="s">
+      <c r="AB96" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC96" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD96" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="97" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="45">
         <v>97</v>
       </c>
@@ -13586,20 +13945,23 @@
       <c r="Y97" s="58" t="s">
         <v>392</v>
       </c>
-      <c r="Z97" s="59" t="s">
-        <v>307</v>
+      <c r="Z97" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA97" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB97" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC97" s="67" t="s">
+      <c r="AB97" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC97" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD97" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="98" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="45">
         <v>98</v>
       </c>
@@ -13683,20 +14045,23 @@
       <c r="Y98" s="58" t="s">
         <v>393</v>
       </c>
-      <c r="Z98" s="59" t="s">
-        <v>307</v>
+      <c r="Z98" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA98" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB98" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC98" s="67" t="s">
+      <c r="AB98" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC98" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD98" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="99" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="45">
         <v>99</v>
       </c>
@@ -13780,20 +14145,23 @@
       <c r="Y99" s="58" t="s">
         <v>394</v>
       </c>
-      <c r="Z99" s="59" t="s">
-        <v>307</v>
+      <c r="Z99" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA99" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB99" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC99" s="67" t="s">
+      <c r="AB99" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC99" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD99" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="100" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="45">
         <v>100</v>
       </c>
@@ -13877,20 +14245,23 @@
       <c r="Y100" s="58" t="s">
         <v>395</v>
       </c>
-      <c r="Z100" s="59" t="s">
-        <v>307</v>
+      <c r="Z100" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA100" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB100" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC100" s="67" t="s">
+      <c r="AB100" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC100" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD100" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="101" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="45">
         <v>101</v>
       </c>
@@ -13974,20 +14345,23 @@
       <c r="Y101" s="58" t="s">
         <v>396</v>
       </c>
-      <c r="Z101" s="59" t="s">
-        <v>307</v>
+      <c r="Z101" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA101" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB101" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC101" s="67" t="s">
+      <c r="AB101" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC101" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD101" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="102" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="45">
         <v>102</v>
       </c>
@@ -14071,20 +14445,23 @@
       <c r="Y102" s="58" t="s">
         <v>399</v>
       </c>
-      <c r="Z102" s="59" t="s">
-        <v>307</v>
+      <c r="Z102" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA102" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB102" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC102" s="67" t="s">
+      <c r="AB102" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC102" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD102" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="103" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="45">
         <v>103</v>
       </c>
@@ -14168,20 +14545,23 @@
       <c r="Y103" s="58" t="s">
         <v>397</v>
       </c>
-      <c r="Z103" s="59" t="s">
-        <v>307</v>
+      <c r="Z103" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA103" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB103" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC103" s="67" t="s">
+      <c r="AB103" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC103" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD103" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="104" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="45">
         <v>104</v>
       </c>
@@ -14265,20 +14645,23 @@
       <c r="Y104" s="58" t="s">
         <v>398</v>
       </c>
-      <c r="Z104" s="59" t="s">
-        <v>307</v>
+      <c r="Z104" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA104" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB104" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC104" s="67" t="s">
+      <c r="AB104" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC104" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD104" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="105" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="45">
         <v>105</v>
       </c>
@@ -14362,20 +14745,23 @@
       <c r="Y105" s="58" t="s">
         <v>400</v>
       </c>
-      <c r="Z105" s="59" t="s">
-        <v>307</v>
+      <c r="Z105" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA105" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB105" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC105" s="67" t="s">
+      <c r="AB105" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC105" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD105" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="106" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="45">
         <v>106</v>
       </c>
@@ -14459,20 +14845,23 @@
       <c r="Y106" s="58" t="s">
         <v>401</v>
       </c>
-      <c r="Z106" s="59" t="s">
-        <v>307</v>
+      <c r="Z106" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA106" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB106" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC106" s="67" t="s">
+      <c r="AB106" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC106" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD106" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="107" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="45">
         <v>107</v>
       </c>
@@ -14556,20 +14945,23 @@
       <c r="Y107" s="58" t="s">
         <v>308</v>
       </c>
-      <c r="Z107" s="59" t="s">
-        <v>307</v>
+      <c r="Z107" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA107" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB107" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC107" s="67" t="s">
+      <c r="AB107" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC107" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD107" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="108" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="45">
         <v>108</v>
       </c>
@@ -14653,20 +15045,23 @@
       <c r="Y108" s="58" t="s">
         <v>309</v>
       </c>
-      <c r="Z108" s="59" t="s">
-        <v>307</v>
+      <c r="Z108" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA108" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB108" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC108" s="67" t="s">
+      <c r="AB108" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC108" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD108" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="109" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="45">
         <v>109</v>
       </c>
@@ -14750,20 +15145,23 @@
       <c r="Y109" s="58" t="s">
         <v>378</v>
       </c>
-      <c r="Z109" s="59" t="s">
-        <v>412</v>
+      <c r="Z109" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA109" s="59" t="s">
         <v>412</v>
       </c>
-      <c r="AB109" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC109" s="67" t="s">
+      <c r="AB109" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC109" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD109" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="110" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="45">
         <v>110</v>
       </c>
@@ -14847,20 +15245,23 @@
       <c r="Y110" s="58" t="s">
         <v>405</v>
       </c>
-      <c r="Z110" s="59" t="s">
-        <v>307</v>
+      <c r="Z110" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA110" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB110" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC110" s="67" t="s">
+      <c r="AB110" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC110" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD110" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="111" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="45">
         <v>111</v>
       </c>
@@ -14944,20 +15345,23 @@
       <c r="Y111" s="58" t="s">
         <v>402</v>
       </c>
-      <c r="Z111" s="59" t="s">
-        <v>307</v>
+      <c r="Z111" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA111" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB111" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC111" s="67" t="s">
+      <c r="AB111" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC111" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD111" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="112" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="45">
         <v>112</v>
       </c>
@@ -15041,20 +15445,23 @@
       <c r="Y112" s="58" t="s">
         <v>403</v>
       </c>
-      <c r="Z112" s="59" t="s">
-        <v>307</v>
+      <c r="Z112" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA112" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB112" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC112" s="67" t="s">
+      <c r="AB112" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC112" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD112" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="113" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="45">
         <v>113</v>
       </c>
@@ -15138,20 +15545,23 @@
       <c r="Y113" s="58" t="s">
         <v>404</v>
       </c>
-      <c r="Z113" s="59" t="s">
-        <v>307</v>
+      <c r="Z113" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA113" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB113" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC113" s="67" t="s">
+      <c r="AB113" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC113" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD113" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="114" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="45">
         <v>114</v>
       </c>
@@ -15235,20 +15645,23 @@
       <c r="Y114" s="58" t="s">
         <v>406</v>
       </c>
-      <c r="Z114" s="59" t="s">
-        <v>307</v>
+      <c r="Z114" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA114" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB114" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC114" s="67" t="s">
+      <c r="AB114" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC114" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD114" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="115" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="45">
         <v>115</v>
       </c>
@@ -15332,20 +15745,23 @@
       <c r="Y115" s="58" t="s">
         <v>407</v>
       </c>
-      <c r="Z115" s="59" t="s">
-        <v>307</v>
+      <c r="Z115" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA115" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB115" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC115" s="67" t="s">
+      <c r="AB115" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC115" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD115" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="116" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="45">
         <v>116</v>
       </c>
@@ -15429,20 +15845,23 @@
       <c r="Y116" s="58" t="s">
         <v>408</v>
       </c>
-      <c r="Z116" s="59" t="s">
-        <v>307</v>
+      <c r="Z116" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA116" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB116" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC116" s="67" t="s">
+      <c r="AB116" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC116" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD116" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="117" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="45">
         <v>117</v>
       </c>
@@ -15526,20 +15945,23 @@
       <c r="Y117" s="58" t="s">
         <v>409</v>
       </c>
-      <c r="Z117" s="59" t="s">
-        <v>307</v>
+      <c r="Z117" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA117" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB117" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC117" s="67" t="s">
+      <c r="AB117" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC117" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD117" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="118" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="45">
         <v>118</v>
       </c>
@@ -15623,20 +16045,23 @@
       <c r="Y118" s="58" t="s">
         <v>410</v>
       </c>
-      <c r="Z118" s="59" t="s">
-        <v>307</v>
+      <c r="Z118" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA118" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB118" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC118" s="67" t="s">
+      <c r="AB118" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC118" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD118" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="119" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="45">
         <v>119</v>
       </c>
@@ -15720,20 +16145,23 @@
       <c r="Y119" s="58" t="s">
         <v>411</v>
       </c>
-      <c r="Z119" s="59" t="s">
-        <v>307</v>
+      <c r="Z119" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA119" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB119" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC119" s="67" t="s">
+      <c r="AB119" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC119" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD119" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="120" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="45">
         <v>120</v>
       </c>
@@ -15817,20 +16245,23 @@
       <c r="Y120" s="58" t="s">
         <v>577</v>
       </c>
-      <c r="Z120" s="59" t="s">
-        <v>307</v>
+      <c r="Z120" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA120" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB120" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC120" s="67" t="s">
+      <c r="AB120" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC120" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD120" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="121" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="45">
         <v>121</v>
       </c>
@@ -15914,20 +16345,23 @@
       <c r="Y121" s="58" t="s">
         <v>575</v>
       </c>
-      <c r="Z121" s="59" t="s">
-        <v>307</v>
+      <c r="Z121" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA121" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB121" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC121" s="67" t="s">
+      <c r="AB121" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC121" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD121" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="122" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="45">
         <v>122</v>
       </c>
@@ -16005,26 +16439,29 @@
         <v>80</v>
       </c>
       <c r="X122" s="54" t="str">
-        <f t="shared" ref="X122:X138" si="50">CONCATENATE("Key-DOCU-",A122)</f>
+        <f t="shared" ref="X122:X137" si="50">CONCATENATE("Key-DOCU-",A122)</f>
         <v>Key-DOCU-122</v>
       </c>
       <c r="Y122" s="58" t="s">
         <v>576</v>
       </c>
-      <c r="Z122" s="59" t="s">
-        <v>307</v>
+      <c r="Z122" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA122" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="AB122" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC122" s="67" t="s">
+      <c r="AB122" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC122" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD122" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="123" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="45">
         <v>123</v>
       </c>
@@ -16105,23 +16542,26 @@
         <f t="shared" si="50"/>
         <v>Key-DOCU-123</v>
       </c>
-      <c r="Y123" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z123" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA123" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB123" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC123" s="67" t="s">
+      <c r="Y123" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z123" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA123" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB123" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC123" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD123" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="124" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="45">
         <v>124</v>
       </c>
@@ -16202,23 +16642,26 @@
         <f t="shared" si="50"/>
         <v>Key-DOCU-124</v>
       </c>
-      <c r="Y124" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z124" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA124" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB124" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC124" s="67" t="s">
+      <c r="Y124" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z124" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA124" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB124" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC124" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD124" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="125" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="45">
         <v>125</v>
       </c>
@@ -16299,23 +16742,26 @@
         <f t="shared" si="50"/>
         <v>Key-DOCU-125</v>
       </c>
-      <c r="Y125" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z125" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA125" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB125" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC125" s="67" t="s">
+      <c r="Y125" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z125" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA125" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB125" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC125" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD125" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="126" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="45">
         <v>126</v>
       </c>
@@ -16396,23 +16842,26 @@
         <f t="shared" si="50"/>
         <v>Key-DOCU-126</v>
       </c>
-      <c r="Y126" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z126" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA126" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB126" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC126" s="67" t="s">
+      <c r="Y126" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z126" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA126" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB126" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC126" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD126" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="127" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="45">
         <v>127</v>
       </c>
@@ -16493,23 +16942,26 @@
         <f t="shared" si="50"/>
         <v>Key-DOCU-127</v>
       </c>
-      <c r="Y127" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z127" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA127" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB127" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC127" s="67" t="s">
+      <c r="Y127" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z127" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA127" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB127" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC127" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD127" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="128" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="45">
         <v>128</v>
       </c>
@@ -16590,23 +17042,26 @@
         <f t="shared" si="50"/>
         <v>Key-DOCU-128</v>
       </c>
-      <c r="Y128" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z128" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA128" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB128" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC128" s="67" t="s">
+      <c r="Y128" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z128" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA128" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB128" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC128" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD128" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="129" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="45">
         <v>129</v>
       </c>
@@ -16687,23 +17142,26 @@
         <f t="shared" si="50"/>
         <v>Key-DOCU-129</v>
       </c>
-      <c r="Y129" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z129" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA129" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB129" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC129" s="67" t="s">
+      <c r="Y129" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z129" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA129" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB129" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC129" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD129" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="130" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="45">
         <v>130</v>
       </c>
@@ -16784,23 +17242,26 @@
         <f t="shared" si="50"/>
         <v>Key-DOCU-130</v>
       </c>
-      <c r="Y130" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z130" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA130" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB130" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC130" s="67" t="s">
+      <c r="Y130" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z130" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA130" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB130" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC130" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD130" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="131" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="45">
         <v>131</v>
       </c>
@@ -16881,23 +17342,26 @@
         <f t="shared" si="50"/>
         <v>Key-DOCU-131</v>
       </c>
-      <c r="Y131" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z131" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA131" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB131" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC131" s="67" t="s">
+      <c r="Y131" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z131" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA131" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB131" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC131" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD131" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="132" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="45">
         <v>132</v>
       </c>
@@ -16978,23 +17442,26 @@
         <f t="shared" si="50"/>
         <v>Key-DOCU-132</v>
       </c>
-      <c r="Y132" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z132" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA132" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB132" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC132" s="67" t="s">
+      <c r="Y132" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z132" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA132" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB132" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC132" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD132" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="133" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="45">
         <v>133</v>
       </c>
@@ -17075,23 +17542,26 @@
         <f t="shared" si="50"/>
         <v>Key-DOCU-133</v>
       </c>
-      <c r="Y133" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z133" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA133" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB133" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC133" s="67" t="s">
+      <c r="Y133" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z133" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA133" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB133" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC133" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD133" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="134" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="45">
         <v>134</v>
       </c>
@@ -17172,23 +17642,26 @@
         <f t="shared" si="50"/>
         <v>Key-DOCU-134</v>
       </c>
-      <c r="Y134" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z134" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA134" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB134" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC134" s="67" t="s">
+      <c r="Y134" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z134" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA134" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB134" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC134" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD134" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="135" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="45">
         <v>135</v>
       </c>
@@ -17269,23 +17742,26 @@
         <f t="shared" si="50"/>
         <v>Key-DOCU-135</v>
       </c>
-      <c r="Y135" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z135" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA135" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB135" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC135" s="67" t="s">
+      <c r="Y135" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z135" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA135" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB135" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC135" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD135" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="136" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="45">
         <v>136</v>
       </c>
@@ -17366,23 +17842,26 @@
         <f t="shared" si="50"/>
         <v>Key-DOCU-136</v>
       </c>
-      <c r="Y136" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z136" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA136" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB136" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC136" s="67" t="s">
+      <c r="Y136" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z136" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA136" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB136" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC136" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD136" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="137" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="45">
         <v>137</v>
       </c>
@@ -17463,89 +17942,92 @@
         <f t="shared" si="50"/>
         <v>Key-DOCU-137</v>
       </c>
-      <c r="Y137" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z137" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA137" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB137" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC137" s="67" t="s">
+      <c r="Y137" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z137" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA137" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB137" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC137" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD137" s="65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="138" spans="1:29" s="68" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:30" s="66" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="45">
         <v>138</v>
       </c>
-      <c r="B138" s="62" t="s">
+      <c r="B138" s="75" t="s">
         <v>899</v>
       </c>
-      <c r="C138" s="63" t="s">
+      <c r="C138" s="76" t="s">
         <v>900</v>
       </c>
-      <c r="D138" s="63" t="s">
+      <c r="D138" s="76" t="s">
         <v>902</v>
       </c>
-      <c r="E138" s="63" t="s">
+      <c r="E138" s="76" t="s">
         <v>901</v>
       </c>
-      <c r="F138" s="63" t="s">
-        <v>903</v>
-      </c>
-      <c r="G138" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="H138" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="I138" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="J138" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="K138" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="L138" s="65" t="str">
-        <f t="shared" ref="L138:O138" si="60">SUBSTITUTE(CONCATENATE("", C138), ".", " ")</f>
+      <c r="F138" s="76" t="s">
+        <v>926</v>
+      </c>
+      <c r="G138" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="H138" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="I138" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="J138" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="K138" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="L138" s="63" t="str">
+        <f t="shared" ref="L138:O142" si="60">SUBSTITUTE(CONCATENATE("", C138), ".", " ")</f>
         <v>De API</v>
       </c>
-      <c r="M138" s="65" t="str">
+      <c r="M138" s="63" t="str">
         <f t="shared" si="60"/>
         <v>Macros</v>
       </c>
-      <c r="N138" s="65" t="str">
+      <c r="N138" s="63" t="str">
         <f t="shared" si="60"/>
         <v>Métodos</v>
       </c>
-      <c r="O138" s="65" t="str">
+      <c r="O138" s="63" t="str">
         <f t="shared" si="60"/>
-        <v>API Revit</v>
-      </c>
-      <c r="P138" s="66" t="s">
-        <v>904</v>
-      </c>
-      <c r="Q138" s="66" t="s">
-        <v>905</v>
-      </c>
-      <c r="R138" s="66" t="s">
-        <v>906</v>
-      </c>
-      <c r="S138" s="66" t="s">
-        <v>9</v>
-      </c>
-      <c r="T138" s="66" t="str">
-        <f t="shared" ref="T138:V138" si="61">SUBSTITUTE(C138, ".", " ")</f>
+        <v>Função Auxiliar</v>
+      </c>
+      <c r="P138" s="64" t="s">
+        <v>927</v>
+      </c>
+      <c r="Q138" s="64" t="s">
+        <v>928</v>
+      </c>
+      <c r="R138" s="64" t="s">
+        <v>929</v>
+      </c>
+      <c r="S138" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="T138" s="64" t="str">
+        <f t="shared" ref="T138:V142" si="61">SUBSTITUTE(C138, ".", " ")</f>
         <v>De API</v>
       </c>
-      <c r="U138" s="66" t="str">
+      <c r="U138" s="64" t="str">
         <f t="shared" si="61"/>
         <v>Macros</v>
       </c>
@@ -17557,22 +18039,425 @@
         <v>80</v>
       </c>
       <c r="X138" s="54" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" ref="X138:X142" si="62">CONCATENATE("Key-DOCU-",A138)</f>
         <v>Key-DOCU-138</v>
       </c>
-      <c r="Y138" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z138" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA138" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB138" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC138" s="67" t="s">
+      <c r="Y138" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z138" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA138" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB138" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC138" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD138" s="65" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="139" spans="1:30" s="66" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A139" s="45">
+        <v>139</v>
+      </c>
+      <c r="B139" s="75" t="s">
+        <v>899</v>
+      </c>
+      <c r="C139" s="76" t="s">
+        <v>900</v>
+      </c>
+      <c r="D139" s="76" t="s">
+        <v>902</v>
+      </c>
+      <c r="E139" s="76" t="s">
+        <v>901</v>
+      </c>
+      <c r="F139" s="76" t="s">
+        <v>930</v>
+      </c>
+      <c r="G139" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="H139" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="I139" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="J139" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="K139" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="L139" s="63" t="str">
+        <f t="shared" si="60"/>
+        <v>De API</v>
+      </c>
+      <c r="M139" s="63" t="str">
+        <f t="shared" si="60"/>
+        <v>Macros</v>
+      </c>
+      <c r="N139" s="63" t="str">
+        <f t="shared" si="60"/>
+        <v>Métodos</v>
+      </c>
+      <c r="O139" s="63" t="str">
+        <f t="shared" si="60"/>
+        <v>Função Global</v>
+      </c>
+      <c r="P139" s="64" t="s">
+        <v>931</v>
+      </c>
+      <c r="Q139" s="64" t="s">
+        <v>932</v>
+      </c>
+      <c r="R139" s="64" t="s">
+        <v>933</v>
+      </c>
+      <c r="S139" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="T139" s="64" t="str">
+        <f t="shared" si="61"/>
+        <v>De API</v>
+      </c>
+      <c r="U139" s="64" t="str">
+        <f t="shared" si="61"/>
+        <v>Macros</v>
+      </c>
+      <c r="V139" s="43" t="str">
+        <f t="shared" si="61"/>
+        <v>Métodos</v>
+      </c>
+      <c r="W139" s="43" t="s">
+        <v>80</v>
+      </c>
+      <c r="X139" s="54" t="str">
+        <f t="shared" si="62"/>
+        <v>Key-DOCU-139</v>
+      </c>
+      <c r="Y139" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z139" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA139" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB139" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC139" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD139" s="65" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="140" spans="1:30" s="66" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A140" s="45">
+        <v>140</v>
+      </c>
+      <c r="B140" s="75" t="s">
+        <v>899</v>
+      </c>
+      <c r="C140" s="76" t="s">
+        <v>900</v>
+      </c>
+      <c r="D140" s="76" t="s">
+        <v>902</v>
+      </c>
+      <c r="E140" s="76" t="s">
+        <v>901</v>
+      </c>
+      <c r="F140" s="76" t="s">
+        <v>934</v>
+      </c>
+      <c r="G140" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="H140" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="I140" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="J140" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="K140" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="L140" s="63" t="str">
+        <f t="shared" si="60"/>
+        <v>De API</v>
+      </c>
+      <c r="M140" s="63" t="str">
+        <f t="shared" si="60"/>
+        <v>Macros</v>
+      </c>
+      <c r="N140" s="63" t="str">
+        <f t="shared" si="60"/>
+        <v>Métodos</v>
+      </c>
+      <c r="O140" s="63" t="str">
+        <f t="shared" si="60"/>
+        <v>Função Local</v>
+      </c>
+      <c r="P140" s="64" t="s">
+        <v>935</v>
+      </c>
+      <c r="Q140" s="64" t="s">
+        <v>936</v>
+      </c>
+      <c r="R140" s="64" t="s">
+        <v>937</v>
+      </c>
+      <c r="S140" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="T140" s="64" t="str">
+        <f t="shared" si="61"/>
+        <v>De API</v>
+      </c>
+      <c r="U140" s="64" t="str">
+        <f t="shared" si="61"/>
+        <v>Macros</v>
+      </c>
+      <c r="V140" s="43" t="str">
+        <f t="shared" si="61"/>
+        <v>Métodos</v>
+      </c>
+      <c r="W140" s="43" t="s">
+        <v>80</v>
+      </c>
+      <c r="X140" s="54" t="str">
+        <f t="shared" si="62"/>
+        <v>Key-DOCU-140</v>
+      </c>
+      <c r="Y140" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z140" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA140" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB140" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC140" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD140" s="65" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="141" spans="1:30" s="66" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A141" s="45">
+        <v>141</v>
+      </c>
+      <c r="B141" s="75" t="s">
+        <v>899</v>
+      </c>
+      <c r="C141" s="76" t="s">
+        <v>900</v>
+      </c>
+      <c r="D141" s="76" t="s">
+        <v>902</v>
+      </c>
+      <c r="E141" s="76" t="s">
+        <v>901</v>
+      </c>
+      <c r="F141" s="76" t="s">
+        <v>938</v>
+      </c>
+      <c r="G141" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="H141" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="I141" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="J141" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="K141" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="L141" s="63" t="str">
+        <f t="shared" si="60"/>
+        <v>De API</v>
+      </c>
+      <c r="M141" s="63" t="str">
+        <f t="shared" si="60"/>
+        <v>Macros</v>
+      </c>
+      <c r="N141" s="63" t="str">
+        <f t="shared" si="60"/>
+        <v>Métodos</v>
+      </c>
+      <c r="O141" s="63" t="str">
+        <f t="shared" si="60"/>
+        <v>Função Filtro</v>
+      </c>
+      <c r="P141" s="64" t="s">
+        <v>939</v>
+      </c>
+      <c r="Q141" s="64" t="s">
+        <v>940</v>
+      </c>
+      <c r="R141" s="64" t="s">
+        <v>941</v>
+      </c>
+      <c r="S141" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="T141" s="64" t="str">
+        <f t="shared" si="61"/>
+        <v>De API</v>
+      </c>
+      <c r="U141" s="64" t="str">
+        <f t="shared" si="61"/>
+        <v>Macros</v>
+      </c>
+      <c r="V141" s="43" t="str">
+        <f t="shared" si="61"/>
+        <v>Métodos</v>
+      </c>
+      <c r="W141" s="43" t="s">
+        <v>80</v>
+      </c>
+      <c r="X141" s="54" t="str">
+        <f t="shared" si="62"/>
+        <v>Key-DOCU-141</v>
+      </c>
+      <c r="Y141" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z141" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA141" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB141" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC141" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD141" s="65" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="142" spans="1:30" s="66" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A142" s="45">
+        <v>142</v>
+      </c>
+      <c r="B142" s="75" t="s">
+        <v>899</v>
+      </c>
+      <c r="C142" s="76" t="s">
+        <v>900</v>
+      </c>
+      <c r="D142" s="76" t="s">
+        <v>902</v>
+      </c>
+      <c r="E142" s="76" t="s">
+        <v>942</v>
+      </c>
+      <c r="F142" s="76" t="s">
+        <v>943</v>
+      </c>
+      <c r="G142" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="H142" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="I142" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="J142" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="K142" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="L142" s="63" t="str">
+        <f t="shared" si="60"/>
+        <v>De API</v>
+      </c>
+      <c r="M142" s="63" t="str">
+        <f t="shared" si="60"/>
+        <v>Macros</v>
+      </c>
+      <c r="N142" s="63" t="str">
+        <f t="shared" si="60"/>
+        <v>Códigos Visuais</v>
+      </c>
+      <c r="O142" s="63" t="str">
+        <f t="shared" si="60"/>
+        <v>Bloco de Código</v>
+      </c>
+      <c r="P142" s="64" t="s">
+        <v>944</v>
+      </c>
+      <c r="Q142" s="64" t="s">
+        <v>945</v>
+      </c>
+      <c r="R142" s="64" t="s">
+        <v>946</v>
+      </c>
+      <c r="S142" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="T142" s="64" t="str">
+        <f t="shared" si="61"/>
+        <v>De API</v>
+      </c>
+      <c r="U142" s="64" t="str">
+        <f t="shared" si="61"/>
+        <v>Macros</v>
+      </c>
+      <c r="V142" s="43" t="str">
+        <f t="shared" si="61"/>
+        <v>Códigos Visuais</v>
+      </c>
+      <c r="W142" s="43" t="s">
+        <v>80</v>
+      </c>
+      <c r="X142" s="54" t="str">
+        <f t="shared" si="62"/>
+        <v>Key-DOCU-142</v>
+      </c>
+      <c r="Y142" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z142" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA142" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB142" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC142" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD142" s="65" t="s">
         <v>9</v>
       </c>
     </row>
@@ -17580,37 +18465,40 @@
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A8:AC138">
     <sortCondition ref="A1:A138"/>
   </sortState>
-  <conditionalFormatting sqref="A2:B138">
-    <cfRule type="cellIs" dxfId="14" priority="2" operator="equal">
+  <conditionalFormatting sqref="A2:B142">
+    <cfRule type="cellIs" dxfId="15" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="E142:F142">
+    <cfRule type="duplicateValues" dxfId="14" priority="2"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="duplicateValues" dxfId="13" priority="37"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="38"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="39"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="40"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="44"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F1:F137 F139:F1048576">
-    <cfRule type="duplicateValues" dxfId="8" priority="13"/>
+  <conditionalFormatting sqref="F1:F137 F143:F1048576">
+    <cfRule type="duplicateValues" dxfId="8" priority="16"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F138">
+  <conditionalFormatting sqref="F138:F141">
     <cfRule type="duplicateValues" dxfId="7" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G1:O1">
-    <cfRule type="cellIs" dxfId="6" priority="31" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="34" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R1:R138">
-    <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
+  <conditionalFormatting sqref="R1:R137">
+    <cfRule type="cellIs" dxfId="5" priority="4" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <ignoredErrors>
-    <ignoredError sqref="AC1 AC139:AC1048576 B36:D61 B95:D95 AD1:XFD137 F95:P95 B96:P117 F36:P61 B62:P94 B3:P11 A139:P1048576 A1:P2 AA8:AA122 S1:X1 S8:Y121 S2:X2 S3:X7 AA139:AA1048576 S139:Y1048576 S123:V123 S124:V134 B120:P137 B119:P119 B118:P118 B13:P21 B12:P12 B23:P35 B22:P22 AD139:XFD1048576 S135:V137 S122:V122 X122:Y122 X123 X124:X134" numberStoredAsText="1"/>
+    <ignoredError sqref="AC1 AC143:AC1048576 B36:D61 B95:D95 AE1:XFD137 F95:P95 B96:P117 F36:P61 B62:P94 B3:P11 A143:P1048576 A1:P2 AA8:AA122 S1:X1 S8:Y121 S2:X2 S3:X7 AA143:AA1048576 S143:Y1048576 S123:V123 S124:V134 B120:P137 B119:P119 B118:P118 B13:P21 B12:P12 B23:P35 B22:P22 AE143:XFD1048576 S135:V137 S122:V122 X122:Y122 X123 X124:X134" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -17618,14 +18506,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{779E4F22-2568-4D5A-A538-DD63A5C43724}">
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultColWidth="5.69140625" defaultRowHeight="7.95" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="5.7109375" defaultRowHeight="7.9" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.69140625" style="11" customWidth="1"/>
-    <col min="2" max="10" width="5.69140625" style="12"/>
-    <col min="11" max="16384" width="5.69140625" style="24"/>
+    <col min="1" max="1" width="2.7109375" style="11" customWidth="1"/>
+    <col min="2" max="10" width="5.7109375" style="12"/>
+    <col min="11" max="16384" width="5.7109375" style="24"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="7.75" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" ht="16.5" x14ac:dyDescent="0.15">
       <c r="A1" s="22">
         <v>1</v>
       </c>
@@ -17690,7 +18578,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="7.75" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21" ht="8.25" x14ac:dyDescent="0.15">
       <c r="A2" s="22">
         <v>2</v>
       </c>
@@ -17763,15 +18651,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4328B84A-AA24-421E-9F4E-92D6A71CA3BE}">
   <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="3" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.15234375" style="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" style="13" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="11" style="13" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="9.15234375" style="13"/>
+    <col min="5" max="16384" width="9.140625" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="8">
         <v>1</v>
       </c>
@@ -17785,7 +18673,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" ht="6.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="7">
         <v>2</v>
       </c>
@@ -17807,48 +18695,48 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{429087C4-377B-4931-BC50-C00BD9684F83}">
   <dimension ref="A1:AK42"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.53515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.84375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.53515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.15234375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.84375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.69140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.69140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="4.3046875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="4.84375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="4.3046875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="4.84375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="4.3046875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="4.84375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="4.85546875" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="6" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="81.15234375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="8.3828125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="15.84375" customWidth="1"/>
-    <col min="18" max="18" width="6.69140625" customWidth="1"/>
+    <col min="15" max="15" width="81.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.85546875" customWidth="1"/>
+    <col min="18" max="18" width="6.7109375" customWidth="1"/>
     <col min="19" max="19" width="7" customWidth="1"/>
-    <col min="20" max="20" width="7.53515625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="12.15234375" customWidth="1"/>
-    <col min="22" max="22" width="7.53515625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.84375" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="7.53515625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.84375" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="7.53515625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="9.3828125" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="4.3046875" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="4.84375" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="4.3046875" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="4.84375" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="4.3046875" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="4.84375" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="4.3046875" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="4.84375" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="4.3046875" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="4.84375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12.140625" customWidth="1"/>
+    <col min="22" max="22" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="4.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" ht="25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:37" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="14" t="s">
         <v>30</v>
       </c>
@@ -17961,7 +18849,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="16">
         <v>2</v>
       </c>
@@ -18037,44 +18925,44 @@
       <c r="Y2" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="Z2" s="76" t="s">
+      <c r="Z2" s="74" t="s">
         <v>9</v>
       </c>
       <c r="AA2" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="AB2" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC2" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD2" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE2" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AF2" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AG2" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AH2" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AI2" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AJ2" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AK2" s="75" t="s">
+      <c r="AB2" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC2" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD2" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE2" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF2" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG2" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH2" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI2" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ2" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK2" s="73" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="16">
         <v>3</v>
       </c>
@@ -18150,44 +19038,44 @@
       <c r="Y3" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="Z3" s="76" t="s">
+      <c r="Z3" s="74" t="s">
         <v>9</v>
       </c>
       <c r="AA3" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="AB3" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC3" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD3" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE3" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AF3" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AG3" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AH3" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AI3" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AJ3" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AK3" s="75" t="s">
+      <c r="AB3" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC3" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD3" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE3" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF3" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG3" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH3" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI3" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ3" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK3" s="73" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="16">
         <v>4</v>
       </c>
@@ -18263,44 +19151,44 @@
       <c r="Y4" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="Z4" s="76" t="s">
+      <c r="Z4" s="74" t="s">
         <v>9</v>
       </c>
       <c r="AA4" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="AB4" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC4" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD4" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE4" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AF4" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AG4" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AH4" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AI4" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AJ4" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AK4" s="75" t="s">
+      <c r="AB4" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC4" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD4" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE4" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF4" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG4" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH4" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI4" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ4" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK4" s="73" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="16">
         <v>5</v>
       </c>
@@ -18376,44 +19264,44 @@
       <c r="Y5" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="Z5" s="76" t="s">
+      <c r="Z5" s="74" t="s">
         <v>9</v>
       </c>
       <c r="AA5" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="AB5" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC5" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD5" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE5" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AF5" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AG5" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AH5" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AI5" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AJ5" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AK5" s="75" t="s">
+      <c r="AB5" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC5" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD5" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE5" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF5" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG5" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH5" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI5" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ5" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK5" s="73" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="16">
         <v>6</v>
       </c>
@@ -18489,44 +19377,44 @@
       <c r="Y6" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="Z6" s="76" t="s">
+      <c r="Z6" s="74" t="s">
         <v>9</v>
       </c>
       <c r="AA6" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="AB6" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC6" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD6" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE6" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AF6" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AG6" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AH6" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AI6" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AJ6" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AK6" s="75" t="s">
+      <c r="AB6" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC6" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD6" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE6" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF6" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG6" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH6" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI6" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ6" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK6" s="73" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="16">
         <v>7</v>
       </c>
@@ -18602,44 +19490,44 @@
       <c r="Y7" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="Z7" s="76" t="s">
+      <c r="Z7" s="74" t="s">
         <v>9</v>
       </c>
       <c r="AA7" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="AB7" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC7" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD7" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE7" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AF7" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AG7" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AH7" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AI7" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AJ7" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AK7" s="75" t="s">
+      <c r="AB7" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC7" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD7" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE7" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF7" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG7" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH7" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI7" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ7" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK7" s="73" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="16">
         <v>8</v>
       </c>
@@ -18715,44 +19603,44 @@
       <c r="Y8" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="Z8" s="76" t="s">
+      <c r="Z8" s="74" t="s">
         <v>9</v>
       </c>
       <c r="AA8" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="AB8" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC8" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD8" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE8" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AF8" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AG8" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AH8" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AI8" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AJ8" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AK8" s="75" t="s">
+      <c r="AB8" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC8" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD8" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE8" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF8" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG8" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH8" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI8" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ8" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK8" s="73" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="16">
         <v>9</v>
       </c>
@@ -18828,44 +19716,44 @@
       <c r="Y9" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="Z9" s="76" t="s">
+      <c r="Z9" s="74" t="s">
         <v>9</v>
       </c>
       <c r="AA9" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="AB9" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC9" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD9" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE9" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AF9" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AG9" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AH9" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AI9" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AJ9" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AK9" s="75" t="s">
+      <c r="AB9" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC9" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD9" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE9" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF9" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG9" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH9" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI9" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ9" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK9" s="73" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="16">
         <v>10</v>
       </c>
@@ -18941,44 +19829,44 @@
       <c r="Y10" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="Z10" s="76" t="s">
+      <c r="Z10" s="74" t="s">
         <v>9</v>
       </c>
       <c r="AA10" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="AB10" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC10" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD10" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE10" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AF10" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AG10" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AH10" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AI10" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AJ10" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AK10" s="75" t="s">
+      <c r="AB10" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC10" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD10" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE10" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF10" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG10" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH10" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI10" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ10" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK10" s="73" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="16">
         <v>11</v>
       </c>
@@ -19054,44 +19942,44 @@
       <c r="Y11" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="Z11" s="76" t="s">
+      <c r="Z11" s="74" t="s">
         <v>9</v>
       </c>
       <c r="AA11" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="AB11" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC11" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD11" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE11" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AF11" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AG11" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AH11" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AI11" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AJ11" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AK11" s="75" t="s">
+      <c r="AB11" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC11" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD11" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE11" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF11" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG11" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH11" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI11" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ11" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK11" s="73" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="16">
         <v>12</v>
       </c>
@@ -19167,44 +20055,44 @@
       <c r="Y12" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="Z12" s="76" t="s">
+      <c r="Z12" s="74" t="s">
         <v>9</v>
       </c>
       <c r="AA12" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="AB12" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC12" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD12" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE12" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AF12" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AG12" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AH12" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AI12" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AJ12" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AK12" s="75" t="s">
+      <c r="AB12" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC12" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD12" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE12" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF12" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG12" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH12" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI12" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ12" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK12" s="73" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="16">
         <v>13</v>
       </c>
@@ -19280,44 +20168,44 @@
       <c r="Y13" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="Z13" s="76" t="s">
+      <c r="Z13" s="74" t="s">
         <v>9</v>
       </c>
       <c r="AA13" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="AB13" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC13" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD13" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE13" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AF13" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AG13" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AH13" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AI13" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AJ13" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AK13" s="75" t="s">
+      <c r="AB13" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC13" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD13" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE13" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF13" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG13" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH13" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI13" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ13" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK13" s="73" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="16">
         <v>14</v>
       </c>
@@ -19393,44 +20281,44 @@
       <c r="Y14" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="Z14" s="76" t="s">
+      <c r="Z14" s="74" t="s">
         <v>9</v>
       </c>
       <c r="AA14" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="AB14" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC14" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD14" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE14" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AF14" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AG14" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AH14" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AI14" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AJ14" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AK14" s="75" t="s">
+      <c r="AB14" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC14" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD14" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE14" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF14" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG14" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH14" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI14" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ14" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK14" s="73" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="16">
         <v>15</v>
       </c>
@@ -19506,44 +20394,44 @@
       <c r="Y15" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="Z15" s="76" t="s">
+      <c r="Z15" s="74" t="s">
         <v>9</v>
       </c>
       <c r="AA15" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="AB15" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC15" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD15" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE15" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AF15" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AG15" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AH15" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AI15" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AJ15" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AK15" s="75" t="s">
+      <c r="AB15" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC15" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD15" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE15" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF15" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG15" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH15" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI15" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ15" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK15" s="73" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="16">
         <v>16</v>
       </c>
@@ -19619,44 +20507,44 @@
       <c r="Y16" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="Z16" s="76" t="s">
+      <c r="Z16" s="74" t="s">
         <v>9</v>
       </c>
       <c r="AA16" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="AB16" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC16" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD16" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE16" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AF16" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AG16" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AH16" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AI16" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AJ16" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AK16" s="75" t="s">
+      <c r="AB16" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC16" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD16" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE16" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF16" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG16" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH16" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI16" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ16" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK16" s="73" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="16">
         <v>17</v>
       </c>
@@ -19732,44 +20620,44 @@
       <c r="Y17" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="Z17" s="76" t="s">
+      <c r="Z17" s="74" t="s">
         <v>9</v>
       </c>
       <c r="AA17" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="AB17" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC17" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD17" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE17" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AF17" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AG17" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AH17" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AI17" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AJ17" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AK17" s="75" t="s">
+      <c r="AB17" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC17" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD17" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE17" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF17" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG17" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH17" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI17" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ17" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK17" s="73" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="16">
         <v>18</v>
       </c>
@@ -19845,44 +20733,44 @@
       <c r="Y18" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="Z18" s="76" t="s">
+      <c r="Z18" s="74" t="s">
         <v>9</v>
       </c>
       <c r="AA18" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="AB18" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC18" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD18" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE18" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AF18" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AG18" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AH18" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AI18" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AJ18" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AK18" s="75" t="s">
+      <c r="AB18" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC18" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD18" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE18" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF18" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG18" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH18" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI18" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ18" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK18" s="73" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="16">
         <v>19</v>
       </c>
@@ -19958,44 +20846,44 @@
       <c r="Y19" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="Z19" s="76" t="s">
+      <c r="Z19" s="74" t="s">
         <v>9</v>
       </c>
       <c r="AA19" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="AB19" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC19" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD19" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE19" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AF19" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AG19" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AH19" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AI19" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AJ19" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AK19" s="75" t="s">
+      <c r="AB19" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC19" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD19" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE19" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF19" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG19" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH19" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI19" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ19" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK19" s="73" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="16">
         <v>20</v>
       </c>
@@ -20071,44 +20959,44 @@
       <c r="Y20" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="Z20" s="76" t="s">
+      <c r="Z20" s="74" t="s">
         <v>9</v>
       </c>
       <c r="AA20" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="AB20" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC20" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD20" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE20" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AF20" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AG20" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AH20" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AI20" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AJ20" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AK20" s="75" t="s">
+      <c r="AB20" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC20" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD20" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE20" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF20" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG20" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH20" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI20" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ20" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK20" s="73" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="16">
         <v>21</v>
       </c>
@@ -20184,44 +21072,44 @@
       <c r="Y21" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="Z21" s="76" t="s">
+      <c r="Z21" s="74" t="s">
         <v>9</v>
       </c>
       <c r="AA21" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="AB21" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC21" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD21" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE21" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AF21" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AG21" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AH21" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AI21" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AJ21" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AK21" s="75" t="s">
+      <c r="AB21" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC21" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD21" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE21" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF21" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG21" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH21" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI21" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ21" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK21" s="73" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="16">
         <v>22</v>
       </c>
@@ -20297,44 +21185,44 @@
       <c r="Y22" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="Z22" s="76" t="s">
+      <c r="Z22" s="74" t="s">
         <v>9</v>
       </c>
       <c r="AA22" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="AB22" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC22" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD22" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE22" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AF22" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AG22" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AH22" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AI22" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AJ22" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AK22" s="75" t="s">
+      <c r="AB22" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC22" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD22" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE22" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF22" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG22" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH22" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI22" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ22" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK22" s="73" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="16">
         <v>23</v>
       </c>
@@ -20410,44 +21298,44 @@
       <c r="Y23" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="Z23" s="76" t="s">
+      <c r="Z23" s="74" t="s">
         <v>9</v>
       </c>
       <c r="AA23" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="AB23" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC23" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD23" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE23" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AF23" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AG23" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AH23" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AI23" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AJ23" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AK23" s="75" t="s">
+      <c r="AB23" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC23" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD23" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE23" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF23" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG23" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH23" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI23" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ23" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK23" s="73" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="16">
         <v>24</v>
       </c>
@@ -20523,44 +21411,44 @@
       <c r="Y24" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="Z24" s="76" t="s">
+      <c r="Z24" s="74" t="s">
         <v>9</v>
       </c>
       <c r="AA24" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="AB24" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC24" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD24" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE24" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AF24" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AG24" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AH24" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AI24" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AJ24" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AK24" s="75" t="s">
+      <c r="AB24" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC24" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD24" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE24" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF24" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG24" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH24" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI24" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ24" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK24" s="73" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="16">
         <v>25</v>
       </c>
@@ -20636,44 +21524,44 @@
       <c r="Y25" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="Z25" s="76" t="s">
+      <c r="Z25" s="74" t="s">
         <v>9</v>
       </c>
       <c r="AA25" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="AB25" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC25" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD25" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE25" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AF25" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AG25" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AH25" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AI25" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AJ25" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AK25" s="75" t="s">
+      <c r="AB25" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC25" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD25" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE25" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF25" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG25" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH25" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI25" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ25" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK25" s="73" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="16">
         <v>26</v>
       </c>
@@ -20749,44 +21637,44 @@
       <c r="Y26" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="Z26" s="76" t="s">
+      <c r="Z26" s="74" t="s">
         <v>9</v>
       </c>
       <c r="AA26" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="AB26" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC26" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD26" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE26" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AF26" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AG26" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AH26" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AI26" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AJ26" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AK26" s="75" t="s">
+      <c r="AB26" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC26" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD26" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE26" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF26" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG26" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH26" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI26" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ26" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK26" s="73" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="16">
         <v>27</v>
       </c>
@@ -20862,44 +21750,44 @@
       <c r="Y27" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="Z27" s="76" t="s">
+      <c r="Z27" s="74" t="s">
         <v>9</v>
       </c>
       <c r="AA27" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="AB27" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC27" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD27" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE27" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AF27" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AG27" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AH27" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AI27" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AJ27" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AK27" s="75" t="s">
+      <c r="AB27" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC27" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD27" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE27" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF27" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG27" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH27" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI27" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ27" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK27" s="73" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="16">
         <v>28</v>
       </c>
@@ -20975,44 +21863,44 @@
       <c r="Y28" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="Z28" s="76" t="s">
+      <c r="Z28" s="74" t="s">
         <v>9</v>
       </c>
       <c r="AA28" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="AB28" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC28" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD28" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE28" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AF28" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AG28" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AH28" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AI28" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AJ28" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AK28" s="75" t="s">
+      <c r="AB28" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC28" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD28" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE28" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF28" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG28" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH28" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI28" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ28" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK28" s="73" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="16">
         <v>29</v>
       </c>
@@ -21088,44 +21976,44 @@
       <c r="Y29" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="Z29" s="76" t="s">
+      <c r="Z29" s="74" t="s">
         <v>9</v>
       </c>
       <c r="AA29" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="AB29" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC29" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD29" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE29" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AF29" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AG29" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AH29" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AI29" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AJ29" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AK29" s="75" t="s">
+      <c r="AB29" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC29" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD29" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE29" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF29" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG29" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH29" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI29" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ29" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK29" s="73" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="30" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="16">
         <v>30</v>
       </c>
@@ -21201,44 +22089,44 @@
       <c r="Y30" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="Z30" s="76" t="s">
+      <c r="Z30" s="74" t="s">
         <v>9</v>
       </c>
       <c r="AA30" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="AB30" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC30" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD30" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE30" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AF30" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AG30" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AH30" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AI30" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AJ30" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AK30" s="75" t="s">
+      <c r="AB30" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC30" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD30" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE30" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF30" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG30" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH30" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI30" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ30" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK30" s="73" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="16">
         <v>31</v>
       </c>
@@ -21314,44 +22202,44 @@
       <c r="Y31" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="Z31" s="76" t="s">
+      <c r="Z31" s="74" t="s">
         <v>9</v>
       </c>
       <c r="AA31" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="AB31" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC31" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD31" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE31" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AF31" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AG31" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AH31" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AI31" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AJ31" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AK31" s="75" t="s">
+      <c r="AB31" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC31" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD31" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE31" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF31" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG31" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH31" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI31" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ31" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK31" s="73" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="16">
         <v>32</v>
       </c>
@@ -21427,44 +22315,44 @@
       <c r="Y32" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="Z32" s="76" t="s">
+      <c r="Z32" s="74" t="s">
         <v>9</v>
       </c>
       <c r="AA32" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="AB32" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC32" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD32" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE32" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AF32" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AG32" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AH32" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AI32" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AJ32" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AK32" s="75" t="s">
+      <c r="AB32" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC32" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD32" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE32" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF32" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG32" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH32" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI32" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ32" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK32" s="73" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="33" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="16">
         <v>33</v>
       </c>
@@ -21540,44 +22428,44 @@
       <c r="Y33" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="Z33" s="76" t="s">
+      <c r="Z33" s="74" t="s">
         <v>9</v>
       </c>
       <c r="AA33" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="AB33" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC33" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD33" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE33" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AF33" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AG33" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AH33" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AI33" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AJ33" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AK33" s="75" t="s">
+      <c r="AB33" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC33" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD33" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE33" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF33" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG33" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH33" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI33" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ33" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK33" s="73" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="16">
         <v>34</v>
       </c>
@@ -21653,44 +22541,44 @@
       <c r="Y34" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="Z34" s="76" t="s">
+      <c r="Z34" s="74" t="s">
         <v>9</v>
       </c>
       <c r="AA34" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="AB34" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC34" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD34" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE34" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AF34" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AG34" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AH34" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AI34" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AJ34" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AK34" s="75" t="s">
+      <c r="AB34" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC34" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD34" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE34" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF34" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG34" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH34" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI34" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ34" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK34" s="73" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="16">
         <v>35</v>
       </c>
@@ -21766,44 +22654,44 @@
       <c r="Y35" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="Z35" s="76" t="s">
+      <c r="Z35" s="74" t="s">
         <v>9</v>
       </c>
       <c r="AA35" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="AB35" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC35" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD35" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE35" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AF35" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AG35" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AH35" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AI35" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AJ35" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AK35" s="75" t="s">
+      <c r="AB35" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC35" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD35" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE35" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF35" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG35" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH35" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI35" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ35" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK35" s="73" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="16">
         <v>36</v>
       </c>
@@ -21879,44 +22767,44 @@
       <c r="Y36" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="Z36" s="76" t="s">
+      <c r="Z36" s="74" t="s">
         <v>9</v>
       </c>
       <c r="AA36" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="AB36" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC36" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD36" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE36" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AF36" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AG36" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AH36" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AI36" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AJ36" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AK36" s="75" t="s">
+      <c r="AB36" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC36" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD36" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE36" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF36" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG36" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH36" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI36" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ36" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK36" s="73" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="37" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="16">
         <v>37</v>
       </c>
@@ -21992,166 +22880,166 @@
       <c r="Y37" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="Z37" s="76" t="s">
+      <c r="Z37" s="74" t="s">
         <v>9</v>
       </c>
       <c r="AA37" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="AB37" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC37" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD37" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE37" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AF37" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AG37" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AH37" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AI37" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AJ37" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AK37" s="75" t="s">
+      <c r="AB37" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC37" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD37" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE37" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF37" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG37" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH37" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI37" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ37" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK37" s="73" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:37" s="73" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:37" s="71" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="16">
         <v>38</v>
       </c>
-      <c r="B38" s="69" t="s">
+      <c r="B38" s="67" t="s">
+        <v>903</v>
+      </c>
+      <c r="C38" s="76" t="s">
+        <v>938</v>
+      </c>
+      <c r="D38" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E38" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="F38" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="G38" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="H38" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="I38" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J38" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="K38" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="L38" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="M38" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="N38" s="68" t="s">
+        <v>16</v>
+      </c>
+      <c r="O38" s="21" t="s">
+        <v>908</v>
+      </c>
+      <c r="P38" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q38" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="R38" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S38" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="T38" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="U38" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="V38" s="30" t="s">
+        <v>904</v>
+      </c>
+      <c r="W38" s="21" t="s">
+        <v>905</v>
+      </c>
+      <c r="X38" s="30" t="s">
+        <v>906</v>
+      </c>
+      <c r="Y38" s="21" t="s">
         <v>907</v>
       </c>
-      <c r="C38" s="63" t="s">
-        <v>903</v>
-      </c>
-      <c r="D38" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="E38" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F38" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="G38" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="H38" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="I38" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="J38" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="K38" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="L38" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="M38" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="N38" s="70" t="s">
-        <v>16</v>
-      </c>
-      <c r="O38" s="21" t="s">
-        <v>912</v>
-      </c>
-      <c r="P38" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q38" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="R38" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="S38" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="T38" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="U38" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="V38" s="30" t="s">
-        <v>908</v>
-      </c>
-      <c r="W38" s="21" t="s">
-        <v>909</v>
-      </c>
-      <c r="X38" s="30" t="s">
-        <v>910</v>
-      </c>
-      <c r="Y38" s="21" t="s">
-        <v>911</v>
-      </c>
-      <c r="Z38" s="71" t="str">
+      <c r="Z38" s="69" t="str">
         <f t="shared" ref="Z38:Z42" si="0">IF(AA38="null", "null", "método.revit")</f>
         <v>método.revit</v>
       </c>
-      <c r="AA38" s="72" t="s">
-        <v>913</v>
-      </c>
-      <c r="AB38" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC38" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD38" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE38" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AF38" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AG38" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AH38" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AI38" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AJ38" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AK38" s="75" t="s">
+      <c r="AA38" s="70" t="s">
+        <v>909</v>
+      </c>
+      <c r="AB38" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC38" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD38" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE38" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF38" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG38" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH38" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI38" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ38" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK38" s="73" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="39" spans="1:37" s="73" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:37" s="71" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="16">
         <v>39</v>
       </c>
-      <c r="B39" s="69" t="s">
-        <v>914</v>
-      </c>
-      <c r="C39" s="63" t="s">
-        <v>903</v>
+      <c r="B39" s="67" t="s">
+        <v>910</v>
+      </c>
+      <c r="C39" s="76" t="s">
+        <v>938</v>
       </c>
       <c r="D39" s="19" t="s">
         <v>9</v>
@@ -22183,11 +23071,11 @@
       <c r="M39" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="N39" s="70" t="s">
+      <c r="N39" s="68" t="s">
         <v>16</v>
       </c>
       <c r="O39" s="21" t="s">
-        <v>916</v>
+        <v>912</v>
       </c>
       <c r="P39" s="30" t="s">
         <v>9</v>
@@ -22208,64 +23096,64 @@
         <v>9</v>
       </c>
       <c r="V39" s="30" t="s">
-        <v>908</v>
+        <v>904</v>
       </c>
       <c r="W39" s="21" t="s">
-        <v>909</v>
+        <v>905</v>
       </c>
       <c r="X39" s="30" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="Y39" s="21" t="s">
-        <v>915</v>
-      </c>
-      <c r="Z39" s="71" t="str">
+        <v>911</v>
+      </c>
+      <c r="Z39" s="69" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
-      <c r="AA39" s="72" t="s">
-        <v>917</v>
-      </c>
-      <c r="AB39" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC39" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD39" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE39" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AF39" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AG39" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AH39" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AI39" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AJ39" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AK39" s="75" t="s">
+      <c r="AA39" s="70" t="s">
+        <v>913</v>
+      </c>
+      <c r="AB39" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC39" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD39" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE39" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF39" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG39" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH39" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI39" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ39" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK39" s="73" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="40" spans="1:37" s="73" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:37" s="71" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="16">
         <v>40</v>
       </c>
-      <c r="B40" s="69" t="s">
-        <v>918</v>
-      </c>
-      <c r="C40" s="63" t="s">
-        <v>903</v>
+      <c r="B40" s="67" t="s">
+        <v>914</v>
+      </c>
+      <c r="C40" s="76" t="s">
+        <v>938</v>
       </c>
       <c r="D40" s="19" t="s">
         <v>9</v>
@@ -22297,11 +23185,11 @@
       <c r="M40" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="N40" s="70" t="s">
+      <c r="N40" s="68" t="s">
         <v>16</v>
       </c>
       <c r="O40" s="21" t="s">
-        <v>920</v>
+        <v>916</v>
       </c>
       <c r="P40" s="30" t="s">
         <v>9</v>
@@ -22322,64 +23210,64 @@
         <v>9</v>
       </c>
       <c r="V40" s="30" t="s">
-        <v>908</v>
+        <v>904</v>
       </c>
       <c r="W40" s="21" t="s">
-        <v>909</v>
+        <v>905</v>
       </c>
       <c r="X40" s="30" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="Y40" s="21" t="s">
-        <v>919</v>
-      </c>
-      <c r="Z40" s="71" t="str">
+        <v>915</v>
+      </c>
+      <c r="Z40" s="69" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
-      <c r="AA40" s="72" t="s">
-        <v>921</v>
-      </c>
-      <c r="AB40" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC40" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD40" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE40" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AF40" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AG40" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AH40" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AI40" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AJ40" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AK40" s="75" t="s">
+      <c r="AA40" s="70" t="s">
+        <v>917</v>
+      </c>
+      <c r="AB40" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC40" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD40" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE40" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF40" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG40" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH40" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI40" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ40" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK40" s="73" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="41" spans="1:37" s="73" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:37" s="71" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="16">
         <v>41</v>
       </c>
-      <c r="B41" s="69" t="s">
-        <v>922</v>
-      </c>
-      <c r="C41" s="63" t="s">
-        <v>903</v>
+      <c r="B41" s="67" t="s">
+        <v>918</v>
+      </c>
+      <c r="C41" s="76" t="s">
+        <v>938</v>
       </c>
       <c r="D41" s="19" t="s">
         <v>9</v>
@@ -22411,11 +23299,11 @@
       <c r="M41" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="N41" s="70" t="s">
+      <c r="N41" s="68" t="s">
         <v>16</v>
       </c>
       <c r="O41" s="21" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="P41" s="30" t="s">
         <v>9</v>
@@ -22436,64 +23324,64 @@
         <v>9</v>
       </c>
       <c r="V41" s="30" t="s">
-        <v>908</v>
+        <v>904</v>
       </c>
       <c r="W41" s="21" t="s">
-        <v>909</v>
+        <v>905</v>
       </c>
       <c r="X41" s="30" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="Y41" s="21" t="s">
-        <v>923</v>
-      </c>
-      <c r="Z41" s="71" t="str">
+        <v>919</v>
+      </c>
+      <c r="Z41" s="69" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
-      <c r="AA41" s="72" t="s">
-        <v>925</v>
-      </c>
-      <c r="AB41" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC41" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD41" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE41" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AF41" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AG41" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AH41" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AI41" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AJ41" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AK41" s="75" t="s">
+      <c r="AA41" s="70" t="s">
+        <v>921</v>
+      </c>
+      <c r="AB41" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC41" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD41" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE41" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF41" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG41" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH41" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI41" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ41" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK41" s="73" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="1:37" s="73" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:37" s="71" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="16">
         <v>42</v>
       </c>
-      <c r="B42" s="69" t="s">
-        <v>926</v>
-      </c>
-      <c r="C42" s="63" t="s">
-        <v>903</v>
+      <c r="B42" s="67" t="s">
+        <v>922</v>
+      </c>
+      <c r="C42" s="76" t="s">
+        <v>938</v>
       </c>
       <c r="D42" s="19" t="s">
         <v>9</v>
@@ -22525,11 +23413,11 @@
       <c r="M42" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="N42" s="70" t="s">
+      <c r="N42" s="68" t="s">
         <v>16</v>
       </c>
       <c r="O42" s="21" t="s">
-        <v>928</v>
+        <v>924</v>
       </c>
       <c r="P42" s="30" t="s">
         <v>9</v>
@@ -22550,71 +23438,71 @@
         <v>9</v>
       </c>
       <c r="V42" s="30" t="s">
-        <v>908</v>
+        <v>904</v>
       </c>
       <c r="W42" s="21" t="s">
-        <v>909</v>
+        <v>905</v>
       </c>
       <c r="X42" s="30" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="Y42" s="21" t="s">
-        <v>927</v>
-      </c>
-      <c r="Z42" s="71" t="str">
+        <v>923</v>
+      </c>
+      <c r="Z42" s="69" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
-      <c r="AA42" s="72" t="s">
-        <v>929</v>
-      </c>
-      <c r="AB42" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC42" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD42" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE42" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AF42" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AG42" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AH42" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AI42" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AJ42" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AK42" s="75" t="s">
+      <c r="AA42" s="70" t="s">
+        <v>925</v>
+      </c>
+      <c r="AB42" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC42" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD42" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE42" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF42" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG42" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH42" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI42" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ42" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK42" s="73" t="s">
         <v>9</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="9" type="noConversion"/>
   <conditionalFormatting sqref="B18:B37 B1:B13">
-    <cfRule type="duplicateValues" dxfId="4" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B38:B42">
-    <cfRule type="duplicateValues" dxfId="3" priority="15"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="V38:AA42">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z2:AK42">
-    <cfRule type="cellIs" dxfId="0" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="8" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/PRO/Ontologia_Documentos.xlsx
+++ b/Versão5/PRO/Ontologia_Documentos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\PRO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A66F9C5-B6CA-4197-A17F-EA6F1CA3D202}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD775810-EB78-43FB-85D0-76F7A75D0F0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="527" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4613" uniqueCount="948">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5191" uniqueCount="1005">
   <si>
     <t>Edição</t>
   </si>
@@ -2916,6 +2916,177 @@
   </si>
   <si>
     <t>KML</t>
+  </si>
+  <si>
+    <t>Projetos</t>
+  </si>
+  <si>
+    <t>Projeto.Contratado</t>
+  </si>
+  <si>
+    <t>Projeto.Finalizado</t>
+  </si>
+  <si>
+    <t>Projeto.Andamento</t>
+  </si>
+  <si>
+    <t>Projeto.Cancelado</t>
+  </si>
+  <si>
+    <t>Projeto.Litigiado</t>
+  </si>
+  <si>
+    <t>Clientes</t>
+  </si>
+  <si>
+    <t>Cliente.Corporativo</t>
+  </si>
+  <si>
+    <t>Cliente.Individual</t>
+  </si>
+  <si>
+    <t>Cliente.Estatal</t>
+  </si>
+  <si>
+    <t>Projeto.Preliminar</t>
+  </si>
+  <si>
+    <t>Projeto.Básico</t>
+  </si>
+  <si>
+    <t>Projeto.Executivo</t>
+  </si>
+  <si>
+    <t>Projeto.Aprovação</t>
+  </si>
+  <si>
+    <t>Projeto.Viabilidade</t>
+  </si>
+  <si>
+    <t>Processuais</t>
+  </si>
+  <si>
+    <t>Equipes</t>
+  </si>
+  <si>
+    <t>Equipe.Própria</t>
+  </si>
+  <si>
+    <t>Equipe.Associada</t>
+  </si>
+  <si>
+    <t>Equipe.Consultora</t>
+  </si>
+  <si>
+    <t>Equipe.Colaboradora</t>
+  </si>
+  <si>
+    <t>Equipe.Terceirizada</t>
+  </si>
+  <si>
+    <t>Equipe Própria</t>
+  </si>
+  <si>
+    <t>Equipe Associada</t>
+  </si>
+  <si>
+    <t>Equipe Consultora</t>
+  </si>
+  <si>
+    <t>Equipe Colaboradora</t>
+  </si>
+  <si>
+    <t>Equipe Terceirizada</t>
+  </si>
+  <si>
+    <t>Cliente individual</t>
+  </si>
+  <si>
+    <t>Cliente corporativo</t>
+  </si>
+  <si>
+    <t>Cliente estatal</t>
+  </si>
+  <si>
+    <t>Projeto está em litígio</t>
+  </si>
+  <si>
+    <t>Projeto foi cancelado</t>
+  </si>
+  <si>
+    <t>Projeto está em andamento</t>
+  </si>
+  <si>
+    <t>Projeto foi finalizado</t>
+  </si>
+  <si>
+    <t>Projeto foi contratado</t>
+  </si>
+  <si>
+    <t>Projeto está em negociação</t>
+  </si>
+  <si>
+    <t>Projeto.Negociado</t>
+  </si>
+  <si>
+    <t>Projeto.Concursado</t>
+  </si>
+  <si>
+    <t>Projeto participante de um concurso</t>
+  </si>
+  <si>
+    <t>Projeto para aprovação por órgão competente (Prefeituras, Corpo de Bombeiros, Licenciamento ambiental, etc.)</t>
+  </si>
+  <si>
+    <t>Projeto em etapa de execução</t>
+  </si>
+  <si>
+    <t>Projeto definido como básico ou anteprojeto</t>
+  </si>
+  <si>
+    <t>Projeto definido como um estudo preliminar</t>
+  </si>
+  <si>
+    <t>Projeto definido como um estudo de viabilidade</t>
+  </si>
+  <si>
+    <t>Tipo.de.Projeto</t>
+  </si>
+  <si>
+    <t>Tipo.de.Cliente</t>
+  </si>
+  <si>
+    <t>Processo.do.Projeto</t>
+  </si>
+  <si>
+    <t>ClienteA</t>
+  </si>
+  <si>
+    <t>é.cliente</t>
+  </si>
+  <si>
+    <t>"Representa o cliente do Projeto 01"</t>
+  </si>
+  <si>
+    <t>nome</t>
+  </si>
+  <si>
+    <t>"Nome do projeto"</t>
+  </si>
+  <si>
+    <t>"Nome do cliente do projeto"</t>
+  </si>
+  <si>
+    <t>Estudo_01</t>
+  </si>
+  <si>
+    <t>Tp.Projeto</t>
+  </si>
+  <si>
+    <t>"Representa a etapa do Projeto 01"</t>
+  </si>
+  <si>
+    <t>"Representa o tipo de Projeto"</t>
   </si>
 </sst>
 </file>
@@ -3258,7 +3429,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -3476,17 +3647,74 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="16">
+  <dxfs count="21">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -3532,14 +3760,6 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
     </dxf>
     <dxf>
       <font>
@@ -4157,7 +4377,7 @@
       </c>
       <c r="B18" s="5">
         <f ca="1">NOW()</f>
-        <v>46268.699871874996</v>
+        <v>46269.583813888887</v>
       </c>
       <c r="C18" s="41" t="s">
         <v>304</v>
@@ -4237,7 +4457,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19BE914A-3965-4A61-9195-D2681A91581F}">
-  <dimension ref="A1:AD142"/>
+  <dimension ref="A1:AD162"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.140625" style="61" bestFit="1" customWidth="1"/>
@@ -17696,19 +17916,19 @@
         <v>9</v>
       </c>
       <c r="L135" s="53" t="str">
-        <f t="shared" ref="L135:L137" si="56">CONCATENATE("", C135)</f>
+        <f t="shared" ref="L135:L139" si="56">CONCATENATE("", C135)</f>
         <v>Documentais</v>
       </c>
       <c r="M135" s="53" t="str">
-        <f t="shared" ref="M135:M137" si="57">CONCATENATE("", D135)</f>
+        <f t="shared" ref="M135:M139" si="57">CONCATENATE("", D135)</f>
         <v>Elemento.de.Publicação</v>
       </c>
       <c r="N135" s="53" t="str">
-        <f t="shared" ref="N135:N137" si="58">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E135),"."," ")," De "," de "))</f>
+        <f t="shared" ref="N135:N139" si="58">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E135),"."," ")," De "," de "))</f>
         <v>Empresarial</v>
       </c>
       <c r="O135" s="53" t="str">
-        <f t="shared" ref="O135:O137" si="59">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",F135),"."," ")," De "," de "))</f>
+        <f t="shared" ref="O135:O139" si="59">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",F135),"."," ")," De "," de "))</f>
         <v>Apresentação</v>
       </c>
       <c r="P135" s="53" t="s">
@@ -17961,85 +18181,87 @@
         <v>9</v>
       </c>
     </row>
-    <row r="138" spans="1:30" s="66" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:30" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="45">
         <v>138</v>
       </c>
-      <c r="B138" s="75" t="s">
+      <c r="B138" s="76" t="s">
         <v>899</v>
       </c>
-      <c r="C138" s="76" t="s">
-        <v>900</v>
-      </c>
-      <c r="D138" s="76" t="s">
-        <v>902</v>
-      </c>
-      <c r="E138" s="76" t="s">
-        <v>901</v>
-      </c>
-      <c r="F138" s="76" t="s">
-        <v>926</v>
-      </c>
-      <c r="G138" s="62" t="s">
-        <v>9</v>
-      </c>
-      <c r="H138" s="62" t="s">
-        <v>9</v>
-      </c>
-      <c r="I138" s="62" t="s">
-        <v>9</v>
-      </c>
-      <c r="J138" s="62" t="s">
-        <v>9</v>
-      </c>
-      <c r="K138" s="62" t="s">
-        <v>9</v>
-      </c>
-      <c r="L138" s="63" t="str">
-        <f t="shared" ref="L138:O142" si="60">SUBSTITUTE(CONCATENATE("", C138), ".", " ")</f>
-        <v>De API</v>
-      </c>
-      <c r="M138" s="63" t="str">
-        <f t="shared" si="60"/>
-        <v>Macros</v>
-      </c>
-      <c r="N138" s="63" t="str">
-        <f t="shared" si="60"/>
-        <v>Métodos</v>
-      </c>
-      <c r="O138" s="63" t="str">
-        <f t="shared" si="60"/>
-        <v>Função Auxiliar</v>
-      </c>
-      <c r="P138" s="64" t="s">
-        <v>927</v>
-      </c>
-      <c r="Q138" s="64" t="s">
-        <v>928</v>
-      </c>
-      <c r="R138" s="64" t="s">
-        <v>929</v>
-      </c>
-      <c r="S138" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="T138" s="64" t="str">
-        <f t="shared" ref="T138:V142" si="61">SUBSTITUTE(C138, ".", " ")</f>
-        <v>De API</v>
-      </c>
-      <c r="U138" s="64" t="str">
-        <f t="shared" si="61"/>
-        <v>Macros</v>
-      </c>
-      <c r="V138" s="43" t="str">
-        <f t="shared" si="61"/>
-        <v>Métodos</v>
+      <c r="C138" s="55" t="s">
+        <v>963</v>
+      </c>
+      <c r="D138" s="57" t="s">
+        <v>954</v>
+      </c>
+      <c r="E138" s="57" t="s">
+        <v>993</v>
+      </c>
+      <c r="F138" s="56" t="s">
+        <v>956</v>
+      </c>
+      <c r="G138" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="H138" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="I138" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="J138" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="K138" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="L138" s="53" t="str">
+        <f t="shared" si="56"/>
+        <v>Processuais</v>
+      </c>
+      <c r="M138" s="53" t="str">
+        <f t="shared" si="57"/>
+        <v>Clientes</v>
+      </c>
+      <c r="N138" s="53" t="str">
+        <f t="shared" si="58"/>
+        <v>Tipo de Cliente</v>
+      </c>
+      <c r="O138" s="53" t="str">
+        <f t="shared" si="59"/>
+        <v>Cliente Individual</v>
+      </c>
+      <c r="P138" s="53" t="s">
+        <v>975</v>
+      </c>
+      <c r="Q138" s="43" t="str">
+        <f>_xlfn.TRANSLATE(P138,"pt","es")</f>
+        <v>Cliente individual</v>
+      </c>
+      <c r="R138" s="43" t="str">
+        <f>_xlfn.TRANSLATE(P138,"pt","en")</f>
+        <v>Individual customer</v>
+      </c>
+      <c r="S138" s="43" t="s">
+        <v>9</v>
+      </c>
+      <c r="T138" s="43" t="str">
+        <f t="shared" ref="T138:T141" si="60">SUBSTITUTE(C138, "_", " ")</f>
+        <v>Processuais</v>
+      </c>
+      <c r="U138" s="43" t="str">
+        <f t="shared" ref="U138:U141" si="61">SUBSTITUTE(D138, "_", " ")</f>
+        <v>Clientes</v>
+      </c>
+      <c r="V138" s="53" t="str">
+        <f t="shared" ref="V138:V141" si="62">SUBSTITUTE(E138, "_", " ")</f>
+        <v>Tipo.de.Cliente</v>
       </c>
       <c r="W138" s="43" t="s">
         <v>80</v>
       </c>
       <c r="X138" s="54" t="str">
-        <f t="shared" ref="X138:X142" si="62">CONCATENATE("Key-DOCU-",A138)</f>
+        <f t="shared" ref="X138:X141" si="63">CONCATENATE("Key-DOCU-",A138)</f>
         <v>Key-DOCU-138</v>
       </c>
       <c r="Y138" s="65" t="s">
@@ -18061,85 +18283,87 @@
         <v>9</v>
       </c>
     </row>
-    <row r="139" spans="1:30" s="66" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:30" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="45">
         <v>139</v>
       </c>
-      <c r="B139" s="75" t="s">
+      <c r="B139" s="76" t="s">
         <v>899</v>
       </c>
-      <c r="C139" s="76" t="s">
-        <v>900</v>
-      </c>
-      <c r="D139" s="76" t="s">
-        <v>902</v>
-      </c>
-      <c r="E139" s="76" t="s">
-        <v>901</v>
-      </c>
-      <c r="F139" s="76" t="s">
-        <v>930</v>
-      </c>
-      <c r="G139" s="62" t="s">
-        <v>9</v>
-      </c>
-      <c r="H139" s="62" t="s">
-        <v>9</v>
-      </c>
-      <c r="I139" s="62" t="s">
-        <v>9</v>
-      </c>
-      <c r="J139" s="62" t="s">
-        <v>9</v>
-      </c>
-      <c r="K139" s="62" t="s">
-        <v>9</v>
-      </c>
-      <c r="L139" s="63" t="str">
+      <c r="C139" s="55" t="s">
+        <v>963</v>
+      </c>
+      <c r="D139" s="57" t="s">
+        <v>954</v>
+      </c>
+      <c r="E139" s="57" t="s">
+        <v>993</v>
+      </c>
+      <c r="F139" s="56" t="s">
+        <v>955</v>
+      </c>
+      <c r="G139" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="H139" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="I139" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="J139" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="K139" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="L139" s="53" t="str">
+        <f t="shared" si="56"/>
+        <v>Processuais</v>
+      </c>
+      <c r="M139" s="53" t="str">
+        <f t="shared" si="57"/>
+        <v>Clientes</v>
+      </c>
+      <c r="N139" s="53" t="str">
+        <f t="shared" si="58"/>
+        <v>Tipo de Cliente</v>
+      </c>
+      <c r="O139" s="53" t="str">
+        <f t="shared" si="59"/>
+        <v>Cliente Corporativo</v>
+      </c>
+      <c r="P139" s="53" t="s">
+        <v>976</v>
+      </c>
+      <c r="Q139" s="43" t="str">
+        <f t="shared" ref="Q139:Q157" si="64">_xlfn.TRANSLATE(P139,"pt","es")</f>
+        <v>Cliente corporativo</v>
+      </c>
+      <c r="R139" s="43" t="str">
+        <f t="shared" ref="R139:R157" si="65">_xlfn.TRANSLATE(P139,"pt","en")</f>
+        <v>Corporate customer</v>
+      </c>
+      <c r="S139" s="43" t="s">
+        <v>9</v>
+      </c>
+      <c r="T139" s="43" t="str">
         <f t="shared" si="60"/>
-        <v>De API</v>
-      </c>
-      <c r="M139" s="63" t="str">
-        <f t="shared" si="60"/>
-        <v>Macros</v>
-      </c>
-      <c r="N139" s="63" t="str">
-        <f t="shared" si="60"/>
-        <v>Métodos</v>
-      </c>
-      <c r="O139" s="63" t="str">
-        <f t="shared" si="60"/>
-        <v>Função Global</v>
-      </c>
-      <c r="P139" s="64" t="s">
-        <v>931</v>
-      </c>
-      <c r="Q139" s="64" t="s">
-        <v>932</v>
-      </c>
-      <c r="R139" s="64" t="s">
-        <v>933</v>
-      </c>
-      <c r="S139" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="T139" s="64" t="str">
+        <v>Processuais</v>
+      </c>
+      <c r="U139" s="43" t="str">
         <f t="shared" si="61"/>
-        <v>De API</v>
-      </c>
-      <c r="U139" s="64" t="str">
-        <f t="shared" si="61"/>
-        <v>Macros</v>
-      </c>
-      <c r="V139" s="43" t="str">
-        <f t="shared" si="61"/>
-        <v>Métodos</v>
+        <v>Clientes</v>
+      </c>
+      <c r="V139" s="53" t="str">
+        <f t="shared" si="62"/>
+        <v>Tipo.de.Cliente</v>
       </c>
       <c r="W139" s="43" t="s">
         <v>80</v>
       </c>
       <c r="X139" s="54" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>Key-DOCU-139</v>
       </c>
       <c r="Y139" s="65" t="s">
@@ -18161,85 +18385,87 @@
         <v>9</v>
       </c>
     </row>
-    <row r="140" spans="1:30" s="66" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:30" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="45">
         <v>140</v>
       </c>
-      <c r="B140" s="75" t="s">
+      <c r="B140" s="76" t="s">
         <v>899</v>
       </c>
-      <c r="C140" s="76" t="s">
-        <v>900</v>
-      </c>
-      <c r="D140" s="76" t="s">
-        <v>902</v>
-      </c>
-      <c r="E140" s="76" t="s">
-        <v>901</v>
-      </c>
-      <c r="F140" s="76" t="s">
-        <v>934</v>
-      </c>
-      <c r="G140" s="62" t="s">
-        <v>9</v>
-      </c>
-      <c r="H140" s="62" t="s">
-        <v>9</v>
-      </c>
-      <c r="I140" s="62" t="s">
-        <v>9</v>
-      </c>
-      <c r="J140" s="62" t="s">
-        <v>9</v>
-      </c>
-      <c r="K140" s="62" t="s">
-        <v>9</v>
-      </c>
-      <c r="L140" s="63" t="str">
+      <c r="C140" s="55" t="s">
+        <v>963</v>
+      </c>
+      <c r="D140" s="57" t="s">
+        <v>954</v>
+      </c>
+      <c r="E140" s="57" t="s">
+        <v>993</v>
+      </c>
+      <c r="F140" s="56" t="s">
+        <v>957</v>
+      </c>
+      <c r="G140" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="H140" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="I140" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="J140" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="K140" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="L140" s="53" t="str">
+        <f t="shared" ref="L140:L143" si="66">CONCATENATE("", C140)</f>
+        <v>Processuais</v>
+      </c>
+      <c r="M140" s="53" t="str">
+        <f t="shared" ref="M140:M143" si="67">CONCATENATE("", D140)</f>
+        <v>Clientes</v>
+      </c>
+      <c r="N140" s="53" t="str">
+        <f t="shared" ref="N140:N143" si="68">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E140),"."," ")," De "," de "))</f>
+        <v>Tipo de Cliente</v>
+      </c>
+      <c r="O140" s="53" t="str">
+        <f t="shared" ref="O140:O143" si="69">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",F140),"."," ")," De "," de "))</f>
+        <v>Cliente Estatal</v>
+      </c>
+      <c r="P140" s="53" t="s">
+        <v>977</v>
+      </c>
+      <c r="Q140" s="43" t="str">
+        <f t="shared" si="64"/>
+        <v>Cliente estatal</v>
+      </c>
+      <c r="R140" s="43" t="str">
+        <f t="shared" si="65"/>
+        <v>State customer</v>
+      </c>
+      <c r="S140" s="43" t="s">
+        <v>9</v>
+      </c>
+      <c r="T140" s="43" t="str">
         <f t="shared" si="60"/>
-        <v>De API</v>
-      </c>
-      <c r="M140" s="63" t="str">
-        <f t="shared" si="60"/>
-        <v>Macros</v>
-      </c>
-      <c r="N140" s="63" t="str">
-        <f t="shared" si="60"/>
-        <v>Métodos</v>
-      </c>
-      <c r="O140" s="63" t="str">
-        <f t="shared" si="60"/>
-        <v>Função Local</v>
-      </c>
-      <c r="P140" s="64" t="s">
-        <v>935</v>
-      </c>
-      <c r="Q140" s="64" t="s">
-        <v>936</v>
-      </c>
-      <c r="R140" s="64" t="s">
-        <v>937</v>
-      </c>
-      <c r="S140" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="T140" s="64" t="str">
+        <v>Processuais</v>
+      </c>
+      <c r="U140" s="43" t="str">
         <f t="shared" si="61"/>
-        <v>De API</v>
-      </c>
-      <c r="U140" s="64" t="str">
-        <f t="shared" si="61"/>
-        <v>Macros</v>
-      </c>
-      <c r="V140" s="43" t="str">
-        <f t="shared" si="61"/>
-        <v>Métodos</v>
+        <v>Clientes</v>
+      </c>
+      <c r="V140" s="53" t="str">
+        <f t="shared" si="62"/>
+        <v>Tipo.de.Cliente</v>
       </c>
       <c r="W140" s="43" t="s">
         <v>80</v>
       </c>
       <c r="X140" s="54" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>Key-DOCU-140</v>
       </c>
       <c r="Y140" s="65" t="s">
@@ -18261,85 +18487,87 @@
         <v>9</v>
       </c>
     </row>
-    <row r="141" spans="1:30" s="66" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:30" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="45">
         <v>141</v>
       </c>
-      <c r="B141" s="75" t="s">
+      <c r="B141" s="76" t="s">
         <v>899</v>
       </c>
-      <c r="C141" s="76" t="s">
-        <v>900</v>
-      </c>
-      <c r="D141" s="76" t="s">
-        <v>902</v>
-      </c>
-      <c r="E141" s="76" t="s">
-        <v>901</v>
-      </c>
-      <c r="F141" s="76" t="s">
-        <v>938</v>
-      </c>
-      <c r="G141" s="62" t="s">
-        <v>9</v>
-      </c>
-      <c r="H141" s="62" t="s">
-        <v>9</v>
-      </c>
-      <c r="I141" s="62" t="s">
-        <v>9</v>
-      </c>
-      <c r="J141" s="62" t="s">
-        <v>9</v>
-      </c>
-      <c r="K141" s="62" t="s">
-        <v>9</v>
-      </c>
-      <c r="L141" s="63" t="str">
+      <c r="C141" s="55" t="s">
+        <v>963</v>
+      </c>
+      <c r="D141" s="55" t="s">
+        <v>948</v>
+      </c>
+      <c r="E141" s="57" t="s">
+        <v>994</v>
+      </c>
+      <c r="F141" s="56" t="s">
+        <v>984</v>
+      </c>
+      <c r="G141" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="H141" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="I141" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="J141" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="K141" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="L141" s="53" t="str">
+        <f t="shared" ref="L141" si="70">CONCATENATE("", C141)</f>
+        <v>Processuais</v>
+      </c>
+      <c r="M141" s="53" t="str">
+        <f t="shared" ref="M141" si="71">CONCATENATE("", D141)</f>
+        <v>Projetos</v>
+      </c>
+      <c r="N141" s="53" t="str">
+        <f t="shared" ref="N141" si="72">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E141),"."," ")," De "," de "))</f>
+        <v>Processo do Projeto</v>
+      </c>
+      <c r="O141" s="53" t="str">
+        <f t="shared" ref="O141" si="73">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",F141),"."," ")," De "," de "))</f>
+        <v>Projeto Negociado</v>
+      </c>
+      <c r="P141" s="53" t="s">
+        <v>983</v>
+      </c>
+      <c r="Q141" s="43" t="str">
+        <f t="shared" si="64"/>
+        <v>El proyecto está en negociación</v>
+      </c>
+      <c r="R141" s="43" t="str">
+        <f t="shared" ref="R141" si="74">_xlfn.TRANSLATE(P141,"pt","en")</f>
+        <v>Project is under negotiation</v>
+      </c>
+      <c r="S141" s="43" t="s">
+        <v>9</v>
+      </c>
+      <c r="T141" s="43" t="str">
         <f t="shared" si="60"/>
-        <v>De API</v>
-      </c>
-      <c r="M141" s="63" t="str">
-        <f t="shared" si="60"/>
-        <v>Macros</v>
-      </c>
-      <c r="N141" s="63" t="str">
-        <f t="shared" si="60"/>
-        <v>Métodos</v>
-      </c>
-      <c r="O141" s="63" t="str">
-        <f t="shared" si="60"/>
-        <v>Função Filtro</v>
-      </c>
-      <c r="P141" s="64" t="s">
-        <v>939</v>
-      </c>
-      <c r="Q141" s="64" t="s">
-        <v>940</v>
-      </c>
-      <c r="R141" s="64" t="s">
-        <v>941</v>
-      </c>
-      <c r="S141" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="T141" s="64" t="str">
+        <v>Processuais</v>
+      </c>
+      <c r="U141" s="43" t="str">
         <f t="shared" si="61"/>
-        <v>De API</v>
-      </c>
-      <c r="U141" s="64" t="str">
-        <f t="shared" si="61"/>
-        <v>Macros</v>
-      </c>
-      <c r="V141" s="43" t="str">
-        <f t="shared" si="61"/>
-        <v>Métodos</v>
+        <v>Projetos</v>
+      </c>
+      <c r="V141" s="53" t="str">
+        <f t="shared" si="62"/>
+        <v>Processo.do.Projeto</v>
       </c>
       <c r="W141" s="43" t="s">
         <v>80</v>
       </c>
       <c r="X141" s="54" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>Key-DOCU-141</v>
       </c>
       <c r="Y141" s="65" t="s">
@@ -18361,85 +18589,87 @@
         <v>9</v>
       </c>
     </row>
-    <row r="142" spans="1:30" s="66" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:30" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="45">
         <v>142</v>
       </c>
-      <c r="B142" s="75" t="s">
+      <c r="B142" s="76" t="s">
         <v>899</v>
       </c>
-      <c r="C142" s="76" t="s">
-        <v>900</v>
-      </c>
-      <c r="D142" s="76" t="s">
-        <v>902</v>
-      </c>
-      <c r="E142" s="76" t="s">
-        <v>942</v>
-      </c>
-      <c r="F142" s="76" t="s">
-        <v>943</v>
-      </c>
-      <c r="G142" s="62" t="s">
-        <v>9</v>
-      </c>
-      <c r="H142" s="62" t="s">
-        <v>9</v>
-      </c>
-      <c r="I142" s="62" t="s">
-        <v>9</v>
-      </c>
-      <c r="J142" s="62" t="s">
-        <v>9</v>
-      </c>
-      <c r="K142" s="62" t="s">
-        <v>9</v>
-      </c>
-      <c r="L142" s="63" t="str">
-        <f t="shared" si="60"/>
-        <v>De API</v>
-      </c>
-      <c r="M142" s="63" t="str">
-        <f t="shared" si="60"/>
-        <v>Macros</v>
-      </c>
-      <c r="N142" s="63" t="str">
-        <f t="shared" si="60"/>
-        <v>Códigos Visuais</v>
-      </c>
-      <c r="O142" s="63" t="str">
-        <f t="shared" si="60"/>
-        <v>Bloco de Código</v>
-      </c>
-      <c r="P142" s="64" t="s">
-        <v>944</v>
-      </c>
-      <c r="Q142" s="64" t="s">
-        <v>945</v>
-      </c>
-      <c r="R142" s="64" t="s">
-        <v>946</v>
-      </c>
-      <c r="S142" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="T142" s="64" t="str">
-        <f t="shared" si="61"/>
-        <v>De API</v>
-      </c>
-      <c r="U142" s="64" t="str">
-        <f t="shared" si="61"/>
-        <v>Macros</v>
-      </c>
-      <c r="V142" s="43" t="str">
-        <f t="shared" si="61"/>
-        <v>Códigos Visuais</v>
+      <c r="C142" s="55" t="s">
+        <v>963</v>
+      </c>
+      <c r="D142" s="55" t="s">
+        <v>948</v>
+      </c>
+      <c r="E142" s="57" t="s">
+        <v>994</v>
+      </c>
+      <c r="F142" s="56" t="s">
+        <v>949</v>
+      </c>
+      <c r="G142" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="H142" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="I142" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="J142" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="K142" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="L142" s="53" t="str">
+        <f t="shared" si="66"/>
+        <v>Processuais</v>
+      </c>
+      <c r="M142" s="53" t="str">
+        <f t="shared" si="67"/>
+        <v>Projetos</v>
+      </c>
+      <c r="N142" s="53" t="str">
+        <f t="shared" si="68"/>
+        <v>Processo do Projeto</v>
+      </c>
+      <c r="O142" s="53" t="str">
+        <f t="shared" si="69"/>
+        <v>Projeto Contratado</v>
+      </c>
+      <c r="P142" s="53" t="s">
+        <v>982</v>
+      </c>
+      <c r="Q142" s="43" t="str">
+        <f t="shared" si="64"/>
+        <v>El proyecto fue contratado</v>
+      </c>
+      <c r="R142" s="43" t="str">
+        <f t="shared" si="65"/>
+        <v>Project was contracted</v>
+      </c>
+      <c r="S142" s="43" t="s">
+        <v>9</v>
+      </c>
+      <c r="T142" s="43" t="str">
+        <f t="shared" ref="T142:T148" si="75">SUBSTITUTE(C142, "_", " ")</f>
+        <v>Processuais</v>
+      </c>
+      <c r="U142" s="43" t="str">
+        <f t="shared" ref="U142:U148" si="76">SUBSTITUTE(D142, "_", " ")</f>
+        <v>Projetos</v>
+      </c>
+      <c r="V142" s="53" t="str">
+        <f t="shared" ref="V142:V148" si="77">SUBSTITUTE(E142, "_", " ")</f>
+        <v>Processo.do.Projeto</v>
       </c>
       <c r="W142" s="43" t="s">
         <v>80</v>
       </c>
       <c r="X142" s="54" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" ref="X142:X148" si="78">CONCATENATE("Key-DOCU-",A142)</f>
         <v>Key-DOCU-142</v>
       </c>
       <c r="Y142" s="65" t="s">
@@ -18458,47 +18688,2072 @@
         <v>9</v>
       </c>
       <c r="AD142" s="65" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="143" spans="1:30" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A143" s="45">
+        <v>143</v>
+      </c>
+      <c r="B143" s="76" t="s">
+        <v>899</v>
+      </c>
+      <c r="C143" s="55" t="s">
+        <v>963</v>
+      </c>
+      <c r="D143" s="55" t="s">
+        <v>948</v>
+      </c>
+      <c r="E143" s="57" t="s">
+        <v>994</v>
+      </c>
+      <c r="F143" s="56" t="s">
+        <v>950</v>
+      </c>
+      <c r="G143" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="H143" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="I143" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="J143" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="K143" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="L143" s="53" t="str">
+        <f t="shared" si="66"/>
+        <v>Processuais</v>
+      </c>
+      <c r="M143" s="53" t="str">
+        <f t="shared" si="67"/>
+        <v>Projetos</v>
+      </c>
+      <c r="N143" s="53" t="str">
+        <f t="shared" si="68"/>
+        <v>Processo do Projeto</v>
+      </c>
+      <c r="O143" s="53" t="str">
+        <f t="shared" si="69"/>
+        <v>Projeto Finalizado</v>
+      </c>
+      <c r="P143" s="53" t="s">
+        <v>981</v>
+      </c>
+      <c r="Q143" s="43" t="str">
+        <f t="shared" si="64"/>
+        <v>El proyecto ha sido finalizado</v>
+      </c>
+      <c r="R143" s="43" t="str">
+        <f t="shared" si="65"/>
+        <v>Project has been completed</v>
+      </c>
+      <c r="S143" s="43" t="s">
+        <v>9</v>
+      </c>
+      <c r="T143" s="43" t="str">
+        <f t="shared" si="75"/>
+        <v>Processuais</v>
+      </c>
+      <c r="U143" s="43" t="str">
+        <f t="shared" si="76"/>
+        <v>Projetos</v>
+      </c>
+      <c r="V143" s="53" t="str">
+        <f t="shared" si="77"/>
+        <v>Processo.do.Projeto</v>
+      </c>
+      <c r="W143" s="43" t="s">
+        <v>80</v>
+      </c>
+      <c r="X143" s="54" t="str">
+        <f t="shared" si="78"/>
+        <v>Key-DOCU-143</v>
+      </c>
+      <c r="Y143" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z143" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA143" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB143" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC143" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD143" s="65" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="144" spans="1:30" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A144" s="45">
+        <v>144</v>
+      </c>
+      <c r="B144" s="76" t="s">
+        <v>899</v>
+      </c>
+      <c r="C144" s="55" t="s">
+        <v>963</v>
+      </c>
+      <c r="D144" s="55" t="s">
+        <v>948</v>
+      </c>
+      <c r="E144" s="57" t="s">
+        <v>994</v>
+      </c>
+      <c r="F144" s="56" t="s">
+        <v>951</v>
+      </c>
+      <c r="G144" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="H144" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="I144" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="J144" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="K144" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="L144" s="53" t="str">
+        <f t="shared" ref="L144:L149" si="79">CONCATENATE("", C144)</f>
+        <v>Processuais</v>
+      </c>
+      <c r="M144" s="53" t="str">
+        <f t="shared" ref="M144:M149" si="80">CONCATENATE("", D144)</f>
+        <v>Projetos</v>
+      </c>
+      <c r="N144" s="53" t="str">
+        <f t="shared" ref="N144:N149" si="81">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E144),"."," ")," De "," de "))</f>
+        <v>Processo do Projeto</v>
+      </c>
+      <c r="O144" s="53" t="str">
+        <f t="shared" ref="O144:O149" si="82">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",F144),"."," ")," De "," de "))</f>
+        <v>Projeto Andamento</v>
+      </c>
+      <c r="P144" s="53" t="s">
+        <v>980</v>
+      </c>
+      <c r="Q144" s="43" t="str">
+        <f t="shared" si="64"/>
+        <v>El proyecto está en marcha</v>
+      </c>
+      <c r="R144" s="43" t="str">
+        <f t="shared" si="65"/>
+        <v>Project is in progress</v>
+      </c>
+      <c r="S144" s="43" t="s">
+        <v>9</v>
+      </c>
+      <c r="T144" s="43" t="str">
+        <f t="shared" si="75"/>
+        <v>Processuais</v>
+      </c>
+      <c r="U144" s="43" t="str">
+        <f t="shared" si="76"/>
+        <v>Projetos</v>
+      </c>
+      <c r="V144" s="53" t="str">
+        <f t="shared" si="77"/>
+        <v>Processo.do.Projeto</v>
+      </c>
+      <c r="W144" s="43" t="s">
+        <v>80</v>
+      </c>
+      <c r="X144" s="54" t="str">
+        <f t="shared" si="78"/>
+        <v>Key-DOCU-144</v>
+      </c>
+      <c r="Y144" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z144" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA144" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB144" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC144" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD144" s="65" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="145" spans="1:30" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A145" s="45">
+        <v>145</v>
+      </c>
+      <c r="B145" s="76" t="s">
+        <v>899</v>
+      </c>
+      <c r="C145" s="55" t="s">
+        <v>963</v>
+      </c>
+      <c r="D145" s="55" t="s">
+        <v>948</v>
+      </c>
+      <c r="E145" s="57" t="s">
+        <v>994</v>
+      </c>
+      <c r="F145" s="56" t="s">
+        <v>952</v>
+      </c>
+      <c r="G145" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="H145" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="I145" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="J145" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="K145" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="L145" s="53" t="str">
+        <f t="shared" si="79"/>
+        <v>Processuais</v>
+      </c>
+      <c r="M145" s="53" t="str">
+        <f t="shared" si="80"/>
+        <v>Projetos</v>
+      </c>
+      <c r="N145" s="53" t="str">
+        <f t="shared" si="81"/>
+        <v>Processo do Projeto</v>
+      </c>
+      <c r="O145" s="53" t="str">
+        <f t="shared" si="82"/>
+        <v>Projeto Cancelado</v>
+      </c>
+      <c r="P145" s="53" t="s">
+        <v>979</v>
+      </c>
+      <c r="Q145" s="43" t="str">
+        <f t="shared" si="64"/>
+        <v>El proyecto fue cancelado</v>
+      </c>
+      <c r="R145" s="43" t="str">
+        <f t="shared" si="65"/>
+        <v>Project was canceled</v>
+      </c>
+      <c r="S145" s="43" t="s">
+        <v>9</v>
+      </c>
+      <c r="T145" s="43" t="str">
+        <f t="shared" si="75"/>
+        <v>Processuais</v>
+      </c>
+      <c r="U145" s="43" t="str">
+        <f t="shared" si="76"/>
+        <v>Projetos</v>
+      </c>
+      <c r="V145" s="53" t="str">
+        <f t="shared" si="77"/>
+        <v>Processo.do.Projeto</v>
+      </c>
+      <c r="W145" s="43" t="s">
+        <v>80</v>
+      </c>
+      <c r="X145" s="54" t="str">
+        <f t="shared" si="78"/>
+        <v>Key-DOCU-145</v>
+      </c>
+      <c r="Y145" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z145" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA145" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB145" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC145" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD145" s="65" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="146" spans="1:30" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A146" s="45">
+        <v>147</v>
+      </c>
+      <c r="B146" s="76" t="s">
+        <v>899</v>
+      </c>
+      <c r="C146" s="55" t="s">
+        <v>963</v>
+      </c>
+      <c r="D146" s="55" t="s">
+        <v>948</v>
+      </c>
+      <c r="E146" s="57" t="s">
+        <v>994</v>
+      </c>
+      <c r="F146" s="56" t="s">
+        <v>985</v>
+      </c>
+      <c r="G146" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="H146" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="I146" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="J146" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="K146" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="L146" s="53" t="str">
+        <f t="shared" ref="L146" si="83">CONCATENATE("", C146)</f>
+        <v>Processuais</v>
+      </c>
+      <c r="M146" s="53" t="str">
+        <f t="shared" ref="M146" si="84">CONCATENATE("", D146)</f>
+        <v>Projetos</v>
+      </c>
+      <c r="N146" s="53" t="str">
+        <f t="shared" ref="N146" si="85">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E146),"."," ")," De "," de "))</f>
+        <v>Processo do Projeto</v>
+      </c>
+      <c r="O146" s="53" t="str">
+        <f t="shared" ref="O146" si="86">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",F146),"."," ")," De "," de "))</f>
+        <v>Projeto Concursado</v>
+      </c>
+      <c r="P146" s="53" t="s">
+        <v>986</v>
+      </c>
+      <c r="Q146" s="43" t="str">
+        <f t="shared" si="64"/>
+        <v>Proyecto participando en un concurso</v>
+      </c>
+      <c r="R146" s="43" t="str">
+        <f t="shared" ref="R146" si="87">_xlfn.TRANSLATE(P146,"pt","en")</f>
+        <v>Project participating in a contest</v>
+      </c>
+      <c r="S146" s="43" t="s">
+        <v>9</v>
+      </c>
+      <c r="T146" s="43" t="str">
+        <f t="shared" ref="T146" si="88">SUBSTITUTE(C146, "_", " ")</f>
+        <v>Processuais</v>
+      </c>
+      <c r="U146" s="43" t="str">
+        <f t="shared" ref="U146" si="89">SUBSTITUTE(D146, "_", " ")</f>
+        <v>Projetos</v>
+      </c>
+      <c r="V146" s="53" t="str">
+        <f t="shared" ref="V146" si="90">SUBSTITUTE(E146, "_", " ")</f>
+        <v>Processo.do.Projeto</v>
+      </c>
+      <c r="W146" s="43" t="s">
+        <v>80</v>
+      </c>
+      <c r="X146" s="54" t="str">
+        <f t="shared" ref="X146" si="91">CONCATENATE("Key-DOCU-",A146)</f>
+        <v>Key-DOCU-147</v>
+      </c>
+      <c r="Y146" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z146" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA146" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB146" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC146" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD146" s="65" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="147" spans="1:30" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A147" s="45">
+        <v>146</v>
+      </c>
+      <c r="B147" s="76" t="s">
+        <v>899</v>
+      </c>
+      <c r="C147" s="55" t="s">
+        <v>963</v>
+      </c>
+      <c r="D147" s="55" t="s">
+        <v>948</v>
+      </c>
+      <c r="E147" s="57" t="s">
+        <v>992</v>
+      </c>
+      <c r="F147" s="56" t="s">
+        <v>953</v>
+      </c>
+      <c r="G147" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="H147" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="I147" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="J147" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="K147" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="L147" s="53" t="str">
+        <f t="shared" si="79"/>
+        <v>Processuais</v>
+      </c>
+      <c r="M147" s="53" t="str">
+        <f t="shared" si="80"/>
+        <v>Projetos</v>
+      </c>
+      <c r="N147" s="53" t="str">
+        <f t="shared" si="81"/>
+        <v>Tipo de Projeto</v>
+      </c>
+      <c r="O147" s="53" t="str">
+        <f t="shared" si="82"/>
+        <v>Projeto Litigiado</v>
+      </c>
+      <c r="P147" s="53" t="s">
+        <v>978</v>
+      </c>
+      <c r="Q147" s="43" t="str">
+        <f t="shared" si="64"/>
+        <v>El proyecto está en litigio</v>
+      </c>
+      <c r="R147" s="43" t="str">
+        <f t="shared" si="65"/>
+        <v>Project is in litigation</v>
+      </c>
+      <c r="S147" s="43" t="s">
+        <v>9</v>
+      </c>
+      <c r="T147" s="43" t="str">
+        <f t="shared" si="75"/>
+        <v>Processuais</v>
+      </c>
+      <c r="U147" s="43" t="str">
+        <f t="shared" si="76"/>
+        <v>Projetos</v>
+      </c>
+      <c r="V147" s="53" t="str">
+        <f t="shared" si="77"/>
+        <v>Tipo.de.Projeto</v>
+      </c>
+      <c r="W147" s="43" t="s">
+        <v>80</v>
+      </c>
+      <c r="X147" s="54" t="str">
+        <f t="shared" si="78"/>
+        <v>Key-DOCU-146</v>
+      </c>
+      <c r="Y147" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z147" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA147" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB147" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC147" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD147" s="65" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="148" spans="1:30" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A148" s="45">
+        <v>148</v>
+      </c>
+      <c r="B148" s="76" t="s">
+        <v>899</v>
+      </c>
+      <c r="C148" s="55" t="s">
+        <v>963</v>
+      </c>
+      <c r="D148" s="55" t="s">
+        <v>948</v>
+      </c>
+      <c r="E148" s="57" t="s">
+        <v>992</v>
+      </c>
+      <c r="F148" s="56" t="s">
+        <v>962</v>
+      </c>
+      <c r="G148" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="H148" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="I148" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="J148" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="K148" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="L148" s="53" t="str">
+        <f t="shared" ref="L148" si="92">CONCATENATE("", C148)</f>
+        <v>Processuais</v>
+      </c>
+      <c r="M148" s="53" t="str">
+        <f t="shared" ref="M148" si="93">CONCATENATE("", D148)</f>
+        <v>Projetos</v>
+      </c>
+      <c r="N148" s="53" t="str">
+        <f t="shared" ref="N148" si="94">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E148),"."," ")," De "," de "))</f>
+        <v>Tipo de Projeto</v>
+      </c>
+      <c r="O148" s="53" t="str">
+        <f t="shared" ref="O148:P148" si="95">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",F148),"."," ")," De "," de "))</f>
+        <v>Projeto Viabilidade</v>
+      </c>
+      <c r="P148" s="53" t="s">
+        <v>991</v>
+      </c>
+      <c r="Q148" s="43" t="str">
+        <f t="shared" si="64"/>
+        <v>Proyecto definido como un estudio de viabilidad</v>
+      </c>
+      <c r="R148" s="43" t="str">
+        <f t="shared" si="65"/>
+        <v>Project defined as a feasibility study</v>
+      </c>
+      <c r="S148" s="43" t="s">
+        <v>9</v>
+      </c>
+      <c r="T148" s="43" t="str">
+        <f t="shared" si="75"/>
+        <v>Processuais</v>
+      </c>
+      <c r="U148" s="43" t="str">
+        <f t="shared" si="76"/>
+        <v>Projetos</v>
+      </c>
+      <c r="V148" s="53" t="str">
+        <f t="shared" si="77"/>
+        <v>Tipo.de.Projeto</v>
+      </c>
+      <c r="W148" s="43" t="s">
+        <v>80</v>
+      </c>
+      <c r="X148" s="54" t="str">
+        <f t="shared" si="78"/>
+        <v>Key-DOCU-148</v>
+      </c>
+      <c r="Y148" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z148" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA148" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB148" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC148" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD148" s="65" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="149" spans="1:30" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A149" s="45">
+        <v>149</v>
+      </c>
+      <c r="B149" s="76" t="s">
+        <v>899</v>
+      </c>
+      <c r="C149" s="55" t="s">
+        <v>963</v>
+      </c>
+      <c r="D149" s="55" t="s">
+        <v>948</v>
+      </c>
+      <c r="E149" s="57" t="s">
+        <v>992</v>
+      </c>
+      <c r="F149" s="56" t="s">
+        <v>958</v>
+      </c>
+      <c r="G149" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="H149" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="I149" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="J149" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="K149" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="L149" s="53" t="str">
+        <f t="shared" si="79"/>
+        <v>Processuais</v>
+      </c>
+      <c r="M149" s="53" t="str">
+        <f t="shared" si="80"/>
+        <v>Projetos</v>
+      </c>
+      <c r="N149" s="53" t="str">
+        <f t="shared" si="81"/>
+        <v>Tipo de Projeto</v>
+      </c>
+      <c r="O149" s="53" t="str">
+        <f t="shared" si="82"/>
+        <v>Projeto Preliminar</v>
+      </c>
+      <c r="P149" s="53" t="s">
+        <v>990</v>
+      </c>
+      <c r="Q149" s="43" t="str">
+        <f t="shared" si="64"/>
+        <v>Proyecto definido como un estudio preliminar</v>
+      </c>
+      <c r="R149" s="43" t="str">
+        <f t="shared" si="65"/>
+        <v>Project defined as a preliminary study</v>
+      </c>
+      <c r="S149" s="43" t="s">
+        <v>9</v>
+      </c>
+      <c r="T149" s="43" t="str">
+        <f t="shared" ref="T149:T153" si="96">SUBSTITUTE(C149, "_", " ")</f>
+        <v>Processuais</v>
+      </c>
+      <c r="U149" s="43" t="str">
+        <f t="shared" ref="U149:U153" si="97">SUBSTITUTE(D149, "_", " ")</f>
+        <v>Projetos</v>
+      </c>
+      <c r="V149" s="53" t="str">
+        <f t="shared" ref="V149:V153" si="98">SUBSTITUTE(E149, "_", " ")</f>
+        <v>Tipo.de.Projeto</v>
+      </c>
+      <c r="W149" s="43" t="s">
+        <v>80</v>
+      </c>
+      <c r="X149" s="54" t="str">
+        <f t="shared" ref="X149:X153" si="99">CONCATENATE("Key-DOCU-",A149)</f>
+        <v>Key-DOCU-149</v>
+      </c>
+      <c r="Y149" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z149" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA149" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB149" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC149" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD149" s="65" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="150" spans="1:30" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A150" s="45">
+        <v>150</v>
+      </c>
+      <c r="B150" s="76" t="s">
+        <v>899</v>
+      </c>
+      <c r="C150" s="55" t="s">
+        <v>963</v>
+      </c>
+      <c r="D150" s="55" t="s">
+        <v>948</v>
+      </c>
+      <c r="E150" s="57" t="s">
+        <v>992</v>
+      </c>
+      <c r="F150" s="56" t="s">
+        <v>959</v>
+      </c>
+      <c r="G150" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="H150" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="I150" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="J150" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="K150" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="L150" s="53" t="str">
+        <f t="shared" ref="L150:L154" si="100">CONCATENATE("", C150)</f>
+        <v>Processuais</v>
+      </c>
+      <c r="M150" s="53" t="str">
+        <f t="shared" ref="M150:M154" si="101">CONCATENATE("", D150)</f>
+        <v>Projetos</v>
+      </c>
+      <c r="N150" s="53" t="str">
+        <f t="shared" ref="N150:N154" si="102">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E150),"."," ")," De "," de "))</f>
+        <v>Tipo de Projeto</v>
+      </c>
+      <c r="O150" s="53" t="str">
+        <f t="shared" ref="O150:P154" si="103">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",F150),"."," ")," De "," de "))</f>
+        <v>Projeto Básico</v>
+      </c>
+      <c r="P150" s="53" t="s">
+        <v>989</v>
+      </c>
+      <c r="Q150" s="43" t="str">
+        <f>_xlfn.TRANSLATE(P150,"pt","es")</f>
+        <v>Proyecto definido como proyecto básico o preliminar</v>
+      </c>
+      <c r="R150" s="43" t="str">
+        <f t="shared" si="65"/>
+        <v>Project defined as basic or preliminary project</v>
+      </c>
+      <c r="S150" s="43" t="s">
+        <v>9</v>
+      </c>
+      <c r="T150" s="43" t="str">
+        <f t="shared" si="96"/>
+        <v>Processuais</v>
+      </c>
+      <c r="U150" s="43" t="str">
+        <f t="shared" si="97"/>
+        <v>Projetos</v>
+      </c>
+      <c r="V150" s="53" t="str">
+        <f t="shared" si="98"/>
+        <v>Tipo.de.Projeto</v>
+      </c>
+      <c r="W150" s="43" t="s">
+        <v>80</v>
+      </c>
+      <c r="X150" s="54" t="str">
+        <f t="shared" si="99"/>
+        <v>Key-DOCU-150</v>
+      </c>
+      <c r="Y150" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z150" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA150" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB150" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC150" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD150" s="65" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="151" spans="1:30" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A151" s="45">
+        <v>151</v>
+      </c>
+      <c r="B151" s="76" t="s">
+        <v>899</v>
+      </c>
+      <c r="C151" s="55" t="s">
+        <v>963</v>
+      </c>
+      <c r="D151" s="55" t="s">
+        <v>948</v>
+      </c>
+      <c r="E151" s="57" t="s">
+        <v>992</v>
+      </c>
+      <c r="F151" s="56" t="s">
+        <v>960</v>
+      </c>
+      <c r="G151" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="H151" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="I151" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="J151" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="K151" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="L151" s="53" t="str">
+        <f t="shared" si="100"/>
+        <v>Processuais</v>
+      </c>
+      <c r="M151" s="53" t="str">
+        <f t="shared" si="101"/>
+        <v>Projetos</v>
+      </c>
+      <c r="N151" s="53" t="str">
+        <f t="shared" si="102"/>
+        <v>Tipo de Projeto</v>
+      </c>
+      <c r="O151" s="53" t="str">
+        <f t="shared" si="103"/>
+        <v>Projeto Executivo</v>
+      </c>
+      <c r="P151" s="53" t="s">
+        <v>988</v>
+      </c>
+      <c r="Q151" s="43" t="str">
+        <f t="shared" si="64"/>
+        <v>Proyecto en la fase de ejecución</v>
+      </c>
+      <c r="R151" s="43" t="str">
+        <f t="shared" si="65"/>
+        <v>Project in the execution stage</v>
+      </c>
+      <c r="S151" s="43" t="s">
+        <v>9</v>
+      </c>
+      <c r="T151" s="43" t="str">
+        <f t="shared" si="96"/>
+        <v>Processuais</v>
+      </c>
+      <c r="U151" s="43" t="str">
+        <f t="shared" si="97"/>
+        <v>Projetos</v>
+      </c>
+      <c r="V151" s="53" t="str">
+        <f t="shared" si="98"/>
+        <v>Tipo.de.Projeto</v>
+      </c>
+      <c r="W151" s="43" t="s">
+        <v>80</v>
+      </c>
+      <c r="X151" s="54" t="str">
+        <f t="shared" si="99"/>
+        <v>Key-DOCU-151</v>
+      </c>
+      <c r="Y151" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z151" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA151" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB151" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC151" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD151" s="65" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="152" spans="1:30" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A152" s="45">
+        <v>152</v>
+      </c>
+      <c r="B152" s="76" t="s">
+        <v>899</v>
+      </c>
+      <c r="C152" s="55" t="s">
+        <v>963</v>
+      </c>
+      <c r="D152" s="55" t="s">
+        <v>948</v>
+      </c>
+      <c r="E152" s="57" t="s">
+        <v>992</v>
+      </c>
+      <c r="F152" s="56" t="s">
+        <v>961</v>
+      </c>
+      <c r="G152" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="H152" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="I152" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="J152" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="K152" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="L152" s="53" t="str">
+        <f t="shared" si="100"/>
+        <v>Processuais</v>
+      </c>
+      <c r="M152" s="53" t="str">
+        <f t="shared" si="101"/>
+        <v>Projetos</v>
+      </c>
+      <c r="N152" s="53" t="str">
+        <f t="shared" si="102"/>
+        <v>Tipo de Projeto</v>
+      </c>
+      <c r="O152" s="53" t="str">
+        <f t="shared" si="103"/>
+        <v>Projeto Aprovação</v>
+      </c>
+      <c r="P152" s="53" t="s">
+        <v>987</v>
+      </c>
+      <c r="Q152" s="43" t="str">
+        <f t="shared" si="64"/>
+        <v>Proyecto para la aprobación por parte de organismos competentes (Ayuntamientos, Departamento de Bomberos, Licencias Medioambientales, etc.)</v>
+      </c>
+      <c r="R152" s="43" t="str">
+        <f t="shared" si="65"/>
+        <v>Project for approval by competent body (City Halls, Fire Department, Environmental Licensing, etc.)</v>
+      </c>
+      <c r="S152" s="43" t="s">
+        <v>9</v>
+      </c>
+      <c r="T152" s="43" t="str">
+        <f t="shared" si="96"/>
+        <v>Processuais</v>
+      </c>
+      <c r="U152" s="43" t="str">
+        <f t="shared" si="97"/>
+        <v>Projetos</v>
+      </c>
+      <c r="V152" s="53" t="str">
+        <f t="shared" si="98"/>
+        <v>Tipo.de.Projeto</v>
+      </c>
+      <c r="W152" s="43" t="s">
+        <v>80</v>
+      </c>
+      <c r="X152" s="54" t="str">
+        <f t="shared" si="99"/>
+        <v>Key-DOCU-152</v>
+      </c>
+      <c r="Y152" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z152" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA152" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB152" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC152" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD152" s="65" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="153" spans="1:30" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A153" s="45">
+        <v>153</v>
+      </c>
+      <c r="B153" s="76" t="s">
+        <v>899</v>
+      </c>
+      <c r="C153" s="55" t="s">
+        <v>963</v>
+      </c>
+      <c r="D153" s="55" t="s">
+        <v>948</v>
+      </c>
+      <c r="E153" s="57" t="s">
+        <v>964</v>
+      </c>
+      <c r="F153" s="56" t="s">
+        <v>965</v>
+      </c>
+      <c r="G153" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="H153" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="I153" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="J153" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="K153" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="L153" s="53" t="str">
+        <f t="shared" si="100"/>
+        <v>Processuais</v>
+      </c>
+      <c r="M153" s="53" t="str">
+        <f t="shared" si="101"/>
+        <v>Projetos</v>
+      </c>
+      <c r="N153" s="53" t="str">
+        <f t="shared" si="102"/>
+        <v>Equipes</v>
+      </c>
+      <c r="O153" s="53" t="str">
+        <f t="shared" si="103"/>
+        <v>Equipe Própria</v>
+      </c>
+      <c r="P153" s="53" t="s">
+        <v>970</v>
+      </c>
+      <c r="Q153" s="43" t="str">
+        <f t="shared" si="64"/>
+        <v>Equipo propio</v>
+      </c>
+      <c r="R153" s="43" t="str">
+        <f t="shared" si="65"/>
+        <v>Own Team</v>
+      </c>
+      <c r="S153" s="43" t="s">
+        <v>9</v>
+      </c>
+      <c r="T153" s="43" t="str">
+        <f t="shared" si="96"/>
+        <v>Processuais</v>
+      </c>
+      <c r="U153" s="43" t="str">
+        <f t="shared" si="97"/>
+        <v>Projetos</v>
+      </c>
+      <c r="V153" s="53" t="str">
+        <f t="shared" si="98"/>
+        <v>Equipes</v>
+      </c>
+      <c r="W153" s="43" t="s">
+        <v>80</v>
+      </c>
+      <c r="X153" s="54" t="str">
+        <f t="shared" si="99"/>
+        <v>Key-DOCU-153</v>
+      </c>
+      <c r="Y153" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z153" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA153" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB153" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC153" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD153" s="65" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="154" spans="1:30" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A154" s="45">
+        <v>154</v>
+      </c>
+      <c r="B154" s="76" t="s">
+        <v>899</v>
+      </c>
+      <c r="C154" s="55" t="s">
+        <v>963</v>
+      </c>
+      <c r="D154" s="55" t="s">
+        <v>948</v>
+      </c>
+      <c r="E154" s="57" t="s">
+        <v>964</v>
+      </c>
+      <c r="F154" s="56" t="s">
+        <v>966</v>
+      </c>
+      <c r="G154" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="H154" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="I154" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="J154" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="K154" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="L154" s="53" t="str">
+        <f t="shared" si="100"/>
+        <v>Processuais</v>
+      </c>
+      <c r="M154" s="53" t="str">
+        <f t="shared" si="101"/>
+        <v>Projetos</v>
+      </c>
+      <c r="N154" s="53" t="str">
+        <f t="shared" si="102"/>
+        <v>Equipes</v>
+      </c>
+      <c r="O154" s="53" t="str">
+        <f t="shared" si="103"/>
+        <v>Equipe Associada</v>
+      </c>
+      <c r="P154" s="53" t="s">
+        <v>971</v>
+      </c>
+      <c r="Q154" s="43" t="str">
+        <f t="shared" si="64"/>
+        <v>Equipo Asociado</v>
+      </c>
+      <c r="R154" s="43" t="str">
+        <f t="shared" si="65"/>
+        <v>Associate Team</v>
+      </c>
+      <c r="S154" s="43" t="s">
+        <v>9</v>
+      </c>
+      <c r="T154" s="43" t="str">
+        <f t="shared" ref="T154:T157" si="104">SUBSTITUTE(C154, "_", " ")</f>
+        <v>Processuais</v>
+      </c>
+      <c r="U154" s="43" t="str">
+        <f t="shared" ref="U154:U157" si="105">SUBSTITUTE(D154, "_", " ")</f>
+        <v>Projetos</v>
+      </c>
+      <c r="V154" s="53" t="str">
+        <f t="shared" ref="V154:V157" si="106">SUBSTITUTE(E154, "_", " ")</f>
+        <v>Equipes</v>
+      </c>
+      <c r="W154" s="43" t="s">
+        <v>80</v>
+      </c>
+      <c r="X154" s="54" t="str">
+        <f t="shared" ref="X154:X157" si="107">CONCATENATE("Key-DOCU-",A154)</f>
+        <v>Key-DOCU-154</v>
+      </c>
+      <c r="Y154" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z154" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA154" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB154" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC154" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD154" s="65" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="155" spans="1:30" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A155" s="45">
+        <v>155</v>
+      </c>
+      <c r="B155" s="76" t="s">
+        <v>899</v>
+      </c>
+      <c r="C155" s="55" t="s">
+        <v>963</v>
+      </c>
+      <c r="D155" s="55" t="s">
+        <v>948</v>
+      </c>
+      <c r="E155" s="57" t="s">
+        <v>964</v>
+      </c>
+      <c r="F155" s="56" t="s">
+        <v>967</v>
+      </c>
+      <c r="G155" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="H155" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="I155" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="J155" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="K155" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="L155" s="53" t="str">
+        <f t="shared" ref="L155:L157" si="108">CONCATENATE("", C155)</f>
+        <v>Processuais</v>
+      </c>
+      <c r="M155" s="53" t="str">
+        <f t="shared" ref="M155:M157" si="109">CONCATENATE("", D155)</f>
+        <v>Projetos</v>
+      </c>
+      <c r="N155" s="53" t="str">
+        <f t="shared" ref="N155:N157" si="110">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E155),"."," ")," De "," de "))</f>
+        <v>Equipes</v>
+      </c>
+      <c r="O155" s="53" t="str">
+        <f t="shared" ref="O155:P157" si="111">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",F155),"."," ")," De "," de "))</f>
+        <v>Equipe Consultora</v>
+      </c>
+      <c r="P155" s="53" t="s">
+        <v>972</v>
+      </c>
+      <c r="Q155" s="43" t="str">
+        <f t="shared" si="64"/>
+        <v>Equipo de Consultoría</v>
+      </c>
+      <c r="R155" s="43" t="str">
+        <f t="shared" si="65"/>
+        <v>Consulting Team</v>
+      </c>
+      <c r="S155" s="43" t="s">
+        <v>9</v>
+      </c>
+      <c r="T155" s="43" t="str">
+        <f t="shared" si="104"/>
+        <v>Processuais</v>
+      </c>
+      <c r="U155" s="43" t="str">
+        <f t="shared" si="105"/>
+        <v>Projetos</v>
+      </c>
+      <c r="V155" s="53" t="str">
+        <f t="shared" si="106"/>
+        <v>Equipes</v>
+      </c>
+      <c r="W155" s="43" t="s">
+        <v>80</v>
+      </c>
+      <c r="X155" s="54" t="str">
+        <f t="shared" si="107"/>
+        <v>Key-DOCU-155</v>
+      </c>
+      <c r="Y155" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z155" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA155" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB155" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC155" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD155" s="65" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="156" spans="1:30" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A156" s="45">
+        <v>156</v>
+      </c>
+      <c r="B156" s="76" t="s">
+        <v>899</v>
+      </c>
+      <c r="C156" s="55" t="s">
+        <v>963</v>
+      </c>
+      <c r="D156" s="55" t="s">
+        <v>948</v>
+      </c>
+      <c r="E156" s="57" t="s">
+        <v>964</v>
+      </c>
+      <c r="F156" s="56" t="s">
+        <v>968</v>
+      </c>
+      <c r="G156" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="H156" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="I156" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="J156" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="K156" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="L156" s="53" t="str">
+        <f t="shared" si="108"/>
+        <v>Processuais</v>
+      </c>
+      <c r="M156" s="53" t="str">
+        <f t="shared" si="109"/>
+        <v>Projetos</v>
+      </c>
+      <c r="N156" s="53" t="str">
+        <f t="shared" si="110"/>
+        <v>Equipes</v>
+      </c>
+      <c r="O156" s="53" t="str">
+        <f t="shared" si="111"/>
+        <v>Equipe Colaboradora</v>
+      </c>
+      <c r="P156" s="53" t="s">
+        <v>973</v>
+      </c>
+      <c r="Q156" s="43" t="str">
+        <f t="shared" si="64"/>
+        <v>Equipo colaborador</v>
+      </c>
+      <c r="R156" s="43" t="str">
+        <f>_xlfn.TRANSLATE(P156,"pt","en")</f>
+        <v>Collaborating Team</v>
+      </c>
+      <c r="S156" s="43" t="s">
+        <v>9</v>
+      </c>
+      <c r="T156" s="43" t="str">
+        <f t="shared" si="104"/>
+        <v>Processuais</v>
+      </c>
+      <c r="U156" s="43" t="str">
+        <f t="shared" si="105"/>
+        <v>Projetos</v>
+      </c>
+      <c r="V156" s="53" t="str">
+        <f t="shared" si="106"/>
+        <v>Equipes</v>
+      </c>
+      <c r="W156" s="43" t="s">
+        <v>80</v>
+      </c>
+      <c r="X156" s="54" t="str">
+        <f t="shared" si="107"/>
+        <v>Key-DOCU-156</v>
+      </c>
+      <c r="Y156" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z156" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA156" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB156" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC156" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD156" s="65" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="157" spans="1:30" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A157" s="45">
+        <v>157</v>
+      </c>
+      <c r="B157" s="76" t="s">
+        <v>899</v>
+      </c>
+      <c r="C157" s="55" t="s">
+        <v>963</v>
+      </c>
+      <c r="D157" s="55" t="s">
+        <v>948</v>
+      </c>
+      <c r="E157" s="57" t="s">
+        <v>964</v>
+      </c>
+      <c r="F157" s="56" t="s">
+        <v>969</v>
+      </c>
+      <c r="G157" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="H157" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="I157" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="J157" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="K157" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="L157" s="53" t="str">
+        <f t="shared" si="108"/>
+        <v>Processuais</v>
+      </c>
+      <c r="M157" s="53" t="str">
+        <f t="shared" si="109"/>
+        <v>Projetos</v>
+      </c>
+      <c r="N157" s="53" t="str">
+        <f t="shared" si="110"/>
+        <v>Equipes</v>
+      </c>
+      <c r="O157" s="53" t="str">
+        <f t="shared" si="111"/>
+        <v>Equipe Terceirizada</v>
+      </c>
+      <c r="P157" s="53" t="s">
+        <v>974</v>
+      </c>
+      <c r="Q157" s="43" t="str">
+        <f t="shared" si="64"/>
+        <v>Equipo externalizado</v>
+      </c>
+      <c r="R157" s="43" t="str">
+        <f t="shared" si="65"/>
+        <v>Outsourced Team</v>
+      </c>
+      <c r="S157" s="43" t="s">
+        <v>9</v>
+      </c>
+      <c r="T157" s="43" t="str">
+        <f t="shared" si="104"/>
+        <v>Processuais</v>
+      </c>
+      <c r="U157" s="43" t="str">
+        <f t="shared" si="105"/>
+        <v>Projetos</v>
+      </c>
+      <c r="V157" s="53" t="str">
+        <f t="shared" si="106"/>
+        <v>Equipes</v>
+      </c>
+      <c r="W157" s="43" t="s">
+        <v>80</v>
+      </c>
+      <c r="X157" s="54" t="str">
+        <f t="shared" si="107"/>
+        <v>Key-DOCU-157</v>
+      </c>
+      <c r="Y157" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z157" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA157" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB157" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC157" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD157" s="65" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="158" spans="1:30" s="66" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A158" s="45">
+        <v>158</v>
+      </c>
+      <c r="B158" s="76" t="s">
+        <v>899</v>
+      </c>
+      <c r="C158" s="77" t="s">
+        <v>900</v>
+      </c>
+      <c r="D158" s="77" t="s">
+        <v>902</v>
+      </c>
+      <c r="E158" s="77" t="s">
+        <v>901</v>
+      </c>
+      <c r="F158" s="77" t="s">
+        <v>926</v>
+      </c>
+      <c r="G158" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="H158" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="I158" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="J158" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="K158" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="L158" s="63" t="str">
+        <f t="shared" ref="L158:O162" si="112">SUBSTITUTE(CONCATENATE("", C158), ".", " ")</f>
+        <v>De API</v>
+      </c>
+      <c r="M158" s="63" t="str">
+        <f t="shared" si="112"/>
+        <v>Macros</v>
+      </c>
+      <c r="N158" s="63" t="str">
+        <f t="shared" si="112"/>
+        <v>Métodos</v>
+      </c>
+      <c r="O158" s="63" t="str">
+        <f t="shared" si="112"/>
+        <v>Função Auxiliar</v>
+      </c>
+      <c r="P158" s="64" t="s">
+        <v>927</v>
+      </c>
+      <c r="Q158" s="64" t="s">
+        <v>928</v>
+      </c>
+      <c r="R158" s="64" t="s">
+        <v>929</v>
+      </c>
+      <c r="S158" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="T158" s="64" t="str">
+        <f t="shared" ref="T158:V162" si="113">SUBSTITUTE(C158, ".", " ")</f>
+        <v>De API</v>
+      </c>
+      <c r="U158" s="64" t="str">
+        <f t="shared" si="113"/>
+        <v>Macros</v>
+      </c>
+      <c r="V158" s="43" t="str">
+        <f t="shared" si="113"/>
+        <v>Métodos</v>
+      </c>
+      <c r="W158" s="43" t="s">
+        <v>80</v>
+      </c>
+      <c r="X158" s="54" t="str">
+        <f t="shared" ref="X158:X162" si="114">CONCATENATE("Key-DOCU-",A158)</f>
+        <v>Key-DOCU-158</v>
+      </c>
+      <c r="Y158" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z158" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA158" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB158" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC158" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD158" s="65" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="159" spans="1:30" s="66" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A159" s="45">
+        <v>159</v>
+      </c>
+      <c r="B159" s="76" t="s">
+        <v>899</v>
+      </c>
+      <c r="C159" s="77" t="s">
+        <v>900</v>
+      </c>
+      <c r="D159" s="77" t="s">
+        <v>902</v>
+      </c>
+      <c r="E159" s="77" t="s">
+        <v>901</v>
+      </c>
+      <c r="F159" s="77" t="s">
+        <v>930</v>
+      </c>
+      <c r="G159" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="H159" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="I159" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="J159" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="K159" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="L159" s="63" t="str">
+        <f t="shared" si="112"/>
+        <v>De API</v>
+      </c>
+      <c r="M159" s="63" t="str">
+        <f t="shared" si="112"/>
+        <v>Macros</v>
+      </c>
+      <c r="N159" s="63" t="str">
+        <f t="shared" si="112"/>
+        <v>Métodos</v>
+      </c>
+      <c r="O159" s="63" t="str">
+        <f t="shared" si="112"/>
+        <v>Função Global</v>
+      </c>
+      <c r="P159" s="64" t="s">
+        <v>931</v>
+      </c>
+      <c r="Q159" s="64" t="s">
+        <v>932</v>
+      </c>
+      <c r="R159" s="64" t="s">
+        <v>933</v>
+      </c>
+      <c r="S159" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="T159" s="64" t="str">
+        <f t="shared" si="113"/>
+        <v>De API</v>
+      </c>
+      <c r="U159" s="64" t="str">
+        <f t="shared" si="113"/>
+        <v>Macros</v>
+      </c>
+      <c r="V159" s="43" t="str">
+        <f t="shared" si="113"/>
+        <v>Métodos</v>
+      </c>
+      <c r="W159" s="43" t="s">
+        <v>80</v>
+      </c>
+      <c r="X159" s="54" t="str">
+        <f t="shared" si="114"/>
+        <v>Key-DOCU-159</v>
+      </c>
+      <c r="Y159" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z159" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA159" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB159" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC159" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD159" s="65" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="160" spans="1:30" s="66" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A160" s="45">
+        <v>160</v>
+      </c>
+      <c r="B160" s="76" t="s">
+        <v>899</v>
+      </c>
+      <c r="C160" s="77" t="s">
+        <v>900</v>
+      </c>
+      <c r="D160" s="77" t="s">
+        <v>902</v>
+      </c>
+      <c r="E160" s="77" t="s">
+        <v>901</v>
+      </c>
+      <c r="F160" s="77" t="s">
+        <v>934</v>
+      </c>
+      <c r="G160" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="H160" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="I160" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="J160" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="K160" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="L160" s="63" t="str">
+        <f t="shared" si="112"/>
+        <v>De API</v>
+      </c>
+      <c r="M160" s="63" t="str">
+        <f t="shared" si="112"/>
+        <v>Macros</v>
+      </c>
+      <c r="N160" s="63" t="str">
+        <f t="shared" si="112"/>
+        <v>Métodos</v>
+      </c>
+      <c r="O160" s="63" t="str">
+        <f t="shared" si="112"/>
+        <v>Função Local</v>
+      </c>
+      <c r="P160" s="64" t="s">
+        <v>935</v>
+      </c>
+      <c r="Q160" s="64" t="s">
+        <v>936</v>
+      </c>
+      <c r="R160" s="64" t="s">
+        <v>937</v>
+      </c>
+      <c r="S160" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="T160" s="64" t="str">
+        <f t="shared" si="113"/>
+        <v>De API</v>
+      </c>
+      <c r="U160" s="64" t="str">
+        <f t="shared" si="113"/>
+        <v>Macros</v>
+      </c>
+      <c r="V160" s="43" t="str">
+        <f t="shared" si="113"/>
+        <v>Métodos</v>
+      </c>
+      <c r="W160" s="43" t="s">
+        <v>80</v>
+      </c>
+      <c r="X160" s="54" t="str">
+        <f t="shared" si="114"/>
+        <v>Key-DOCU-160</v>
+      </c>
+      <c r="Y160" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z160" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA160" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB160" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC160" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD160" s="65" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="161" spans="1:30" s="66" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A161" s="45">
+        <v>161</v>
+      </c>
+      <c r="B161" s="76" t="s">
+        <v>899</v>
+      </c>
+      <c r="C161" s="77" t="s">
+        <v>900</v>
+      </c>
+      <c r="D161" s="77" t="s">
+        <v>902</v>
+      </c>
+      <c r="E161" s="77" t="s">
+        <v>901</v>
+      </c>
+      <c r="F161" s="77" t="s">
+        <v>938</v>
+      </c>
+      <c r="G161" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="H161" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="I161" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="J161" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="K161" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="L161" s="63" t="str">
+        <f t="shared" si="112"/>
+        <v>De API</v>
+      </c>
+      <c r="M161" s="63" t="str">
+        <f t="shared" si="112"/>
+        <v>Macros</v>
+      </c>
+      <c r="N161" s="63" t="str">
+        <f t="shared" si="112"/>
+        <v>Métodos</v>
+      </c>
+      <c r="O161" s="63" t="str">
+        <f t="shared" si="112"/>
+        <v>Função Filtro</v>
+      </c>
+      <c r="P161" s="64" t="s">
+        <v>939</v>
+      </c>
+      <c r="Q161" s="64" t="s">
+        <v>940</v>
+      </c>
+      <c r="R161" s="64" t="s">
+        <v>941</v>
+      </c>
+      <c r="S161" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="T161" s="64" t="str">
+        <f t="shared" si="113"/>
+        <v>De API</v>
+      </c>
+      <c r="U161" s="64" t="str">
+        <f t="shared" si="113"/>
+        <v>Macros</v>
+      </c>
+      <c r="V161" s="43" t="str">
+        <f t="shared" si="113"/>
+        <v>Métodos</v>
+      </c>
+      <c r="W161" s="43" t="s">
+        <v>80</v>
+      </c>
+      <c r="X161" s="54" t="str">
+        <f t="shared" si="114"/>
+        <v>Key-DOCU-161</v>
+      </c>
+      <c r="Y161" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z161" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA161" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB161" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC161" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD161" s="65" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="162" spans="1:30" s="66" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A162" s="45">
+        <v>162</v>
+      </c>
+      <c r="B162" s="76" t="s">
+        <v>899</v>
+      </c>
+      <c r="C162" s="77" t="s">
+        <v>900</v>
+      </c>
+      <c r="D162" s="77" t="s">
+        <v>902</v>
+      </c>
+      <c r="E162" s="77" t="s">
+        <v>942</v>
+      </c>
+      <c r="F162" s="77" t="s">
+        <v>943</v>
+      </c>
+      <c r="G162" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="H162" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="I162" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="J162" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="K162" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="L162" s="63" t="str">
+        <f t="shared" si="112"/>
+        <v>De API</v>
+      </c>
+      <c r="M162" s="63" t="str">
+        <f t="shared" si="112"/>
+        <v>Macros</v>
+      </c>
+      <c r="N162" s="63" t="str">
+        <f t="shared" si="112"/>
+        <v>Códigos Visuais</v>
+      </c>
+      <c r="O162" s="63" t="str">
+        <f t="shared" si="112"/>
+        <v>Bloco de Código</v>
+      </c>
+      <c r="P162" s="64" t="s">
+        <v>944</v>
+      </c>
+      <c r="Q162" s="64" t="s">
+        <v>945</v>
+      </c>
+      <c r="R162" s="64" t="s">
+        <v>946</v>
+      </c>
+      <c r="S162" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="T162" s="64" t="str">
+        <f t="shared" si="113"/>
+        <v>De API</v>
+      </c>
+      <c r="U162" s="64" t="str">
+        <f t="shared" si="113"/>
+        <v>Macros</v>
+      </c>
+      <c r="V162" s="43" t="str">
+        <f t="shared" si="113"/>
+        <v>Códigos Visuais</v>
+      </c>
+      <c r="W162" s="43" t="s">
+        <v>80</v>
+      </c>
+      <c r="X162" s="54" t="str">
+        <f t="shared" si="114"/>
+        <v>Key-DOCU-162</v>
+      </c>
+      <c r="Y162" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z162" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA162" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB162" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC162" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD162" s="65" t="s">
         <v>9</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A8:AC138">
-    <sortCondition ref="A1:A138"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A8:AC158">
+    <sortCondition ref="A1:A158"/>
   </sortState>
-  <conditionalFormatting sqref="A2:B142">
-    <cfRule type="cellIs" dxfId="15" priority="1" operator="equal">
+  <conditionalFormatting sqref="R1:R137 A2:B162">
+    <cfRule type="cellIs" dxfId="20" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E142:F142">
-    <cfRule type="duplicateValues" dxfId="14" priority="2"/>
+  <conditionalFormatting sqref="E162:F162">
+    <cfRule type="duplicateValues" dxfId="19" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="duplicateValues" dxfId="13" priority="40"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="41"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="42"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="43"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="44"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F1:F137 F143:F1048576">
-    <cfRule type="duplicateValues" dxfId="8" priority="16"/>
+  <conditionalFormatting sqref="F163:F1048576 F1:F157">
+    <cfRule type="duplicateValues" dxfId="13" priority="16"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F138:F141">
-    <cfRule type="duplicateValues" dxfId="7" priority="3"/>
+  <conditionalFormatting sqref="F158:F161">
+    <cfRule type="duplicateValues" dxfId="12" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G1:O1">
-    <cfRule type="cellIs" dxfId="6" priority="34" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R1:R137">
-    <cfRule type="cellIs" dxfId="5" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="34" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <ignoredErrors>
-    <ignoredError sqref="AC1 AC143:AC1048576 B36:D61 B95:D95 AE1:XFD137 F95:P95 B96:P117 F36:P61 B62:P94 B3:P11 A143:P1048576 A1:P2 AA8:AA122 S1:X1 S8:Y121 S2:X2 S3:X7 AA143:AA1048576 S143:Y1048576 S123:V123 S124:V134 B120:P137 B119:P119 B118:P118 B13:P21 B12:P12 B23:P35 B22:P22 AE143:XFD1048576 S135:V137 S122:V122 X122:Y122 X123 X124:X134" numberStoredAsText="1"/>
+    <ignoredError sqref="AC1 AC163:AC1048576 B36:D61 B95:D95 AE1:XFD137 F95:P95 B96:P117 F36:P61 B62:P94 B3:P11 A163:P1048576 A1:P1 AA8:AA122 S1:X1 S8:Y121 S2:X2 S3:X7 AA163:AA1048576 S163:Y1048576 S123:V123 S124:V134 B120:P137 B119:P119 B118:P118 B13:P21 B12:P12 B23:P35 B22:P22 AE163:XFD1048576 S135:V137 S122:V122 X122:Y122 X123 X124:X134 B2:P2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -18694,7 +20949,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{429087C4-377B-4931-BC50-C00BD9684F83}">
-  <dimension ref="A1:AK42"/>
+  <dimension ref="A1:AM45"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.5703125" bestFit="1" customWidth="1"/>
@@ -18711,21 +20966,21 @@
     <col min="12" max="12" width="4.28515625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="4.85546875" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="6" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="81.140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="15.85546875" customWidth="1"/>
-    <col min="18" max="18" width="6.7109375" customWidth="1"/>
-    <col min="19" max="19" width="7" customWidth="1"/>
-    <col min="20" max="20" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="12.140625" customWidth="1"/>
+    <col min="15" max="15" width="13.85546875" customWidth="1"/>
+    <col min="16" max="16" width="6" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="81.140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15.85546875" customWidth="1"/>
+    <col min="20" max="20" width="6.7109375" customWidth="1"/>
+    <col min="21" max="21" width="7" customWidth="1"/>
     <col min="22" max="22" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="12.140625" customWidth="1"/>
     <col min="24" max="24" width="7.5703125" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="14.85546875" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="9.42578125" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="4.28515625" bestFit="1" customWidth="1"/>
     <col min="31" max="31" width="4.85546875" bestFit="1" customWidth="1"/>
     <col min="32" max="32" width="4.28515625" bestFit="1" customWidth="1"/>
@@ -18734,9 +20989,11 @@
     <col min="35" max="35" width="4.85546875" bestFit="1" customWidth="1"/>
     <col min="36" max="36" width="4.28515625" bestFit="1" customWidth="1"/>
     <col min="37" max="37" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="4.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:39" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="14" t="s">
         <v>30</v>
       </c>
@@ -18782,10 +21039,10 @@
       <c r="O1" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="P1" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" s="15" t="s">
+      <c r="P1" s="31" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q1" s="28" t="s">
         <v>2</v>
       </c>
       <c r="R1" s="15" t="s">
@@ -18848,8 +21105,14 @@
       <c r="AK1" s="15" t="s">
         <v>2</v>
       </c>
+      <c r="AL1" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="AM1" s="15" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="2" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:39" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="16">
         <v>2</v>
       </c>
@@ -18857,7 +21120,7 @@
         <v>612</v>
       </c>
       <c r="C2" s="55" t="s">
-        <v>616</v>
+        <v>985</v>
       </c>
       <c r="D2" s="19" t="s">
         <v>9</v>
@@ -18890,17 +21153,17 @@
         <v>9</v>
       </c>
       <c r="N2" s="30" t="s">
+        <v>998</v>
+      </c>
+      <c r="O2" s="29" t="s">
+        <v>999</v>
+      </c>
+      <c r="P2" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="O2" s="29" t="s">
+      <c r="Q2" s="29" t="s">
         <v>617</v>
       </c>
-      <c r="P2" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q2" s="21" t="s">
-        <v>9</v>
-      </c>
       <c r="R2" s="30" t="s">
         <v>9</v>
       </c>
@@ -18925,16 +21188,16 @@
       <c r="Y2" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="Z2" s="74" t="s">
+      <c r="Z2" s="30" t="s">
         <v>9</v>
       </c>
       <c r="AA2" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="AB2" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC2" s="73" t="s">
+      <c r="AB2" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC2" s="21" t="s">
         <v>9</v>
       </c>
       <c r="AD2" s="72" t="s">
@@ -18961,19 +21224,25 @@
       <c r="AK2" s="73" t="s">
         <v>9</v>
       </c>
+      <c r="AL2" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AM2" s="73" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="3" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:39" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="16">
         <v>3</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>598</v>
-      </c>
-      <c r="C3" s="18" t="s">
-        <v>582</v>
+        <v>995</v>
+      </c>
+      <c r="C3" s="55" t="s">
+        <v>955</v>
       </c>
       <c r="D3" s="19" t="s">
-        <v>596</v>
+        <v>996</v>
       </c>
       <c r="E3" s="20" t="s">
         <v>612</v>
@@ -19003,16 +21272,16 @@
         <v>9</v>
       </c>
       <c r="N3" s="30" t="s">
+        <v>998</v>
+      </c>
+      <c r="O3" s="29" t="s">
+        <v>1000</v>
+      </c>
+      <c r="P3" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="O3" s="29" t="s">
-        <v>599</v>
-      </c>
-      <c r="P3" s="30" t="s">
-        <v>603</v>
-      </c>
-      <c r="Q3" s="21" t="s">
-        <v>604</v>
+      <c r="Q3" s="29" t="s">
+        <v>997</v>
       </c>
       <c r="R3" s="30" t="s">
         <v>9</v>
@@ -19038,16 +21307,16 @@
       <c r="Y3" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="Z3" s="74" t="s">
+      <c r="Z3" s="30" t="s">
         <v>9</v>
       </c>
       <c r="AA3" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="AB3" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC3" s="73" t="s">
+      <c r="AB3" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC3" s="21" t="s">
         <v>9</v>
       </c>
       <c r="AD3" s="72" t="s">
@@ -19074,16 +21343,22 @@
       <c r="AK3" s="73" t="s">
         <v>9</v>
       </c>
+      <c r="AL3" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AM3" s="73" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="4" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:39" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="16">
         <v>4</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>597</v>
-      </c>
-      <c r="C4" s="18" t="s">
-        <v>582</v>
+        <v>1001</v>
+      </c>
+      <c r="C4" s="56" t="s">
+        <v>958</v>
       </c>
       <c r="D4" s="19" t="s">
         <v>596</v>
@@ -19116,16 +21391,16 @@
         <v>9</v>
       </c>
       <c r="N4" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="O4" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="P4" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="O4" s="29" t="s">
-        <v>600</v>
-      </c>
-      <c r="P4" s="30" t="s">
-        <v>603</v>
-      </c>
-      <c r="Q4" s="21" t="s">
-        <v>604</v>
+      <c r="Q4" s="29" t="s">
+        <v>1003</v>
       </c>
       <c r="R4" s="30" t="s">
         <v>9</v>
@@ -19151,16 +21426,16 @@
       <c r="Y4" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="Z4" s="74" t="s">
+      <c r="Z4" s="30" t="s">
         <v>9</v>
       </c>
       <c r="AA4" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="AB4" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC4" s="73" t="s">
+      <c r="AB4" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC4" s="21" t="s">
         <v>9</v>
       </c>
       <c r="AD4" s="72" t="s">
@@ -19187,19 +21462,25 @@
       <c r="AK4" s="73" t="s">
         <v>9</v>
       </c>
+      <c r="AL4" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AM4" s="73" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="5" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:39" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="16">
         <v>5</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>594</v>
-      </c>
-      <c r="C5" s="18" t="s">
-        <v>585</v>
+        <v>1002</v>
+      </c>
+      <c r="C5" s="56" t="s">
+        <v>985</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>613</v>
+        <v>596</v>
       </c>
       <c r="E5" s="20" t="s">
         <v>612</v>
@@ -19229,16 +21510,16 @@
         <v>9</v>
       </c>
       <c r="N5" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="O5" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="P5" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="O5" s="29" t="s">
-        <v>601</v>
-      </c>
-      <c r="P5" s="30" t="s">
-        <v>603</v>
-      </c>
-      <c r="Q5" s="21" t="s">
-        <v>604</v>
+      <c r="Q5" s="29" t="s">
+        <v>1004</v>
       </c>
       <c r="R5" s="30" t="s">
         <v>9</v>
@@ -19264,16 +21545,16 @@
       <c r="Y5" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="Z5" s="74" t="s">
+      <c r="Z5" s="30" t="s">
         <v>9</v>
       </c>
       <c r="AA5" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="AB5" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC5" s="73" t="s">
+      <c r="AB5" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC5" s="21" t="s">
         <v>9</v>
       </c>
       <c r="AD5" s="72" t="s">
@@ -19300,19 +21581,25 @@
       <c r="AK5" s="73" t="s">
         <v>9</v>
       </c>
+      <c r="AL5" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AM5" s="73" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="6" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:39" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="16">
         <v>6</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>613</v>
+        <v>596</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>612</v>
@@ -19342,23 +21629,23 @@
         <v>9</v>
       </c>
       <c r="N6" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="O6" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="P6" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="O6" s="29" t="s">
-        <v>602</v>
-      </c>
-      <c r="P6" s="30" t="s">
+      <c r="Q6" s="29" t="s">
+        <v>599</v>
+      </c>
+      <c r="R6" s="30" t="s">
         <v>603</v>
       </c>
-      <c r="Q6" s="21" t="s">
+      <c r="S6" s="21" t="s">
         <v>604</v>
       </c>
-      <c r="R6" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="S6" s="21" t="s">
-        <v>9</v>
-      </c>
       <c r="T6" s="30" t="s">
         <v>9</v>
       </c>
@@ -19377,16 +21664,16 @@
       <c r="Y6" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="Z6" s="74" t="s">
+      <c r="Z6" s="30" t="s">
         <v>9</v>
       </c>
       <c r="AA6" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="AB6" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC6" s="73" t="s">
+      <c r="AB6" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC6" s="21" t="s">
         <v>9</v>
       </c>
       <c r="AD6" s="72" t="s">
@@ -19413,19 +21700,25 @@
       <c r="AK6" s="73" t="s">
         <v>9</v>
       </c>
+      <c r="AL6" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AM6" s="73" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="7" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:39" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="16">
         <v>7</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>606</v>
+        <v>582</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>613</v>
+        <v>596</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>612</v>
@@ -19455,28 +21748,28 @@
         <v>9</v>
       </c>
       <c r="N7" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="O7" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="P7" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="O7" s="29" t="s">
-        <v>609</v>
-      </c>
-      <c r="P7" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q7" s="21" t="s">
-        <v>9</v>
+      <c r="Q7" s="29" t="s">
+        <v>600</v>
       </c>
       <c r="R7" s="30" t="s">
-        <v>9</v>
+        <v>603</v>
       </c>
       <c r="S7" s="21" t="s">
-        <v>9</v>
+        <v>604</v>
       </c>
       <c r="T7" s="30" t="s">
-        <v>610</v>
+        <v>9</v>
       </c>
       <c r="U7" s="21" t="s">
-        <v>611</v>
+        <v>9</v>
       </c>
       <c r="V7" s="30" t="s">
         <v>9</v>
@@ -19490,16 +21783,16 @@
       <c r="Y7" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="Z7" s="74" t="s">
+      <c r="Z7" s="30" t="s">
         <v>9</v>
       </c>
       <c r="AA7" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="AB7" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC7" s="73" t="s">
+      <c r="AB7" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC7" s="21" t="s">
         <v>9</v>
       </c>
       <c r="AD7" s="72" t="s">
@@ -19526,28 +21819,34 @@
       <c r="AK7" s="73" t="s">
         <v>9</v>
       </c>
+      <c r="AL7" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AM7" s="73" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="8" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:39" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="16">
         <v>8</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>220</v>
+        <v>594</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>148</v>
+        <v>585</v>
       </c>
       <c r="D8" s="19" t="s">
-        <v>596</v>
+        <v>613</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>597</v>
+        <v>612</v>
       </c>
       <c r="F8" s="19" t="s">
-        <v>596</v>
+        <v>9</v>
       </c>
       <c r="G8" s="20" t="s">
-        <v>605</v>
+        <v>9</v>
       </c>
       <c r="H8" s="19" t="s">
         <v>9</v>
@@ -19568,22 +21867,22 @@
         <v>9</v>
       </c>
       <c r="N8" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="O8" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="P8" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="O8" s="29" t="s">
-        <v>293</v>
-      </c>
-      <c r="P8" s="30" t="s">
-        <v>197</v>
-      </c>
-      <c r="Q8" s="21" t="s">
-        <v>618</v>
+      <c r="Q8" s="29" t="s">
+        <v>601</v>
       </c>
       <c r="R8" s="30" t="s">
-        <v>542</v>
+        <v>603</v>
       </c>
       <c r="S8" s="21" t="s">
-        <v>214</v>
+        <v>604</v>
       </c>
       <c r="T8" s="30" t="s">
         <v>9</v>
@@ -19603,16 +21902,16 @@
       <c r="Y8" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="Z8" s="74" t="s">
+      <c r="Z8" s="30" t="s">
         <v>9</v>
       </c>
       <c r="AA8" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="AB8" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC8" s="73" t="s">
+      <c r="AB8" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC8" s="21" t="s">
         <v>9</v>
       </c>
       <c r="AD8" s="72" t="s">
@@ -19639,28 +21938,34 @@
       <c r="AK8" s="73" t="s">
         <v>9</v>
       </c>
+      <c r="AL8" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AM8" s="73" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="9" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:39" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="16">
         <v>9</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>221</v>
+        <v>595</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>148</v>
+        <v>585</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>596</v>
+        <v>613</v>
       </c>
       <c r="E9" s="20" t="s">
-        <v>597</v>
+        <v>612</v>
       </c>
       <c r="F9" s="19" t="s">
-        <v>596</v>
+        <v>9</v>
       </c>
       <c r="G9" s="20" t="s">
-        <v>605</v>
+        <v>9</v>
       </c>
       <c r="H9" s="19" t="s">
         <v>9</v>
@@ -19681,22 +21986,22 @@
         <v>9</v>
       </c>
       <c r="N9" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="O9" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="P9" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="O9" s="29" t="s">
-        <v>294</v>
-      </c>
-      <c r="P9" s="30" t="s">
-        <v>197</v>
-      </c>
-      <c r="Q9" s="21" t="s">
-        <v>618</v>
+      <c r="Q9" s="29" t="s">
+        <v>602</v>
       </c>
       <c r="R9" s="30" t="s">
-        <v>542</v>
+        <v>603</v>
       </c>
       <c r="S9" s="21" t="s">
-        <v>215</v>
+        <v>604</v>
       </c>
       <c r="T9" s="30" t="s">
         <v>9</v>
@@ -19716,16 +22021,16 @@
       <c r="Y9" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="Z9" s="74" t="s">
+      <c r="Z9" s="30" t="s">
         <v>9</v>
       </c>
       <c r="AA9" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="AB9" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC9" s="73" t="s">
+      <c r="AB9" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC9" s="21" t="s">
         <v>9</v>
       </c>
       <c r="AD9" s="72" t="s">
@@ -19752,28 +22057,34 @@
       <c r="AK9" s="73" t="s">
         <v>9</v>
       </c>
+      <c r="AL9" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AM9" s="73" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="10" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:39" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="16">
         <v>10</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>222</v>
+        <v>605</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>148</v>
+        <v>606</v>
       </c>
       <c r="D10" s="19" t="s">
-        <v>596</v>
+        <v>613</v>
       </c>
       <c r="E10" s="20" t="s">
-        <v>597</v>
+        <v>612</v>
       </c>
       <c r="F10" s="19" t="s">
-        <v>596</v>
+        <v>9</v>
       </c>
       <c r="G10" s="20" t="s">
-        <v>605</v>
+        <v>9</v>
       </c>
       <c r="H10" s="19" t="s">
         <v>9</v>
@@ -19794,22 +22105,22 @@
         <v>9</v>
       </c>
       <c r="N10" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="O10" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="P10" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="O10" s="29" t="s">
-        <v>295</v>
-      </c>
-      <c r="P10" s="30" t="s">
-        <v>197</v>
-      </c>
-      <c r="Q10" s="21" t="s">
-        <v>618</v>
+      <c r="Q10" s="29" t="s">
+        <v>609</v>
       </c>
       <c r="R10" s="30" t="s">
-        <v>542</v>
+        <v>9</v>
       </c>
       <c r="S10" s="21" t="s">
-        <v>216</v>
+        <v>9</v>
       </c>
       <c r="T10" s="30" t="s">
         <v>9</v>
@@ -19818,10 +22129,10 @@
         <v>9</v>
       </c>
       <c r="V10" s="30" t="s">
-        <v>9</v>
+        <v>610</v>
       </c>
       <c r="W10" s="21" t="s">
-        <v>9</v>
+        <v>611</v>
       </c>
       <c r="X10" s="30" t="s">
         <v>9</v>
@@ -19829,16 +22140,16 @@
       <c r="Y10" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="Z10" s="74" t="s">
+      <c r="Z10" s="30" t="s">
         <v>9</v>
       </c>
       <c r="AA10" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="AB10" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC10" s="73" t="s">
+      <c r="AB10" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC10" s="21" t="s">
         <v>9</v>
       </c>
       <c r="AD10" s="72" t="s">
@@ -19865,13 +22176,19 @@
       <c r="AK10" s="73" t="s">
         <v>9</v>
       </c>
+      <c r="AL10" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AM10" s="73" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="11" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:39" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="16">
         <v>11</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C11" s="18" t="s">
         <v>148</v>
@@ -19907,28 +22224,28 @@
         <v>9</v>
       </c>
       <c r="N11" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="O11" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="P11" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="O11" s="29" t="s">
-        <v>296</v>
-      </c>
-      <c r="P11" s="30" t="s">
+      <c r="Q11" s="29" t="s">
+        <v>293</v>
+      </c>
+      <c r="R11" s="30" t="s">
         <v>197</v>
       </c>
-      <c r="Q11" s="21" t="s">
+      <c r="S11" s="21" t="s">
         <v>618</v>
       </c>
-      <c r="R11" s="30" t="s">
+      <c r="T11" s="30" t="s">
         <v>542</v>
       </c>
-      <c r="S11" s="21" t="s">
-        <v>217</v>
-      </c>
-      <c r="T11" s="30" t="s">
-        <v>9</v>
-      </c>
       <c r="U11" s="21" t="s">
-        <v>9</v>
+        <v>214</v>
       </c>
       <c r="V11" s="30" t="s">
         <v>9</v>
@@ -19942,16 +22259,16 @@
       <c r="Y11" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="Z11" s="74" t="s">
+      <c r="Z11" s="30" t="s">
         <v>9</v>
       </c>
       <c r="AA11" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="AB11" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC11" s="73" t="s">
+      <c r="AB11" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC11" s="21" t="s">
         <v>9</v>
       </c>
       <c r="AD11" s="72" t="s">
@@ -19978,13 +22295,19 @@
       <c r="AK11" s="73" t="s">
         <v>9</v>
       </c>
+      <c r="AL11" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AM11" s="73" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="12" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:39" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="16">
         <v>12</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>195</v>
+        <v>221</v>
       </c>
       <c r="C12" s="18" t="s">
         <v>148</v>
@@ -20020,28 +22343,28 @@
         <v>9</v>
       </c>
       <c r="N12" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="O12" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="P12" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="O12" s="29" t="s">
-        <v>297</v>
-      </c>
-      <c r="P12" s="30" t="s">
+      <c r="Q12" s="29" t="s">
+        <v>294</v>
+      </c>
+      <c r="R12" s="30" t="s">
         <v>197</v>
       </c>
-      <c r="Q12" s="21" t="s">
+      <c r="S12" s="21" t="s">
         <v>618</v>
       </c>
-      <c r="R12" s="30" t="s">
+      <c r="T12" s="30" t="s">
         <v>542</v>
       </c>
-      <c r="S12" s="21" t="s">
-        <v>218</v>
-      </c>
-      <c r="T12" s="30" t="s">
-        <v>9</v>
-      </c>
       <c r="U12" s="21" t="s">
-        <v>9</v>
+        <v>215</v>
       </c>
       <c r="V12" s="30" t="s">
         <v>9</v>
@@ -20055,16 +22378,16 @@
       <c r="Y12" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="Z12" s="74" t="s">
+      <c r="Z12" s="30" t="s">
         <v>9</v>
       </c>
       <c r="AA12" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="AB12" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC12" s="73" t="s">
+      <c r="AB12" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC12" s="21" t="s">
         <v>9</v>
       </c>
       <c r="AD12" s="72" t="s">
@@ -20091,13 +22414,19 @@
       <c r="AK12" s="73" t="s">
         <v>9</v>
       </c>
+      <c r="AL12" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AM12" s="73" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="13" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:39" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="16">
         <v>13</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>196</v>
+        <v>222</v>
       </c>
       <c r="C13" s="18" t="s">
         <v>148</v>
@@ -20133,28 +22462,28 @@
         <v>9</v>
       </c>
       <c r="N13" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="O13" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="P13" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="O13" s="29" t="s">
-        <v>298</v>
-      </c>
-      <c r="P13" s="30" t="s">
+      <c r="Q13" s="29" t="s">
+        <v>295</v>
+      </c>
+      <c r="R13" s="30" t="s">
         <v>197</v>
       </c>
-      <c r="Q13" s="21" t="s">
+      <c r="S13" s="21" t="s">
         <v>618</v>
       </c>
-      <c r="R13" s="30" t="s">
+      <c r="T13" s="30" t="s">
         <v>542</v>
       </c>
-      <c r="S13" s="21" t="s">
-        <v>219</v>
-      </c>
-      <c r="T13" s="30" t="s">
-        <v>9</v>
-      </c>
       <c r="U13" s="21" t="s">
-        <v>9</v>
+        <v>216</v>
       </c>
       <c r="V13" s="30" t="s">
         <v>9</v>
@@ -20168,16 +22497,16 @@
       <c r="Y13" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="Z13" s="74" t="s">
+      <c r="Z13" s="30" t="s">
         <v>9</v>
       </c>
       <c r="AA13" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="AB13" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC13" s="73" t="s">
+      <c r="AB13" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC13" s="21" t="s">
         <v>9</v>
       </c>
       <c r="AD13" s="72" t="s">
@@ -20204,16 +22533,22 @@
       <c r="AK13" s="73" t="s">
         <v>9</v>
       </c>
+      <c r="AL13" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AM13" s="73" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:39" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="16">
         <v>14</v>
       </c>
-      <c r="B14" s="33" t="s">
-        <v>199</v>
+      <c r="B14" s="17" t="s">
+        <v>223</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="D14" s="19" t="s">
         <v>596</v>
@@ -20246,28 +22581,28 @@
         <v>9</v>
       </c>
       <c r="N14" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="O14" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="P14" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="O14" s="29" t="s">
-        <v>201</v>
-      </c>
-      <c r="P14" s="30" t="s">
+      <c r="Q14" s="29" t="s">
+        <v>296</v>
+      </c>
+      <c r="R14" s="30" t="s">
         <v>197</v>
       </c>
-      <c r="Q14" s="21" t="s">
-        <v>619</v>
-      </c>
-      <c r="R14" s="30" t="s">
+      <c r="S14" s="21" t="s">
+        <v>618</v>
+      </c>
+      <c r="T14" s="30" t="s">
         <v>542</v>
       </c>
-      <c r="S14" s="21" t="s">
-        <v>206</v>
-      </c>
-      <c r="T14" s="30" t="s">
-        <v>9</v>
-      </c>
       <c r="U14" s="21" t="s">
-        <v>9</v>
+        <v>217</v>
       </c>
       <c r="V14" s="30" t="s">
         <v>9</v>
@@ -20281,16 +22616,16 @@
       <c r="Y14" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="Z14" s="74" t="s">
+      <c r="Z14" s="30" t="s">
         <v>9</v>
       </c>
       <c r="AA14" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="AB14" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC14" s="73" t="s">
+      <c r="AB14" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC14" s="21" t="s">
         <v>9</v>
       </c>
       <c r="AD14" s="72" t="s">
@@ -20317,16 +22652,22 @@
       <c r="AK14" s="73" t="s">
         <v>9</v>
       </c>
+      <c r="AL14" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AM14" s="73" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="15" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:39" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="16">
         <v>15</v>
       </c>
-      <c r="B15" s="33" t="s">
-        <v>198</v>
+      <c r="B15" s="17" t="s">
+        <v>195</v>
       </c>
       <c r="C15" s="18" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="D15" s="19" t="s">
         <v>596</v>
@@ -20359,28 +22700,28 @@
         <v>9</v>
       </c>
       <c r="N15" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="O15" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="P15" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="O15" s="29" t="s">
-        <v>202</v>
-      </c>
-      <c r="P15" s="30" t="s">
+      <c r="Q15" s="29" t="s">
+        <v>297</v>
+      </c>
+      <c r="R15" s="30" t="s">
         <v>197</v>
       </c>
-      <c r="Q15" s="21" t="s">
-        <v>619</v>
-      </c>
-      <c r="R15" s="30" t="s">
+      <c r="S15" s="21" t="s">
+        <v>618</v>
+      </c>
+      <c r="T15" s="30" t="s">
         <v>542</v>
       </c>
-      <c r="S15" s="21" t="s">
-        <v>207</v>
-      </c>
-      <c r="T15" s="30" t="s">
-        <v>9</v>
-      </c>
       <c r="U15" s="21" t="s">
-        <v>9</v>
+        <v>218</v>
       </c>
       <c r="V15" s="30" t="s">
         <v>9</v>
@@ -20394,16 +22735,16 @@
       <c r="Y15" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="Z15" s="74" t="s">
+      <c r="Z15" s="30" t="s">
         <v>9</v>
       </c>
       <c r="AA15" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="AB15" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC15" s="73" t="s">
+      <c r="AB15" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC15" s="21" t="s">
         <v>9</v>
       </c>
       <c r="AD15" s="72" t="s">
@@ -20430,16 +22771,22 @@
       <c r="AK15" s="73" t="s">
         <v>9</v>
       </c>
+      <c r="AL15" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AM15" s="73" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="16" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:39" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="16">
         <v>16</v>
       </c>
-      <c r="B16" s="33" t="s">
-        <v>200</v>
+      <c r="B16" s="17" t="s">
+        <v>196</v>
       </c>
       <c r="C16" s="18" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="D16" s="19" t="s">
         <v>596</v>
@@ -20472,28 +22819,28 @@
         <v>9</v>
       </c>
       <c r="N16" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="O16" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="P16" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="O16" s="29" t="s">
-        <v>203</v>
-      </c>
-      <c r="P16" s="30" t="s">
+      <c r="Q16" s="29" t="s">
+        <v>298</v>
+      </c>
+      <c r="R16" s="30" t="s">
         <v>197</v>
       </c>
-      <c r="Q16" s="21" t="s">
-        <v>619</v>
-      </c>
-      <c r="R16" s="30" t="s">
+      <c r="S16" s="21" t="s">
+        <v>618</v>
+      </c>
+      <c r="T16" s="30" t="s">
         <v>542</v>
       </c>
-      <c r="S16" s="21" t="s">
-        <v>208</v>
-      </c>
-      <c r="T16" s="30" t="s">
-        <v>9</v>
-      </c>
       <c r="U16" s="21" t="s">
-        <v>9</v>
+        <v>219</v>
       </c>
       <c r="V16" s="30" t="s">
         <v>9</v>
@@ -20507,16 +22854,16 @@
       <c r="Y16" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="Z16" s="74" t="s">
+      <c r="Z16" s="30" t="s">
         <v>9</v>
       </c>
       <c r="AA16" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="AB16" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC16" s="73" t="s">
+      <c r="AB16" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC16" s="21" t="s">
         <v>9</v>
       </c>
       <c r="AD16" s="72" t="s">
@@ -20543,13 +22890,19 @@
       <c r="AK16" s="73" t="s">
         <v>9</v>
       </c>
+      <c r="AL16" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AM16" s="73" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="17" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:39" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="16">
         <v>17</v>
       </c>
       <c r="B17" s="33" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="C17" s="18" t="s">
         <v>141</v>
@@ -20585,28 +22938,28 @@
         <v>9</v>
       </c>
       <c r="N17" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="O17" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="P17" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="O17" s="29" t="s">
-        <v>205</v>
-      </c>
-      <c r="P17" s="30" t="s">
+      <c r="Q17" s="29" t="s">
+        <v>201</v>
+      </c>
+      <c r="R17" s="30" t="s">
         <v>197</v>
       </c>
-      <c r="Q17" s="21" t="s">
+      <c r="S17" s="21" t="s">
         <v>619</v>
       </c>
-      <c r="R17" s="30" t="s">
+      <c r="T17" s="30" t="s">
         <v>542</v>
       </c>
-      <c r="S17" s="21" t="s">
-        <v>209</v>
-      </c>
-      <c r="T17" s="30" t="s">
-        <v>9</v>
-      </c>
       <c r="U17" s="21" t="s">
-        <v>9</v>
+        <v>206</v>
       </c>
       <c r="V17" s="30" t="s">
         <v>9</v>
@@ -20620,16 +22973,16 @@
       <c r="Y17" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="Z17" s="74" t="s">
+      <c r="Z17" s="30" t="s">
         <v>9</v>
       </c>
       <c r="AA17" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="AB17" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC17" s="73" t="s">
+      <c r="AB17" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC17" s="21" t="s">
         <v>9</v>
       </c>
       <c r="AD17" s="72" t="s">
@@ -20656,16 +23009,22 @@
       <c r="AK17" s="73" t="s">
         <v>9</v>
       </c>
+      <c r="AL17" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AM17" s="73" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="18" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:39" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="16">
         <v>18</v>
       </c>
-      <c r="B18" s="34" t="s">
-        <v>237</v>
-      </c>
-      <c r="C18" s="32" t="s">
-        <v>171</v>
+      <c r="B18" s="33" t="s">
+        <v>198</v>
+      </c>
+      <c r="C18" s="18" t="s">
+        <v>141</v>
       </c>
       <c r="D18" s="19" t="s">
         <v>596</v>
@@ -20698,28 +23057,28 @@
         <v>9</v>
       </c>
       <c r="N18" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="O18" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="P18" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="O18" s="29" t="s">
-        <v>224</v>
-      </c>
-      <c r="P18" s="30" t="s">
+      <c r="Q18" s="29" t="s">
+        <v>202</v>
+      </c>
+      <c r="R18" s="30" t="s">
         <v>197</v>
       </c>
-      <c r="Q18" s="21" t="s">
-        <v>620</v>
-      </c>
-      <c r="R18" s="30" t="s">
+      <c r="S18" s="21" t="s">
+        <v>619</v>
+      </c>
+      <c r="T18" s="30" t="s">
         <v>542</v>
       </c>
-      <c r="S18" s="21" t="s">
-        <v>212</v>
-      </c>
-      <c r="T18" s="30" t="s">
-        <v>9</v>
-      </c>
       <c r="U18" s="21" t="s">
-        <v>9</v>
+        <v>207</v>
       </c>
       <c r="V18" s="30" t="s">
         <v>9</v>
@@ -20733,16 +23092,16 @@
       <c r="Y18" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="Z18" s="74" t="s">
+      <c r="Z18" s="30" t="s">
         <v>9</v>
       </c>
       <c r="AA18" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="AB18" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC18" s="73" t="s">
+      <c r="AB18" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC18" s="21" t="s">
         <v>9</v>
       </c>
       <c r="AD18" s="72" t="s">
@@ -20769,16 +23128,22 @@
       <c r="AK18" s="73" t="s">
         <v>9</v>
       </c>
+      <c r="AL18" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AM18" s="73" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="19" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:39" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="16">
         <v>19</v>
       </c>
-      <c r="B19" s="34" t="s">
-        <v>238</v>
-      </c>
-      <c r="C19" s="32" t="s">
-        <v>171</v>
+      <c r="B19" s="33" t="s">
+        <v>200</v>
+      </c>
+      <c r="C19" s="18" t="s">
+        <v>141</v>
       </c>
       <c r="D19" s="19" t="s">
         <v>596</v>
@@ -20811,28 +23176,28 @@
         <v>9</v>
       </c>
       <c r="N19" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="O19" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="P19" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="O19" s="29" t="s">
-        <v>210</v>
-      </c>
-      <c r="P19" s="30" t="s">
+      <c r="Q19" s="29" t="s">
+        <v>203</v>
+      </c>
+      <c r="R19" s="30" t="s">
         <v>197</v>
       </c>
-      <c r="Q19" s="21" t="s">
-        <v>621</v>
-      </c>
-      <c r="R19" s="30" t="s">
+      <c r="S19" s="21" t="s">
+        <v>619</v>
+      </c>
+      <c r="T19" s="30" t="s">
         <v>542</v>
       </c>
-      <c r="S19" s="21" t="s">
-        <v>213</v>
-      </c>
-      <c r="T19" s="30" t="s">
-        <v>9</v>
-      </c>
       <c r="U19" s="21" t="s">
-        <v>9</v>
+        <v>208</v>
       </c>
       <c r="V19" s="30" t="s">
         <v>9</v>
@@ -20846,16 +23211,16 @@
       <c r="Y19" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="Z19" s="74" t="s">
+      <c r="Z19" s="30" t="s">
         <v>9</v>
       </c>
       <c r="AA19" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="AB19" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC19" s="73" t="s">
+      <c r="AB19" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC19" s="21" t="s">
         <v>9</v>
       </c>
       <c r="AD19" s="72" t="s">
@@ -20882,16 +23247,22 @@
       <c r="AK19" s="73" t="s">
         <v>9</v>
       </c>
+      <c r="AL19" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AM19" s="73" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="20" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:39" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="16">
         <v>20</v>
       </c>
-      <c r="B20" s="34" t="s">
-        <v>239</v>
-      </c>
-      <c r="C20" s="32" t="s">
-        <v>171</v>
+      <c r="B20" s="33" t="s">
+        <v>204</v>
+      </c>
+      <c r="C20" s="18" t="s">
+        <v>141</v>
       </c>
       <c r="D20" s="19" t="s">
         <v>596</v>
@@ -20924,28 +23295,28 @@
         <v>9</v>
       </c>
       <c r="N20" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="O20" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="P20" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="O20" s="29" t="s">
-        <v>211</v>
-      </c>
-      <c r="P20" s="30" t="s">
+      <c r="Q20" s="29" t="s">
+        <v>205</v>
+      </c>
+      <c r="R20" s="30" t="s">
         <v>197</v>
       </c>
-      <c r="Q20" s="21" t="s">
-        <v>622</v>
-      </c>
-      <c r="R20" s="30" t="s">
+      <c r="S20" s="21" t="s">
+        <v>619</v>
+      </c>
+      <c r="T20" s="30" t="s">
         <v>542</v>
       </c>
-      <c r="S20" s="21" t="s">
-        <v>228</v>
-      </c>
-      <c r="T20" s="30" t="s">
-        <v>9</v>
-      </c>
       <c r="U20" s="21" t="s">
-        <v>9</v>
+        <v>209</v>
       </c>
       <c r="V20" s="30" t="s">
         <v>9</v>
@@ -20959,16 +23330,16 @@
       <c r="Y20" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="Z20" s="74" t="s">
+      <c r="Z20" s="30" t="s">
         <v>9</v>
       </c>
       <c r="AA20" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="AB20" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC20" s="73" t="s">
+      <c r="AB20" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC20" s="21" t="s">
         <v>9</v>
       </c>
       <c r="AD20" s="72" t="s">
@@ -20995,13 +23366,19 @@
       <c r="AK20" s="73" t="s">
         <v>9</v>
       </c>
+      <c r="AL20" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AM20" s="73" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="21" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:39" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="16">
         <v>21</v>
       </c>
       <c r="B21" s="34" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="C21" s="32" t="s">
         <v>171</v>
@@ -21037,28 +23414,28 @@
         <v>9</v>
       </c>
       <c r="N21" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="O21" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="P21" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="O21" s="29" t="s">
-        <v>225</v>
-      </c>
-      <c r="P21" s="30" t="s">
+      <c r="Q21" s="29" t="s">
+        <v>224</v>
+      </c>
+      <c r="R21" s="30" t="s">
         <v>197</v>
       </c>
-      <c r="Q21" s="21" t="s">
-        <v>623</v>
-      </c>
-      <c r="R21" s="30" t="s">
+      <c r="S21" s="21" t="s">
+        <v>620</v>
+      </c>
+      <c r="T21" s="30" t="s">
         <v>542</v>
       </c>
-      <c r="S21" s="21" t="s">
-        <v>229</v>
-      </c>
-      <c r="T21" s="30" t="s">
-        <v>9</v>
-      </c>
       <c r="U21" s="21" t="s">
-        <v>9</v>
+        <v>212</v>
       </c>
       <c r="V21" s="30" t="s">
         <v>9</v>
@@ -21072,16 +23449,16 @@
       <c r="Y21" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="Z21" s="74" t="s">
+      <c r="Z21" s="30" t="s">
         <v>9</v>
       </c>
       <c r="AA21" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="AB21" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC21" s="73" t="s">
+      <c r="AB21" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC21" s="21" t="s">
         <v>9</v>
       </c>
       <c r="AD21" s="72" t="s">
@@ -21108,13 +23485,19 @@
       <c r="AK21" s="73" t="s">
         <v>9</v>
       </c>
+      <c r="AL21" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AM21" s="73" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="22" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:39" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="16">
         <v>22</v>
       </c>
       <c r="B22" s="34" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="C22" s="32" t="s">
         <v>171</v>
@@ -21150,28 +23533,28 @@
         <v>9</v>
       </c>
       <c r="N22" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="O22" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="P22" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="O22" s="29" t="s">
-        <v>226</v>
-      </c>
-      <c r="P22" s="30" t="s">
+      <c r="Q22" s="29" t="s">
+        <v>210</v>
+      </c>
+      <c r="R22" s="30" t="s">
         <v>197</v>
       </c>
-      <c r="Q22" s="21" t="s">
-        <v>624</v>
-      </c>
-      <c r="R22" s="30" t="s">
+      <c r="S22" s="21" t="s">
+        <v>621</v>
+      </c>
+      <c r="T22" s="30" t="s">
         <v>542</v>
       </c>
-      <c r="S22" s="21" t="s">
-        <v>230</v>
-      </c>
-      <c r="T22" s="30" t="s">
-        <v>9</v>
-      </c>
       <c r="U22" s="21" t="s">
-        <v>9</v>
+        <v>213</v>
       </c>
       <c r="V22" s="30" t="s">
         <v>9</v>
@@ -21185,16 +23568,16 @@
       <c r="Y22" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="Z22" s="74" t="s">
+      <c r="Z22" s="30" t="s">
         <v>9</v>
       </c>
       <c r="AA22" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="AB22" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC22" s="73" t="s">
+      <c r="AB22" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC22" s="21" t="s">
         <v>9</v>
       </c>
       <c r="AD22" s="72" t="s">
@@ -21221,13 +23604,19 @@
       <c r="AK22" s="73" t="s">
         <v>9</v>
       </c>
+      <c r="AL22" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AM22" s="73" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="23" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:39" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="16">
         <v>23</v>
       </c>
       <c r="B23" s="34" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="C23" s="32" t="s">
         <v>171</v>
@@ -21263,28 +23652,28 @@
         <v>9</v>
       </c>
       <c r="N23" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="O23" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="P23" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="O23" s="29" t="s">
-        <v>227</v>
-      </c>
-      <c r="P23" s="30" t="s">
+      <c r="Q23" s="29" t="s">
+        <v>211</v>
+      </c>
+      <c r="R23" s="30" t="s">
         <v>197</v>
       </c>
-      <c r="Q23" s="21" t="s">
-        <v>625</v>
-      </c>
-      <c r="R23" s="30" t="s">
+      <c r="S23" s="21" t="s">
+        <v>622</v>
+      </c>
+      <c r="T23" s="30" t="s">
         <v>542</v>
       </c>
-      <c r="S23" s="21" t="s">
-        <v>231</v>
-      </c>
-      <c r="T23" s="30" t="s">
-        <v>9</v>
-      </c>
       <c r="U23" s="21" t="s">
-        <v>9</v>
+        <v>228</v>
       </c>
       <c r="V23" s="30" t="s">
         <v>9</v>
@@ -21298,16 +23687,16 @@
       <c r="Y23" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="Z23" s="74" t="s">
+      <c r="Z23" s="30" t="s">
         <v>9</v>
       </c>
       <c r="AA23" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="AB23" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC23" s="73" t="s">
+      <c r="AB23" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC23" s="21" t="s">
         <v>9</v>
       </c>
       <c r="AD23" s="72" t="s">
@@ -21334,28 +23723,34 @@
       <c r="AK23" s="73" t="s">
         <v>9</v>
       </c>
+      <c r="AL23" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AM23" s="73" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="24" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:39" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="16">
         <v>24</v>
       </c>
-      <c r="B24" s="35" t="s">
-        <v>243</v>
-      </c>
-      <c r="C24" s="18" t="s">
-        <v>545</v>
+      <c r="B24" s="34" t="s">
+        <v>240</v>
+      </c>
+      <c r="C24" s="32" t="s">
+        <v>171</v>
       </c>
       <c r="D24" s="19" t="s">
-        <v>9</v>
+        <v>596</v>
       </c>
       <c r="E24" s="20" t="s">
-        <v>9</v>
+        <v>597</v>
       </c>
       <c r="F24" s="19" t="s">
-        <v>9</v>
+        <v>596</v>
       </c>
       <c r="G24" s="20" t="s">
-        <v>9</v>
+        <v>605</v>
       </c>
       <c r="H24" s="19" t="s">
         <v>9</v>
@@ -21376,28 +23771,28 @@
         <v>9</v>
       </c>
       <c r="N24" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="O24" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="P24" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="O24" s="36" t="s">
-        <v>235</v>
-      </c>
-      <c r="P24" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q24" s="21" t="s">
-        <v>9</v>
+      <c r="Q24" s="29" t="s">
+        <v>225</v>
       </c>
       <c r="R24" s="30" t="s">
-        <v>9</v>
+        <v>197</v>
       </c>
       <c r="S24" s="21" t="s">
-        <v>9</v>
+        <v>623</v>
       </c>
       <c r="T24" s="30" t="s">
-        <v>9</v>
+        <v>542</v>
       </c>
       <c r="U24" s="21" t="s">
-        <v>9</v>
+        <v>229</v>
       </c>
       <c r="V24" s="30" t="s">
         <v>9</v>
@@ -21411,16 +23806,16 @@
       <c r="Y24" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="Z24" s="74" t="s">
+      <c r="Z24" s="30" t="s">
         <v>9</v>
       </c>
       <c r="AA24" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="AB24" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC24" s="73" t="s">
+      <c r="AB24" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC24" s="21" t="s">
         <v>9</v>
       </c>
       <c r="AD24" s="72" t="s">
@@ -21447,28 +23842,34 @@
       <c r="AK24" s="73" t="s">
         <v>9</v>
       </c>
+      <c r="AL24" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AM24" s="73" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="25" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:39" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="16">
         <v>25</v>
       </c>
-      <c r="B25" s="35" t="s">
-        <v>244</v>
-      </c>
-      <c r="C25" s="18" t="s">
-        <v>545</v>
+      <c r="B25" s="34" t="s">
+        <v>241</v>
+      </c>
+      <c r="C25" s="32" t="s">
+        <v>171</v>
       </c>
       <c r="D25" s="19" t="s">
-        <v>9</v>
+        <v>596</v>
       </c>
       <c r="E25" s="20" t="s">
-        <v>9</v>
+        <v>597</v>
       </c>
       <c r="F25" s="19" t="s">
-        <v>9</v>
+        <v>596</v>
       </c>
       <c r="G25" s="20" t="s">
-        <v>9</v>
+        <v>605</v>
       </c>
       <c r="H25" s="19" t="s">
         <v>9</v>
@@ -21489,28 +23890,28 @@
         <v>9</v>
       </c>
       <c r="N25" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="O25" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="P25" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="O25" s="36" t="s">
-        <v>236</v>
-      </c>
-      <c r="P25" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q25" s="21" t="s">
-        <v>9</v>
+      <c r="Q25" s="29" t="s">
+        <v>226</v>
       </c>
       <c r="R25" s="30" t="s">
-        <v>9</v>
+        <v>197</v>
       </c>
       <c r="S25" s="21" t="s">
-        <v>9</v>
+        <v>624</v>
       </c>
       <c r="T25" s="30" t="s">
-        <v>9</v>
+        <v>542</v>
       </c>
       <c r="U25" s="21" t="s">
-        <v>9</v>
+        <v>230</v>
       </c>
       <c r="V25" s="30" t="s">
         <v>9</v>
@@ -21524,16 +23925,16 @@
       <c r="Y25" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="Z25" s="74" t="s">
+      <c r="Z25" s="30" t="s">
         <v>9</v>
       </c>
       <c r="AA25" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="AB25" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC25" s="73" t="s">
+      <c r="AB25" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC25" s="21" t="s">
         <v>9</v>
       </c>
       <c r="AD25" s="72" t="s">
@@ -21560,28 +23961,34 @@
       <c r="AK25" s="73" t="s">
         <v>9</v>
       </c>
+      <c r="AL25" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AM25" s="73" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="26" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:39" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="16">
         <v>26</v>
       </c>
-      <c r="B26" s="35" t="s">
-        <v>232</v>
-      </c>
-      <c r="C26" s="18" t="s">
-        <v>545</v>
+      <c r="B26" s="34" t="s">
+        <v>242</v>
+      </c>
+      <c r="C26" s="32" t="s">
+        <v>171</v>
       </c>
       <c r="D26" s="19" t="s">
-        <v>9</v>
+        <v>596</v>
       </c>
       <c r="E26" s="20" t="s">
-        <v>9</v>
+        <v>597</v>
       </c>
       <c r="F26" s="19" t="s">
-        <v>9</v>
+        <v>596</v>
       </c>
       <c r="G26" s="20" t="s">
-        <v>9</v>
+        <v>605</v>
       </c>
       <c r="H26" s="19" t="s">
         <v>9</v>
@@ -21602,28 +24009,28 @@
         <v>9</v>
       </c>
       <c r="N26" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="O26" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="P26" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="O26" s="36" t="s">
-        <v>233</v>
-      </c>
-      <c r="P26" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q26" s="21" t="s">
-        <v>9</v>
+      <c r="Q26" s="29" t="s">
+        <v>227</v>
       </c>
       <c r="R26" s="30" t="s">
-        <v>9</v>
+        <v>197</v>
       </c>
       <c r="S26" s="21" t="s">
-        <v>9</v>
+        <v>625</v>
       </c>
       <c r="T26" s="30" t="s">
-        <v>9</v>
+        <v>542</v>
       </c>
       <c r="U26" s="21" t="s">
-        <v>9</v>
+        <v>231</v>
       </c>
       <c r="V26" s="30" t="s">
         <v>9</v>
@@ -21637,16 +24044,16 @@
       <c r="Y26" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="Z26" s="74" t="s">
+      <c r="Z26" s="30" t="s">
         <v>9</v>
       </c>
       <c r="AA26" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="AB26" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC26" s="73" t="s">
+      <c r="AB26" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC26" s="21" t="s">
         <v>9</v>
       </c>
       <c r="AD26" s="72" t="s">
@@ -21673,16 +24080,22 @@
       <c r="AK26" s="73" t="s">
         <v>9</v>
       </c>
+      <c r="AL26" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AM26" s="73" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="27" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:39" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="16">
         <v>27</v>
       </c>
       <c r="B27" s="35" t="s">
-        <v>546</v>
+        <v>243</v>
       </c>
       <c r="C27" s="18" t="s">
-        <v>249</v>
+        <v>545</v>
       </c>
       <c r="D27" s="19" t="s">
         <v>9</v>
@@ -21715,16 +24128,16 @@
         <v>9</v>
       </c>
       <c r="N27" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="O27" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="P27" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="O27" s="36" t="s">
-        <v>581</v>
-      </c>
-      <c r="P27" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q27" s="21" t="s">
-        <v>9</v>
+      <c r="Q27" s="36" t="s">
+        <v>235</v>
       </c>
       <c r="R27" s="30" t="s">
         <v>9</v>
@@ -21750,16 +24163,16 @@
       <c r="Y27" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="Z27" s="74" t="s">
+      <c r="Z27" s="30" t="s">
         <v>9</v>
       </c>
       <c r="AA27" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="AB27" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC27" s="73" t="s">
+      <c r="AB27" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC27" s="21" t="s">
         <v>9</v>
       </c>
       <c r="AD27" s="72" t="s">
@@ -21786,16 +24199,22 @@
       <c r="AK27" s="73" t="s">
         <v>9</v>
       </c>
+      <c r="AL27" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AM27" s="73" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="28" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:39" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="16">
         <v>28</v>
       </c>
       <c r="B28" s="35" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="C28" s="18" t="s">
-        <v>234</v>
+        <v>545</v>
       </c>
       <c r="D28" s="19" t="s">
         <v>9</v>
@@ -21828,16 +24247,16 @@
         <v>9</v>
       </c>
       <c r="N28" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="O28" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="P28" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="O28" s="36" t="s">
-        <v>254</v>
-      </c>
-      <c r="P28" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q28" s="21" t="s">
-        <v>9</v>
+      <c r="Q28" s="36" t="s">
+        <v>236</v>
       </c>
       <c r="R28" s="30" t="s">
         <v>9</v>
@@ -21863,16 +24282,16 @@
       <c r="Y28" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="Z28" s="74" t="s">
+      <c r="Z28" s="30" t="s">
         <v>9</v>
       </c>
       <c r="AA28" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="AB28" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC28" s="73" t="s">
+      <c r="AB28" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC28" s="21" t="s">
         <v>9</v>
       </c>
       <c r="AD28" s="72" t="s">
@@ -21899,16 +24318,22 @@
       <c r="AK28" s="73" t="s">
         <v>9</v>
       </c>
+      <c r="AL28" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AM28" s="73" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="29" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:39" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="16">
         <v>29</v>
       </c>
       <c r="B29" s="35" t="s">
-        <v>250</v>
+        <v>232</v>
       </c>
       <c r="C29" s="18" t="s">
-        <v>234</v>
+        <v>545</v>
       </c>
       <c r="D29" s="19" t="s">
         <v>9</v>
@@ -21941,16 +24366,16 @@
         <v>9</v>
       </c>
       <c r="N29" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="O29" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="P29" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="O29" s="36" t="s">
-        <v>253</v>
-      </c>
-      <c r="P29" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q29" s="21" t="s">
-        <v>9</v>
+      <c r="Q29" s="36" t="s">
+        <v>233</v>
       </c>
       <c r="R29" s="30" t="s">
         <v>9</v>
@@ -21976,16 +24401,16 @@
       <c r="Y29" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="Z29" s="74" t="s">
+      <c r="Z29" s="30" t="s">
         <v>9</v>
       </c>
       <c r="AA29" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="AB29" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC29" s="73" t="s">
+      <c r="AB29" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC29" s="21" t="s">
         <v>9</v>
       </c>
       <c r="AD29" s="72" t="s">
@@ -22012,16 +24437,22 @@
       <c r="AK29" s="73" t="s">
         <v>9</v>
       </c>
+      <c r="AL29" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AM29" s="73" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="30" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:39" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="16">
         <v>30</v>
       </c>
       <c r="B30" s="35" t="s">
-        <v>251</v>
+        <v>546</v>
       </c>
       <c r="C30" s="18" t="s">
-        <v>234</v>
+        <v>249</v>
       </c>
       <c r="D30" s="19" t="s">
         <v>9</v>
@@ -22054,16 +24485,16 @@
         <v>9</v>
       </c>
       <c r="N30" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="O30" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="P30" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="O30" s="36" t="s">
-        <v>255</v>
-      </c>
-      <c r="P30" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q30" s="21" t="s">
-        <v>9</v>
+      <c r="Q30" s="36" t="s">
+        <v>581</v>
       </c>
       <c r="R30" s="30" t="s">
         <v>9</v>
@@ -22089,16 +24520,16 @@
       <c r="Y30" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="Z30" s="74" t="s">
+      <c r="Z30" s="30" t="s">
         <v>9</v>
       </c>
       <c r="AA30" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="AB30" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC30" s="73" t="s">
+      <c r="AB30" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC30" s="21" t="s">
         <v>9</v>
       </c>
       <c r="AD30" s="72" t="s">
@@ -22125,16 +24556,22 @@
       <c r="AK30" s="73" t="s">
         <v>9</v>
       </c>
+      <c r="AL30" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AM30" s="73" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="31" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:39" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="16">
         <v>31</v>
       </c>
       <c r="B31" s="35" t="s">
-        <v>272</v>
+        <v>252</v>
       </c>
       <c r="C31" s="18" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="D31" s="19" t="s">
         <v>9</v>
@@ -22167,16 +24604,16 @@
         <v>9</v>
       </c>
       <c r="N31" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="O31" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="P31" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="O31" s="36" t="s">
-        <v>256</v>
-      </c>
-      <c r="P31" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q31" s="21" t="s">
-        <v>9</v>
+      <c r="Q31" s="36" t="s">
+        <v>254</v>
       </c>
       <c r="R31" s="30" t="s">
         <v>9</v>
@@ -22202,16 +24639,16 @@
       <c r="Y31" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="Z31" s="74" t="s">
+      <c r="Z31" s="30" t="s">
         <v>9</v>
       </c>
       <c r="AA31" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="AB31" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC31" s="73" t="s">
+      <c r="AB31" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC31" s="21" t="s">
         <v>9</v>
       </c>
       <c r="AD31" s="72" t="s">
@@ -22238,16 +24675,22 @@
       <c r="AK31" s="73" t="s">
         <v>9</v>
       </c>
+      <c r="AL31" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AM31" s="73" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="32" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:39" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="16">
         <v>32</v>
       </c>
-      <c r="B32" s="34" t="s">
-        <v>291</v>
+      <c r="B32" s="35" t="s">
+        <v>250</v>
       </c>
       <c r="C32" s="18" t="s">
-        <v>257</v>
+        <v>234</v>
       </c>
       <c r="D32" s="19" t="s">
         <v>9</v>
@@ -22280,16 +24723,16 @@
         <v>9</v>
       </c>
       <c r="N32" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="O32" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="P32" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="O32" s="36" t="s">
-        <v>292</v>
-      </c>
-      <c r="P32" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q32" s="21" t="s">
-        <v>9</v>
+      <c r="Q32" s="36" t="s">
+        <v>253</v>
       </c>
       <c r="R32" s="30" t="s">
         <v>9</v>
@@ -22315,16 +24758,16 @@
       <c r="Y32" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="Z32" s="74" t="s">
+      <c r="Z32" s="30" t="s">
         <v>9</v>
       </c>
       <c r="AA32" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="AB32" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC32" s="73" t="s">
+      <c r="AB32" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC32" s="21" t="s">
         <v>9</v>
       </c>
       <c r="AD32" s="72" t="s">
@@ -22351,16 +24794,22 @@
       <c r="AK32" s="73" t="s">
         <v>9</v>
       </c>
+      <c r="AL32" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AM32" s="73" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="33" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:39" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="16">
         <v>33</v>
       </c>
       <c r="B33" s="35" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="C33" s="18" t="s">
-        <v>257</v>
+        <v>234</v>
       </c>
       <c r="D33" s="19" t="s">
         <v>9</v>
@@ -22393,16 +24842,16 @@
         <v>9</v>
       </c>
       <c r="N33" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="O33" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="P33" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="O33" s="36" t="s">
-        <v>261</v>
-      </c>
-      <c r="P33" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q33" s="21" t="s">
-        <v>9</v>
+      <c r="Q33" s="36" t="s">
+        <v>255</v>
       </c>
       <c r="R33" s="30" t="s">
         <v>9</v>
@@ -22428,16 +24877,16 @@
       <c r="Y33" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="Z33" s="74" t="s">
+      <c r="Z33" s="30" t="s">
         <v>9</v>
       </c>
       <c r="AA33" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="AB33" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC33" s="73" t="s">
+      <c r="AB33" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC33" s="21" t="s">
         <v>9</v>
       </c>
       <c r="AD33" s="72" t="s">
@@ -22464,16 +24913,22 @@
       <c r="AK33" s="73" t="s">
         <v>9</v>
       </c>
+      <c r="AL33" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AM33" s="73" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="34" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:39" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="16">
         <v>34</v>
       </c>
       <c r="B34" s="35" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="C34" s="18" t="s">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="D34" s="19" t="s">
         <v>9</v>
@@ -22506,16 +24961,16 @@
         <v>9</v>
       </c>
       <c r="N34" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="O34" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="P34" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="O34" s="37" t="s">
-        <v>262</v>
-      </c>
-      <c r="P34" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q34" s="21" t="s">
-        <v>9</v>
+      <c r="Q34" s="36" t="s">
+        <v>256</v>
       </c>
       <c r="R34" s="30" t="s">
         <v>9</v>
@@ -22541,16 +24996,16 @@
       <c r="Y34" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="Z34" s="74" t="s">
+      <c r="Z34" s="30" t="s">
         <v>9</v>
       </c>
       <c r="AA34" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="AB34" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC34" s="73" t="s">
+      <c r="AB34" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC34" s="21" t="s">
         <v>9</v>
       </c>
       <c r="AD34" s="72" t="s">
@@ -22577,22 +25032,28 @@
       <c r="AK34" s="73" t="s">
         <v>9</v>
       </c>
+      <c r="AL34" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AM34" s="73" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="35" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:39" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="16">
         <v>35</v>
       </c>
       <c r="B35" s="34" t="s">
-        <v>266</v>
+        <v>291</v>
       </c>
       <c r="C35" s="18" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D35" s="19" t="s">
-        <v>614</v>
+        <v>9</v>
       </c>
       <c r="E35" s="20" t="s">
-        <v>273</v>
+        <v>9</v>
       </c>
       <c r="F35" s="19" t="s">
         <v>9</v>
@@ -22619,16 +25080,16 @@
         <v>9</v>
       </c>
       <c r="N35" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="O35" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="P35" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="O35" s="36" t="s">
-        <v>259</v>
-      </c>
-      <c r="P35" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q35" s="21" t="s">
-        <v>9</v>
+      <c r="Q35" s="36" t="s">
+        <v>292</v>
       </c>
       <c r="R35" s="30" t="s">
         <v>9</v>
@@ -22654,16 +25115,16 @@
       <c r="Y35" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="Z35" s="74" t="s">
+      <c r="Z35" s="30" t="s">
         <v>9</v>
       </c>
       <c r="AA35" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="AB35" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC35" s="73" t="s">
+      <c r="AB35" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC35" s="21" t="s">
         <v>9</v>
       </c>
       <c r="AD35" s="72" t="s">
@@ -22690,16 +25151,22 @@
       <c r="AK35" s="73" t="s">
         <v>9</v>
       </c>
+      <c r="AL35" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AM35" s="73" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="36" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:39" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="16">
         <v>36</v>
       </c>
-      <c r="B36" s="34" t="s">
-        <v>263</v>
+      <c r="B36" s="35" t="s">
+        <v>265</v>
       </c>
       <c r="C36" s="18" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D36" s="19" t="s">
         <v>9</v>
@@ -22732,16 +25199,16 @@
         <v>9</v>
       </c>
       <c r="N36" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="O36" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="P36" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="O36" s="36" t="s">
-        <v>260</v>
-      </c>
-      <c r="P36" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q36" s="21" t="s">
-        <v>9</v>
+      <c r="Q36" s="36" t="s">
+        <v>261</v>
       </c>
       <c r="R36" s="30" t="s">
         <v>9</v>
@@ -22767,16 +25234,16 @@
       <c r="Y36" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="Z36" s="74" t="s">
+      <c r="Z36" s="30" t="s">
         <v>9</v>
       </c>
       <c r="AA36" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="AB36" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC36" s="73" t="s">
+      <c r="AB36" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC36" s="21" t="s">
         <v>9</v>
       </c>
       <c r="AD36" s="72" t="s">
@@ -22803,22 +25270,28 @@
       <c r="AK36" s="73" t="s">
         <v>9</v>
       </c>
+      <c r="AL36" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AM36" s="73" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="37" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:39" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="16">
         <v>37</v>
       </c>
-      <c r="B37" s="34" t="s">
-        <v>273</v>
+      <c r="B37" s="35" t="s">
+        <v>264</v>
       </c>
       <c r="C37" s="18" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D37" s="19" t="s">
-        <v>275</v>
-      </c>
-      <c r="E37" s="38" t="s">
-        <v>266</v>
+        <v>9</v>
+      </c>
+      <c r="E37" s="20" t="s">
+        <v>9</v>
       </c>
       <c r="F37" s="19" t="s">
         <v>9</v>
@@ -22845,16 +25318,16 @@
         <v>9</v>
       </c>
       <c r="N37" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="O37" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="P37" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="O37" s="36" t="s">
-        <v>274</v>
-      </c>
-      <c r="P37" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q37" s="21" t="s">
-        <v>9</v>
+      <c r="Q37" s="37" t="s">
+        <v>262</v>
       </c>
       <c r="R37" s="30" t="s">
         <v>9</v>
@@ -22880,16 +25353,16 @@
       <c r="Y37" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="Z37" s="74" t="s">
+      <c r="Z37" s="30" t="s">
         <v>9</v>
       </c>
       <c r="AA37" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="AB37" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC37" s="73" t="s">
+      <c r="AB37" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC37" s="21" t="s">
         <v>9</v>
       </c>
       <c r="AD37" s="72" t="s">
@@ -22916,22 +25389,28 @@
       <c r="AK37" s="73" t="s">
         <v>9</v>
       </c>
+      <c r="AL37" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AM37" s="73" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="38" spans="1:37" s="71" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:39" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="16">
         <v>38</v>
       </c>
-      <c r="B38" s="67" t="s">
-        <v>903</v>
-      </c>
-      <c r="C38" s="76" t="s">
-        <v>938</v>
+      <c r="B38" s="34" t="s">
+        <v>266</v>
+      </c>
+      <c r="C38" s="18" t="s">
+        <v>258</v>
       </c>
       <c r="D38" s="19" t="s">
-        <v>9</v>
+        <v>614</v>
       </c>
       <c r="E38" s="20" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="F38" s="19" t="s">
         <v>9</v>
@@ -22957,17 +25436,17 @@
       <c r="M38" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="N38" s="68" t="s">
+      <c r="N38" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="O38" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="P38" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="O38" s="21" t="s">
-        <v>908</v>
-      </c>
-      <c r="P38" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q38" s="21" t="s">
-        <v>9</v>
+      <c r="Q38" s="36" t="s">
+        <v>259</v>
       </c>
       <c r="R38" s="30" t="s">
         <v>9</v>
@@ -22982,28 +25461,27 @@
         <v>9</v>
       </c>
       <c r="V38" s="30" t="s">
-        <v>904</v>
+        <v>9</v>
       </c>
       <c r="W38" s="21" t="s">
-        <v>905</v>
+        <v>9</v>
       </c>
       <c r="X38" s="30" t="s">
-        <v>906</v>
+        <v>9</v>
       </c>
       <c r="Y38" s="21" t="s">
-        <v>907</v>
-      </c>
-      <c r="Z38" s="69" t="str">
-        <f t="shared" ref="Z38:Z42" si="0">IF(AA38="null", "null", "método.revit")</f>
-        <v>método.revit</v>
-      </c>
-      <c r="AA38" s="70" t="s">
-        <v>909</v>
-      </c>
-      <c r="AB38" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC38" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z38" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA38" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB38" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC38" s="21" t="s">
         <v>9</v>
       </c>
       <c r="AD38" s="72" t="s">
@@ -23030,481 +25508,890 @@
       <c r="AK38" s="73" t="s">
         <v>9</v>
       </c>
+      <c r="AL38" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AM38" s="73" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="39" spans="1:37" s="71" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:39" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="16">
         <v>39</v>
       </c>
-      <c r="B39" s="67" t="s">
+      <c r="B39" s="34" t="s">
+        <v>263</v>
+      </c>
+      <c r="C39" s="18" t="s">
+        <v>258</v>
+      </c>
+      <c r="D39" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E39" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="F39" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="G39" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="H39" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="I39" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J39" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="K39" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="L39" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="M39" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="N39" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="O39" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="P39" s="30" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q39" s="36" t="s">
+        <v>260</v>
+      </c>
+      <c r="R39" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S39" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="T39" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="U39" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="V39" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="W39" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="X39" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y39" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z39" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA39" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB39" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC39" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD39" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE39" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF39" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG39" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH39" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI39" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ39" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK39" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AL39" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AM39" s="73" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="40" spans="1:39" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="16">
+        <v>40</v>
+      </c>
+      <c r="B40" s="34" t="s">
+        <v>273</v>
+      </c>
+      <c r="C40" s="18" t="s">
+        <v>258</v>
+      </c>
+      <c r="D40" s="19" t="s">
+        <v>275</v>
+      </c>
+      <c r="E40" s="38" t="s">
+        <v>266</v>
+      </c>
+      <c r="F40" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="G40" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="H40" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="I40" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J40" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="K40" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="L40" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="M40" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="N40" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="O40" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="P40" s="30" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q40" s="36" t="s">
+        <v>274</v>
+      </c>
+      <c r="R40" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S40" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="T40" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="U40" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="V40" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="W40" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="X40" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y40" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z40" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA40" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB40" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC40" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD40" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE40" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF40" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG40" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH40" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI40" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ40" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK40" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AL40" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AM40" s="73" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="41" spans="1:39" s="71" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="16">
+        <v>41</v>
+      </c>
+      <c r="B41" s="67" t="s">
+        <v>903</v>
+      </c>
+      <c r="C41" s="75" t="s">
+        <v>938</v>
+      </c>
+      <c r="D41" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E41" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="F41" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="G41" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="H41" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="I41" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J41" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="K41" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="L41" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="M41" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="N41" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="O41" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="P41" s="68" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q41" s="21" t="s">
+        <v>908</v>
+      </c>
+      <c r="R41" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S41" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="T41" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="U41" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="V41" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="W41" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="X41" s="30" t="s">
+        <v>904</v>
+      </c>
+      <c r="Y41" s="21" t="s">
+        <v>905</v>
+      </c>
+      <c r="Z41" s="30" t="s">
+        <v>906</v>
+      </c>
+      <c r="AA41" s="21" t="s">
+        <v>907</v>
+      </c>
+      <c r="AB41" s="69" t="str">
+        <f t="shared" ref="AB41:AB45" si="0">IF(AC41="null", "null", "método.revit")</f>
+        <v>método.revit</v>
+      </c>
+      <c r="AC41" s="70" t="s">
+        <v>909</v>
+      </c>
+      <c r="AD41" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE41" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF41" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG41" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH41" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI41" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ41" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK41" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AL41" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AM41" s="73" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="42" spans="1:39" s="71" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="16">
+        <v>42</v>
+      </c>
+      <c r="B42" s="67" t="s">
         <v>910</v>
       </c>
-      <c r="C39" s="76" t="s">
+      <c r="C42" s="75" t="s">
         <v>938</v>
       </c>
-      <c r="D39" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="E39" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F39" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="G39" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="H39" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="I39" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="J39" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="K39" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="L39" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="M39" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="N39" s="68" t="s">
+      <c r="D42" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E42" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="F42" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="G42" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="H42" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="I42" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J42" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="K42" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="L42" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="M42" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="N42" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="O42" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="P42" s="68" t="s">
         <v>16</v>
       </c>
-      <c r="O39" s="21" t="s">
+      <c r="Q42" s="21" t="s">
         <v>912</v>
       </c>
-      <c r="P39" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q39" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="R39" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="S39" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="T39" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="U39" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="V39" s="30" t="s">
+      <c r="R42" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S42" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="T42" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="U42" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="V42" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="W42" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="X42" s="30" t="s">
         <v>904</v>
       </c>
-      <c r="W39" s="21" t="s">
+      <c r="Y42" s="21" t="s">
         <v>905</v>
       </c>
-      <c r="X39" s="30" t="s">
+      <c r="Z42" s="30" t="s">
         <v>906</v>
       </c>
-      <c r="Y39" s="21" t="s">
+      <c r="AA42" s="21" t="s">
         <v>911</v>
       </c>
-      <c r="Z39" s="69" t="str">
+      <c r="AB42" s="69" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
-      <c r="AA39" s="70" t="s">
+      <c r="AC42" s="70" t="s">
         <v>913</v>
       </c>
-      <c r="AB39" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC39" s="73" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD39" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE39" s="73" t="s">
-        <v>9</v>
-      </c>
-      <c r="AF39" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AG39" s="73" t="s">
-        <v>9</v>
-      </c>
-      <c r="AH39" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AI39" s="73" t="s">
-        <v>9</v>
-      </c>
-      <c r="AJ39" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AK39" s="73" t="s">
+      <c r="AD42" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE42" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF42" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG42" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH42" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI42" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ42" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK42" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AL42" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AM42" s="73" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="40" spans="1:37" s="71" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="16">
-        <v>40</v>
-      </c>
-      <c r="B40" s="67" t="s">
+    <row r="43" spans="1:39" s="71" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="16">
+        <v>43</v>
+      </c>
+      <c r="B43" s="67" t="s">
         <v>914</v>
       </c>
-      <c r="C40" s="76" t="s">
+      <c r="C43" s="75" t="s">
         <v>938</v>
       </c>
-      <c r="D40" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="E40" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F40" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="G40" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="H40" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="I40" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="J40" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="K40" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="L40" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="M40" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="N40" s="68" t="s">
+      <c r="D43" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E43" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="F43" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="G43" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="H43" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="I43" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J43" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="K43" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="L43" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="M43" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="N43" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="O43" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="P43" s="68" t="s">
         <v>16</v>
       </c>
-      <c r="O40" s="21" t="s">
+      <c r="Q43" s="21" t="s">
         <v>916</v>
       </c>
-      <c r="P40" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q40" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="R40" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="S40" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="T40" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="U40" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="V40" s="30" t="s">
+      <c r="R43" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S43" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="T43" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="U43" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="V43" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="W43" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="X43" s="30" t="s">
         <v>904</v>
       </c>
-      <c r="W40" s="21" t="s">
+      <c r="Y43" s="21" t="s">
         <v>905</v>
       </c>
-      <c r="X40" s="30" t="s">
+      <c r="Z43" s="30" t="s">
         <v>906</v>
       </c>
-      <c r="Y40" s="21" t="s">
+      <c r="AA43" s="21" t="s">
         <v>915</v>
       </c>
-      <c r="Z40" s="69" t="str">
+      <c r="AB43" s="69" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
-      <c r="AA40" s="70" t="s">
+      <c r="AC43" s="70" t="s">
         <v>917</v>
       </c>
-      <c r="AB40" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC40" s="73" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD40" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE40" s="73" t="s">
-        <v>9</v>
-      </c>
-      <c r="AF40" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AG40" s="73" t="s">
-        <v>9</v>
-      </c>
-      <c r="AH40" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AI40" s="73" t="s">
-        <v>9</v>
-      </c>
-      <c r="AJ40" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AK40" s="73" t="s">
+      <c r="AD43" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE43" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF43" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG43" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH43" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI43" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ43" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK43" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AL43" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AM43" s="73" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="41" spans="1:37" s="71" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="16">
-        <v>41</v>
-      </c>
-      <c r="B41" s="67" t="s">
+    <row r="44" spans="1:39" s="71" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="16">
+        <v>44</v>
+      </c>
+      <c r="B44" s="67" t="s">
         <v>918</v>
       </c>
-      <c r="C41" s="76" t="s">
+      <c r="C44" s="75" t="s">
         <v>938</v>
       </c>
-      <c r="D41" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="E41" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F41" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="G41" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="H41" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="I41" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="J41" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="K41" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="L41" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="M41" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="N41" s="68" t="s">
+      <c r="D44" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E44" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="F44" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="G44" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="H44" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="I44" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J44" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="K44" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="L44" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="M44" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="N44" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="O44" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="P44" s="68" t="s">
         <v>16</v>
       </c>
-      <c r="O41" s="21" t="s">
+      <c r="Q44" s="21" t="s">
         <v>920</v>
       </c>
-      <c r="P41" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q41" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="R41" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="S41" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="T41" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="U41" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="V41" s="30" t="s">
+      <c r="R44" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S44" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="T44" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="U44" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="V44" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="W44" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="X44" s="30" t="s">
         <v>904</v>
       </c>
-      <c r="W41" s="21" t="s">
+      <c r="Y44" s="21" t="s">
         <v>905</v>
       </c>
-      <c r="X41" s="30" t="s">
+      <c r="Z44" s="30" t="s">
         <v>906</v>
       </c>
-      <c r="Y41" s="21" t="s">
+      <c r="AA44" s="21" t="s">
         <v>919</v>
       </c>
-      <c r="Z41" s="69" t="str">
+      <c r="AB44" s="69" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
-      <c r="AA41" s="70" t="s">
+      <c r="AC44" s="70" t="s">
         <v>921</v>
       </c>
-      <c r="AB41" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC41" s="73" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD41" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE41" s="73" t="s">
-        <v>9</v>
-      </c>
-      <c r="AF41" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AG41" s="73" t="s">
-        <v>9</v>
-      </c>
-      <c r="AH41" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AI41" s="73" t="s">
-        <v>9</v>
-      </c>
-      <c r="AJ41" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AK41" s="73" t="s">
+      <c r="AD44" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE44" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF44" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG44" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH44" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI44" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ44" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK44" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AL44" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AM44" s="73" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="1:37" s="71" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="16">
-        <v>42</v>
-      </c>
-      <c r="B42" s="67" t="s">
+    <row r="45" spans="1:39" s="71" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="16">
+        <v>45</v>
+      </c>
+      <c r="B45" s="67" t="s">
         <v>922</v>
       </c>
-      <c r="C42" s="76" t="s">
+      <c r="C45" s="75" t="s">
         <v>938</v>
       </c>
-      <c r="D42" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="E42" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F42" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="G42" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="H42" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="I42" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="J42" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="K42" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="L42" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="M42" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="N42" s="68" t="s">
+      <c r="D45" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E45" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="F45" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="G45" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="H45" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="I45" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J45" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="K45" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="L45" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="M45" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="N45" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="O45" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="P45" s="68" t="s">
         <v>16</v>
       </c>
-      <c r="O42" s="21" t="s">
+      <c r="Q45" s="21" t="s">
         <v>924</v>
       </c>
-      <c r="P42" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q42" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="R42" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="S42" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="T42" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="U42" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="V42" s="30" t="s">
+      <c r="R45" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S45" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="T45" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="U45" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="V45" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="W45" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="X45" s="30" t="s">
         <v>904</v>
       </c>
-      <c r="W42" s="21" t="s">
+      <c r="Y45" s="21" t="s">
         <v>905</v>
       </c>
-      <c r="X42" s="30" t="s">
+      <c r="Z45" s="30" t="s">
         <v>906</v>
       </c>
-      <c r="Y42" s="21" t="s">
+      <c r="AA45" s="21" t="s">
         <v>923</v>
       </c>
-      <c r="Z42" s="69" t="str">
+      <c r="AB45" s="69" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
-      <c r="AA42" s="70" t="s">
+      <c r="AC45" s="70" t="s">
         <v>925</v>
       </c>
-      <c r="AB42" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC42" s="73" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD42" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE42" s="73" t="s">
-        <v>9</v>
-      </c>
-      <c r="AF42" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AG42" s="73" t="s">
-        <v>9</v>
-      </c>
-      <c r="AH42" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AI42" s="73" t="s">
-        <v>9</v>
-      </c>
-      <c r="AJ42" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AK42" s="73" t="s">
+      <c r="AD45" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE45" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF45" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG45" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH45" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI45" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ45" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK45" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AL45" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="AM45" s="73" t="s">
         <v>9</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="9" type="noConversion"/>
-  <conditionalFormatting sqref="B18:B37 B1:B13">
-    <cfRule type="duplicateValues" dxfId="4" priority="35"/>
+  <conditionalFormatting sqref="B21:B40 B1:B16">
+    <cfRule type="duplicateValues" dxfId="10" priority="41"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B38:B42">
-    <cfRule type="duplicateValues" dxfId="3" priority="16"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="17"/>
+  <conditionalFormatting sqref="B41:B45">
+    <cfRule type="duplicateValues" dxfId="9" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="23"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V38:AA42">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+  <conditionalFormatting sqref="X41:AC45 AB6:AM45">
+    <cfRule type="cellIs" dxfId="7" priority="8" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Z2:AK42">
-    <cfRule type="cellIs" dxfId="0" priority="8" operator="equal">
+  <conditionalFormatting sqref="AB5:AM5">
+    <cfRule type="cellIs" dxfId="6" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AB2:AM2">
+    <cfRule type="cellIs" dxfId="5" priority="5" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AB3:AM3">
+    <cfRule type="cellIs" dxfId="4" priority="4" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AB4:AM4">
+    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C5">
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C4">
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
